--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6802577A-EF41-44E9-B72C-C21706750E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9296441A-8649-460F-9EEA-68164000E06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="26676" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -4158,9 +4158,6 @@
     <t>彩虹节拍</t>
   </si>
   <si>
-    <t>彩虹答辩</t>
-  </si>
-  <si>
     <t>剥裤袜,僕は,bkw,bokuwa,我心危,我里危险,扎聋耳朵</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -4278,6 +4275,10 @@
   </si>
   <si>
     <t>蔷薇王座,tor</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>彩虹答辩,彩虹大便</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5948,7 +5949,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -7169,7 +7170,7 @@
         <v>446</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7961,7 +7962,7 @@
         <v>588</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -8423,7 +8424,7 @@
         <v>671</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8434,7 +8435,7 @@
         <v>672</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -9839,7 +9840,7 @@
         <v>922</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -10232,7 +10233,7 @@
         <v>991</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10526,7 +10527,7 @@
         <v>1042</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -11015,7 +11016,7 @@
         <v>1129</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11037,7 +11038,7 @@
         <v>937</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11048,7 +11049,7 @@
         <v>939</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11103,7 +11104,7 @@
         <v>1140</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11298,7 +11299,7 @@
         <v>1174</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11628,7 +11629,7 @@
         <v>1233</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11639,7 +11640,7 @@
         <v>1234</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11702,7 +11703,7 @@
         <v>724</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11779,7 +11780,7 @@
         <v>1257</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11964,7 +11965,7 @@
       </c>
       <c r="B662" s="1"/>
       <c r="C662" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11986,7 +11987,7 @@
         <v>1292</v>
       </c>
       <c r="C664" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -12141,10 +12142,10 @@
         <v>772</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C679" s="3" t="s">
         <v>1322</v>
-      </c>
-      <c r="C679" s="3" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12153,7 +12154,7 @@
       </c>
       <c r="B680" s="1"/>
       <c r="C680" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12162,7 +12163,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12171,7 +12172,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12180,7 +12181,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12189,7 +12190,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12198,7 +12199,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12207,7 +12208,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12216,7 +12217,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -12225,7 +12226,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
@@ -12235,8 +12236,8 @@
       <c r="B689" t="s">
         <v>1318</v>
       </c>
-      <c r="C689" t="s">
-        <v>1319</v>
+      <c r="C689" s="3" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -12255,7 +12256,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A689:C689 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C529 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A689:B689 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C529 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9296441A-8649-460F-9EEA-68164000E06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020FF152-D290-4103-86CA-574610343870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="816" yWindow="1536" windowWidth="20832" windowHeight="14268" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -842,9 +842,6 @@
     <t>ロミオとシンデレラ</t>
   </si>
   <si>
-    <t>辛德瑞拉,罗密欧与朱丽叶,罗密欧与灰姑娘</t>
-  </si>
-  <si>
     <t>エイリアンエイリアン</t>
   </si>
   <si>
@@ -1680,9 +1677,6 @@
   </si>
   <si>
     <t>右肩の蝶</t>
-  </si>
-  <si>
-    <t>右肩之蝶,右肩蝶</t>
   </si>
   <si>
     <t>深海少女</t>
@@ -4101,9 +4095,6 @@
     <t>デビルじゃないもん</t>
   </si>
   <si>
-    <t>我不是魔鬼,才不是恶魔</t>
-  </si>
-  <si>
     <t>イケナイ太陽</t>
   </si>
   <si>
@@ -4279,6 +4270,18 @@
   </si>
   <si>
     <t>彩虹答辩,彩虹大便</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不是魔鬼,才不是恶魔呢</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>辛德瑞拉,罗密欧与朱丽叶,罗密欧与灰姑娘,罗密欧与辛德瑞拉</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>右肩之蝶,右肩蝶,右肩的蝶</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5949,7 +5952,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -6135,8 +6138,8 @@
       <c r="B130" t="s">
         <v>258</v>
       </c>
-      <c r="C130" t="s">
-        <v>259</v>
+      <c r="C130" s="3" t="s">
+        <v>1348</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -6144,10 +6147,10 @@
         <v>139</v>
       </c>
       <c r="B131" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" t="s">
         <v>260</v>
-      </c>
-      <c r="C131" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -6155,10 +6158,10 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
+        <v>261</v>
+      </c>
+      <c r="C132" t="s">
         <v>262</v>
-      </c>
-      <c r="C132" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -6166,10 +6169,10 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
+        <v>263</v>
+      </c>
+      <c r="C133" t="s">
         <v>264</v>
-      </c>
-      <c r="C133" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6177,10 +6180,10 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134" t="s">
         <v>266</v>
-      </c>
-      <c r="C134" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -6188,10 +6191,10 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
+        <v>267</v>
+      </c>
+      <c r="C135" t="s">
         <v>268</v>
-      </c>
-      <c r="C135" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -6199,10 +6202,10 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
+        <v>269</v>
+      </c>
+      <c r="C136" t="s">
         <v>270</v>
-      </c>
-      <c r="C136" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -6210,10 +6213,10 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
+        <v>271</v>
+      </c>
+      <c r="C137" t="s">
         <v>272</v>
-      </c>
-      <c r="C137" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -6221,10 +6224,10 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
+        <v>273</v>
+      </c>
+      <c r="C138" t="s">
         <v>274</v>
-      </c>
-      <c r="C138" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -6232,10 +6235,10 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
+        <v>275</v>
+      </c>
+      <c r="C139" t="s">
         <v>276</v>
-      </c>
-      <c r="C139" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -6243,10 +6246,10 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
+        <v>277</v>
+      </c>
+      <c r="C140" t="s">
         <v>278</v>
-      </c>
-      <c r="C140" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -6254,10 +6257,10 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
+        <v>279</v>
+      </c>
+      <c r="C141" t="s">
         <v>280</v>
-      </c>
-      <c r="C141" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -6265,10 +6268,10 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
+        <v>281</v>
+      </c>
+      <c r="C142" t="s">
         <v>282</v>
-      </c>
-      <c r="C142" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -6276,10 +6279,10 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
+        <v>283</v>
+      </c>
+      <c r="C143" t="s">
         <v>284</v>
-      </c>
-      <c r="C143" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -6287,10 +6290,10 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
+        <v>285</v>
+      </c>
+      <c r="C144" t="s">
         <v>286</v>
-      </c>
-      <c r="C144" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -6298,10 +6301,10 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
+        <v>287</v>
+      </c>
+      <c r="C145" t="s">
         <v>288</v>
-      </c>
-      <c r="C145" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6309,10 +6312,10 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
+        <v>289</v>
+      </c>
+      <c r="C146" t="s">
         <v>290</v>
-      </c>
-      <c r="C146" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -6320,10 +6323,10 @@
         <v>155</v>
       </c>
       <c r="B147" t="s">
+        <v>291</v>
+      </c>
+      <c r="C147" t="s">
         <v>292</v>
-      </c>
-      <c r="C147" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -6331,10 +6334,10 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
+        <v>293</v>
+      </c>
+      <c r="C148" t="s">
         <v>294</v>
-      </c>
-      <c r="C148" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -6342,10 +6345,10 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
+        <v>295</v>
+      </c>
+      <c r="C149" t="s">
         <v>296</v>
-      </c>
-      <c r="C149" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -6353,10 +6356,10 @@
         <v>158</v>
       </c>
       <c r="B150" t="s">
+        <v>297</v>
+      </c>
+      <c r="C150" t="s">
         <v>298</v>
-      </c>
-      <c r="C150" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6364,10 +6367,10 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
+        <v>299</v>
+      </c>
+      <c r="C151" t="s">
         <v>300</v>
-      </c>
-      <c r="C151" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -6375,10 +6378,10 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
+        <v>301</v>
+      </c>
+      <c r="C152" t="s">
         <v>302</v>
-      </c>
-      <c r="C152" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -6386,10 +6389,10 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
+        <v>303</v>
+      </c>
+      <c r="C153" t="s">
         <v>304</v>
-      </c>
-      <c r="C153" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -6397,10 +6400,10 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
+        <v>305</v>
+      </c>
+      <c r="C154" t="s">
         <v>306</v>
-      </c>
-      <c r="C154" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6408,10 +6411,10 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
+        <v>307</v>
+      </c>
+      <c r="C155" t="s">
         <v>308</v>
-      </c>
-      <c r="C155" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -6419,10 +6422,10 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
+        <v>309</v>
+      </c>
+      <c r="C156" t="s">
         <v>310</v>
-      </c>
-      <c r="C156" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -6430,10 +6433,10 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
+        <v>311</v>
+      </c>
+      <c r="C157" t="s">
         <v>312</v>
-      </c>
-      <c r="C157" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -6441,10 +6444,10 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
+        <v>313</v>
+      </c>
+      <c r="C158" t="s">
         <v>314</v>
-      </c>
-      <c r="C158" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -6452,10 +6455,10 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
+        <v>315</v>
+      </c>
+      <c r="C159" t="s">
         <v>316</v>
-      </c>
-      <c r="C159" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -6463,10 +6466,10 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
+        <v>317</v>
+      </c>
+      <c r="C160" t="s">
         <v>318</v>
-      </c>
-      <c r="C160" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -6474,10 +6477,10 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
+        <v>319</v>
+      </c>
+      <c r="C161" t="s">
         <v>320</v>
-      </c>
-      <c r="C161" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -6485,10 +6488,10 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
+        <v>321</v>
+      </c>
+      <c r="C162" t="s">
         <v>322</v>
-      </c>
-      <c r="C162" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6496,10 +6499,10 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
+        <v>323</v>
+      </c>
+      <c r="C163" t="s">
         <v>324</v>
-      </c>
-      <c r="C163" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -6507,10 +6510,10 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
+        <v>325</v>
+      </c>
+      <c r="C164" t="s">
         <v>326</v>
-      </c>
-      <c r="C164" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -6518,10 +6521,10 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
+        <v>327</v>
+      </c>
+      <c r="C165" t="s">
         <v>328</v>
-      </c>
-      <c r="C165" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -6529,10 +6532,10 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
+        <v>329</v>
+      </c>
+      <c r="C166" t="s">
         <v>330</v>
-      </c>
-      <c r="C166" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -6540,10 +6543,10 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
+        <v>331</v>
+      </c>
+      <c r="C167" t="s">
         <v>332</v>
-      </c>
-      <c r="C167" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6551,10 +6554,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
+        <v>333</v>
+      </c>
+      <c r="C168" t="s">
         <v>334</v>
-      </c>
-      <c r="C168" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -6562,10 +6565,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
+        <v>335</v>
+      </c>
+      <c r="C169" t="s">
         <v>336</v>
-      </c>
-      <c r="C169" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -6573,10 +6576,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
+        <v>337</v>
+      </c>
+      <c r="C170" t="s">
         <v>338</v>
-      </c>
-      <c r="C170" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -6584,10 +6587,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
+        <v>339</v>
+      </c>
+      <c r="C171" t="s">
         <v>340</v>
-      </c>
-      <c r="C171" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -6595,10 +6598,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
+        <v>341</v>
+      </c>
+      <c r="C172" t="s">
         <v>342</v>
-      </c>
-      <c r="C172" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -6606,10 +6609,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
+        <v>343</v>
+      </c>
+      <c r="C173" t="s">
         <v>344</v>
-      </c>
-      <c r="C173" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -6617,10 +6620,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
+        <v>345</v>
+      </c>
+      <c r="C174" t="s">
         <v>346</v>
-      </c>
-      <c r="C174" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -6628,10 +6631,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
+        <v>347</v>
+      </c>
+      <c r="C175" t="s">
         <v>348</v>
-      </c>
-      <c r="C175" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -6639,10 +6642,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
+        <v>349</v>
+      </c>
+      <c r="C176" t="s">
         <v>350</v>
-      </c>
-      <c r="C176" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -6650,10 +6653,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
+        <v>351</v>
+      </c>
+      <c r="C177" t="s">
         <v>352</v>
-      </c>
-      <c r="C177" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -6661,10 +6664,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
+        <v>353</v>
+      </c>
+      <c r="C178" t="s">
         <v>354</v>
-      </c>
-      <c r="C178" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -6672,10 +6675,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
+        <v>355</v>
+      </c>
+      <c r="C179" t="s">
         <v>356</v>
-      </c>
-      <c r="C179" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -6683,10 +6686,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
+        <v>357</v>
+      </c>
+      <c r="C180" t="s">
         <v>358</v>
-      </c>
-      <c r="C180" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -6694,10 +6697,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
+        <v>359</v>
+      </c>
+      <c r="C181" t="s">
         <v>360</v>
-      </c>
-      <c r="C181" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -6705,10 +6708,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>361</v>
+      </c>
+      <c r="C182" t="s">
         <v>362</v>
-      </c>
-      <c r="C182" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -6716,10 +6719,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
+        <v>363</v>
+      </c>
+      <c r="C183" t="s">
         <v>364</v>
-      </c>
-      <c r="C183" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -6727,10 +6730,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>365</v>
+      </c>
+      <c r="C184" t="s">
         <v>366</v>
-      </c>
-      <c r="C184" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -6738,10 +6741,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
+        <v>367</v>
+      </c>
+      <c r="C185" t="s">
         <v>368</v>
-      </c>
-      <c r="C185" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -6749,10 +6752,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
+        <v>369</v>
+      </c>
+      <c r="C186" t="s">
         <v>370</v>
-      </c>
-      <c r="C186" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -6760,10 +6763,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
+        <v>371</v>
+      </c>
+      <c r="C187" t="s">
         <v>372</v>
-      </c>
-      <c r="C187" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -6771,10 +6774,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
+        <v>373</v>
+      </c>
+      <c r="C188" t="s">
         <v>374</v>
-      </c>
-      <c r="C188" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -6782,10 +6785,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
+        <v>375</v>
+      </c>
+      <c r="C189" t="s">
         <v>376</v>
-      </c>
-      <c r="C189" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -6793,10 +6796,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
+        <v>377</v>
+      </c>
+      <c r="C190" t="s">
         <v>378</v>
-      </c>
-      <c r="C190" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -6804,10 +6807,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" t="s">
         <v>380</v>
-      </c>
-      <c r="C191" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -6815,10 +6818,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
+        <v>381</v>
+      </c>
+      <c r="C192" t="s">
         <v>382</v>
-      </c>
-      <c r="C192" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -6826,10 +6829,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>383</v>
+      </c>
+      <c r="C193" t="s">
         <v>384</v>
-      </c>
-      <c r="C193" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -6837,10 +6840,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
+        <v>385</v>
+      </c>
+      <c r="C194" t="s">
         <v>386</v>
-      </c>
-      <c r="C194" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -6848,10 +6851,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
+        <v>387</v>
+      </c>
+      <c r="C195" t="s">
         <v>388</v>
-      </c>
-      <c r="C195" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -6859,10 +6862,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
+        <v>389</v>
+      </c>
+      <c r="C196" t="s">
         <v>390</v>
-      </c>
-      <c r="C196" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -6870,10 +6873,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
+        <v>391</v>
+      </c>
+      <c r="C197" t="s">
         <v>392</v>
-      </c>
-      <c r="C197" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -6881,10 +6884,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
+        <v>393</v>
+      </c>
+      <c r="C198" t="s">
         <v>394</v>
-      </c>
-      <c r="C198" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -6892,10 +6895,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
+        <v>395</v>
+      </c>
+      <c r="C199" t="s">
         <v>396</v>
-      </c>
-      <c r="C199" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -6903,10 +6906,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
+        <v>397</v>
+      </c>
+      <c r="C200" t="s">
         <v>398</v>
-      </c>
-      <c r="C200" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -6914,10 +6917,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
+        <v>399</v>
+      </c>
+      <c r="C201" t="s">
         <v>400</v>
-      </c>
-      <c r="C201" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -6925,10 +6928,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
+        <v>401</v>
+      </c>
+      <c r="C202" t="s">
         <v>402</v>
-      </c>
-      <c r="C202" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -6936,10 +6939,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
+        <v>403</v>
+      </c>
+      <c r="C203" t="s">
         <v>404</v>
-      </c>
-      <c r="C203" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -6947,10 +6950,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
+        <v>405</v>
+      </c>
+      <c r="C204" t="s">
         <v>406</v>
-      </c>
-      <c r="C204" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -6958,10 +6961,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
+        <v>407</v>
+      </c>
+      <c r="C205" t="s">
         <v>408</v>
-      </c>
-      <c r="C205" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -6969,10 +6972,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
+        <v>409</v>
+      </c>
+      <c r="C206" t="s">
         <v>410</v>
-      </c>
-      <c r="C206" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -6980,10 +6983,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
+        <v>411</v>
+      </c>
+      <c r="C207" t="s">
         <v>412</v>
-      </c>
-      <c r="C207" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -6991,10 +6994,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
+        <v>413</v>
+      </c>
+      <c r="C208" t="s">
         <v>414</v>
-      </c>
-      <c r="C208" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7002,10 +7005,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
+        <v>415</v>
+      </c>
+      <c r="C209" t="s">
         <v>416</v>
-      </c>
-      <c r="C209" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -7013,10 +7016,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
+        <v>417</v>
+      </c>
+      <c r="C210" t="s">
         <v>418</v>
-      </c>
-      <c r="C210" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -7024,10 +7027,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
+        <v>419</v>
+      </c>
+      <c r="C211" t="s">
         <v>420</v>
-      </c>
-      <c r="C211" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -7035,10 +7038,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
+        <v>421</v>
+      </c>
+      <c r="C212" t="s">
         <v>422</v>
-      </c>
-      <c r="C212" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -7046,10 +7049,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
+        <v>423</v>
+      </c>
+      <c r="C213" t="s">
         <v>424</v>
-      </c>
-      <c r="C213" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -7057,10 +7060,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
+        <v>425</v>
+      </c>
+      <c r="C214" t="s">
         <v>426</v>
-      </c>
-      <c r="C214" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -7068,10 +7071,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
+        <v>427</v>
+      </c>
+      <c r="C215" t="s">
         <v>428</v>
-      </c>
-      <c r="C215" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -7079,10 +7082,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
+        <v>429</v>
+      </c>
+      <c r="C216" t="s">
         <v>430</v>
-      </c>
-      <c r="C216" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -7090,10 +7093,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
+        <v>431</v>
+      </c>
+      <c r="C217" t="s">
         <v>432</v>
-      </c>
-      <c r="C217" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -7101,10 +7104,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
+        <v>433</v>
+      </c>
+      <c r="C218" t="s">
         <v>434</v>
-      </c>
-      <c r="C218" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -7112,10 +7115,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
+        <v>435</v>
+      </c>
+      <c r="C219" t="s">
         <v>436</v>
-      </c>
-      <c r="C219" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -7123,10 +7126,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
+        <v>437</v>
+      </c>
+      <c r="C220" t="s">
         <v>438</v>
-      </c>
-      <c r="C220" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -7134,10 +7137,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
+        <v>439</v>
+      </c>
+      <c r="C221" t="s">
         <v>440</v>
-      </c>
-      <c r="C221" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -7145,10 +7148,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
+        <v>441</v>
+      </c>
+      <c r="C222" t="s">
         <v>442</v>
-      </c>
-      <c r="C222" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -7156,10 +7159,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
+        <v>443</v>
+      </c>
+      <c r="C223" t="s">
         <v>444</v>
-      </c>
-      <c r="C223" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -7167,10 +7170,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7178,10 +7181,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>446</v>
+      </c>
+      <c r="C225" t="s">
         <v>447</v>
-      </c>
-      <c r="C225" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -7189,10 +7192,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>448</v>
+      </c>
+      <c r="C226" t="s">
         <v>449</v>
-      </c>
-      <c r="C226" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -7200,10 +7203,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>450</v>
+      </c>
+      <c r="C227" t="s">
         <v>451</v>
-      </c>
-      <c r="C227" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -7211,10 +7214,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>452</v>
+      </c>
+      <c r="C228" t="s">
         <v>453</v>
-      </c>
-      <c r="C228" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -7222,10 +7225,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
+        <v>454</v>
+      </c>
+      <c r="C229" t="s">
         <v>455</v>
-      </c>
-      <c r="C229" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7233,10 +7236,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
+        <v>456</v>
+      </c>
+      <c r="C230" t="s">
         <v>457</v>
-      </c>
-      <c r="C230" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7244,10 +7247,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>458</v>
+      </c>
+      <c r="C231" t="s">
         <v>459</v>
-      </c>
-      <c r="C231" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -7255,10 +7258,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>460</v>
+      </c>
+      <c r="C232" t="s">
         <v>461</v>
-      </c>
-      <c r="C232" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -7266,10 +7269,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>462</v>
+      </c>
+      <c r="C233" t="s">
         <v>463</v>
-      </c>
-      <c r="C233" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -7277,10 +7280,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
+        <v>464</v>
+      </c>
+      <c r="C234" t="s">
         <v>465</v>
-      </c>
-      <c r="C234" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7288,10 +7291,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>466</v>
+      </c>
+      <c r="C235" t="s">
         <v>467</v>
-      </c>
-      <c r="C235" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -7299,10 +7302,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>468</v>
+      </c>
+      <c r="C236" t="s">
         <v>469</v>
-      </c>
-      <c r="C236" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -7310,10 +7313,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>470</v>
+      </c>
+      <c r="C237" t="s">
         <v>471</v>
-      </c>
-      <c r="C237" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -7321,10 +7324,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>472</v>
+      </c>
+      <c r="C238" t="s">
         <v>473</v>
-      </c>
-      <c r="C238" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -7332,10 +7335,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>474</v>
+      </c>
+      <c r="C239" t="s">
         <v>475</v>
-      </c>
-      <c r="C239" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -7343,10 +7346,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>476</v>
+      </c>
+      <c r="C240" t="s">
         <v>477</v>
-      </c>
-      <c r="C240" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -7354,10 +7357,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>478</v>
+      </c>
+      <c r="C241" t="s">
         <v>479</v>
-      </c>
-      <c r="C241" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -7365,10 +7368,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>480</v>
+      </c>
+      <c r="C242" t="s">
         <v>481</v>
-      </c>
-      <c r="C242" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -7376,10 +7379,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>482</v>
+      </c>
+      <c r="C243" t="s">
         <v>483</v>
-      </c>
-      <c r="C243" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -7387,10 +7390,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>484</v>
+      </c>
+      <c r="C244" t="s">
         <v>485</v>
-      </c>
-      <c r="C244" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -7398,10 +7401,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>486</v>
+      </c>
+      <c r="C245" t="s">
         <v>487</v>
-      </c>
-      <c r="C245" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -7409,10 +7412,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>488</v>
+      </c>
+      <c r="C246" t="s">
         <v>489</v>
-      </c>
-      <c r="C246" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -7420,10 +7423,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>490</v>
+      </c>
+      <c r="C247" t="s">
         <v>491</v>
-      </c>
-      <c r="C247" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -7431,10 +7434,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>492</v>
+      </c>
+      <c r="C248" t="s">
         <v>493</v>
-      </c>
-      <c r="C248" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -7442,10 +7445,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>494</v>
+      </c>
+      <c r="C249" t="s">
         <v>495</v>
-      </c>
-      <c r="C249" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -7453,10 +7456,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
+        <v>496</v>
+      </c>
+      <c r="C250" t="s">
         <v>497</v>
-      </c>
-      <c r="C250" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7464,10 +7467,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
+        <v>498</v>
+      </c>
+      <c r="C251" t="s">
         <v>499</v>
-      </c>
-      <c r="C251" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7475,10 +7478,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C252" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7486,10 +7489,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>501</v>
+      </c>
+      <c r="C253" t="s">
         <v>502</v>
-      </c>
-      <c r="C253" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7497,10 +7500,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
+        <v>503</v>
+      </c>
+      <c r="C254" t="s">
         <v>504</v>
-      </c>
-      <c r="C254" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7508,10 +7511,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>505</v>
+      </c>
+      <c r="C255" t="s">
         <v>506</v>
-      </c>
-      <c r="C255" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7519,10 +7522,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>507</v>
+      </c>
+      <c r="C256" t="s">
         <v>508</v>
-      </c>
-      <c r="C256" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7530,10 +7533,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>509</v>
+      </c>
+      <c r="C257" t="s">
         <v>510</v>
-      </c>
-      <c r="C257" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7541,10 +7544,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>511</v>
+      </c>
+      <c r="C258" t="s">
         <v>512</v>
-      </c>
-      <c r="C258" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7552,10 +7555,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>513</v>
+      </c>
+      <c r="C259" t="s">
         <v>514</v>
-      </c>
-      <c r="C259" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7563,10 +7566,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>515</v>
+      </c>
+      <c r="C260" t="s">
         <v>516</v>
-      </c>
-      <c r="C260" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7574,10 +7577,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>517</v>
+      </c>
+      <c r="C261" t="s">
         <v>518</v>
-      </c>
-      <c r="C261" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7585,10 +7588,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>519</v>
+      </c>
+      <c r="C262" t="s">
         <v>520</v>
-      </c>
-      <c r="C262" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7596,10 +7599,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>521</v>
+      </c>
+      <c r="C263" t="s">
         <v>522</v>
-      </c>
-      <c r="C263" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7607,10 +7610,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>523</v>
+      </c>
+      <c r="C264" t="s">
         <v>524</v>
-      </c>
-      <c r="C264" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7618,10 +7621,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>525</v>
+      </c>
+      <c r="C265" t="s">
         <v>526</v>
-      </c>
-      <c r="C265" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7629,10 +7632,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>527</v>
+      </c>
+      <c r="C266" t="s">
         <v>528</v>
-      </c>
-      <c r="C266" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7640,10 +7643,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>529</v>
+      </c>
+      <c r="C267" t="s">
         <v>530</v>
-      </c>
-      <c r="C267" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7651,10 +7654,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>531</v>
+      </c>
+      <c r="C268" t="s">
         <v>532</v>
-      </c>
-      <c r="C268" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7662,10 +7665,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>533</v>
+      </c>
+      <c r="C269" t="s">
         <v>534</v>
-      </c>
-      <c r="C269" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7673,10 +7676,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>535</v>
+      </c>
+      <c r="C270" t="s">
         <v>536</v>
-      </c>
-      <c r="C270" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7684,10 +7687,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>538</v>
-      </c>
-      <c r="C271" t="s">
-        <v>539</v>
+        <v>537</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7695,10 +7698,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C272" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7706,10 +7709,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C273" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7717,10 +7720,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C274" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7728,10 +7731,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C275" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7739,10 +7742,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C276" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7750,10 +7753,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C277" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7761,10 +7764,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C278" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7772,10 +7775,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C279" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7783,10 +7786,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C280" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7794,10 +7797,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C281" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -7805,10 +7808,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C282" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -7816,10 +7819,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C283" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -7827,10 +7830,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C284" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -7838,10 +7841,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C285" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -7849,10 +7852,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C286" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7860,10 +7863,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C287" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -7871,10 +7874,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C288" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -7882,10 +7885,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C289" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -7893,10 +7896,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C290" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -7904,10 +7907,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C291" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -7915,10 +7918,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C292" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -7926,10 +7929,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C293" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -7937,10 +7940,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C294" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -7948,10 +7951,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C295" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -7959,10 +7962,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -7970,10 +7973,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C297" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -7981,10 +7984,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C298" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -7992,10 +7995,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C299" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -8003,10 +8006,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C300" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -8014,10 +8017,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C301" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8025,10 +8028,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C302" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8036,10 +8039,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C303" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8047,10 +8050,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C304" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8058,10 +8061,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C305" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8069,10 +8072,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C306" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8080,10 +8083,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C307" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8091,10 +8094,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C308" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8102,10 +8105,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C309" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8113,10 +8116,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C310" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8124,10 +8127,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C311" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8135,10 +8138,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C312" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8146,10 +8149,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C313" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8157,10 +8160,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C314" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8168,10 +8171,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C315" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8179,10 +8182,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C316" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8190,10 +8193,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C317" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8201,10 +8204,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C318" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8212,10 +8215,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C319" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8223,10 +8226,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C320" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8234,10 +8237,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C321" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8245,10 +8248,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C322" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8256,10 +8259,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C323" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8267,10 +8270,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C324" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8278,10 +8281,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C325" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8289,10 +8292,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C326" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8300,10 +8303,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C327" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8311,10 +8314,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C328" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8322,10 +8325,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C329" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8333,10 +8336,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C330" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8344,10 +8347,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C331" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8355,10 +8358,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C332" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8366,10 +8369,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C333" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8377,10 +8380,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C334" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8388,10 +8391,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C335" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8399,10 +8402,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C336" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8410,10 +8413,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C337" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8421,10 +8424,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8432,10 +8435,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8443,10 +8446,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C340" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8454,10 +8457,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C341" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8465,10 +8468,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C342" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8476,10 +8479,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C343" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8487,10 +8490,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C344" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8498,10 +8501,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C345" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8509,10 +8512,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C346" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8520,10 +8523,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C347" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8531,10 +8534,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C348" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8542,10 +8545,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C349" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8553,10 +8556,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C350" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8564,10 +8567,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C351" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8575,10 +8578,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C352" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8586,10 +8589,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C353" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8597,10 +8600,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C354" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8608,10 +8611,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C355" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8619,10 +8622,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C356" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8630,10 +8633,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C357" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8641,10 +8644,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C358" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8652,10 +8655,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C359" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8663,10 +8666,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C360" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8674,10 +8677,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C361" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8685,10 +8688,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C362" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8696,10 +8699,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C363" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8707,10 +8710,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C364" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8718,10 +8721,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C365" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8729,10 +8732,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C366" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8740,10 +8743,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C367" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8751,10 +8754,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C368" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8762,10 +8765,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C369" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8773,10 +8776,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C370" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -8784,10 +8787,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C371" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -8795,10 +8798,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C372" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -8806,10 +8809,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C373" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -8817,10 +8820,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C374" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8828,10 +8831,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C375" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -8839,10 +8842,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C376" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -8850,10 +8853,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C377" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8861,10 +8864,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C378" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -8872,10 +8875,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C379" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8883,10 +8886,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C380" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -8894,10 +8897,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C381" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -8905,10 +8908,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C382" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -8916,10 +8919,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C383" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -8927,10 +8930,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C384" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -8938,10 +8941,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C385" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -8949,10 +8952,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C386" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -8960,10 +8963,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C387" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -8971,10 +8974,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C388" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -8982,10 +8985,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C389" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -8993,10 +8996,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C390" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9004,10 +9007,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C391" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9015,10 +9018,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C392" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9026,10 +9029,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C393" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9037,10 +9040,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C394" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9048,10 +9051,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C395" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9059,10 +9062,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C396" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9070,10 +9073,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C397" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9081,10 +9084,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C398" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9092,10 +9095,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C399" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9103,10 +9106,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C400" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9114,10 +9117,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C401" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9125,10 +9128,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C402" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9136,10 +9139,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C403" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9147,10 +9150,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C404" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9158,10 +9161,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C405" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9169,10 +9172,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C406" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9180,10 +9183,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C407" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9191,10 +9194,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C408" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9202,10 +9205,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C409" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9213,10 +9216,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C410" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9224,10 +9227,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C411" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9235,10 +9238,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C412" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9246,10 +9249,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C413" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9257,10 +9260,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C414" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9268,10 +9271,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C415" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9279,10 +9282,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C416" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9290,10 +9293,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C417" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9301,10 +9304,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C418" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9312,10 +9315,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C419" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9323,10 +9326,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C420" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9334,10 +9337,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C421" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9345,10 +9348,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C422" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9356,10 +9359,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C423" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9367,10 +9370,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C424" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9378,10 +9381,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C425" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9389,10 +9392,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C426" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9400,10 +9403,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C427" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9411,10 +9414,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C428" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9422,10 +9425,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C429" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9433,10 +9436,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C430" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9444,10 +9447,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C431" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9455,10 +9458,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C432" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9466,10 +9469,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C433" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9477,10 +9480,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C434" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9488,10 +9491,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C435" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9499,10 +9502,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C436" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9510,10 +9513,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C437" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9521,10 +9524,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C438" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9532,10 +9535,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C439" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9543,10 +9546,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C440" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9554,10 +9557,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C441" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9565,10 +9568,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C442" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9576,10 +9579,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C443" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9587,10 +9590,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C444" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9598,10 +9601,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C445" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9609,10 +9612,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C446" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9620,10 +9623,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C447" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9631,10 +9634,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C448" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9642,10 +9645,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C449" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9653,10 +9656,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C450" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9664,10 +9667,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C451" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9675,10 +9678,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C452" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9686,10 +9689,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C453" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9697,10 +9700,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C454" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9708,10 +9711,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C455" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9719,10 +9722,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C456" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9730,10 +9733,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C457" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9741,10 +9744,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C458" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9752,10 +9755,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C459" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9763,7 +9766,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9771,10 +9774,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C461" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9782,10 +9785,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C462" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9793,10 +9796,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C463" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9804,10 +9807,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C464" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9815,10 +9818,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C465" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9826,10 +9829,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C466" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9837,10 +9840,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9848,10 +9851,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C468" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9859,10 +9862,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C469" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9870,10 +9873,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C470" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9881,10 +9884,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C471" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9892,10 +9895,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C472" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9903,10 +9906,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C473" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9914,10 +9917,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C474" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9925,10 +9928,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C475" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9936,10 +9939,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C476" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9947,10 +9950,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C477" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9958,10 +9961,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C478" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9969,10 +9972,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C479" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9980,10 +9983,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C480" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -9991,10 +9994,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C481" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -10002,10 +10005,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C482" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10013,10 +10016,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C483" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10024,10 +10027,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C484" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10035,10 +10038,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C485" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10046,10 +10049,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C486" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10057,10 +10060,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C487" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10068,10 +10071,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C488" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10079,10 +10082,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C489" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10090,10 +10093,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C490" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10101,10 +10104,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C491" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10112,10 +10115,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C492" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10123,10 +10126,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C493" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10134,10 +10137,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C494" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10145,10 +10148,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C495" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10156,10 +10159,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C496" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10167,10 +10170,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C497" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10178,10 +10181,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C498" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10189,7 +10192,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10197,10 +10200,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C500" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10208,10 +10211,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C501" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10219,10 +10222,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C502" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10230,10 +10233,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10241,10 +10244,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C504" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10252,10 +10255,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C505" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10263,10 +10266,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C506" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10274,10 +10277,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C507" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10285,10 +10288,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C508" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10296,10 +10299,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C509" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10307,10 +10310,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C510" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10318,10 +10321,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C511" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10329,10 +10332,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C512" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10340,10 +10343,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C513" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10351,10 +10354,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C514" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10362,10 +10365,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C515" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10373,10 +10376,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C516" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10384,10 +10387,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C517" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10395,7 +10398,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10403,10 +10406,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C519" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10414,10 +10417,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C520" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10425,10 +10428,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C521" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10436,10 +10439,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C522" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10447,10 +10450,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C523" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10458,10 +10461,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C524" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10469,10 +10472,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C525" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10480,10 +10483,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C526" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10491,10 +10494,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C527" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10502,10 +10505,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C528" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10513,10 +10516,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C529" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10524,10 +10527,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10535,10 +10538,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C531" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10546,10 +10549,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C532" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10557,10 +10560,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C533" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10568,10 +10571,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C534" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10579,10 +10582,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C535" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10590,10 +10593,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C536" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10601,10 +10604,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C537" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10612,10 +10615,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C538" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10623,10 +10626,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C539" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10634,10 +10637,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C540" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10645,10 +10648,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C541" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10656,10 +10659,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C542" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10667,10 +10670,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C543" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10678,10 +10681,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C544" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10689,10 +10692,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C545" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10700,10 +10703,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C546" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10711,7 +10714,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10719,10 +10722,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C548" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10730,10 +10733,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C549" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10741,10 +10744,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C550" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10752,10 +10755,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C551" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10763,10 +10766,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C552" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10774,10 +10777,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C553" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10785,10 +10788,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C554" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10796,10 +10799,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C555" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10807,10 +10810,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C556" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10818,10 +10821,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C557" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10829,10 +10832,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C558" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10840,7 +10843,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10848,10 +10851,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C560" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10859,10 +10862,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C561" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10870,10 +10873,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C562" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10881,10 +10884,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C563" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10892,10 +10895,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C564" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10903,10 +10906,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C565" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10914,10 +10917,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C566" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10925,10 +10928,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C567" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10936,10 +10939,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C568" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10947,10 +10950,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C569" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10958,10 +10961,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C570" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10969,10 +10972,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C571" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10980,10 +10983,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="C572" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10991,10 +10994,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C573" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11002,10 +11005,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C574" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11013,10 +11016,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11024,10 +11027,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C576" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11035,10 +11038,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11046,10 +11049,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11057,10 +11060,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C579" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11068,10 +11071,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C580" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11079,10 +11082,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C581" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11090,10 +11093,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C582" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11101,10 +11104,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11112,10 +11115,10 @@
         <v>612</v>
       </c>
       <c r="B584" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C584" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11123,10 +11126,10 @@
         <v>615</v>
       </c>
       <c r="B585" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C585" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11134,10 +11137,10 @@
         <v>617</v>
       </c>
       <c r="B586" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C586" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11145,10 +11148,10 @@
         <v>618</v>
       </c>
       <c r="B587" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C587" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11156,10 +11159,10 @@
         <v>625</v>
       </c>
       <c r="B588" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C588" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11167,10 +11170,10 @@
         <v>624</v>
       </c>
       <c r="B589" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C589" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11178,10 +11181,10 @@
         <v>626</v>
       </c>
       <c r="B590" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C590" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11189,10 +11192,10 @@
         <v>629</v>
       </c>
       <c r="B591" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C591" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11200,10 +11203,10 @@
         <v>630</v>
       </c>
       <c r="B592" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C592" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11211,7 +11214,7 @@
         <v>632</v>
       </c>
       <c r="C593" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11219,10 +11222,10 @@
         <v>633</v>
       </c>
       <c r="B594" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C594" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11230,10 +11233,10 @@
         <v>635</v>
       </c>
       <c r="B595" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C595" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11241,10 +11244,10 @@
         <v>636</v>
       </c>
       <c r="B596" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C596" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11252,10 +11255,10 @@
         <v>642</v>
       </c>
       <c r="B597" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C597" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11263,10 +11266,10 @@
         <v>644</v>
       </c>
       <c r="B598" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C598" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11274,10 +11277,10 @@
         <v>646</v>
       </c>
       <c r="B599" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C599" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11285,10 +11288,10 @@
         <v>649</v>
       </c>
       <c r="B600" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C600" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11296,10 +11299,10 @@
         <v>650</v>
       </c>
       <c r="B601" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11307,10 +11310,10 @@
         <v>651</v>
       </c>
       <c r="B602" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C602" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11318,10 +11321,10 @@
         <v>653</v>
       </c>
       <c r="B603" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C603" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11329,10 +11332,10 @@
         <v>654</v>
       </c>
       <c r="B604" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C604" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11340,10 +11343,10 @@
         <v>655</v>
       </c>
       <c r="B605" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C605" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11351,10 +11354,10 @@
         <v>659</v>
       </c>
       <c r="B606" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C606" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11362,10 +11365,10 @@
         <v>660</v>
       </c>
       <c r="B607" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C607" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11373,10 +11376,10 @@
         <v>661</v>
       </c>
       <c r="B608" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C608" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11384,10 +11387,10 @@
         <v>663</v>
       </c>
       <c r="B609" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C609" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11395,10 +11398,10 @@
         <v>667</v>
       </c>
       <c r="B610" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C610" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11406,10 +11409,10 @@
         <v>670</v>
       </c>
       <c r="B611" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C611" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11417,10 +11420,10 @@
         <v>673</v>
       </c>
       <c r="B612" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C612" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11428,10 +11431,10 @@
         <v>674</v>
       </c>
       <c r="B613" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C613" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11439,10 +11442,10 @@
         <v>675</v>
       </c>
       <c r="B614" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C614" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11450,10 +11453,10 @@
         <v>680</v>
       </c>
       <c r="B615" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C615" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11461,10 +11464,10 @@
         <v>681</v>
       </c>
       <c r="B616" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C616" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11472,10 +11475,10 @@
         <v>682</v>
       </c>
       <c r="B617" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C617" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11483,10 +11486,10 @@
         <v>683</v>
       </c>
       <c r="B618" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C618" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11494,10 +11497,10 @@
         <v>684</v>
       </c>
       <c r="B619" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C619" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11505,10 +11508,10 @@
         <v>685</v>
       </c>
       <c r="B620" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C620" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11516,10 +11519,10 @@
         <v>686</v>
       </c>
       <c r="B621" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C621" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11527,10 +11530,10 @@
         <v>689</v>
       </c>
       <c r="B622" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C622" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11538,10 +11541,10 @@
         <v>697</v>
       </c>
       <c r="B623" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C623" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11549,10 +11552,10 @@
         <v>701</v>
       </c>
       <c r="B624" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C624" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11560,10 +11563,10 @@
         <v>702</v>
       </c>
       <c r="B625" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C625" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11571,10 +11574,10 @@
         <v>704</v>
       </c>
       <c r="B626" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C626" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11582,10 +11585,10 @@
         <v>705</v>
       </c>
       <c r="B627" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C627" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11593,10 +11596,10 @@
         <v>710</v>
       </c>
       <c r="B628" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C628" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11604,10 +11607,10 @@
         <v>711</v>
       </c>
       <c r="B629" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C629" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11615,10 +11618,10 @@
         <v>712</v>
       </c>
       <c r="B630" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C630" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11626,10 +11629,10 @@
         <v>714</v>
       </c>
       <c r="B631" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11637,10 +11640,10 @@
         <v>717</v>
       </c>
       <c r="B632" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11648,10 +11651,10 @@
         <v>718</v>
       </c>
       <c r="B633" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C633" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11659,10 +11662,10 @@
         <v>719</v>
       </c>
       <c r="B634" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C634" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11670,10 +11673,10 @@
         <v>721</v>
       </c>
       <c r="B635" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C635" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11681,10 +11684,10 @@
         <v>722</v>
       </c>
       <c r="B636" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="C636" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11692,10 +11695,10 @@
         <v>723</v>
       </c>
       <c r="B637" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C637" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11703,7 +11706,7 @@
         <v>724</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11711,10 +11714,10 @@
         <v>725</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C639" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11722,10 +11725,10 @@
         <v>726</v>
       </c>
       <c r="B640" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="C640" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11733,10 +11736,10 @@
         <v>727</v>
       </c>
       <c r="B641" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C641" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11744,10 +11747,10 @@
         <v>728</v>
       </c>
       <c r="B642" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C642" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11755,10 +11758,10 @@
         <v>729</v>
       </c>
       <c r="B643" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C643" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11766,10 +11769,10 @@
         <v>730</v>
       </c>
       <c r="B644" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C644" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11777,10 +11780,10 @@
         <v>731</v>
       </c>
       <c r="B645" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11788,10 +11791,10 @@
         <v>733</v>
       </c>
       <c r="B646" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C646" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11799,10 +11802,10 @@
         <v>735</v>
       </c>
       <c r="B647" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C647" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11810,10 +11813,10 @@
         <v>736</v>
       </c>
       <c r="B648" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C648" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11821,10 +11824,10 @@
         <v>737</v>
       </c>
       <c r="B649" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C649" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11832,10 +11835,10 @@
         <v>738</v>
       </c>
       <c r="B650" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C650" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11843,10 +11846,10 @@
         <v>739</v>
       </c>
       <c r="B651" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C651" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11854,10 +11857,10 @@
         <v>740</v>
       </c>
       <c r="B652" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C652" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11865,10 +11868,10 @@
         <v>741</v>
       </c>
       <c r="B653" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C653" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11876,10 +11879,10 @@
         <v>742</v>
       </c>
       <c r="B654" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C654" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11887,10 +11890,10 @@
         <v>743</v>
       </c>
       <c r="B655" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C655" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11898,10 +11901,10 @@
         <v>744</v>
       </c>
       <c r="B656" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C656" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11909,10 +11912,10 @@
         <v>745</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C657" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11920,10 +11923,10 @@
         <v>746</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C658" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11931,10 +11934,10 @@
         <v>747</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C659" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11942,10 +11945,10 @@
         <v>748</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C660" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11953,10 +11956,10 @@
         <v>749</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C661" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11965,7 +11968,7 @@
       </c>
       <c r="B662" s="1"/>
       <c r="C662" s="3" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11973,10 +11976,10 @@
         <v>753</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C663" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11984,10 +11987,10 @@
         <v>755</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C664" s="3" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11995,10 +11998,10 @@
         <v>756</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C665" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12006,10 +12009,10 @@
         <v>757</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C666" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12017,10 +12020,10 @@
         <v>758</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C667" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12028,10 +12031,10 @@
         <v>759</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1300</v>
+        <v>1297</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>1347</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12039,10 +12042,10 @@
         <v>760</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="C669" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12050,10 +12053,10 @@
         <v>761</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="C670" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12061,10 +12064,10 @@
         <v>762</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="C671" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12072,10 +12075,10 @@
         <v>763</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="C672" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12083,10 +12086,10 @@
         <v>764</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="C673" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -12094,10 +12097,10 @@
         <v>765</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="C674" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12111,10 +12114,10 @@
         <v>767</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C676" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12123,7 +12126,7 @@
       </c>
       <c r="B677" s="1"/>
       <c r="C677" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12131,10 +12134,10 @@
         <v>769</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="C678" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12142,10 +12145,10 @@
         <v>772</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="C679" s="3" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12154,7 +12157,7 @@
       </c>
       <c r="B680" s="1"/>
       <c r="C680" s="3" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12163,7 +12166,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12172,7 +12175,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12181,7 +12184,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12190,7 +12193,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12199,7 +12202,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12208,7 +12211,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12217,7 +12220,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -12226,7 +12229,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
@@ -12234,10 +12237,10 @@
         <v>10001</v>
       </c>
       <c r="B689" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="C689" s="3" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -12245,10 +12248,10 @@
         <v>10003</v>
       </c>
       <c r="B690" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="C690" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
   </sheetData>
@@ -12256,7 +12259,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A689:B689 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C529 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A689:B689 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C529 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020FF152-D290-4103-86CA-574610343870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A643064-318C-4F0D-8E5B-5BAF3448A820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="816" yWindow="1536" windowWidth="20832" windowHeight="14268" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="1351">
   <si>
     <t>Id</t>
   </si>
@@ -4282,6 +4282,10 @@
   </si>
   <si>
     <t>右肩之蝶,右肩蝶,右肩的蝶</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花天堂</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4703,7 +4707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C690"/>
+  <dimension ref="A1:C691"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.69921875" customWidth="1"/>
@@ -11112,1145 +11116,1153 @@
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584">
-        <v>612</v>
-      </c>
-      <c r="B584" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1140</v>
+        <v>609</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B585" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C585" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B586" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C586" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B587" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C587" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="B588" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C588" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B589" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C589" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B590" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C590" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B591" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C591" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B592" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C592" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593">
-        <v>632</v>
+        <v>630</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1155</v>
       </c>
       <c r="C593" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594">
-        <v>633</v>
-      </c>
-      <c r="B594" t="s">
-        <v>1158</v>
+        <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B595" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C595" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B596" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C596" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B597" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C597" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B598" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C598" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B599" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C599" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B600" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C600" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B601" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C601" s="3" t="s">
-        <v>1320</v>
+        <v>1170</v>
+      </c>
+      <c r="C601" t="s">
+        <v>1171</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1174</v>
+        <v>1172</v>
+      </c>
+      <c r="C602" s="3" t="s">
+        <v>1320</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B603" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C603" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B604" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C604" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B605" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C605" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B606" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C606" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B607" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C607" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B608" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C608" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B609" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C609" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B610" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C610" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B611" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C611" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B612" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C612" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B613" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C613" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B614" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C614" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B615" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C615" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B616" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C616" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B617" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C617" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B618" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C618" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B619" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C619" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B620" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C620" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B621" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C621" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B622" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C622" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B623" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C623" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B624" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C624" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B625" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C625" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B626" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C626" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B627" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C627" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B628" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C628" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B629" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C629" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B630" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C630" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B631" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C631" s="3" t="s">
-        <v>1321</v>
+        <v>1229</v>
+      </c>
+      <c r="C631" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1344</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1234</v>
+        <v>1232</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>1344</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634">
+        <v>718</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C634" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A635">
         <v>719</v>
       </c>
-      <c r="B634" t="s">
+      <c r="B635" t="s">
         <v>1235</v>
       </c>
-      <c r="C634" t="s">
+      <c r="C635" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A635">
+    <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A636">
         <v>721</v>
       </c>
-      <c r="B635" t="s">
+      <c r="B636" t="s">
         <v>1237</v>
       </c>
-      <c r="C635" t="s">
+      <c r="C636" t="s">
         <v>1238</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A636">
-        <v>722</v>
-      </c>
-      <c r="B636" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B637" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="C637" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638">
-        <v>724</v>
-      </c>
-      <c r="C638" s="3" t="s">
-        <v>1338</v>
+        <v>723</v>
+      </c>
+      <c r="B638" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C638" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639">
-        <v>725</v>
-      </c>
-      <c r="B639" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1244</v>
+        <v>724</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>1338</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640">
-        <v>726</v>
-      </c>
-      <c r="B640" t="s">
-        <v>1245</v>
+        <v>725</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>1243</v>
       </c>
       <c r="C640" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641">
+        <v>726</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C641" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A642">
         <v>727</v>
       </c>
-      <c r="B641" t="s">
+      <c r="B642" t="s">
         <v>1247</v>
       </c>
-      <c r="C641" t="s">
+      <c r="C642" t="s">
         <v>1248</v>
-      </c>
-    </row>
-    <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A642">
-        <v>728</v>
-      </c>
-      <c r="B642" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A643">
+        <v>728</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C643" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A644">
         <v>729</v>
       </c>
-      <c r="B643" t="s">
+      <c r="B644" t="s">
         <v>1251</v>
       </c>
-      <c r="C643" t="s">
+      <c r="C644" t="s">
         <v>1252</v>
-      </c>
-    </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A644">
-        <v>730</v>
-      </c>
-      <c r="B644" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B645" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C645" s="3" t="s">
-        <v>1317</v>
+        <v>1253</v>
+      </c>
+      <c r="C645" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1257</v>
+        <v>1255</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>1317</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B647" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C647" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B648" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C648" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B649" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C649" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B650" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C650" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B651" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C651" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B652" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C652" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B653" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C653" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B654" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C654" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B655" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C655" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656">
+        <v>743</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C656" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A657">
         <v>744</v>
       </c>
-      <c r="B656" t="s">
+      <c r="B657" t="s">
         <v>1276</v>
       </c>
-      <c r="C656" t="s">
+      <c r="C657" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="657" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A657">
+    <row r="658" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A658">
         <v>745</v>
       </c>
-      <c r="B657" s="1" t="s">
+      <c r="B658" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="C657" t="s">
+      <c r="C658" t="s">
         <v>1279</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A658">
-        <v>746</v>
-      </c>
-      <c r="B658" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C659" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C660" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C661" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662">
-        <v>750</v>
-      </c>
-      <c r="B662" s="1"/>
-      <c r="C662" s="3" t="s">
-        <v>1343</v>
+        <v>749</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C662" t="s">
+        <v>1287</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663">
-        <v>753</v>
-      </c>
-      <c r="B663" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1289</v>
+        <v>750</v>
+      </c>
+      <c r="B663" s="1"/>
+      <c r="C663" s="3" t="s">
+        <v>1343</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C664" s="3" t="s">
-        <v>1339</v>
+        <v>1288</v>
+      </c>
+      <c r="C664" t="s">
+        <v>1289</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1292</v>
+        <v>1290</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>1339</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C666" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C667" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C668" s="3" t="s">
-        <v>1347</v>
+        <v>1295</v>
+      </c>
+      <c r="C668" t="s">
+        <v>1296</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1299</v>
+        <v>1297</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>1347</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A670">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C670" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A671">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C671" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A672">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C672" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C673" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C674" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675">
-        <v>766</v>
-      </c>
-      <c r="B675" s="1"/>
+        <v>765</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C675" t="s">
+        <v>1309</v>
+      </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676">
-        <v>767</v>
-      </c>
-      <c r="B676" s="1" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1311</v>
-      </c>
+        <v>766</v>
+      </c>
+      <c r="B676" s="1"/>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677">
-        <v>768</v>
-      </c>
-      <c r="B677" s="1"/>
+        <v>767</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>1310</v>
+      </c>
       <c r="C677" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678">
-        <v>769</v>
-      </c>
-      <c r="B678" s="1" t="s">
-        <v>1313</v>
-      </c>
+        <v>768</v>
+      </c>
+      <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C679" s="3" t="s">
-        <v>1319</v>
+        <v>1313</v>
+      </c>
+      <c r="C679" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680">
-        <v>773</v>
-      </c>
-      <c r="B680" s="1"/>
+        <v>772</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>1318</v>
+      </c>
       <c r="C680" s="3" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A681">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1333</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A684">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A689">
-        <v>10001</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1315</v>
-      </c>
+        <v>782</v>
+      </c>
+      <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1346</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A690">
+        <v>10001</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691">
         <v>10003</v>
       </c>
-      <c r="B690" t="s">
+      <c r="B691" t="s">
         <v>1313</v>
       </c>
-      <c r="C690" t="s">
+      <c r="C691" t="s">
         <v>1314</v>
       </c>
     </row>
@@ -12259,7 +12271,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A689:B689 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C529 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C529 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A643064-318C-4F0D-8E5B-5BAF3448A820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF284C8-0D0A-4AA5-BF38-E065016B23F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1562,9 +1562,6 @@
     <t>ルカルカ★ナイトフィーバー</t>
   </si>
   <si>
-    <t>卢卡卢卡,露卡露卡,LukaLuka,LucaLuca,lukaluka</t>
-  </si>
-  <si>
     <t>群青日和</t>
   </si>
   <si>
@@ -4286,6 +4283,10 @@
   </si>
   <si>
     <t>花天堂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢卡卢卡,露卡露卡,LukaLuka,LucaLuca,lukaluka,时停</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5956,7 +5957,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -6143,7 +6144,7 @@
         <v>258</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -7177,7 +7178,7 @@
         <v>445</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7473,8 +7474,8 @@
       <c r="B251" t="s">
         <v>498</v>
       </c>
-      <c r="C251" t="s">
-        <v>499</v>
+      <c r="C251" s="3" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7482,10 +7483,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C252" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7493,10 +7494,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>500</v>
+      </c>
+      <c r="C253" t="s">
         <v>501</v>
-      </c>
-      <c r="C253" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7504,10 +7505,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
+        <v>502</v>
+      </c>
+      <c r="C254" t="s">
         <v>503</v>
-      </c>
-      <c r="C254" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7515,10 +7516,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>504</v>
+      </c>
+      <c r="C255" t="s">
         <v>505</v>
-      </c>
-      <c r="C255" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7526,10 +7527,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>506</v>
+      </c>
+      <c r="C256" t="s">
         <v>507</v>
-      </c>
-      <c r="C256" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7537,10 +7538,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>508</v>
+      </c>
+      <c r="C257" t="s">
         <v>509</v>
-      </c>
-      <c r="C257" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7548,10 +7549,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>510</v>
+      </c>
+      <c r="C258" t="s">
         <v>511</v>
-      </c>
-      <c r="C258" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7559,10 +7560,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>512</v>
+      </c>
+      <c r="C259" t="s">
         <v>513</v>
-      </c>
-      <c r="C259" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7570,10 +7571,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>514</v>
+      </c>
+      <c r="C260" t="s">
         <v>515</v>
-      </c>
-      <c r="C260" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7581,10 +7582,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>516</v>
+      </c>
+      <c r="C261" t="s">
         <v>517</v>
-      </c>
-      <c r="C261" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7592,10 +7593,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>518</v>
+      </c>
+      <c r="C262" t="s">
         <v>519</v>
-      </c>
-      <c r="C262" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7603,10 +7604,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>520</v>
+      </c>
+      <c r="C263" t="s">
         <v>521</v>
-      </c>
-      <c r="C263" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7614,10 +7615,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>522</v>
+      </c>
+      <c r="C264" t="s">
         <v>523</v>
-      </c>
-      <c r="C264" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7625,10 +7626,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>524</v>
+      </c>
+      <c r="C265" t="s">
         <v>525</v>
-      </c>
-      <c r="C265" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7636,10 +7637,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>526</v>
+      </c>
+      <c r="C266" t="s">
         <v>527</v>
-      </c>
-      <c r="C266" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7647,10 +7648,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>528</v>
+      </c>
+      <c r="C267" t="s">
         <v>529</v>
-      </c>
-      <c r="C267" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7658,10 +7659,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>530</v>
+      </c>
+      <c r="C268" t="s">
         <v>531</v>
-      </c>
-      <c r="C268" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7669,10 +7670,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>532</v>
+      </c>
+      <c r="C269" t="s">
         <v>533</v>
-      </c>
-      <c r="C269" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7680,10 +7681,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>534</v>
+      </c>
+      <c r="C270" t="s">
         <v>535</v>
-      </c>
-      <c r="C270" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7691,10 +7692,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7702,10 +7703,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>537</v>
+      </c>
+      <c r="C272" t="s">
         <v>538</v>
-      </c>
-      <c r="C272" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7713,10 +7714,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>539</v>
+      </c>
+      <c r="C273" t="s">
         <v>540</v>
-      </c>
-      <c r="C273" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7724,10 +7725,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>541</v>
+      </c>
+      <c r="C274" t="s">
         <v>542</v>
-      </c>
-      <c r="C274" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7735,10 +7736,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>543</v>
+      </c>
+      <c r="C275" t="s">
         <v>544</v>
-      </c>
-      <c r="C275" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7746,10 +7747,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>545</v>
+      </c>
+      <c r="C276" t="s">
         <v>546</v>
-      </c>
-      <c r="C276" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7757,10 +7758,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>547</v>
+      </c>
+      <c r="C277" t="s">
         <v>548</v>
-      </c>
-      <c r="C277" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7768,10 +7769,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>549</v>
+      </c>
+      <c r="C278" t="s">
         <v>550</v>
-      </c>
-      <c r="C278" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7779,10 +7780,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>551</v>
+      </c>
+      <c r="C279" t="s">
         <v>552</v>
-      </c>
-      <c r="C279" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7790,10 +7791,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>553</v>
+      </c>
+      <c r="C280" t="s">
         <v>554</v>
-      </c>
-      <c r="C280" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7801,10 +7802,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>555</v>
+      </c>
+      <c r="C281" t="s">
         <v>556</v>
-      </c>
-      <c r="C281" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -7812,10 +7813,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>557</v>
+      </c>
+      <c r="C282" t="s">
         <v>558</v>
-      </c>
-      <c r="C282" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -7823,10 +7824,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>559</v>
+      </c>
+      <c r="C283" t="s">
         <v>560</v>
-      </c>
-      <c r="C283" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -7834,10 +7835,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>561</v>
+      </c>
+      <c r="C284" t="s">
         <v>562</v>
-      </c>
-      <c r="C284" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -7845,10 +7846,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>563</v>
+      </c>
+      <c r="C285" t="s">
         <v>564</v>
-      </c>
-      <c r="C285" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -7856,10 +7857,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>565</v>
+      </c>
+      <c r="C286" t="s">
         <v>566</v>
-      </c>
-      <c r="C286" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7867,10 +7868,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>567</v>
+      </c>
+      <c r="C287" t="s">
         <v>568</v>
-      </c>
-      <c r="C287" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -7878,10 +7879,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>569</v>
+      </c>
+      <c r="C288" t="s">
         <v>570</v>
-      </c>
-      <c r="C288" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -7889,10 +7890,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>571</v>
+      </c>
+      <c r="C289" t="s">
         <v>572</v>
-      </c>
-      <c r="C289" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -7900,10 +7901,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>573</v>
+      </c>
+      <c r="C290" t="s">
         <v>574</v>
-      </c>
-      <c r="C290" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -7911,10 +7912,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>575</v>
+      </c>
+      <c r="C291" t="s">
         <v>576</v>
-      </c>
-      <c r="C291" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -7922,10 +7923,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>577</v>
+      </c>
+      <c r="C292" t="s">
         <v>578</v>
-      </c>
-      <c r="C292" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -7933,10 +7934,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>579</v>
+      </c>
+      <c r="C293" t="s">
         <v>580</v>
-      </c>
-      <c r="C293" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -7944,10 +7945,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>581</v>
+      </c>
+      <c r="C294" t="s">
         <v>582</v>
-      </c>
-      <c r="C294" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -7955,10 +7956,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>583</v>
+      </c>
+      <c r="C295" t="s">
         <v>584</v>
-      </c>
-      <c r="C295" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -7966,10 +7967,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -7977,10 +7978,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>586</v>
+      </c>
+      <c r="C297" t="s">
         <v>587</v>
-      </c>
-      <c r="C297" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -7988,10 +7989,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>588</v>
+      </c>
+      <c r="C298" t="s">
         <v>589</v>
-      </c>
-      <c r="C298" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -7999,10 +8000,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>590</v>
+      </c>
+      <c r="C299" t="s">
         <v>591</v>
-      </c>
-      <c r="C299" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -8010,10 +8011,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>592</v>
+      </c>
+      <c r="C300" t="s">
         <v>593</v>
-      </c>
-      <c r="C300" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -8021,10 +8022,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>594</v>
+      </c>
+      <c r="C301" t="s">
         <v>595</v>
-      </c>
-      <c r="C301" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8032,10 +8033,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>596</v>
+      </c>
+      <c r="C302" t="s">
         <v>597</v>
-      </c>
-      <c r="C302" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8043,10 +8044,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>598</v>
+      </c>
+      <c r="C303" t="s">
         <v>599</v>
-      </c>
-      <c r="C303" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8054,10 +8055,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>600</v>
+      </c>
+      <c r="C304" t="s">
         <v>601</v>
-      </c>
-      <c r="C304" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8065,10 +8066,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>602</v>
+      </c>
+      <c r="C305" t="s">
         <v>603</v>
-      </c>
-      <c r="C305" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8076,10 +8077,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>604</v>
+      </c>
+      <c r="C306" t="s">
         <v>605</v>
-      </c>
-      <c r="C306" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8087,10 +8088,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>606</v>
+      </c>
+      <c r="C307" t="s">
         <v>607</v>
-      </c>
-      <c r="C307" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8098,10 +8099,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>608</v>
+      </c>
+      <c r="C308" t="s">
         <v>609</v>
-      </c>
-      <c r="C308" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8109,10 +8110,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>610</v>
+      </c>
+      <c r="C309" t="s">
         <v>611</v>
-      </c>
-      <c r="C309" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8120,10 +8121,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>612</v>
+      </c>
+      <c r="C310" t="s">
         <v>613</v>
-      </c>
-      <c r="C310" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8131,10 +8132,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>614</v>
+      </c>
+      <c r="C311" t="s">
         <v>615</v>
-      </c>
-      <c r="C311" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8142,10 +8143,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>616</v>
+      </c>
+      <c r="C312" t="s">
         <v>617</v>
-      </c>
-      <c r="C312" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8153,10 +8154,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>618</v>
+      </c>
+      <c r="C313" t="s">
         <v>619</v>
-      </c>
-      <c r="C313" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8164,10 +8165,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>620</v>
+      </c>
+      <c r="C314" t="s">
         <v>621</v>
-      </c>
-      <c r="C314" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8175,10 +8176,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>622</v>
+      </c>
+      <c r="C315" t="s">
         <v>623</v>
-      </c>
-      <c r="C315" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8186,10 +8187,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>624</v>
+      </c>
+      <c r="C316" t="s">
         <v>625</v>
-      </c>
-      <c r="C316" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8197,10 +8198,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>626</v>
+      </c>
+      <c r="C317" t="s">
         <v>627</v>
-      </c>
-      <c r="C317" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8208,10 +8209,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>628</v>
+      </c>
+      <c r="C318" t="s">
         <v>629</v>
-      </c>
-      <c r="C318" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8219,10 +8220,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>630</v>
+      </c>
+      <c r="C319" t="s">
         <v>631</v>
-      </c>
-      <c r="C319" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8230,10 +8231,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>632</v>
+      </c>
+      <c r="C320" t="s">
         <v>633</v>
-      </c>
-      <c r="C320" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8241,10 +8242,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>634</v>
+      </c>
+      <c r="C321" t="s">
         <v>635</v>
-      </c>
-      <c r="C321" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8252,10 +8253,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>636</v>
+      </c>
+      <c r="C322" t="s">
         <v>637</v>
-      </c>
-      <c r="C322" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8263,10 +8264,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>638</v>
+      </c>
+      <c r="C323" t="s">
         <v>639</v>
-      </c>
-      <c r="C323" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8274,10 +8275,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>640</v>
+      </c>
+      <c r="C324" t="s">
         <v>641</v>
-      </c>
-      <c r="C324" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8285,10 +8286,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>642</v>
+      </c>
+      <c r="C325" t="s">
         <v>643</v>
-      </c>
-      <c r="C325" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8296,10 +8297,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>644</v>
+      </c>
+      <c r="C326" t="s">
         <v>645</v>
-      </c>
-      <c r="C326" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8307,10 +8308,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>646</v>
+      </c>
+      <c r="C327" t="s">
         <v>647</v>
-      </c>
-      <c r="C327" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8318,10 +8319,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>648</v>
+      </c>
+      <c r="C328" t="s">
         <v>649</v>
-      </c>
-      <c r="C328" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8329,10 +8330,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>650</v>
+      </c>
+      <c r="C329" t="s">
         <v>651</v>
-      </c>
-      <c r="C329" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8340,10 +8341,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>652</v>
+      </c>
+      <c r="C330" t="s">
         <v>653</v>
-      </c>
-      <c r="C330" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8351,10 +8352,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>654</v>
+      </c>
+      <c r="C331" t="s">
         <v>655</v>
-      </c>
-      <c r="C331" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8362,10 +8363,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>656</v>
+      </c>
+      <c r="C332" t="s">
         <v>657</v>
-      </c>
-      <c r="C332" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8373,10 +8374,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>658</v>
+      </c>
+      <c r="C333" t="s">
         <v>659</v>
-      </c>
-      <c r="C333" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8384,10 +8385,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>660</v>
+      </c>
+      <c r="C334" t="s">
         <v>661</v>
-      </c>
-      <c r="C334" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8395,10 +8396,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>662</v>
+      </c>
+      <c r="C335" t="s">
         <v>663</v>
-      </c>
-      <c r="C335" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8406,10 +8407,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>664</v>
+      </c>
+      <c r="C336" t="s">
         <v>665</v>
-      </c>
-      <c r="C336" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8417,10 +8418,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>666</v>
+      </c>
+      <c r="C337" t="s">
         <v>667</v>
-      </c>
-      <c r="C337" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8428,10 +8429,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8439,10 +8440,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8450,10 +8451,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>670</v>
+      </c>
+      <c r="C340" t="s">
         <v>671</v>
-      </c>
-      <c r="C340" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8461,10 +8462,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>672</v>
+      </c>
+      <c r="C341" t="s">
         <v>673</v>
-      </c>
-      <c r="C341" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8472,10 +8473,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>674</v>
+      </c>
+      <c r="C342" t="s">
         <v>675</v>
-      </c>
-      <c r="C342" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8483,10 +8484,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>676</v>
+      </c>
+      <c r="C343" t="s">
         <v>677</v>
-      </c>
-      <c r="C343" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8494,10 +8495,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>678</v>
+      </c>
+      <c r="C344" t="s">
         <v>679</v>
-      </c>
-      <c r="C344" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8505,10 +8506,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>680</v>
+      </c>
+      <c r="C345" t="s">
         <v>681</v>
-      </c>
-      <c r="C345" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8516,10 +8517,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>682</v>
+      </c>
+      <c r="C346" t="s">
         <v>683</v>
-      </c>
-      <c r="C346" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8527,10 +8528,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>684</v>
+      </c>
+      <c r="C347" t="s">
         <v>685</v>
-      </c>
-      <c r="C347" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8538,10 +8539,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>686</v>
+      </c>
+      <c r="C348" t="s">
         <v>687</v>
-      </c>
-      <c r="C348" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8549,10 +8550,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>688</v>
+      </c>
+      <c r="C349" t="s">
         <v>689</v>
-      </c>
-      <c r="C349" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8560,10 +8561,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>690</v>
+      </c>
+      <c r="C350" t="s">
         <v>691</v>
-      </c>
-      <c r="C350" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8571,10 +8572,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>692</v>
+      </c>
+      <c r="C351" t="s">
         <v>693</v>
-      </c>
-      <c r="C351" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8582,10 +8583,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>694</v>
+      </c>
+      <c r="C352" t="s">
         <v>695</v>
-      </c>
-      <c r="C352" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8593,10 +8594,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>696</v>
+      </c>
+      <c r="C353" t="s">
         <v>697</v>
-      </c>
-      <c r="C353" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8604,10 +8605,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>698</v>
+      </c>
+      <c r="C354" t="s">
         <v>699</v>
-      </c>
-      <c r="C354" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8615,10 +8616,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>700</v>
+      </c>
+      <c r="C355" t="s">
         <v>701</v>
-      </c>
-      <c r="C355" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8626,10 +8627,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>702</v>
+      </c>
+      <c r="C356" t="s">
         <v>703</v>
-      </c>
-      <c r="C356" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8637,10 +8638,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>704</v>
+      </c>
+      <c r="C357" t="s">
         <v>705</v>
-      </c>
-      <c r="C357" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8648,10 +8649,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>706</v>
+      </c>
+      <c r="C358" t="s">
         <v>707</v>
-      </c>
-      <c r="C358" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8659,10 +8660,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>708</v>
+      </c>
+      <c r="C359" t="s">
         <v>709</v>
-      </c>
-      <c r="C359" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8670,10 +8671,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>710</v>
+      </c>
+      <c r="C360" t="s">
         <v>711</v>
-      </c>
-      <c r="C360" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8681,10 +8682,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>712</v>
+      </c>
+      <c r="C361" t="s">
         <v>713</v>
-      </c>
-      <c r="C361" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8692,10 +8693,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>714</v>
+      </c>
+      <c r="C362" t="s">
         <v>715</v>
-      </c>
-      <c r="C362" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8703,10 +8704,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>716</v>
+      </c>
+      <c r="C363" t="s">
         <v>717</v>
-      </c>
-      <c r="C363" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8714,10 +8715,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>718</v>
+      </c>
+      <c r="C364" t="s">
         <v>719</v>
-      </c>
-      <c r="C364" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8725,10 +8726,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>720</v>
+      </c>
+      <c r="C365" t="s">
         <v>721</v>
-      </c>
-      <c r="C365" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8736,10 +8737,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>722</v>
+      </c>
+      <c r="C366" t="s">
         <v>723</v>
-      </c>
-      <c r="C366" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8747,10 +8748,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>724</v>
+      </c>
+      <c r="C367" t="s">
         <v>725</v>
-      </c>
-      <c r="C367" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8758,10 +8759,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>726</v>
+      </c>
+      <c r="C368" t="s">
         <v>727</v>
-      </c>
-      <c r="C368" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8769,10 +8770,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>728</v>
+      </c>
+      <c r="C369" t="s">
         <v>729</v>
-      </c>
-      <c r="C369" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8780,10 +8781,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>730</v>
+      </c>
+      <c r="C370" t="s">
         <v>731</v>
-      </c>
-      <c r="C370" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -8791,10 +8792,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>732</v>
+      </c>
+      <c r="C371" t="s">
         <v>733</v>
-      </c>
-      <c r="C371" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -8802,10 +8803,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>734</v>
+      </c>
+      <c r="C372" t="s">
         <v>735</v>
-      </c>
-      <c r="C372" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -8813,10 +8814,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>736</v>
+      </c>
+      <c r="C373" t="s">
         <v>737</v>
-      </c>
-      <c r="C373" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -8824,10 +8825,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>738</v>
+      </c>
+      <c r="C374" t="s">
         <v>739</v>
-      </c>
-      <c r="C374" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8835,10 +8836,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>740</v>
+      </c>
+      <c r="C375" t="s">
         <v>741</v>
-      </c>
-      <c r="C375" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -8846,10 +8847,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>742</v>
+      </c>
+      <c r="C376" t="s">
         <v>743</v>
-      </c>
-      <c r="C376" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -8857,10 +8858,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>744</v>
+      </c>
+      <c r="C377" t="s">
         <v>745</v>
-      </c>
-      <c r="C377" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8868,10 +8869,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>746</v>
+      </c>
+      <c r="C378" t="s">
         <v>747</v>
-      </c>
-      <c r="C378" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -8879,10 +8880,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>748</v>
+      </c>
+      <c r="C379" t="s">
         <v>749</v>
-      </c>
-      <c r="C379" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8890,10 +8891,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>750</v>
+      </c>
+      <c r="C380" t="s">
         <v>751</v>
-      </c>
-      <c r="C380" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -8901,10 +8902,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>752</v>
+      </c>
+      <c r="C381" t="s">
         <v>753</v>
-      </c>
-      <c r="C381" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -8912,10 +8913,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>754</v>
+      </c>
+      <c r="C382" t="s">
         <v>755</v>
-      </c>
-      <c r="C382" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -8923,10 +8924,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>756</v>
+      </c>
+      <c r="C383" t="s">
         <v>757</v>
-      </c>
-      <c r="C383" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -8934,10 +8935,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>758</v>
+      </c>
+      <c r="C384" t="s">
         <v>759</v>
-      </c>
-      <c r="C384" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -8945,10 +8946,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>760</v>
+      </c>
+      <c r="C385" t="s">
         <v>761</v>
-      </c>
-      <c r="C385" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -8956,10 +8957,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>762</v>
+      </c>
+      <c r="C386" t="s">
         <v>763</v>
-      </c>
-      <c r="C386" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -8967,10 +8968,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>764</v>
+      </c>
+      <c r="C387" t="s">
         <v>765</v>
-      </c>
-      <c r="C387" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -8978,10 +8979,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>766</v>
+      </c>
+      <c r="C388" t="s">
         <v>767</v>
-      </c>
-      <c r="C388" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -8989,10 +8990,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>768</v>
+      </c>
+      <c r="C389" t="s">
         <v>769</v>
-      </c>
-      <c r="C389" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -9000,10 +9001,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>770</v>
+      </c>
+      <c r="C390" t="s">
         <v>771</v>
-      </c>
-      <c r="C390" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9011,10 +9012,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>772</v>
+      </c>
+      <c r="C391" t="s">
         <v>773</v>
-      </c>
-      <c r="C391" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9022,10 +9023,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>774</v>
+      </c>
+      <c r="C392" t="s">
         <v>775</v>
-      </c>
-      <c r="C392" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9033,10 +9034,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>776</v>
+      </c>
+      <c r="C393" t="s">
         <v>777</v>
-      </c>
-      <c r="C393" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9044,10 +9045,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>778</v>
+      </c>
+      <c r="C394" t="s">
         <v>779</v>
-      </c>
-      <c r="C394" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9055,10 +9056,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>780</v>
+      </c>
+      <c r="C395" t="s">
         <v>781</v>
-      </c>
-      <c r="C395" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9066,10 +9067,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>782</v>
+      </c>
+      <c r="C396" t="s">
         <v>783</v>
-      </c>
-      <c r="C396" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9077,10 +9078,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>784</v>
+      </c>
+      <c r="C397" t="s">
         <v>785</v>
-      </c>
-      <c r="C397" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9088,10 +9089,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>786</v>
+      </c>
+      <c r="C398" t="s">
         <v>787</v>
-      </c>
-      <c r="C398" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9099,10 +9100,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>788</v>
+      </c>
+      <c r="C399" t="s">
         <v>789</v>
-      </c>
-      <c r="C399" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9110,10 +9111,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>790</v>
+      </c>
+      <c r="C400" t="s">
         <v>791</v>
-      </c>
-      <c r="C400" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9121,10 +9122,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>792</v>
+      </c>
+      <c r="C401" t="s">
         <v>793</v>
-      </c>
-      <c r="C401" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9132,10 +9133,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>794</v>
+      </c>
+      <c r="C402" t="s">
         <v>795</v>
-      </c>
-      <c r="C402" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9143,10 +9144,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>796</v>
+      </c>
+      <c r="C403" t="s">
         <v>797</v>
-      </c>
-      <c r="C403" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9154,10 +9155,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>798</v>
+      </c>
+      <c r="C404" t="s">
         <v>799</v>
-      </c>
-      <c r="C404" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9165,10 +9166,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>800</v>
+      </c>
+      <c r="C405" t="s">
         <v>801</v>
-      </c>
-      <c r="C405" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9176,10 +9177,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>802</v>
+      </c>
+      <c r="C406" t="s">
         <v>803</v>
-      </c>
-      <c r="C406" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9187,10 +9188,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>804</v>
+      </c>
+      <c r="C407" t="s">
         <v>805</v>
-      </c>
-      <c r="C407" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9198,10 +9199,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>806</v>
+      </c>
+      <c r="C408" t="s">
         <v>807</v>
-      </c>
-      <c r="C408" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9209,10 +9210,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>808</v>
+      </c>
+      <c r="C409" t="s">
         <v>809</v>
-      </c>
-      <c r="C409" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9220,10 +9221,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>810</v>
+      </c>
+      <c r="C410" t="s">
         <v>811</v>
-      </c>
-      <c r="C410" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9231,10 +9232,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>812</v>
+      </c>
+      <c r="C411" t="s">
         <v>813</v>
-      </c>
-      <c r="C411" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9242,10 +9243,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>814</v>
+      </c>
+      <c r="C412" t="s">
         <v>815</v>
-      </c>
-      <c r="C412" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9253,10 +9254,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>816</v>
+      </c>
+      <c r="C413" t="s">
         <v>817</v>
-      </c>
-      <c r="C413" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9264,10 +9265,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>818</v>
+      </c>
+      <c r="C414" t="s">
         <v>819</v>
-      </c>
-      <c r="C414" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9275,10 +9276,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>820</v>
+      </c>
+      <c r="C415" t="s">
         <v>821</v>
-      </c>
-      <c r="C415" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9286,10 +9287,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>822</v>
+      </c>
+      <c r="C416" t="s">
         <v>823</v>
-      </c>
-      <c r="C416" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9297,10 +9298,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>824</v>
+      </c>
+      <c r="C417" t="s">
         <v>825</v>
-      </c>
-      <c r="C417" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9308,10 +9309,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>826</v>
+      </c>
+      <c r="C418" t="s">
         <v>827</v>
-      </c>
-      <c r="C418" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9319,10 +9320,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>828</v>
+      </c>
+      <c r="C419" t="s">
         <v>829</v>
-      </c>
-      <c r="C419" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9330,10 +9331,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>830</v>
+      </c>
+      <c r="C420" t="s">
         <v>831</v>
-      </c>
-      <c r="C420" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9341,10 +9342,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>832</v>
+      </c>
+      <c r="C421" t="s">
         <v>833</v>
-      </c>
-      <c r="C421" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9352,10 +9353,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>834</v>
+      </c>
+      <c r="C422" t="s">
         <v>835</v>
-      </c>
-      <c r="C422" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9363,10 +9364,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>836</v>
+      </c>
+      <c r="C423" t="s">
         <v>837</v>
-      </c>
-      <c r="C423" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9374,10 +9375,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>838</v>
+      </c>
+      <c r="C424" t="s">
         <v>839</v>
-      </c>
-      <c r="C424" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9385,10 +9386,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>840</v>
+      </c>
+      <c r="C425" t="s">
         <v>841</v>
-      </c>
-      <c r="C425" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9396,10 +9397,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>842</v>
+      </c>
+      <c r="C426" t="s">
         <v>843</v>
-      </c>
-      <c r="C426" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9407,10 +9408,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>844</v>
+      </c>
+      <c r="C427" t="s">
         <v>845</v>
-      </c>
-      <c r="C427" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9418,10 +9419,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C428" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9429,10 +9430,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C429" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9440,10 +9441,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>848</v>
+      </c>
+      <c r="C430" t="s">
         <v>849</v>
-      </c>
-      <c r="C430" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9451,10 +9452,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>850</v>
+      </c>
+      <c r="C431" t="s">
         <v>851</v>
-      </c>
-      <c r="C431" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9462,10 +9463,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>852</v>
+      </c>
+      <c r="C432" t="s">
         <v>853</v>
-      </c>
-      <c r="C432" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9473,10 +9474,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>854</v>
+      </c>
+      <c r="C433" t="s">
         <v>855</v>
-      </c>
-      <c r="C433" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9484,10 +9485,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>856</v>
+      </c>
+      <c r="C434" t="s">
         <v>857</v>
-      </c>
-      <c r="C434" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9495,10 +9496,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>858</v>
+      </c>
+      <c r="C435" t="s">
         <v>859</v>
-      </c>
-      <c r="C435" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9506,10 +9507,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>860</v>
+      </c>
+      <c r="C436" t="s">
         <v>861</v>
-      </c>
-      <c r="C436" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9517,10 +9518,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>862</v>
+      </c>
+      <c r="C437" t="s">
         <v>863</v>
-      </c>
-      <c r="C437" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9528,10 +9529,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>864</v>
+      </c>
+      <c r="C438" t="s">
         <v>865</v>
-      </c>
-      <c r="C438" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9539,10 +9540,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>866</v>
+      </c>
+      <c r="C439" t="s">
         <v>867</v>
-      </c>
-      <c r="C439" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9550,10 +9551,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>868</v>
+      </c>
+      <c r="C440" t="s">
         <v>869</v>
-      </c>
-      <c r="C440" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9561,10 +9562,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>870</v>
+      </c>
+      <c r="C441" t="s">
         <v>871</v>
-      </c>
-      <c r="C441" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9572,10 +9573,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>872</v>
+      </c>
+      <c r="C442" t="s">
         <v>873</v>
-      </c>
-      <c r="C442" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9583,10 +9584,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>874</v>
+      </c>
+      <c r="C443" t="s">
         <v>875</v>
-      </c>
-      <c r="C443" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9594,10 +9595,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>876</v>
+      </c>
+      <c r="C444" t="s">
         <v>877</v>
-      </c>
-      <c r="C444" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9605,10 +9606,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>878</v>
+      </c>
+      <c r="C445" t="s">
         <v>879</v>
-      </c>
-      <c r="C445" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9616,10 +9617,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>880</v>
+      </c>
+      <c r="C446" t="s">
         <v>881</v>
-      </c>
-      <c r="C446" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9627,10 +9628,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>882</v>
+      </c>
+      <c r="C447" t="s">
         <v>883</v>
-      </c>
-      <c r="C447" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9638,10 +9639,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>884</v>
+      </c>
+      <c r="C448" t="s">
         <v>885</v>
-      </c>
-      <c r="C448" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9649,10 +9650,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>886</v>
+      </c>
+      <c r="C449" t="s">
         <v>887</v>
-      </c>
-      <c r="C449" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9660,10 +9661,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>888</v>
+      </c>
+      <c r="C450" t="s">
         <v>889</v>
-      </c>
-      <c r="C450" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9671,10 +9672,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C451" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9682,10 +9683,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>891</v>
+      </c>
+      <c r="C452" t="s">
         <v>892</v>
-      </c>
-      <c r="C452" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9693,10 +9694,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>893</v>
+      </c>
+      <c r="C453" t="s">
         <v>894</v>
-      </c>
-      <c r="C453" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9704,10 +9705,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>895</v>
+      </c>
+      <c r="C454" t="s">
         <v>896</v>
-      </c>
-      <c r="C454" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9715,10 +9716,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>897</v>
+      </c>
+      <c r="C455" t="s">
         <v>898</v>
-      </c>
-      <c r="C455" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9726,10 +9727,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C456" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9737,10 +9738,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>900</v>
+      </c>
+      <c r="C457" t="s">
         <v>901</v>
-      </c>
-      <c r="C457" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9748,10 +9749,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>902</v>
+      </c>
+      <c r="C458" t="s">
         <v>903</v>
-      </c>
-      <c r="C458" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9759,10 +9760,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>904</v>
+      </c>
+      <c r="C459" t="s">
         <v>905</v>
-      </c>
-      <c r="C459" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9770,7 +9771,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9778,10 +9779,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>907</v>
+      </c>
+      <c r="C461" t="s">
         <v>908</v>
-      </c>
-      <c r="C461" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9789,10 +9790,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>909</v>
+      </c>
+      <c r="C462" t="s">
         <v>910</v>
-      </c>
-      <c r="C462" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9800,10 +9801,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>911</v>
+      </c>
+      <c r="C463" t="s">
         <v>912</v>
-      </c>
-      <c r="C463" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9811,10 +9812,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>913</v>
+      </c>
+      <c r="C464" t="s">
         <v>914</v>
-      </c>
-      <c r="C464" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9822,10 +9823,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>915</v>
+      </c>
+      <c r="C465" t="s">
         <v>916</v>
-      </c>
-      <c r="C465" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9833,10 +9834,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>917</v>
+      </c>
+      <c r="C466" t="s">
         <v>918</v>
-      </c>
-      <c r="C466" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9844,10 +9845,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9855,10 +9856,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>920</v>
+      </c>
+      <c r="C468" t="s">
         <v>921</v>
-      </c>
-      <c r="C468" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9866,10 +9867,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>922</v>
+      </c>
+      <c r="C469" t="s">
         <v>923</v>
-      </c>
-      <c r="C469" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9877,10 +9878,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>924</v>
+      </c>
+      <c r="C470" t="s">
         <v>925</v>
-      </c>
-      <c r="C470" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9888,10 +9889,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>926</v>
+      </c>
+      <c r="C471" t="s">
         <v>927</v>
-      </c>
-      <c r="C471" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9899,10 +9900,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>928</v>
+      </c>
+      <c r="C472" t="s">
         <v>929</v>
-      </c>
-      <c r="C472" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9910,10 +9911,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>930</v>
+      </c>
+      <c r="C473" t="s">
         <v>931</v>
-      </c>
-      <c r="C473" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9921,10 +9922,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>932</v>
+      </c>
+      <c r="C474" t="s">
         <v>933</v>
-      </c>
-      <c r="C474" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9932,10 +9933,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>934</v>
+      </c>
+      <c r="C475" t="s">
         <v>935</v>
-      </c>
-      <c r="C475" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9943,10 +9944,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>936</v>
+      </c>
+      <c r="C476" t="s">
         <v>937</v>
-      </c>
-      <c r="C476" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9954,10 +9955,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>938</v>
+      </c>
+      <c r="C477" t="s">
         <v>939</v>
-      </c>
-      <c r="C477" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9965,10 +9966,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C478" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9976,10 +9977,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>941</v>
+      </c>
+      <c r="C479" t="s">
         <v>942</v>
-      </c>
-      <c r="C479" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9987,10 +9988,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>943</v>
+      </c>
+      <c r="C480" t="s">
         <v>944</v>
-      </c>
-      <c r="C480" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -9998,10 +9999,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>945</v>
+      </c>
+      <c r="C481" t="s">
         <v>946</v>
-      </c>
-      <c r="C481" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -10009,10 +10010,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>947</v>
+      </c>
+      <c r="C482" t="s">
         <v>948</v>
-      </c>
-      <c r="C482" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10020,10 +10021,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>949</v>
+      </c>
+      <c r="C483" t="s">
         <v>950</v>
-      </c>
-      <c r="C483" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10031,10 +10032,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>951</v>
+      </c>
+      <c r="C484" t="s">
         <v>952</v>
-      </c>
-      <c r="C484" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10042,10 +10043,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>953</v>
+      </c>
+      <c r="C485" t="s">
         <v>954</v>
-      </c>
-      <c r="C485" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10053,10 +10054,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>955</v>
+      </c>
+      <c r="C486" t="s">
         <v>956</v>
-      </c>
-      <c r="C486" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10064,10 +10065,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>957</v>
+      </c>
+      <c r="C487" t="s">
         <v>958</v>
-      </c>
-      <c r="C487" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10075,10 +10076,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>959</v>
+      </c>
+      <c r="C488" t="s">
         <v>960</v>
-      </c>
-      <c r="C488" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10086,10 +10087,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>961</v>
+      </c>
+      <c r="C489" t="s">
         <v>962</v>
-      </c>
-      <c r="C489" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10097,10 +10098,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>963</v>
+      </c>
+      <c r="C490" t="s">
         <v>964</v>
-      </c>
-      <c r="C490" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10108,10 +10109,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>965</v>
+      </c>
+      <c r="C491" t="s">
         <v>966</v>
-      </c>
-      <c r="C491" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10119,10 +10120,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>967</v>
+      </c>
+      <c r="C492" t="s">
         <v>968</v>
-      </c>
-      <c r="C492" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10130,10 +10131,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>969</v>
+      </c>
+      <c r="C493" t="s">
         <v>970</v>
-      </c>
-      <c r="C493" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10141,10 +10142,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>971</v>
+      </c>
+      <c r="C494" t="s">
         <v>972</v>
-      </c>
-      <c r="C494" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10152,10 +10153,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>973</v>
+      </c>
+      <c r="C495" t="s">
         <v>974</v>
-      </c>
-      <c r="C495" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10163,10 +10164,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>975</v>
+      </c>
+      <c r="C496" t="s">
         <v>976</v>
-      </c>
-      <c r="C496" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10174,10 +10175,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>977</v>
+      </c>
+      <c r="C497" t="s">
         <v>978</v>
-      </c>
-      <c r="C497" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10185,10 +10186,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>979</v>
+      </c>
+      <c r="C498" t="s">
         <v>980</v>
-      </c>
-      <c r="C498" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10196,7 +10197,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10204,10 +10205,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>982</v>
+      </c>
+      <c r="C500" t="s">
         <v>983</v>
-      </c>
-      <c r="C500" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10215,10 +10216,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>984</v>
+      </c>
+      <c r="C501" t="s">
         <v>985</v>
-      </c>
-      <c r="C501" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10226,10 +10227,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>986</v>
+      </c>
+      <c r="C502" t="s">
         <v>987</v>
-      </c>
-      <c r="C502" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10237,10 +10238,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10248,10 +10249,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>989</v>
+      </c>
+      <c r="C504" t="s">
         <v>990</v>
-      </c>
-      <c r="C504" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10259,10 +10260,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>991</v>
+      </c>
+      <c r="C505" t="s">
         <v>992</v>
-      </c>
-      <c r="C505" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10270,10 +10271,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>993</v>
+      </c>
+      <c r="C506" t="s">
         <v>994</v>
-      </c>
-      <c r="C506" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10281,10 +10282,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>995</v>
+      </c>
+      <c r="C507" t="s">
         <v>996</v>
-      </c>
-      <c r="C507" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10292,10 +10293,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>997</v>
+      </c>
+      <c r="C508" t="s">
         <v>998</v>
-      </c>
-      <c r="C508" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10303,10 +10304,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>999</v>
+      </c>
+      <c r="C509" t="s">
         <v>1000</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10314,10 +10315,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C510" t="s">
         <v>1002</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10325,10 +10326,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C511" t="s">
         <v>1004</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10336,10 +10337,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C512" t="s">
         <v>1006</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10347,10 +10348,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C513" t="s">
         <v>1008</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10358,10 +10359,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C514" t="s">
         <v>1010</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10369,10 +10370,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C515" t="s">
         <v>1012</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10380,10 +10381,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C516" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10391,10 +10392,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C517" t="s">
         <v>1015</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10402,7 +10403,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10410,10 +10411,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C519" t="s">
         <v>1018</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10421,10 +10422,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C520" t="s">
         <v>1020</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10432,10 +10433,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C521" t="s">
         <v>1022</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10443,10 +10444,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C522" t="s">
         <v>1024</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10454,10 +10455,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C523" t="s">
         <v>1026</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10465,10 +10466,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C524" t="s">
         <v>1028</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10476,10 +10477,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C525" t="s">
         <v>1030</v>
-      </c>
-      <c r="C525" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10487,10 +10488,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C526" t="s">
         <v>1032</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10498,10 +10499,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C527" t="s">
         <v>1034</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10509,10 +10510,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C528" t="s">
         <v>1036</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10520,10 +10521,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C529" t="s">
         <v>1038</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10531,10 +10532,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10542,10 +10543,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C531" t="s">
         <v>1041</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10553,10 +10554,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C532" t="s">
         <v>1043</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10564,10 +10565,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C533" t="s">
         <v>1045</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10575,10 +10576,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C534" t="s">
         <v>1047</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10586,10 +10587,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C535" t="s">
         <v>1049</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10597,10 +10598,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C536" t="s">
         <v>1051</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10608,10 +10609,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C537" t="s">
         <v>1053</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10619,10 +10620,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C538" t="s">
         <v>1055</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10630,10 +10631,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C539" t="s">
         <v>1057</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10641,10 +10642,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C540" t="s">
         <v>1059</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10652,10 +10653,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C541" t="s">
         <v>1061</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10663,10 +10664,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C542" t="s">
         <v>1063</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10674,10 +10675,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C543" t="s">
         <v>1065</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10685,10 +10686,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C544" t="s">
         <v>1067</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10696,10 +10697,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C545" t="s">
         <v>1069</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10707,10 +10708,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C546" t="s">
         <v>1071</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10718,7 +10719,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10726,10 +10727,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C548" t="s">
         <v>1074</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10737,10 +10738,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C549" t="s">
         <v>1076</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10748,10 +10749,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C550" t="s">
         <v>1078</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10759,10 +10760,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C551" t="s">
         <v>1080</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10770,10 +10771,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C552" t="s">
         <v>1082</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10781,10 +10782,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C553" t="s">
         <v>1084</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10792,10 +10793,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C554" t="s">
         <v>1086</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10803,10 +10804,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C555" t="s">
         <v>1088</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10814,10 +10815,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C556" t="s">
         <v>1090</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10825,10 +10826,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C557" t="s">
         <v>1092</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10836,10 +10837,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C558" t="s">
         <v>1094</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10847,7 +10848,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10855,10 +10856,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C560" t="s">
         <v>1097</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10866,10 +10867,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C561" t="s">
         <v>1099</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10877,10 +10878,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C562" t="s">
         <v>1101</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10888,10 +10889,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C563" t="s">
         <v>1103</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10899,10 +10900,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C564" t="s">
         <v>1105</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10910,10 +10911,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C565" t="s">
         <v>1107</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10921,10 +10922,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C566" t="s">
         <v>1109</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10932,10 +10933,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C567" t="s">
         <v>1111</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10943,10 +10944,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C568" t="s">
         <v>1113</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10954,10 +10955,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C569" t="s">
         <v>1115</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10965,10 +10966,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C570" t="s">
         <v>1117</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10976,10 +10977,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C571" t="s">
         <v>1119</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10987,10 +10988,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C572" t="s">
         <v>1121</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10998,10 +10999,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C573" t="s">
         <v>1123</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11009,10 +11010,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C574" t="s">
         <v>1125</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11020,10 +11021,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11031,10 +11032,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C576" t="s">
         <v>1128</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11042,10 +11043,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11053,10 +11054,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11064,10 +11065,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C579" t="s">
         <v>1130</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11075,10 +11076,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C580" t="s">
         <v>1132</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11086,10 +11087,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C581" t="s">
         <v>1134</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11097,10 +11098,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C582" t="s">
         <v>1136</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11108,10 +11109,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11119,7 +11120,7 @@
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11127,10 +11128,10 @@
         <v>612</v>
       </c>
       <c r="B585" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C585" t="s">
         <v>1139</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11138,10 +11139,10 @@
         <v>615</v>
       </c>
       <c r="B586" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C586" t="s">
         <v>1141</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11149,10 +11150,10 @@
         <v>617</v>
       </c>
       <c r="B587" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C587" t="s">
         <v>1143</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11160,10 +11161,10 @@
         <v>618</v>
       </c>
       <c r="B588" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C588" t="s">
         <v>1145</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11171,10 +11172,10 @@
         <v>625</v>
       </c>
       <c r="B589" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C589" t="s">
         <v>1147</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11182,10 +11183,10 @@
         <v>624</v>
       </c>
       <c r="B590" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C590" t="s">
         <v>1149</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11193,10 +11194,10 @@
         <v>626</v>
       </c>
       <c r="B591" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C591" t="s">
         <v>1151</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11204,10 +11205,10 @@
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C592" t="s">
         <v>1153</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11215,10 +11216,10 @@
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C593" t="s">
         <v>1155</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11226,7 +11227,7 @@
         <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11234,10 +11235,10 @@
         <v>633</v>
       </c>
       <c r="B595" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C595" t="s">
         <v>1158</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11245,10 +11246,10 @@
         <v>635</v>
       </c>
       <c r="B596" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C596" t="s">
         <v>1160</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11256,10 +11257,10 @@
         <v>636</v>
       </c>
       <c r="B597" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C597" t="s">
         <v>1162</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11267,10 +11268,10 @@
         <v>642</v>
       </c>
       <c r="B598" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C598" t="s">
         <v>1164</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11278,10 +11279,10 @@
         <v>644</v>
       </c>
       <c r="B599" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C599" t="s">
         <v>1166</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11289,10 +11290,10 @@
         <v>646</v>
       </c>
       <c r="B600" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C600" t="s">
         <v>1168</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11300,10 +11301,10 @@
         <v>649</v>
       </c>
       <c r="B601" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C601" t="s">
         <v>1170</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11311,10 +11312,10 @@
         <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11322,10 +11323,10 @@
         <v>651</v>
       </c>
       <c r="B603" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C603" t="s">
         <v>1173</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11333,10 +11334,10 @@
         <v>653</v>
       </c>
       <c r="B604" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C604" t="s">
         <v>1175</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11344,10 +11345,10 @@
         <v>654</v>
       </c>
       <c r="B605" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C605" t="s">
         <v>1177</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11355,10 +11356,10 @@
         <v>655</v>
       </c>
       <c r="B606" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C606" t="s">
         <v>1179</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11366,10 +11367,10 @@
         <v>659</v>
       </c>
       <c r="B607" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C607" t="s">
         <v>1181</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11377,10 +11378,10 @@
         <v>660</v>
       </c>
       <c r="B608" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C608" t="s">
         <v>1183</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11388,10 +11389,10 @@
         <v>661</v>
       </c>
       <c r="B609" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C609" t="s">
         <v>1185</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11399,10 +11400,10 @@
         <v>663</v>
       </c>
       <c r="B610" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C610" t="s">
         <v>1187</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11410,10 +11411,10 @@
         <v>667</v>
       </c>
       <c r="B611" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C611" t="s">
         <v>1189</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11421,10 +11422,10 @@
         <v>670</v>
       </c>
       <c r="B612" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C612" t="s">
         <v>1191</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11432,10 +11433,10 @@
         <v>673</v>
       </c>
       <c r="B613" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C613" t="s">
         <v>1193</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11443,10 +11444,10 @@
         <v>674</v>
       </c>
       <c r="B614" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C614" t="s">
         <v>1195</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11454,10 +11455,10 @@
         <v>675</v>
       </c>
       <c r="B615" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C615" t="s">
         <v>1197</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11465,10 +11466,10 @@
         <v>680</v>
       </c>
       <c r="B616" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C616" t="s">
         <v>1199</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11476,10 +11477,10 @@
         <v>681</v>
       </c>
       <c r="B617" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C617" t="s">
         <v>1201</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11487,10 +11488,10 @@
         <v>682</v>
       </c>
       <c r="B618" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C618" t="s">
         <v>1203</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11498,10 +11499,10 @@
         <v>683</v>
       </c>
       <c r="B619" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C619" t="s">
         <v>1205</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11509,10 +11510,10 @@
         <v>684</v>
       </c>
       <c r="B620" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C620" t="s">
         <v>1207</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11520,10 +11521,10 @@
         <v>685</v>
       </c>
       <c r="B621" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C621" t="s">
         <v>1209</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11531,10 +11532,10 @@
         <v>686</v>
       </c>
       <c r="B622" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C622" t="s">
         <v>1211</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11542,10 +11543,10 @@
         <v>689</v>
       </c>
       <c r="B623" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C623" t="s">
         <v>1213</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11553,10 +11554,10 @@
         <v>697</v>
       </c>
       <c r="B624" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C624" t="s">
         <v>1215</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11564,10 +11565,10 @@
         <v>701</v>
       </c>
       <c r="B625" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C625" t="s">
         <v>1217</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11575,10 +11576,10 @@
         <v>702</v>
       </c>
       <c r="B626" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C626" t="s">
         <v>1219</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11586,10 +11587,10 @@
         <v>704</v>
       </c>
       <c r="B627" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C627" t="s">
         <v>1221</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11597,10 +11598,10 @@
         <v>705</v>
       </c>
       <c r="B628" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C628" t="s">
         <v>1223</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11608,10 +11609,10 @@
         <v>710</v>
       </c>
       <c r="B629" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C629" t="s">
         <v>1225</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11619,10 +11620,10 @@
         <v>711</v>
       </c>
       <c r="B630" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C630" t="s">
         <v>1227</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11630,10 +11631,10 @@
         <v>712</v>
       </c>
       <c r="B631" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C631" t="s">
         <v>1229</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11641,10 +11642,10 @@
         <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11652,10 +11653,10 @@
         <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11663,10 +11664,10 @@
         <v>718</v>
       </c>
       <c r="B634" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C634" t="s">
         <v>1233</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11674,10 +11675,10 @@
         <v>719</v>
       </c>
       <c r="B635" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C635" t="s">
         <v>1235</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11685,10 +11686,10 @@
         <v>721</v>
       </c>
       <c r="B636" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C636" t="s">
         <v>1237</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11696,10 +11697,10 @@
         <v>722</v>
       </c>
       <c r="B637" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C637" t="s">
         <v>1239</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11707,10 +11708,10 @@
         <v>723</v>
       </c>
       <c r="B638" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C638" t="s">
         <v>1241</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11718,7 +11719,7 @@
         <v>724</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11726,10 +11727,10 @@
         <v>725</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C640" t="s">
         <v>1243</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11737,10 +11738,10 @@
         <v>726</v>
       </c>
       <c r="B641" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C641" t="s">
         <v>1245</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11748,10 +11749,10 @@
         <v>727</v>
       </c>
       <c r="B642" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C642" t="s">
         <v>1247</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11759,10 +11760,10 @@
         <v>728</v>
       </c>
       <c r="B643" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C643" t="s">
         <v>1249</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11770,10 +11771,10 @@
         <v>729</v>
       </c>
       <c r="B644" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C644" t="s">
         <v>1251</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11781,10 +11782,10 @@
         <v>730</v>
       </c>
       <c r="B645" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C645" t="s">
         <v>1253</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11792,10 +11793,10 @@
         <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11803,10 +11804,10 @@
         <v>733</v>
       </c>
       <c r="B647" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C647" t="s">
         <v>1256</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11814,10 +11815,10 @@
         <v>735</v>
       </c>
       <c r="B648" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C648" t="s">
         <v>1258</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11825,10 +11826,10 @@
         <v>736</v>
       </c>
       <c r="B649" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C649" t="s">
         <v>1260</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11836,10 +11837,10 @@
         <v>737</v>
       </c>
       <c r="B650" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C650" t="s">
         <v>1262</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11847,10 +11848,10 @@
         <v>738</v>
       </c>
       <c r="B651" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C651" t="s">
         <v>1264</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11858,10 +11859,10 @@
         <v>739</v>
       </c>
       <c r="B652" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C652" t="s">
         <v>1266</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11869,10 +11870,10 @@
         <v>740</v>
       </c>
       <c r="B653" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C653" t="s">
         <v>1268</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11880,10 +11881,10 @@
         <v>741</v>
       </c>
       <c r="B654" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C654" t="s">
         <v>1270</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11891,10 +11892,10 @@
         <v>742</v>
       </c>
       <c r="B655" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C655" t="s">
         <v>1272</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11902,10 +11903,10 @@
         <v>743</v>
       </c>
       <c r="B656" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C656" t="s">
         <v>1274</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11913,10 +11914,10 @@
         <v>744</v>
       </c>
       <c r="B657" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C657" t="s">
         <v>1276</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11924,10 +11925,10 @@
         <v>745</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C658" t="s">
         <v>1278</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11935,10 +11936,10 @@
         <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C659" t="s">
         <v>1280</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11946,10 +11947,10 @@
         <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C660" t="s">
         <v>1282</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11957,10 +11958,10 @@
         <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C661" t="s">
         <v>1284</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11968,10 +11969,10 @@
         <v>749</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C662" t="s">
         <v>1286</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11980,7 +11981,7 @@
       </c>
       <c r="B663" s="1"/>
       <c r="C663" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11988,10 +11989,10 @@
         <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C664" t="s">
         <v>1288</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11999,10 +12000,10 @@
         <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12010,10 +12011,10 @@
         <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C666" t="s">
         <v>1291</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12021,10 +12022,10 @@
         <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C667" t="s">
         <v>1293</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12032,10 +12033,10 @@
         <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C668" t="s">
         <v>1295</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12043,10 +12044,10 @@
         <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12054,10 +12055,10 @@
         <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C670" t="s">
         <v>1298</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12065,10 +12066,10 @@
         <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C671" t="s">
         <v>1300</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12076,10 +12077,10 @@
         <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C672" t="s">
         <v>1302</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12087,10 +12088,10 @@
         <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C673" t="s">
         <v>1304</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -12098,10 +12099,10 @@
         <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C674" t="s">
         <v>1306</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12109,10 +12110,10 @@
         <v>765</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C675" t="s">
         <v>1308</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12126,10 +12127,10 @@
         <v>767</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C677" t="s">
         <v>1310</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12138,7 +12139,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12146,10 +12147,10 @@
         <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C679" t="s">
         <v>1313</v>
-      </c>
-      <c r="C679" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12157,10 +12158,10 @@
         <v>772</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C680" s="3" t="s">
         <v>1318</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12169,7 +12170,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12178,7 +12179,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12187,7 +12188,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12196,7 +12197,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12205,7 +12206,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12214,7 +12215,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12223,7 +12224,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -12232,7 +12233,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
@@ -12241,7 +12242,7 @@
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -12249,10 +12250,10 @@
         <v>10001</v>
       </c>
       <c r="B690" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
@@ -12260,10 +12261,10 @@
         <v>10003</v>
       </c>
       <c r="B691" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C691" t="s">
         <v>1313</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1314</v>
       </c>
     </row>
   </sheetData>

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF284C8-0D0A-4AA5-BF38-E065016B23F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13A1195-8313-445D-8AC3-30A73F49C1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4274,10 +4274,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>辛德瑞拉,罗密欧与朱丽叶,罗密欧与灰姑娘,罗密欧与辛德瑞拉</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>右肩之蝶,右肩蝶,右肩的蝶</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -4287,6 +4283,10 @@
   </si>
   <si>
     <t>卢卡卢卡,露卡露卡,LukaLuka,LucaLuca,lukaluka,时停</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>辛德瑞拉,罗密欧与朱丽叶,罗密欧与灰姑娘,罗密欧与辛德瑞拉,罗密欧与辛得瑞拉</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -6144,7 +6144,7 @@
         <v>258</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -7475,7 +7475,7 @@
         <v>498</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7695,7 +7695,7 @@
         <v>536</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -11120,7 +11120,7 @@
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13A1195-8313-445D-8AC3-30A73F49C1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303FADC5-60BB-4B33-AC1B-CB9B86D94B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3204,9 +3204,6 @@
     <t>ヒバナ-Reloaded-</t>
   </si>
   <si>
-    <t>火花,七八十,敷衍了事</t>
-  </si>
-  <si>
     <t>トウキョウ・シャンディ・ランデヴ</t>
   </si>
   <si>
@@ -4287,6 +4284,10 @@
   </si>
   <si>
     <t>辛德瑞拉,罗密欧与朱丽叶,罗密欧与灰姑娘,罗密欧与辛德瑞拉,罗密欧与辛得瑞拉</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>火花,七八十,敷衍了事,火花reloaded</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5957,7 +5958,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -6144,7 +6145,7 @@
         <v>258</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -7178,7 +7179,7 @@
         <v>445</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7475,7 +7476,7 @@
         <v>498</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7695,7 +7696,7 @@
         <v>536</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7970,7 +7971,7 @@
         <v>585</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -8432,7 +8433,7 @@
         <v>668</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8443,7 +8444,7 @@
         <v>669</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -9848,7 +9849,7 @@
         <v>919</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -10241,7 +10242,7 @@
         <v>988</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10479,8 +10480,8 @@
       <c r="B525" t="s">
         <v>1029</v>
       </c>
-      <c r="C525" t="s">
-        <v>1030</v>
+      <c r="C525" s="3" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10488,10 +10489,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C526" t="s">
         <v>1031</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10499,10 +10500,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C527" t="s">
         <v>1033</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10510,10 +10511,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C528" t="s">
         <v>1035</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10521,10 +10522,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C529" t="s">
         <v>1037</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10532,10 +10533,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10543,10 +10544,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C531" t="s">
         <v>1040</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10554,10 +10555,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C532" t="s">
         <v>1042</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10565,10 +10566,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C533" t="s">
         <v>1044</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10576,10 +10577,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C534" t="s">
         <v>1046</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10587,10 +10588,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C535" t="s">
         <v>1048</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10598,10 +10599,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C536" t="s">
         <v>1050</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10609,10 +10610,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C537" t="s">
         <v>1052</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10620,10 +10621,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C538" t="s">
         <v>1054</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10631,10 +10632,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C539" t="s">
         <v>1056</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10642,10 +10643,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C540" t="s">
         <v>1058</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10653,10 +10654,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C541" t="s">
         <v>1060</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10664,10 +10665,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C542" t="s">
         <v>1062</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10675,10 +10676,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C543" t="s">
         <v>1064</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10686,10 +10687,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C544" t="s">
         <v>1066</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10697,10 +10698,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C545" t="s">
         <v>1068</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10708,10 +10709,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C546" t="s">
         <v>1070</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10719,7 +10720,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10727,10 +10728,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C548" t="s">
         <v>1073</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10738,10 +10739,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C549" t="s">
         <v>1075</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10749,10 +10750,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C550" t="s">
         <v>1077</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10760,10 +10761,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C551" t="s">
         <v>1079</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10771,10 +10772,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C552" t="s">
         <v>1081</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10782,10 +10783,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C553" t="s">
         <v>1083</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10793,10 +10794,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C554" t="s">
         <v>1085</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10804,10 +10805,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C555" t="s">
         <v>1087</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10815,10 +10816,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C556" t="s">
         <v>1089</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10826,10 +10827,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C557" t="s">
         <v>1091</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10837,10 +10838,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C558" t="s">
         <v>1093</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10848,7 +10849,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10856,10 +10857,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C560" t="s">
         <v>1096</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10867,10 +10868,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C561" t="s">
         <v>1098</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10878,10 +10879,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C562" t="s">
         <v>1100</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10889,10 +10890,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C563" t="s">
         <v>1102</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10900,10 +10901,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C564" t="s">
         <v>1104</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10911,10 +10912,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C565" t="s">
         <v>1106</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10922,10 +10923,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C566" t="s">
         <v>1108</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10933,10 +10934,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C567" t="s">
         <v>1110</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10944,10 +10945,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C568" t="s">
         <v>1112</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10955,10 +10956,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C569" t="s">
         <v>1114</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10966,10 +10967,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C570" t="s">
         <v>1116</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10977,10 +10978,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C571" t="s">
         <v>1118</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10988,10 +10989,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C572" t="s">
         <v>1120</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10999,10 +11000,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C573" t="s">
         <v>1122</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11010,10 +11011,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C574" t="s">
         <v>1124</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11021,10 +11022,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11032,10 +11033,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C576" t="s">
         <v>1127</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11046,7 +11047,7 @@
         <v>934</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11057,7 +11058,7 @@
         <v>936</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11065,10 +11066,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C579" t="s">
         <v>1129</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11076,10 +11077,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C580" t="s">
         <v>1131</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11087,10 +11088,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C581" t="s">
         <v>1133</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11098,10 +11099,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C582" t="s">
         <v>1135</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11109,10 +11110,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11120,7 +11121,7 @@
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11128,10 +11129,10 @@
         <v>612</v>
       </c>
       <c r="B585" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C585" t="s">
         <v>1138</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11139,10 +11140,10 @@
         <v>615</v>
       </c>
       <c r="B586" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C586" t="s">
         <v>1140</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11150,10 +11151,10 @@
         <v>617</v>
       </c>
       <c r="B587" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C587" t="s">
         <v>1142</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11161,10 +11162,10 @@
         <v>618</v>
       </c>
       <c r="B588" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C588" t="s">
         <v>1144</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11172,10 +11173,10 @@
         <v>625</v>
       </c>
       <c r="B589" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C589" t="s">
         <v>1146</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11183,10 +11184,10 @@
         <v>624</v>
       </c>
       <c r="B590" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C590" t="s">
         <v>1148</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11194,10 +11195,10 @@
         <v>626</v>
       </c>
       <c r="B591" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C591" t="s">
         <v>1150</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11205,10 +11206,10 @@
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C592" t="s">
         <v>1152</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11216,10 +11217,10 @@
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C593" t="s">
         <v>1154</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11227,7 +11228,7 @@
         <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11235,10 +11236,10 @@
         <v>633</v>
       </c>
       <c r="B595" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C595" t="s">
         <v>1157</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11246,10 +11247,10 @@
         <v>635</v>
       </c>
       <c r="B596" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C596" t="s">
         <v>1159</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11257,10 +11258,10 @@
         <v>636</v>
       </c>
       <c r="B597" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C597" t="s">
         <v>1161</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11268,10 +11269,10 @@
         <v>642</v>
       </c>
       <c r="B598" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C598" t="s">
         <v>1163</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11279,10 +11280,10 @@
         <v>644</v>
       </c>
       <c r="B599" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C599" t="s">
         <v>1165</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11290,10 +11291,10 @@
         <v>646</v>
       </c>
       <c r="B600" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C600" t="s">
         <v>1167</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11301,10 +11302,10 @@
         <v>649</v>
       </c>
       <c r="B601" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C601" t="s">
         <v>1169</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11312,10 +11313,10 @@
         <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11323,10 +11324,10 @@
         <v>651</v>
       </c>
       <c r="B603" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C603" t="s">
         <v>1172</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11334,10 +11335,10 @@
         <v>653</v>
       </c>
       <c r="B604" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C604" t="s">
         <v>1174</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11345,10 +11346,10 @@
         <v>654</v>
       </c>
       <c r="B605" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C605" t="s">
         <v>1176</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11356,10 +11357,10 @@
         <v>655</v>
       </c>
       <c r="B606" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C606" t="s">
         <v>1178</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11367,10 +11368,10 @@
         <v>659</v>
       </c>
       <c r="B607" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C607" t="s">
         <v>1180</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11378,10 +11379,10 @@
         <v>660</v>
       </c>
       <c r="B608" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C608" t="s">
         <v>1182</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11389,10 +11390,10 @@
         <v>661</v>
       </c>
       <c r="B609" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C609" t="s">
         <v>1184</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11400,10 +11401,10 @@
         <v>663</v>
       </c>
       <c r="B610" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C610" t="s">
         <v>1186</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11411,10 +11412,10 @@
         <v>667</v>
       </c>
       <c r="B611" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C611" t="s">
         <v>1188</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11422,10 +11423,10 @@
         <v>670</v>
       </c>
       <c r="B612" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C612" t="s">
         <v>1190</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11433,10 +11434,10 @@
         <v>673</v>
       </c>
       <c r="B613" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C613" t="s">
         <v>1192</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11444,10 +11445,10 @@
         <v>674</v>
       </c>
       <c r="B614" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C614" t="s">
         <v>1194</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11455,10 +11456,10 @@
         <v>675</v>
       </c>
       <c r="B615" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C615" t="s">
         <v>1196</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11466,10 +11467,10 @@
         <v>680</v>
       </c>
       <c r="B616" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C616" t="s">
         <v>1198</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11477,10 +11478,10 @@
         <v>681</v>
       </c>
       <c r="B617" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C617" t="s">
         <v>1200</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11488,10 +11489,10 @@
         <v>682</v>
       </c>
       <c r="B618" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C618" t="s">
         <v>1202</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11499,10 +11500,10 @@
         <v>683</v>
       </c>
       <c r="B619" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C619" t="s">
         <v>1204</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11510,10 +11511,10 @@
         <v>684</v>
       </c>
       <c r="B620" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C620" t="s">
         <v>1206</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11521,10 +11522,10 @@
         <v>685</v>
       </c>
       <c r="B621" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C621" t="s">
         <v>1208</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11532,10 +11533,10 @@
         <v>686</v>
       </c>
       <c r="B622" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C622" t="s">
         <v>1210</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11543,10 +11544,10 @@
         <v>689</v>
       </c>
       <c r="B623" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C623" t="s">
         <v>1212</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11554,10 +11555,10 @@
         <v>697</v>
       </c>
       <c r="B624" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C624" t="s">
         <v>1214</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11565,10 +11566,10 @@
         <v>701</v>
       </c>
       <c r="B625" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C625" t="s">
         <v>1216</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11576,10 +11577,10 @@
         <v>702</v>
       </c>
       <c r="B626" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C626" t="s">
         <v>1218</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11587,10 +11588,10 @@
         <v>704</v>
       </c>
       <c r="B627" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C627" t="s">
         <v>1220</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11598,10 +11599,10 @@
         <v>705</v>
       </c>
       <c r="B628" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C628" t="s">
         <v>1222</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11609,10 +11610,10 @@
         <v>710</v>
       </c>
       <c r="B629" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C629" t="s">
         <v>1224</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11620,10 +11621,10 @@
         <v>711</v>
       </c>
       <c r="B630" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C630" t="s">
         <v>1226</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11631,10 +11632,10 @@
         <v>712</v>
       </c>
       <c r="B631" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C631" t="s">
         <v>1228</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11642,10 +11643,10 @@
         <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11653,10 +11654,10 @@
         <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11664,10 +11665,10 @@
         <v>718</v>
       </c>
       <c r="B634" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C634" t="s">
         <v>1232</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11675,10 +11676,10 @@
         <v>719</v>
       </c>
       <c r="B635" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C635" t="s">
         <v>1234</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11686,10 +11687,10 @@
         <v>721</v>
       </c>
       <c r="B636" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C636" t="s">
         <v>1236</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11697,10 +11698,10 @@
         <v>722</v>
       </c>
       <c r="B637" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C637" t="s">
         <v>1238</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11708,10 +11709,10 @@
         <v>723</v>
       </c>
       <c r="B638" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C638" t="s">
         <v>1240</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11719,7 +11720,7 @@
         <v>724</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11727,10 +11728,10 @@
         <v>725</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C640" t="s">
         <v>1242</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11738,10 +11739,10 @@
         <v>726</v>
       </c>
       <c r="B641" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C641" t="s">
         <v>1244</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11749,10 +11750,10 @@
         <v>727</v>
       </c>
       <c r="B642" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C642" t="s">
         <v>1246</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11760,10 +11761,10 @@
         <v>728</v>
       </c>
       <c r="B643" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C643" t="s">
         <v>1248</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11771,10 +11772,10 @@
         <v>729</v>
       </c>
       <c r="B644" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C644" t="s">
         <v>1250</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11782,10 +11783,10 @@
         <v>730</v>
       </c>
       <c r="B645" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C645" t="s">
         <v>1252</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11793,10 +11794,10 @@
         <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11804,10 +11805,10 @@
         <v>733</v>
       </c>
       <c r="B647" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C647" t="s">
         <v>1255</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11815,10 +11816,10 @@
         <v>735</v>
       </c>
       <c r="B648" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C648" t="s">
         <v>1257</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11826,10 +11827,10 @@
         <v>736</v>
       </c>
       <c r="B649" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C649" t="s">
         <v>1259</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11837,10 +11838,10 @@
         <v>737</v>
       </c>
       <c r="B650" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C650" t="s">
         <v>1261</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11848,10 +11849,10 @@
         <v>738</v>
       </c>
       <c r="B651" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C651" t="s">
         <v>1263</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11859,10 +11860,10 @@
         <v>739</v>
       </c>
       <c r="B652" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C652" t="s">
         <v>1265</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11870,10 +11871,10 @@
         <v>740</v>
       </c>
       <c r="B653" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C653" t="s">
         <v>1267</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11881,10 +11882,10 @@
         <v>741</v>
       </c>
       <c r="B654" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C654" t="s">
         <v>1269</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11892,10 +11893,10 @@
         <v>742</v>
       </c>
       <c r="B655" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C655" t="s">
         <v>1271</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11903,10 +11904,10 @@
         <v>743</v>
       </c>
       <c r="B656" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C656" t="s">
         <v>1273</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11914,10 +11915,10 @@
         <v>744</v>
       </c>
       <c r="B657" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C657" t="s">
         <v>1275</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11925,10 +11926,10 @@
         <v>745</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C658" t="s">
         <v>1277</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11936,10 +11937,10 @@
         <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C659" t="s">
         <v>1279</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11947,10 +11948,10 @@
         <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C660" t="s">
         <v>1281</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11958,10 +11959,10 @@
         <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C661" t="s">
         <v>1283</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11969,10 +11970,10 @@
         <v>749</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C662" t="s">
         <v>1285</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11981,7 +11982,7 @@
       </c>
       <c r="B663" s="1"/>
       <c r="C663" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11989,10 +11990,10 @@
         <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C664" t="s">
         <v>1287</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -12000,10 +12001,10 @@
         <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12011,10 +12012,10 @@
         <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C666" t="s">
         <v>1290</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12022,10 +12023,10 @@
         <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C667" t="s">
         <v>1292</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12033,10 +12034,10 @@
         <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C668" t="s">
         <v>1294</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12044,10 +12045,10 @@
         <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12055,10 +12056,10 @@
         <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C670" t="s">
         <v>1297</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12066,10 +12067,10 @@
         <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C671" t="s">
         <v>1299</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12077,10 +12078,10 @@
         <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C672" t="s">
         <v>1301</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12088,10 +12089,10 @@
         <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C673" t="s">
         <v>1303</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -12099,10 +12100,10 @@
         <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C674" t="s">
         <v>1305</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12110,10 +12111,10 @@
         <v>765</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C675" t="s">
         <v>1307</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12127,10 +12128,10 @@
         <v>767</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C677" t="s">
         <v>1309</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12139,7 +12140,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12147,10 +12148,10 @@
         <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C679" t="s">
         <v>1312</v>
-      </c>
-      <c r="C679" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12158,10 +12159,10 @@
         <v>772</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C680" s="3" t="s">
         <v>1317</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12170,7 +12171,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12179,7 +12180,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12188,7 +12189,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12197,7 +12198,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12206,7 +12207,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12215,7 +12216,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12224,7 +12225,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -12233,7 +12234,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
@@ -12242,7 +12243,7 @@
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -12250,10 +12251,10 @@
         <v>10001</v>
       </c>
       <c r="B690" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
@@ -12261,10 +12262,10 @@
         <v>10003</v>
       </c>
       <c r="B691" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C691" t="s">
         <v>1312</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1313</v>
       </c>
     </row>
   </sheetData>
@@ -12272,7 +12273,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C529 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303FADC5-60BB-4B33-AC1B-CB9B86D94B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA137AAE-FE2F-4AB2-BCE3-087BCF2FAAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24480" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -407,9 +407,6 @@
     <t>ゆら・ゆらRing-Dong-Dance</t>
   </si>
   <si>
-    <t>彩千圣,情歌对唱,摇摇曳曳圆舞曲</t>
-  </si>
-  <si>
     <t>夏のドーン！</t>
   </si>
   <si>
@@ -4288,6 +4285,10 @@
   </si>
   <si>
     <t>火花,七八十,敷衍了事,火花reloaded</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>彩千圣,情歌对唱,摇摇曳曳圆舞曲,摇曳摇曳圆舞曲</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5341,8 +5342,8 @@
       <c r="B57" t="s">
         <v>113</v>
       </c>
-      <c r="C57" t="s">
-        <v>114</v>
+      <c r="C57" s="3" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -5350,10 +5351,10 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" t="s">
         <v>115</v>
-      </c>
-      <c r="C58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -5361,10 +5362,10 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" t="s">
         <v>117</v>
-      </c>
-      <c r="C59" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -5372,10 +5373,10 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" t="s">
         <v>119</v>
-      </c>
-      <c r="C60" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -5383,10 +5384,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" t="s">
         <v>121</v>
-      </c>
-      <c r="C61" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -5394,10 +5395,10 @@
         <v>65</v>
       </c>
       <c r="B62" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" t="s">
         <v>123</v>
-      </c>
-      <c r="C62" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -5405,10 +5406,10 @@
         <v>66</v>
       </c>
       <c r="B63" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" t="s">
         <v>125</v>
-      </c>
-      <c r="C63" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -5416,10 +5417,10 @@
         <v>67</v>
       </c>
       <c r="B64" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" t="s">
         <v>127</v>
-      </c>
-      <c r="C64" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -5427,10 +5428,10 @@
         <v>68</v>
       </c>
       <c r="B65" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" t="s">
         <v>129</v>
-      </c>
-      <c r="C65" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -5438,10 +5439,10 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" t="s">
         <v>131</v>
-      </c>
-      <c r="C66" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -5449,10 +5450,10 @@
         <v>70</v>
       </c>
       <c r="B67" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" t="s">
         <v>133</v>
-      </c>
-      <c r="C67" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -5460,10 +5461,10 @@
         <v>71</v>
       </c>
       <c r="B68" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" t="s">
         <v>135</v>
-      </c>
-      <c r="C68" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -5471,10 +5472,10 @@
         <v>72</v>
       </c>
       <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" t="s">
         <v>137</v>
-      </c>
-      <c r="C69" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -5482,10 +5483,10 @@
         <v>73</v>
       </c>
       <c r="B70" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" t="s">
         <v>139</v>
-      </c>
-      <c r="C70" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -5493,10 +5494,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" t="s">
         <v>141</v>
-      </c>
-      <c r="C71" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -5504,10 +5505,10 @@
         <v>75</v>
       </c>
       <c r="B72" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" t="s">
         <v>143</v>
-      </c>
-      <c r="C72" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -5515,10 +5516,10 @@
         <v>76</v>
       </c>
       <c r="B73" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" t="s">
         <v>145</v>
-      </c>
-      <c r="C73" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -5526,10 +5527,10 @@
         <v>77</v>
       </c>
       <c r="B74" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" t="s">
         <v>147</v>
-      </c>
-      <c r="C74" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -5537,10 +5538,10 @@
         <v>78</v>
       </c>
       <c r="B75" t="s">
+        <v>148</v>
+      </c>
+      <c r="C75" t="s">
         <v>149</v>
-      </c>
-      <c r="C75" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -5548,10 +5549,10 @@
         <v>79</v>
       </c>
       <c r="B76" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" t="s">
         <v>151</v>
-      </c>
-      <c r="C76" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -5559,10 +5560,10 @@
         <v>80</v>
       </c>
       <c r="B77" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" t="s">
         <v>153</v>
-      </c>
-      <c r="C77" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -5570,10 +5571,10 @@
         <v>81</v>
       </c>
       <c r="B78" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" t="s">
         <v>155</v>
-      </c>
-      <c r="C78" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -5581,10 +5582,10 @@
         <v>82</v>
       </c>
       <c r="B79" t="s">
+        <v>156</v>
+      </c>
+      <c r="C79" t="s">
         <v>157</v>
-      </c>
-      <c r="C79" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -5592,10 +5593,10 @@
         <v>83</v>
       </c>
       <c r="B80" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" t="s">
         <v>159</v>
-      </c>
-      <c r="C80" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -5603,10 +5604,10 @@
         <v>84</v>
       </c>
       <c r="B81" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" t="s">
         <v>161</v>
-      </c>
-      <c r="C81" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -5614,10 +5615,10 @@
         <v>85</v>
       </c>
       <c r="B82" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82" t="s">
         <v>163</v>
-      </c>
-      <c r="C82" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -5625,10 +5626,10 @@
         <v>86</v>
       </c>
       <c r="B83" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" t="s">
         <v>165</v>
-      </c>
-      <c r="C83" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -5636,10 +5637,10 @@
         <v>87</v>
       </c>
       <c r="B84" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84" t="s">
         <v>167</v>
-      </c>
-      <c r="C84" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -5647,10 +5648,10 @@
         <v>88</v>
       </c>
       <c r="B85" t="s">
+        <v>168</v>
+      </c>
+      <c r="C85" t="s">
         <v>169</v>
-      </c>
-      <c r="C85" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -5658,10 +5659,10 @@
         <v>89</v>
       </c>
       <c r="B86" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" t="s">
         <v>171</v>
-      </c>
-      <c r="C86" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -5669,10 +5670,10 @@
         <v>90</v>
       </c>
       <c r="B87" t="s">
+        <v>172</v>
+      </c>
+      <c r="C87" t="s">
         <v>173</v>
-      </c>
-      <c r="C87" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -5680,10 +5681,10 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
+        <v>174</v>
+      </c>
+      <c r="C88" t="s">
         <v>175</v>
-      </c>
-      <c r="C88" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -5691,10 +5692,10 @@
         <v>92</v>
       </c>
       <c r="B89" t="s">
+        <v>176</v>
+      </c>
+      <c r="C89" t="s">
         <v>177</v>
-      </c>
-      <c r="C89" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -5702,10 +5703,10 @@
         <v>93</v>
       </c>
       <c r="B90" t="s">
+        <v>178</v>
+      </c>
+      <c r="C90" t="s">
         <v>179</v>
-      </c>
-      <c r="C90" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -5713,10 +5714,10 @@
         <v>94</v>
       </c>
       <c r="B91" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" t="s">
         <v>181</v>
-      </c>
-      <c r="C91" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -5724,10 +5725,10 @@
         <v>95</v>
       </c>
       <c r="B92" t="s">
+        <v>182</v>
+      </c>
+      <c r="C92" t="s">
         <v>183</v>
-      </c>
-      <c r="C92" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -5735,10 +5736,10 @@
         <v>96</v>
       </c>
       <c r="B93" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93" t="s">
         <v>185</v>
-      </c>
-      <c r="C93" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -5746,10 +5747,10 @@
         <v>97</v>
       </c>
       <c r="B94" t="s">
+        <v>186</v>
+      </c>
+      <c r="C94" t="s">
         <v>187</v>
-      </c>
-      <c r="C94" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -5757,10 +5758,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
+        <v>188</v>
+      </c>
+      <c r="C95" t="s">
         <v>189</v>
-      </c>
-      <c r="C95" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -5768,10 +5769,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
+        <v>190</v>
+      </c>
+      <c r="C96" t="s">
         <v>191</v>
-      </c>
-      <c r="C96" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -5779,10 +5780,10 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" t="s">
         <v>193</v>
-      </c>
-      <c r="C97" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -5790,10 +5791,10 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" t="s">
         <v>195</v>
-      </c>
-      <c r="C98" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -5801,10 +5802,10 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" t="s">
         <v>197</v>
-      </c>
-      <c r="C99" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -5812,10 +5813,10 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" t="s">
         <v>199</v>
-      </c>
-      <c r="C100" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -5823,10 +5824,10 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" t="s">
         <v>201</v>
-      </c>
-      <c r="C101" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -5834,10 +5835,10 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" t="s">
         <v>203</v>
-      </c>
-      <c r="C102" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -5845,10 +5846,10 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" t="s">
         <v>205</v>
-      </c>
-      <c r="C103" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -5856,10 +5857,10 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
+        <v>206</v>
+      </c>
+      <c r="C104" t="s">
         <v>207</v>
-      </c>
-      <c r="C104" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -5867,10 +5868,10 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" t="s">
         <v>209</v>
-      </c>
-      <c r="C105" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -5878,10 +5879,10 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" t="s">
         <v>211</v>
-      </c>
-      <c r="C106" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -5889,10 +5890,10 @@
         <v>115</v>
       </c>
       <c r="B107" t="s">
+        <v>212</v>
+      </c>
+      <c r="C107" t="s">
         <v>213</v>
-      </c>
-      <c r="C107" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -5900,10 +5901,10 @@
         <v>116</v>
       </c>
       <c r="B108" t="s">
+        <v>214</v>
+      </c>
+      <c r="C108" t="s">
         <v>215</v>
-      </c>
-      <c r="C108" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -5911,10 +5912,10 @@
         <v>117</v>
       </c>
       <c r="B109" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" t="s">
         <v>217</v>
-      </c>
-      <c r="C109" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -5922,10 +5923,10 @@
         <v>118</v>
       </c>
       <c r="B110" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" t="s">
         <v>219</v>
-      </c>
-      <c r="C110" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -5933,10 +5934,10 @@
         <v>119</v>
       </c>
       <c r="B111" t="s">
+        <v>220</v>
+      </c>
+      <c r="C111" t="s">
         <v>221</v>
-      </c>
-      <c r="C111" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -5944,10 +5945,10 @@
         <v>120</v>
       </c>
       <c r="B112" t="s">
+        <v>222</v>
+      </c>
+      <c r="C112" t="s">
         <v>223</v>
-      </c>
-      <c r="C112" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -5955,10 +5956,10 @@
         <v>121</v>
       </c>
       <c r="B113" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -5966,10 +5967,10 @@
         <v>122</v>
       </c>
       <c r="B114" t="s">
+        <v>225</v>
+      </c>
+      <c r="C114" t="s">
         <v>226</v>
-      </c>
-      <c r="C114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -5977,10 +5978,10 @@
         <v>123</v>
       </c>
       <c r="B115" t="s">
+        <v>227</v>
+      </c>
+      <c r="C115" t="s">
         <v>228</v>
-      </c>
-      <c r="C115" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -5988,10 +5989,10 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" t="s">
         <v>230</v>
-      </c>
-      <c r="C116" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -5999,10 +6000,10 @@
         <v>125</v>
       </c>
       <c r="B117" t="s">
+        <v>231</v>
+      </c>
+      <c r="C117" t="s">
         <v>232</v>
-      </c>
-      <c r="C117" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -6010,10 +6011,10 @@
         <v>126</v>
       </c>
       <c r="B118" t="s">
+        <v>233</v>
+      </c>
+      <c r="C118" t="s">
         <v>234</v>
-      </c>
-      <c r="C118" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -6021,10 +6022,10 @@
         <v>127</v>
       </c>
       <c r="B119" t="s">
+        <v>235</v>
+      </c>
+      <c r="C119" t="s">
         <v>236</v>
-      </c>
-      <c r="C119" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -6032,10 +6033,10 @@
         <v>128</v>
       </c>
       <c r="B120" t="s">
+        <v>237</v>
+      </c>
+      <c r="C120" t="s">
         <v>238</v>
-      </c>
-      <c r="C120" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -6043,10 +6044,10 @@
         <v>129</v>
       </c>
       <c r="B121" t="s">
+        <v>239</v>
+      </c>
+      <c r="C121" t="s">
         <v>240</v>
-      </c>
-      <c r="C121" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -6054,10 +6055,10 @@
         <v>130</v>
       </c>
       <c r="B122" t="s">
+        <v>241</v>
+      </c>
+      <c r="C122" t="s">
         <v>242</v>
-      </c>
-      <c r="C122" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -6065,10 +6066,10 @@
         <v>131</v>
       </c>
       <c r="B123" t="s">
+        <v>243</v>
+      </c>
+      <c r="C123" t="s">
         <v>244</v>
-      </c>
-      <c r="C123" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -6076,10 +6077,10 @@
         <v>132</v>
       </c>
       <c r="B124" t="s">
+        <v>245</v>
+      </c>
+      <c r="C124" t="s">
         <v>246</v>
-      </c>
-      <c r="C124" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -6087,10 +6088,10 @@
         <v>133</v>
       </c>
       <c r="B125" t="s">
+        <v>247</v>
+      </c>
+      <c r="C125" t="s">
         <v>248</v>
-      </c>
-      <c r="C125" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -6098,10 +6099,10 @@
         <v>134</v>
       </c>
       <c r="B126" t="s">
+        <v>249</v>
+      </c>
+      <c r="C126" t="s">
         <v>250</v>
-      </c>
-      <c r="C126" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -6109,10 +6110,10 @@
         <v>135</v>
       </c>
       <c r="B127" t="s">
+        <v>251</v>
+      </c>
+      <c r="C127" t="s">
         <v>252</v>
-      </c>
-      <c r="C127" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -6120,10 +6121,10 @@
         <v>136</v>
       </c>
       <c r="B128" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" t="s">
         <v>254</v>
-      </c>
-      <c r="C128" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6131,10 +6132,10 @@
         <v>137</v>
       </c>
       <c r="B129" t="s">
+        <v>255</v>
+      </c>
+      <c r="C129" t="s">
         <v>256</v>
-      </c>
-      <c r="C129" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -6142,10 +6143,10 @@
         <v>138</v>
       </c>
       <c r="B130" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -6153,10 +6154,10 @@
         <v>139</v>
       </c>
       <c r="B131" t="s">
+        <v>258</v>
+      </c>
+      <c r="C131" t="s">
         <v>259</v>
-      </c>
-      <c r="C131" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -6164,10 +6165,10 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
+        <v>260</v>
+      </c>
+      <c r="C132" t="s">
         <v>261</v>
-      </c>
-      <c r="C132" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -6175,10 +6176,10 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
+        <v>262</v>
+      </c>
+      <c r="C133" t="s">
         <v>263</v>
-      </c>
-      <c r="C133" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6186,10 +6187,10 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
+        <v>264</v>
+      </c>
+      <c r="C134" t="s">
         <v>265</v>
-      </c>
-      <c r="C134" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -6197,10 +6198,10 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
+        <v>266</v>
+      </c>
+      <c r="C135" t="s">
         <v>267</v>
-      </c>
-      <c r="C135" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -6208,10 +6209,10 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
+        <v>268</v>
+      </c>
+      <c r="C136" t="s">
         <v>269</v>
-      </c>
-      <c r="C136" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -6219,10 +6220,10 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
+        <v>270</v>
+      </c>
+      <c r="C137" t="s">
         <v>271</v>
-      </c>
-      <c r="C137" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -6230,10 +6231,10 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
+        <v>272</v>
+      </c>
+      <c r="C138" t="s">
         <v>273</v>
-      </c>
-      <c r="C138" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -6241,10 +6242,10 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
+        <v>274</v>
+      </c>
+      <c r="C139" t="s">
         <v>275</v>
-      </c>
-      <c r="C139" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -6252,10 +6253,10 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
+        <v>276</v>
+      </c>
+      <c r="C140" t="s">
         <v>277</v>
-      </c>
-      <c r="C140" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -6263,10 +6264,10 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
+        <v>278</v>
+      </c>
+      <c r="C141" t="s">
         <v>279</v>
-      </c>
-      <c r="C141" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -6274,10 +6275,10 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
+        <v>280</v>
+      </c>
+      <c r="C142" t="s">
         <v>281</v>
-      </c>
-      <c r="C142" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -6285,10 +6286,10 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
+        <v>282</v>
+      </c>
+      <c r="C143" t="s">
         <v>283</v>
-      </c>
-      <c r="C143" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -6296,10 +6297,10 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
+        <v>284</v>
+      </c>
+      <c r="C144" t="s">
         <v>285</v>
-      </c>
-      <c r="C144" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -6307,10 +6308,10 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
+        <v>286</v>
+      </c>
+      <c r="C145" t="s">
         <v>287</v>
-      </c>
-      <c r="C145" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6318,10 +6319,10 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
+        <v>288</v>
+      </c>
+      <c r="C146" t="s">
         <v>289</v>
-      </c>
-      <c r="C146" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -6329,10 +6330,10 @@
         <v>155</v>
       </c>
       <c r="B147" t="s">
+        <v>290</v>
+      </c>
+      <c r="C147" t="s">
         <v>291</v>
-      </c>
-      <c r="C147" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -6340,10 +6341,10 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
+        <v>292</v>
+      </c>
+      <c r="C148" t="s">
         <v>293</v>
-      </c>
-      <c r="C148" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -6351,10 +6352,10 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
+        <v>294</v>
+      </c>
+      <c r="C149" t="s">
         <v>295</v>
-      </c>
-      <c r="C149" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -6362,10 +6363,10 @@
         <v>158</v>
       </c>
       <c r="B150" t="s">
+        <v>296</v>
+      </c>
+      <c r="C150" t="s">
         <v>297</v>
-      </c>
-      <c r="C150" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6373,10 +6374,10 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
+        <v>298</v>
+      </c>
+      <c r="C151" t="s">
         <v>299</v>
-      </c>
-      <c r="C151" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -6384,10 +6385,10 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
+        <v>300</v>
+      </c>
+      <c r="C152" t="s">
         <v>301</v>
-      </c>
-      <c r="C152" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -6395,10 +6396,10 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
+        <v>302</v>
+      </c>
+      <c r="C153" t="s">
         <v>303</v>
-      </c>
-      <c r="C153" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -6406,10 +6407,10 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
+        <v>304</v>
+      </c>
+      <c r="C154" t="s">
         <v>305</v>
-      </c>
-      <c r="C154" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6417,10 +6418,10 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
+        <v>306</v>
+      </c>
+      <c r="C155" t="s">
         <v>307</v>
-      </c>
-      <c r="C155" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -6428,10 +6429,10 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
+        <v>308</v>
+      </c>
+      <c r="C156" t="s">
         <v>309</v>
-      </c>
-      <c r="C156" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -6439,10 +6440,10 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
+        <v>310</v>
+      </c>
+      <c r="C157" t="s">
         <v>311</v>
-      </c>
-      <c r="C157" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -6450,10 +6451,10 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
+        <v>312</v>
+      </c>
+      <c r="C158" t="s">
         <v>313</v>
-      </c>
-      <c r="C158" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -6461,10 +6462,10 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
+        <v>314</v>
+      </c>
+      <c r="C159" t="s">
         <v>315</v>
-      </c>
-      <c r="C159" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -6472,10 +6473,10 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
+        <v>316</v>
+      </c>
+      <c r="C160" t="s">
         <v>317</v>
-      </c>
-      <c r="C160" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -6483,10 +6484,10 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
+        <v>318</v>
+      </c>
+      <c r="C161" t="s">
         <v>319</v>
-      </c>
-      <c r="C161" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -6494,10 +6495,10 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
+        <v>320</v>
+      </c>
+      <c r="C162" t="s">
         <v>321</v>
-      </c>
-      <c r="C162" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6505,10 +6506,10 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
+        <v>322</v>
+      </c>
+      <c r="C163" t="s">
         <v>323</v>
-      </c>
-      <c r="C163" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -6516,10 +6517,10 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
+        <v>324</v>
+      </c>
+      <c r="C164" t="s">
         <v>325</v>
-      </c>
-      <c r="C164" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -6527,10 +6528,10 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
+        <v>326</v>
+      </c>
+      <c r="C165" t="s">
         <v>327</v>
-      </c>
-      <c r="C165" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -6538,10 +6539,10 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
+        <v>328</v>
+      </c>
+      <c r="C166" t="s">
         <v>329</v>
-      </c>
-      <c r="C166" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -6549,10 +6550,10 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
+        <v>330</v>
+      </c>
+      <c r="C167" t="s">
         <v>331</v>
-      </c>
-      <c r="C167" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6560,10 +6561,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
+        <v>332</v>
+      </c>
+      <c r="C168" t="s">
         <v>333</v>
-      </c>
-      <c r="C168" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -6571,10 +6572,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
+        <v>334</v>
+      </c>
+      <c r="C169" t="s">
         <v>335</v>
-      </c>
-      <c r="C169" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -6582,10 +6583,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
+        <v>336</v>
+      </c>
+      <c r="C170" t="s">
         <v>337</v>
-      </c>
-      <c r="C170" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -6593,10 +6594,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
+        <v>338</v>
+      </c>
+      <c r="C171" t="s">
         <v>339</v>
-      </c>
-      <c r="C171" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -6604,10 +6605,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
+        <v>340</v>
+      </c>
+      <c r="C172" t="s">
         <v>341</v>
-      </c>
-      <c r="C172" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -6615,10 +6616,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
+        <v>342</v>
+      </c>
+      <c r="C173" t="s">
         <v>343</v>
-      </c>
-      <c r="C173" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -6626,10 +6627,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
+        <v>344</v>
+      </c>
+      <c r="C174" t="s">
         <v>345</v>
-      </c>
-      <c r="C174" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -6637,10 +6638,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
+        <v>346</v>
+      </c>
+      <c r="C175" t="s">
         <v>347</v>
-      </c>
-      <c r="C175" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -6648,10 +6649,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
+        <v>348</v>
+      </c>
+      <c r="C176" t="s">
         <v>349</v>
-      </c>
-      <c r="C176" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -6659,10 +6660,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
+        <v>350</v>
+      </c>
+      <c r="C177" t="s">
         <v>351</v>
-      </c>
-      <c r="C177" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -6670,10 +6671,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
+        <v>352</v>
+      </c>
+      <c r="C178" t="s">
         <v>353</v>
-      </c>
-      <c r="C178" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -6681,10 +6682,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
+        <v>354</v>
+      </c>
+      <c r="C179" t="s">
         <v>355</v>
-      </c>
-      <c r="C179" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -6692,10 +6693,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
+        <v>356</v>
+      </c>
+      <c r="C180" t="s">
         <v>357</v>
-      </c>
-      <c r="C180" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -6703,10 +6704,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
+        <v>358</v>
+      </c>
+      <c r="C181" t="s">
         <v>359</v>
-      </c>
-      <c r="C181" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -6714,10 +6715,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>360</v>
+      </c>
+      <c r="C182" t="s">
         <v>361</v>
-      </c>
-      <c r="C182" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -6725,10 +6726,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
+        <v>362</v>
+      </c>
+      <c r="C183" t="s">
         <v>363</v>
-      </c>
-      <c r="C183" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -6736,10 +6737,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>364</v>
+      </c>
+      <c r="C184" t="s">
         <v>365</v>
-      </c>
-      <c r="C184" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -6747,10 +6748,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
+        <v>366</v>
+      </c>
+      <c r="C185" t="s">
         <v>367</v>
-      </c>
-      <c r="C185" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -6758,10 +6759,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
+        <v>368</v>
+      </c>
+      <c r="C186" t="s">
         <v>369</v>
-      </c>
-      <c r="C186" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -6769,10 +6770,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
+        <v>370</v>
+      </c>
+      <c r="C187" t="s">
         <v>371</v>
-      </c>
-      <c r="C187" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -6780,10 +6781,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
+        <v>372</v>
+      </c>
+      <c r="C188" t="s">
         <v>373</v>
-      </c>
-      <c r="C188" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -6791,10 +6792,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
+        <v>374</v>
+      </c>
+      <c r="C189" t="s">
         <v>375</v>
-      </c>
-      <c r="C189" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -6802,10 +6803,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
+        <v>376</v>
+      </c>
+      <c r="C190" t="s">
         <v>377</v>
-      </c>
-      <c r="C190" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -6813,10 +6814,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
+        <v>378</v>
+      </c>
+      <c r="C191" t="s">
         <v>379</v>
-      </c>
-      <c r="C191" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -6824,10 +6825,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" t="s">
         <v>381</v>
-      </c>
-      <c r="C192" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -6835,10 +6836,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>382</v>
+      </c>
+      <c r="C193" t="s">
         <v>383</v>
-      </c>
-      <c r="C193" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -6846,10 +6847,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
+        <v>384</v>
+      </c>
+      <c r="C194" t="s">
         <v>385</v>
-      </c>
-      <c r="C194" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -6857,10 +6858,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
+        <v>386</v>
+      </c>
+      <c r="C195" t="s">
         <v>387</v>
-      </c>
-      <c r="C195" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -6868,10 +6869,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
+        <v>388</v>
+      </c>
+      <c r="C196" t="s">
         <v>389</v>
-      </c>
-      <c r="C196" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -6879,10 +6880,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
+        <v>390</v>
+      </c>
+      <c r="C197" t="s">
         <v>391</v>
-      </c>
-      <c r="C197" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -6890,10 +6891,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
+        <v>392</v>
+      </c>
+      <c r="C198" t="s">
         <v>393</v>
-      </c>
-      <c r="C198" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -6901,10 +6902,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
+        <v>394</v>
+      </c>
+      <c r="C199" t="s">
         <v>395</v>
-      </c>
-      <c r="C199" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -6912,10 +6913,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
+        <v>396</v>
+      </c>
+      <c r="C200" t="s">
         <v>397</v>
-      </c>
-      <c r="C200" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -6923,10 +6924,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
+        <v>398</v>
+      </c>
+      <c r="C201" t="s">
         <v>399</v>
-      </c>
-      <c r="C201" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -6934,10 +6935,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
+        <v>400</v>
+      </c>
+      <c r="C202" t="s">
         <v>401</v>
-      </c>
-      <c r="C202" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -6945,10 +6946,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
+        <v>402</v>
+      </c>
+      <c r="C203" t="s">
         <v>403</v>
-      </c>
-      <c r="C203" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -6956,10 +6957,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
+        <v>404</v>
+      </c>
+      <c r="C204" t="s">
         <v>405</v>
-      </c>
-      <c r="C204" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -6967,10 +6968,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
+        <v>406</v>
+      </c>
+      <c r="C205" t="s">
         <v>407</v>
-      </c>
-      <c r="C205" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -6978,10 +6979,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
+        <v>408</v>
+      </c>
+      <c r="C206" t="s">
         <v>409</v>
-      </c>
-      <c r="C206" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -6989,10 +6990,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
+        <v>410</v>
+      </c>
+      <c r="C207" t="s">
         <v>411</v>
-      </c>
-      <c r="C207" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -7000,10 +7001,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
+        <v>412</v>
+      </c>
+      <c r="C208" t="s">
         <v>413</v>
-      </c>
-      <c r="C208" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7011,10 +7012,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
+        <v>414</v>
+      </c>
+      <c r="C209" t="s">
         <v>415</v>
-      </c>
-      <c r="C209" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -7022,10 +7023,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
+        <v>416</v>
+      </c>
+      <c r="C210" t="s">
         <v>417</v>
-      </c>
-      <c r="C210" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -7033,10 +7034,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
+        <v>418</v>
+      </c>
+      <c r="C211" t="s">
         <v>419</v>
-      </c>
-      <c r="C211" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -7044,10 +7045,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
+        <v>420</v>
+      </c>
+      <c r="C212" t="s">
         <v>421</v>
-      </c>
-      <c r="C212" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -7055,10 +7056,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
+        <v>422</v>
+      </c>
+      <c r="C213" t="s">
         <v>423</v>
-      </c>
-      <c r="C213" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -7066,10 +7067,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
+        <v>424</v>
+      </c>
+      <c r="C214" t="s">
         <v>425</v>
-      </c>
-      <c r="C214" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -7077,10 +7078,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
+        <v>426</v>
+      </c>
+      <c r="C215" t="s">
         <v>427</v>
-      </c>
-      <c r="C215" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -7088,10 +7089,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
+        <v>428</v>
+      </c>
+      <c r="C216" t="s">
         <v>429</v>
-      </c>
-      <c r="C216" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -7099,10 +7100,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
+        <v>430</v>
+      </c>
+      <c r="C217" t="s">
         <v>431</v>
-      </c>
-      <c r="C217" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -7110,10 +7111,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
+        <v>432</v>
+      </c>
+      <c r="C218" t="s">
         <v>433</v>
-      </c>
-      <c r="C218" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -7121,10 +7122,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
+        <v>434</v>
+      </c>
+      <c r="C219" t="s">
         <v>435</v>
-      </c>
-      <c r="C219" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -7132,10 +7133,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
+        <v>436</v>
+      </c>
+      <c r="C220" t="s">
         <v>437</v>
-      </c>
-      <c r="C220" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -7143,10 +7144,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
+        <v>438</v>
+      </c>
+      <c r="C221" t="s">
         <v>439</v>
-      </c>
-      <c r="C221" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -7154,10 +7155,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
+        <v>440</v>
+      </c>
+      <c r="C222" t="s">
         <v>441</v>
-      </c>
-      <c r="C222" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -7165,10 +7166,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
+        <v>442</v>
+      </c>
+      <c r="C223" t="s">
         <v>443</v>
-      </c>
-      <c r="C223" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -7176,10 +7177,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7187,10 +7188,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>445</v>
+      </c>
+      <c r="C225" t="s">
         <v>446</v>
-      </c>
-      <c r="C225" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -7198,10 +7199,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>447</v>
+      </c>
+      <c r="C226" t="s">
         <v>448</v>
-      </c>
-      <c r="C226" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -7209,10 +7210,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>449</v>
+      </c>
+      <c r="C227" t="s">
         <v>450</v>
-      </c>
-      <c r="C227" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -7220,10 +7221,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>451</v>
+      </c>
+      <c r="C228" t="s">
         <v>452</v>
-      </c>
-      <c r="C228" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -7231,10 +7232,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
+        <v>453</v>
+      </c>
+      <c r="C229" t="s">
         <v>454</v>
-      </c>
-      <c r="C229" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7242,10 +7243,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
+        <v>455</v>
+      </c>
+      <c r="C230" t="s">
         <v>456</v>
-      </c>
-      <c r="C230" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7253,10 +7254,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>457</v>
+      </c>
+      <c r="C231" t="s">
         <v>458</v>
-      </c>
-      <c r="C231" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -7264,10 +7265,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>459</v>
+      </c>
+      <c r="C232" t="s">
         <v>460</v>
-      </c>
-      <c r="C232" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -7275,10 +7276,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>461</v>
+      </c>
+      <c r="C233" t="s">
         <v>462</v>
-      </c>
-      <c r="C233" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -7286,10 +7287,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
+        <v>463</v>
+      </c>
+      <c r="C234" t="s">
         <v>464</v>
-      </c>
-      <c r="C234" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7297,10 +7298,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>465</v>
+      </c>
+      <c r="C235" t="s">
         <v>466</v>
-      </c>
-      <c r="C235" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -7308,10 +7309,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>467</v>
+      </c>
+      <c r="C236" t="s">
         <v>468</v>
-      </c>
-      <c r="C236" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -7319,10 +7320,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>469</v>
+      </c>
+      <c r="C237" t="s">
         <v>470</v>
-      </c>
-      <c r="C237" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -7330,10 +7331,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>471</v>
+      </c>
+      <c r="C238" t="s">
         <v>472</v>
-      </c>
-      <c r="C238" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -7341,10 +7342,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>473</v>
+      </c>
+      <c r="C239" t="s">
         <v>474</v>
-      </c>
-      <c r="C239" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -7352,10 +7353,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>475</v>
+      </c>
+      <c r="C240" t="s">
         <v>476</v>
-      </c>
-      <c r="C240" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -7363,10 +7364,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>477</v>
+      </c>
+      <c r="C241" t="s">
         <v>478</v>
-      </c>
-      <c r="C241" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -7374,10 +7375,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>479</v>
+      </c>
+      <c r="C242" t="s">
         <v>480</v>
-      </c>
-      <c r="C242" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -7385,10 +7386,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>481</v>
+      </c>
+      <c r="C243" t="s">
         <v>482</v>
-      </c>
-      <c r="C243" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -7396,10 +7397,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>483</v>
+      </c>
+      <c r="C244" t="s">
         <v>484</v>
-      </c>
-      <c r="C244" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -7407,10 +7408,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>485</v>
+      </c>
+      <c r="C245" t="s">
         <v>486</v>
-      </c>
-      <c r="C245" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -7418,10 +7419,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>487</v>
+      </c>
+      <c r="C246" t="s">
         <v>488</v>
-      </c>
-      <c r="C246" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -7429,10 +7430,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>489</v>
+      </c>
+      <c r="C247" t="s">
         <v>490</v>
-      </c>
-      <c r="C247" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -7440,10 +7441,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>491</v>
+      </c>
+      <c r="C248" t="s">
         <v>492</v>
-      </c>
-      <c r="C248" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -7451,10 +7452,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>493</v>
+      </c>
+      <c r="C249" t="s">
         <v>494</v>
-      </c>
-      <c r="C249" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -7462,10 +7463,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
+        <v>495</v>
+      </c>
+      <c r="C250" t="s">
         <v>496</v>
-      </c>
-      <c r="C250" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7473,10 +7474,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7484,10 +7485,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C252" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7495,10 +7496,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>499</v>
+      </c>
+      <c r="C253" t="s">
         <v>500</v>
-      </c>
-      <c r="C253" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7506,10 +7507,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
+        <v>501</v>
+      </c>
+      <c r="C254" t="s">
         <v>502</v>
-      </c>
-      <c r="C254" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7517,10 +7518,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>503</v>
+      </c>
+      <c r="C255" t="s">
         <v>504</v>
-      </c>
-      <c r="C255" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7528,10 +7529,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>505</v>
+      </c>
+      <c r="C256" t="s">
         <v>506</v>
-      </c>
-      <c r="C256" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7539,10 +7540,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>507</v>
+      </c>
+      <c r="C257" t="s">
         <v>508</v>
-      </c>
-      <c r="C257" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7550,10 +7551,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>509</v>
+      </c>
+      <c r="C258" t="s">
         <v>510</v>
-      </c>
-      <c r="C258" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7561,10 +7562,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>511</v>
+      </c>
+      <c r="C259" t="s">
         <v>512</v>
-      </c>
-      <c r="C259" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7572,10 +7573,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>513</v>
+      </c>
+      <c r="C260" t="s">
         <v>514</v>
-      </c>
-      <c r="C260" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7583,10 +7584,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>515</v>
+      </c>
+      <c r="C261" t="s">
         <v>516</v>
-      </c>
-      <c r="C261" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7594,10 +7595,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>517</v>
+      </c>
+      <c r="C262" t="s">
         <v>518</v>
-      </c>
-      <c r="C262" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7605,10 +7606,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>519</v>
+      </c>
+      <c r="C263" t="s">
         <v>520</v>
-      </c>
-      <c r="C263" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7616,10 +7617,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>521</v>
+      </c>
+      <c r="C264" t="s">
         <v>522</v>
-      </c>
-      <c r="C264" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7627,10 +7628,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>523</v>
+      </c>
+      <c r="C265" t="s">
         <v>524</v>
-      </c>
-      <c r="C265" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7638,10 +7639,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>525</v>
+      </c>
+      <c r="C266" t="s">
         <v>526</v>
-      </c>
-      <c r="C266" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7649,10 +7650,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>527</v>
+      </c>
+      <c r="C267" t="s">
         <v>528</v>
-      </c>
-      <c r="C267" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7660,10 +7661,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>529</v>
+      </c>
+      <c r="C268" t="s">
         <v>530</v>
-      </c>
-      <c r="C268" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7671,10 +7672,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>531</v>
+      </c>
+      <c r="C269" t="s">
         <v>532</v>
-      </c>
-      <c r="C269" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7682,10 +7683,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>533</v>
+      </c>
+      <c r="C270" t="s">
         <v>534</v>
-      </c>
-      <c r="C270" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7693,10 +7694,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7704,10 +7705,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>536</v>
+      </c>
+      <c r="C272" t="s">
         <v>537</v>
-      </c>
-      <c r="C272" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7715,10 +7716,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>538</v>
+      </c>
+      <c r="C273" t="s">
         <v>539</v>
-      </c>
-      <c r="C273" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7726,10 +7727,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>540</v>
+      </c>
+      <c r="C274" t="s">
         <v>541</v>
-      </c>
-      <c r="C274" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7737,10 +7738,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>542</v>
+      </c>
+      <c r="C275" t="s">
         <v>543</v>
-      </c>
-      <c r="C275" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7748,10 +7749,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>544</v>
+      </c>
+      <c r="C276" t="s">
         <v>545</v>
-      </c>
-      <c r="C276" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7759,10 +7760,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>546</v>
+      </c>
+      <c r="C277" t="s">
         <v>547</v>
-      </c>
-      <c r="C277" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7770,10 +7771,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>548</v>
+      </c>
+      <c r="C278" t="s">
         <v>549</v>
-      </c>
-      <c r="C278" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7781,10 +7782,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>550</v>
+      </c>
+      <c r="C279" t="s">
         <v>551</v>
-      </c>
-      <c r="C279" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7792,10 +7793,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>552</v>
+      </c>
+      <c r="C280" t="s">
         <v>553</v>
-      </c>
-      <c r="C280" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7803,10 +7804,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>554</v>
+      </c>
+      <c r="C281" t="s">
         <v>555</v>
-      </c>
-      <c r="C281" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -7814,10 +7815,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>556</v>
+      </c>
+      <c r="C282" t="s">
         <v>557</v>
-      </c>
-      <c r="C282" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -7825,10 +7826,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>558</v>
+      </c>
+      <c r="C283" t="s">
         <v>559</v>
-      </c>
-      <c r="C283" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -7836,10 +7837,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>560</v>
+      </c>
+      <c r="C284" t="s">
         <v>561</v>
-      </c>
-      <c r="C284" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -7847,10 +7848,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>562</v>
+      </c>
+      <c r="C285" t="s">
         <v>563</v>
-      </c>
-      <c r="C285" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -7858,10 +7859,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>564</v>
+      </c>
+      <c r="C286" t="s">
         <v>565</v>
-      </c>
-      <c r="C286" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7869,10 +7870,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>566</v>
+      </c>
+      <c r="C287" t="s">
         <v>567</v>
-      </c>
-      <c r="C287" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -7880,10 +7881,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>568</v>
+      </c>
+      <c r="C288" t="s">
         <v>569</v>
-      </c>
-      <c r="C288" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -7891,10 +7892,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>570</v>
+      </c>
+      <c r="C289" t="s">
         <v>571</v>
-      </c>
-      <c r="C289" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -7902,10 +7903,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>572</v>
+      </c>
+      <c r="C290" t="s">
         <v>573</v>
-      </c>
-      <c r="C290" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -7913,10 +7914,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>574</v>
+      </c>
+      <c r="C291" t="s">
         <v>575</v>
-      </c>
-      <c r="C291" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -7924,10 +7925,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>576</v>
+      </c>
+      <c r="C292" t="s">
         <v>577</v>
-      </c>
-      <c r="C292" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -7935,10 +7936,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>578</v>
+      </c>
+      <c r="C293" t="s">
         <v>579</v>
-      </c>
-      <c r="C293" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -7946,10 +7947,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>580</v>
+      </c>
+      <c r="C294" t="s">
         <v>581</v>
-      </c>
-      <c r="C294" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -7957,10 +7958,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>582</v>
+      </c>
+      <c r="C295" t="s">
         <v>583</v>
-      </c>
-      <c r="C295" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -7968,10 +7969,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -7979,10 +7980,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>585</v>
+      </c>
+      <c r="C297" t="s">
         <v>586</v>
-      </c>
-      <c r="C297" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -7990,10 +7991,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>587</v>
+      </c>
+      <c r="C298" t="s">
         <v>588</v>
-      </c>
-      <c r="C298" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -8001,10 +8002,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>589</v>
+      </c>
+      <c r="C299" t="s">
         <v>590</v>
-      </c>
-      <c r="C299" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -8012,10 +8013,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>591</v>
+      </c>
+      <c r="C300" t="s">
         <v>592</v>
-      </c>
-      <c r="C300" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -8023,10 +8024,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>593</v>
+      </c>
+      <c r="C301" t="s">
         <v>594</v>
-      </c>
-      <c r="C301" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8034,10 +8035,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>595</v>
+      </c>
+      <c r="C302" t="s">
         <v>596</v>
-      </c>
-      <c r="C302" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8045,10 +8046,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>597</v>
+      </c>
+      <c r="C303" t="s">
         <v>598</v>
-      </c>
-      <c r="C303" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8056,10 +8057,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>599</v>
+      </c>
+      <c r="C304" t="s">
         <v>600</v>
-      </c>
-      <c r="C304" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8067,10 +8068,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>601</v>
+      </c>
+      <c r="C305" t="s">
         <v>602</v>
-      </c>
-      <c r="C305" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8078,10 +8079,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>603</v>
+      </c>
+      <c r="C306" t="s">
         <v>604</v>
-      </c>
-      <c r="C306" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8089,10 +8090,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>605</v>
+      </c>
+      <c r="C307" t="s">
         <v>606</v>
-      </c>
-      <c r="C307" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8100,10 +8101,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>607</v>
+      </c>
+      <c r="C308" t="s">
         <v>608</v>
-      </c>
-      <c r="C308" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8111,10 +8112,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>609</v>
+      </c>
+      <c r="C309" t="s">
         <v>610</v>
-      </c>
-      <c r="C309" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8122,10 +8123,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>611</v>
+      </c>
+      <c r="C310" t="s">
         <v>612</v>
-      </c>
-      <c r="C310" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8133,10 +8134,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>613</v>
+      </c>
+      <c r="C311" t="s">
         <v>614</v>
-      </c>
-      <c r="C311" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8144,10 +8145,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>615</v>
+      </c>
+      <c r="C312" t="s">
         <v>616</v>
-      </c>
-      <c r="C312" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8155,10 +8156,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>617</v>
+      </c>
+      <c r="C313" t="s">
         <v>618</v>
-      </c>
-      <c r="C313" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8166,10 +8167,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>619</v>
+      </c>
+      <c r="C314" t="s">
         <v>620</v>
-      </c>
-      <c r="C314" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8177,10 +8178,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>621</v>
+      </c>
+      <c r="C315" t="s">
         <v>622</v>
-      </c>
-      <c r="C315" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8188,10 +8189,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>623</v>
+      </c>
+      <c r="C316" t="s">
         <v>624</v>
-      </c>
-      <c r="C316" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8199,10 +8200,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>625</v>
+      </c>
+      <c r="C317" t="s">
         <v>626</v>
-      </c>
-      <c r="C317" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8210,10 +8211,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>627</v>
+      </c>
+      <c r="C318" t="s">
         <v>628</v>
-      </c>
-      <c r="C318" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8221,10 +8222,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>629</v>
+      </c>
+      <c r="C319" t="s">
         <v>630</v>
-      </c>
-      <c r="C319" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8232,10 +8233,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>631</v>
+      </c>
+      <c r="C320" t="s">
         <v>632</v>
-      </c>
-      <c r="C320" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8243,10 +8244,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>633</v>
+      </c>
+      <c r="C321" t="s">
         <v>634</v>
-      </c>
-      <c r="C321" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8254,10 +8255,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>635</v>
+      </c>
+      <c r="C322" t="s">
         <v>636</v>
-      </c>
-      <c r="C322" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8265,10 +8266,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>637</v>
+      </c>
+      <c r="C323" t="s">
         <v>638</v>
-      </c>
-      <c r="C323" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8276,10 +8277,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>639</v>
+      </c>
+      <c r="C324" t="s">
         <v>640</v>
-      </c>
-      <c r="C324" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8287,10 +8288,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>641</v>
+      </c>
+      <c r="C325" t="s">
         <v>642</v>
-      </c>
-      <c r="C325" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8298,10 +8299,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>643</v>
+      </c>
+      <c r="C326" t="s">
         <v>644</v>
-      </c>
-      <c r="C326" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8309,10 +8310,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>645</v>
+      </c>
+      <c r="C327" t="s">
         <v>646</v>
-      </c>
-      <c r="C327" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8320,10 +8321,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>647</v>
+      </c>
+      <c r="C328" t="s">
         <v>648</v>
-      </c>
-      <c r="C328" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8331,10 +8332,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>649</v>
+      </c>
+      <c r="C329" t="s">
         <v>650</v>
-      </c>
-      <c r="C329" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8342,10 +8343,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>651</v>
+      </c>
+      <c r="C330" t="s">
         <v>652</v>
-      </c>
-      <c r="C330" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8353,10 +8354,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>653</v>
+      </c>
+      <c r="C331" t="s">
         <v>654</v>
-      </c>
-      <c r="C331" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8364,10 +8365,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>655</v>
+      </c>
+      <c r="C332" t="s">
         <v>656</v>
-      </c>
-      <c r="C332" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8375,10 +8376,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>657</v>
+      </c>
+      <c r="C333" t="s">
         <v>658</v>
-      </c>
-      <c r="C333" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8386,10 +8387,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>659</v>
+      </c>
+      <c r="C334" t="s">
         <v>660</v>
-      </c>
-      <c r="C334" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8397,10 +8398,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>661</v>
+      </c>
+      <c r="C335" t="s">
         <v>662</v>
-      </c>
-      <c r="C335" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8408,10 +8409,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>663</v>
+      </c>
+      <c r="C336" t="s">
         <v>664</v>
-      </c>
-      <c r="C336" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8419,10 +8420,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>665</v>
+      </c>
+      <c r="C337" t="s">
         <v>666</v>
-      </c>
-      <c r="C337" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8430,10 +8431,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8441,10 +8442,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8452,10 +8453,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>669</v>
+      </c>
+      <c r="C340" t="s">
         <v>670</v>
-      </c>
-      <c r="C340" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8463,10 +8464,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>671</v>
+      </c>
+      <c r="C341" t="s">
         <v>672</v>
-      </c>
-      <c r="C341" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8474,10 +8475,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>673</v>
+      </c>
+      <c r="C342" t="s">
         <v>674</v>
-      </c>
-      <c r="C342" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8485,10 +8486,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>675</v>
+      </c>
+      <c r="C343" t="s">
         <v>676</v>
-      </c>
-      <c r="C343" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8496,10 +8497,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>677</v>
+      </c>
+      <c r="C344" t="s">
         <v>678</v>
-      </c>
-      <c r="C344" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8507,10 +8508,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>679</v>
+      </c>
+      <c r="C345" t="s">
         <v>680</v>
-      </c>
-      <c r="C345" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8518,10 +8519,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>681</v>
+      </c>
+      <c r="C346" t="s">
         <v>682</v>
-      </c>
-      <c r="C346" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8529,10 +8530,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>683</v>
+      </c>
+      <c r="C347" t="s">
         <v>684</v>
-      </c>
-      <c r="C347" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8540,10 +8541,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>685</v>
+      </c>
+      <c r="C348" t="s">
         <v>686</v>
-      </c>
-      <c r="C348" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8551,10 +8552,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>687</v>
+      </c>
+      <c r="C349" t="s">
         <v>688</v>
-      </c>
-      <c r="C349" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8562,10 +8563,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>689</v>
+      </c>
+      <c r="C350" t="s">
         <v>690</v>
-      </c>
-      <c r="C350" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8573,10 +8574,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>691</v>
+      </c>
+      <c r="C351" t="s">
         <v>692</v>
-      </c>
-      <c r="C351" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8584,10 +8585,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>693</v>
+      </c>
+      <c r="C352" t="s">
         <v>694</v>
-      </c>
-      <c r="C352" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8595,10 +8596,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>695</v>
+      </c>
+      <c r="C353" t="s">
         <v>696</v>
-      </c>
-      <c r="C353" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8606,10 +8607,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>697</v>
+      </c>
+      <c r="C354" t="s">
         <v>698</v>
-      </c>
-      <c r="C354" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8617,10 +8618,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>699</v>
+      </c>
+      <c r="C355" t="s">
         <v>700</v>
-      </c>
-      <c r="C355" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8628,10 +8629,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>701</v>
+      </c>
+      <c r="C356" t="s">
         <v>702</v>
-      </c>
-      <c r="C356" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8639,10 +8640,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>703</v>
+      </c>
+      <c r="C357" t="s">
         <v>704</v>
-      </c>
-      <c r="C357" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8650,10 +8651,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>705</v>
+      </c>
+      <c r="C358" t="s">
         <v>706</v>
-      </c>
-      <c r="C358" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8661,10 +8662,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>707</v>
+      </c>
+      <c r="C359" t="s">
         <v>708</v>
-      </c>
-      <c r="C359" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8672,10 +8673,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>709</v>
+      </c>
+      <c r="C360" t="s">
         <v>710</v>
-      </c>
-      <c r="C360" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8683,10 +8684,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>711</v>
+      </c>
+      <c r="C361" t="s">
         <v>712</v>
-      </c>
-      <c r="C361" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8694,10 +8695,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>713</v>
+      </c>
+      <c r="C362" t="s">
         <v>714</v>
-      </c>
-      <c r="C362" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8705,10 +8706,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>715</v>
+      </c>
+      <c r="C363" t="s">
         <v>716</v>
-      </c>
-      <c r="C363" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8716,10 +8717,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>717</v>
+      </c>
+      <c r="C364" t="s">
         <v>718</v>
-      </c>
-      <c r="C364" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8727,10 +8728,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>719</v>
+      </c>
+      <c r="C365" t="s">
         <v>720</v>
-      </c>
-      <c r="C365" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8738,10 +8739,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>721</v>
+      </c>
+      <c r="C366" t="s">
         <v>722</v>
-      </c>
-      <c r="C366" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8749,10 +8750,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>723</v>
+      </c>
+      <c r="C367" t="s">
         <v>724</v>
-      </c>
-      <c r="C367" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8760,10 +8761,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>725</v>
+      </c>
+      <c r="C368" t="s">
         <v>726</v>
-      </c>
-      <c r="C368" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8771,10 +8772,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>727</v>
+      </c>
+      <c r="C369" t="s">
         <v>728</v>
-      </c>
-      <c r="C369" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8782,10 +8783,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>729</v>
+      </c>
+      <c r="C370" t="s">
         <v>730</v>
-      </c>
-      <c r="C370" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -8793,10 +8794,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>731</v>
+      </c>
+      <c r="C371" t="s">
         <v>732</v>
-      </c>
-      <c r="C371" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -8804,10 +8805,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>733</v>
+      </c>
+      <c r="C372" t="s">
         <v>734</v>
-      </c>
-      <c r="C372" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -8815,10 +8816,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>735</v>
+      </c>
+      <c r="C373" t="s">
         <v>736</v>
-      </c>
-      <c r="C373" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -8826,10 +8827,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>737</v>
+      </c>
+      <c r="C374" t="s">
         <v>738</v>
-      </c>
-      <c r="C374" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8837,10 +8838,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>739</v>
+      </c>
+      <c r="C375" t="s">
         <v>740</v>
-      </c>
-      <c r="C375" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -8848,10 +8849,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>741</v>
+      </c>
+      <c r="C376" t="s">
         <v>742</v>
-      </c>
-      <c r="C376" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -8859,10 +8860,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>743</v>
+      </c>
+      <c r="C377" t="s">
         <v>744</v>
-      </c>
-      <c r="C377" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8870,10 +8871,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>745</v>
+      </c>
+      <c r="C378" t="s">
         <v>746</v>
-      </c>
-      <c r="C378" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -8881,10 +8882,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>747</v>
+      </c>
+      <c r="C379" t="s">
         <v>748</v>
-      </c>
-      <c r="C379" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8892,10 +8893,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>749</v>
+      </c>
+      <c r="C380" t="s">
         <v>750</v>
-      </c>
-      <c r="C380" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -8903,10 +8904,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>751</v>
+      </c>
+      <c r="C381" t="s">
         <v>752</v>
-      </c>
-      <c r="C381" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -8914,10 +8915,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>753</v>
+      </c>
+      <c r="C382" t="s">
         <v>754</v>
-      </c>
-      <c r="C382" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -8925,10 +8926,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>755</v>
+      </c>
+      <c r="C383" t="s">
         <v>756</v>
-      </c>
-      <c r="C383" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -8936,10 +8937,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>757</v>
+      </c>
+      <c r="C384" t="s">
         <v>758</v>
-      </c>
-      <c r="C384" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -8947,10 +8948,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>759</v>
+      </c>
+      <c r="C385" t="s">
         <v>760</v>
-      </c>
-      <c r="C385" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -8958,10 +8959,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>761</v>
+      </c>
+      <c r="C386" t="s">
         <v>762</v>
-      </c>
-      <c r="C386" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -8969,10 +8970,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>763</v>
+      </c>
+      <c r="C387" t="s">
         <v>764</v>
-      </c>
-      <c r="C387" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -8980,10 +8981,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>765</v>
+      </c>
+      <c r="C388" t="s">
         <v>766</v>
-      </c>
-      <c r="C388" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -8991,10 +8992,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>767</v>
+      </c>
+      <c r="C389" t="s">
         <v>768</v>
-      </c>
-      <c r="C389" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -9002,10 +9003,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>769</v>
+      </c>
+      <c r="C390" t="s">
         <v>770</v>
-      </c>
-      <c r="C390" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9013,10 +9014,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>771</v>
+      </c>
+      <c r="C391" t="s">
         <v>772</v>
-      </c>
-      <c r="C391" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9024,10 +9025,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>773</v>
+      </c>
+      <c r="C392" t="s">
         <v>774</v>
-      </c>
-      <c r="C392" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9035,10 +9036,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>775</v>
+      </c>
+      <c r="C393" t="s">
         <v>776</v>
-      </c>
-      <c r="C393" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9046,10 +9047,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>777</v>
+      </c>
+      <c r="C394" t="s">
         <v>778</v>
-      </c>
-      <c r="C394" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9057,10 +9058,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>779</v>
+      </c>
+      <c r="C395" t="s">
         <v>780</v>
-      </c>
-      <c r="C395" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9068,10 +9069,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>781</v>
+      </c>
+      <c r="C396" t="s">
         <v>782</v>
-      </c>
-      <c r="C396" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9079,10 +9080,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>783</v>
+      </c>
+      <c r="C397" t="s">
         <v>784</v>
-      </c>
-      <c r="C397" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9090,10 +9091,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>785</v>
+      </c>
+      <c r="C398" t="s">
         <v>786</v>
-      </c>
-      <c r="C398" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9101,10 +9102,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>787</v>
+      </c>
+      <c r="C399" t="s">
         <v>788</v>
-      </c>
-      <c r="C399" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9112,10 +9113,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>789</v>
+      </c>
+      <c r="C400" t="s">
         <v>790</v>
-      </c>
-      <c r="C400" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9123,10 +9124,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>791</v>
+      </c>
+      <c r="C401" t="s">
         <v>792</v>
-      </c>
-      <c r="C401" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9134,10 +9135,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>793</v>
+      </c>
+      <c r="C402" t="s">
         <v>794</v>
-      </c>
-      <c r="C402" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9145,10 +9146,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>795</v>
+      </c>
+      <c r="C403" t="s">
         <v>796</v>
-      </c>
-      <c r="C403" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9156,10 +9157,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>797</v>
+      </c>
+      <c r="C404" t="s">
         <v>798</v>
-      </c>
-      <c r="C404" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9167,10 +9168,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>799</v>
+      </c>
+      <c r="C405" t="s">
         <v>800</v>
-      </c>
-      <c r="C405" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9178,10 +9179,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>801</v>
+      </c>
+      <c r="C406" t="s">
         <v>802</v>
-      </c>
-      <c r="C406" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9189,10 +9190,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>803</v>
+      </c>
+      <c r="C407" t="s">
         <v>804</v>
-      </c>
-      <c r="C407" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9200,10 +9201,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>805</v>
+      </c>
+      <c r="C408" t="s">
         <v>806</v>
-      </c>
-      <c r="C408" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9211,10 +9212,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>807</v>
+      </c>
+      <c r="C409" t="s">
         <v>808</v>
-      </c>
-      <c r="C409" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9222,10 +9223,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>809</v>
+      </c>
+      <c r="C410" t="s">
         <v>810</v>
-      </c>
-      <c r="C410" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9233,10 +9234,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>811</v>
+      </c>
+      <c r="C411" t="s">
         <v>812</v>
-      </c>
-      <c r="C411" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9244,10 +9245,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>813</v>
+      </c>
+      <c r="C412" t="s">
         <v>814</v>
-      </c>
-      <c r="C412" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9255,10 +9256,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>815</v>
+      </c>
+      <c r="C413" t="s">
         <v>816</v>
-      </c>
-      <c r="C413" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9266,10 +9267,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>817</v>
+      </c>
+      <c r="C414" t="s">
         <v>818</v>
-      </c>
-      <c r="C414" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9277,10 +9278,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>819</v>
+      </c>
+      <c r="C415" t="s">
         <v>820</v>
-      </c>
-      <c r="C415" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9288,10 +9289,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>821</v>
+      </c>
+      <c r="C416" t="s">
         <v>822</v>
-      </c>
-      <c r="C416" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9299,10 +9300,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>823</v>
+      </c>
+      <c r="C417" t="s">
         <v>824</v>
-      </c>
-      <c r="C417" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9310,10 +9311,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>825</v>
+      </c>
+      <c r="C418" t="s">
         <v>826</v>
-      </c>
-      <c r="C418" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9321,10 +9322,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>827</v>
+      </c>
+      <c r="C419" t="s">
         <v>828</v>
-      </c>
-      <c r="C419" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9332,10 +9333,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>829</v>
+      </c>
+      <c r="C420" t="s">
         <v>830</v>
-      </c>
-      <c r="C420" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9343,10 +9344,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>831</v>
+      </c>
+      <c r="C421" t="s">
         <v>832</v>
-      </c>
-      <c r="C421" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9354,10 +9355,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>833</v>
+      </c>
+      <c r="C422" t="s">
         <v>834</v>
-      </c>
-      <c r="C422" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9365,10 +9366,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>835</v>
+      </c>
+      <c r="C423" t="s">
         <v>836</v>
-      </c>
-      <c r="C423" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9376,10 +9377,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>837</v>
+      </c>
+      <c r="C424" t="s">
         <v>838</v>
-      </c>
-      <c r="C424" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9387,10 +9388,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>839</v>
+      </c>
+      <c r="C425" t="s">
         <v>840</v>
-      </c>
-      <c r="C425" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9398,10 +9399,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>841</v>
+      </c>
+      <c r="C426" t="s">
         <v>842</v>
-      </c>
-      <c r="C426" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9409,10 +9410,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>843</v>
+      </c>
+      <c r="C427" t="s">
         <v>844</v>
-      </c>
-      <c r="C427" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9420,10 +9421,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C428" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9431,10 +9432,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C429" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9442,10 +9443,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>847</v>
+      </c>
+      <c r="C430" t="s">
         <v>848</v>
-      </c>
-      <c r="C430" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9453,10 +9454,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>849</v>
+      </c>
+      <c r="C431" t="s">
         <v>850</v>
-      </c>
-      <c r="C431" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9464,10 +9465,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>851</v>
+      </c>
+      <c r="C432" t="s">
         <v>852</v>
-      </c>
-      <c r="C432" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9475,10 +9476,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>853</v>
+      </c>
+      <c r="C433" t="s">
         <v>854</v>
-      </c>
-      <c r="C433" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9486,10 +9487,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>855</v>
+      </c>
+      <c r="C434" t="s">
         <v>856</v>
-      </c>
-      <c r="C434" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9497,10 +9498,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>857</v>
+      </c>
+      <c r="C435" t="s">
         <v>858</v>
-      </c>
-      <c r="C435" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9508,10 +9509,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>859</v>
+      </c>
+      <c r="C436" t="s">
         <v>860</v>
-      </c>
-      <c r="C436" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9519,10 +9520,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>861</v>
+      </c>
+      <c r="C437" t="s">
         <v>862</v>
-      </c>
-      <c r="C437" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9530,10 +9531,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>863</v>
+      </c>
+      <c r="C438" t="s">
         <v>864</v>
-      </c>
-      <c r="C438" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9541,10 +9542,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>865</v>
+      </c>
+      <c r="C439" t="s">
         <v>866</v>
-      </c>
-      <c r="C439" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9552,10 +9553,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>867</v>
+      </c>
+      <c r="C440" t="s">
         <v>868</v>
-      </c>
-      <c r="C440" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9563,10 +9564,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>869</v>
+      </c>
+      <c r="C441" t="s">
         <v>870</v>
-      </c>
-      <c r="C441" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9574,10 +9575,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>871</v>
+      </c>
+      <c r="C442" t="s">
         <v>872</v>
-      </c>
-      <c r="C442" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9585,10 +9586,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>873</v>
+      </c>
+      <c r="C443" t="s">
         <v>874</v>
-      </c>
-      <c r="C443" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9596,10 +9597,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>875</v>
+      </c>
+      <c r="C444" t="s">
         <v>876</v>
-      </c>
-      <c r="C444" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9607,10 +9608,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>877</v>
+      </c>
+      <c r="C445" t="s">
         <v>878</v>
-      </c>
-      <c r="C445" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9618,10 +9619,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>879</v>
+      </c>
+      <c r="C446" t="s">
         <v>880</v>
-      </c>
-      <c r="C446" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9629,10 +9630,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>881</v>
+      </c>
+      <c r="C447" t="s">
         <v>882</v>
-      </c>
-      <c r="C447" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9640,10 +9641,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>883</v>
+      </c>
+      <c r="C448" t="s">
         <v>884</v>
-      </c>
-      <c r="C448" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9651,10 +9652,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>885</v>
+      </c>
+      <c r="C449" t="s">
         <v>886</v>
-      </c>
-      <c r="C449" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9662,10 +9663,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>887</v>
+      </c>
+      <c r="C450" t="s">
         <v>888</v>
-      </c>
-      <c r="C450" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9673,10 +9674,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C451" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9684,10 +9685,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>890</v>
+      </c>
+      <c r="C452" t="s">
         <v>891</v>
-      </c>
-      <c r="C452" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9695,10 +9696,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>892</v>
+      </c>
+      <c r="C453" t="s">
         <v>893</v>
-      </c>
-      <c r="C453" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9706,10 +9707,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>894</v>
+      </c>
+      <c r="C454" t="s">
         <v>895</v>
-      </c>
-      <c r="C454" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9717,10 +9718,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>896</v>
+      </c>
+      <c r="C455" t="s">
         <v>897</v>
-      </c>
-      <c r="C455" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9728,10 +9729,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C456" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9739,10 +9740,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>899</v>
+      </c>
+      <c r="C457" t="s">
         <v>900</v>
-      </c>
-      <c r="C457" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9750,10 +9751,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>901</v>
+      </c>
+      <c r="C458" t="s">
         <v>902</v>
-      </c>
-      <c r="C458" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9761,10 +9762,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>903</v>
+      </c>
+      <c r="C459" t="s">
         <v>904</v>
-      </c>
-      <c r="C459" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9772,7 +9773,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9780,10 +9781,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>906</v>
+      </c>
+      <c r="C461" t="s">
         <v>907</v>
-      </c>
-      <c r="C461" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9791,10 +9792,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>908</v>
+      </c>
+      <c r="C462" t="s">
         <v>909</v>
-      </c>
-      <c r="C462" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9802,10 +9803,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>910</v>
+      </c>
+      <c r="C463" t="s">
         <v>911</v>
-      </c>
-      <c r="C463" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9813,10 +9814,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>912</v>
+      </c>
+      <c r="C464" t="s">
         <v>913</v>
-      </c>
-      <c r="C464" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9824,10 +9825,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>914</v>
+      </c>
+      <c r="C465" t="s">
         <v>915</v>
-      </c>
-      <c r="C465" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9835,10 +9836,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>916</v>
+      </c>
+      <c r="C466" t="s">
         <v>917</v>
-      </c>
-      <c r="C466" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9846,10 +9847,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9857,10 +9858,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>919</v>
+      </c>
+      <c r="C468" t="s">
         <v>920</v>
-      </c>
-      <c r="C468" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9868,10 +9869,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>921</v>
+      </c>
+      <c r="C469" t="s">
         <v>922</v>
-      </c>
-      <c r="C469" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9879,10 +9880,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>923</v>
+      </c>
+      <c r="C470" t="s">
         <v>924</v>
-      </c>
-      <c r="C470" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9890,10 +9891,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>925</v>
+      </c>
+      <c r="C471" t="s">
         <v>926</v>
-      </c>
-      <c r="C471" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9901,10 +9902,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>927</v>
+      </c>
+      <c r="C472" t="s">
         <v>928</v>
-      </c>
-      <c r="C472" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9912,10 +9913,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>929</v>
+      </c>
+      <c r="C473" t="s">
         <v>930</v>
-      </c>
-      <c r="C473" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9923,10 +9924,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>931</v>
+      </c>
+      <c r="C474" t="s">
         <v>932</v>
-      </c>
-      <c r="C474" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9934,10 +9935,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>933</v>
+      </c>
+      <c r="C475" t="s">
         <v>934</v>
-      </c>
-      <c r="C475" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9945,10 +9946,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>935</v>
+      </c>
+      <c r="C476" t="s">
         <v>936</v>
-      </c>
-      <c r="C476" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9956,10 +9957,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>937</v>
+      </c>
+      <c r="C477" t="s">
         <v>938</v>
-      </c>
-      <c r="C477" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9967,10 +9968,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C478" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9978,10 +9979,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>940</v>
+      </c>
+      <c r="C479" t="s">
         <v>941</v>
-      </c>
-      <c r="C479" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9989,10 +9990,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>942</v>
+      </c>
+      <c r="C480" t="s">
         <v>943</v>
-      </c>
-      <c r="C480" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -10000,10 +10001,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>944</v>
+      </c>
+      <c r="C481" t="s">
         <v>945</v>
-      </c>
-      <c r="C481" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -10011,10 +10012,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>946</v>
+      </c>
+      <c r="C482" t="s">
         <v>947</v>
-      </c>
-      <c r="C482" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10022,10 +10023,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>948</v>
+      </c>
+      <c r="C483" t="s">
         <v>949</v>
-      </c>
-      <c r="C483" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10033,10 +10034,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>950</v>
+      </c>
+      <c r="C484" t="s">
         <v>951</v>
-      </c>
-      <c r="C484" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10044,10 +10045,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>952</v>
+      </c>
+      <c r="C485" t="s">
         <v>953</v>
-      </c>
-      <c r="C485" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10055,10 +10056,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>954</v>
+      </c>
+      <c r="C486" t="s">
         <v>955</v>
-      </c>
-      <c r="C486" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10066,10 +10067,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>956</v>
+      </c>
+      <c r="C487" t="s">
         <v>957</v>
-      </c>
-      <c r="C487" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10077,10 +10078,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>958</v>
+      </c>
+      <c r="C488" t="s">
         <v>959</v>
-      </c>
-      <c r="C488" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10088,10 +10089,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>960</v>
+      </c>
+      <c r="C489" t="s">
         <v>961</v>
-      </c>
-      <c r="C489" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10099,10 +10100,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>962</v>
+      </c>
+      <c r="C490" t="s">
         <v>963</v>
-      </c>
-      <c r="C490" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10110,10 +10111,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>964</v>
+      </c>
+      <c r="C491" t="s">
         <v>965</v>
-      </c>
-      <c r="C491" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10121,10 +10122,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>966</v>
+      </c>
+      <c r="C492" t="s">
         <v>967</v>
-      </c>
-      <c r="C492" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10132,10 +10133,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>968</v>
+      </c>
+      <c r="C493" t="s">
         <v>969</v>
-      </c>
-      <c r="C493" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10143,10 +10144,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>970</v>
+      </c>
+      <c r="C494" t="s">
         <v>971</v>
-      </c>
-      <c r="C494" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10154,10 +10155,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>972</v>
+      </c>
+      <c r="C495" t="s">
         <v>973</v>
-      </c>
-      <c r="C495" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10165,10 +10166,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>974</v>
+      </c>
+      <c r="C496" t="s">
         <v>975</v>
-      </c>
-      <c r="C496" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10176,10 +10177,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>976</v>
+      </c>
+      <c r="C497" t="s">
         <v>977</v>
-      </c>
-      <c r="C497" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10187,10 +10188,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>978</v>
+      </c>
+      <c r="C498" t="s">
         <v>979</v>
-      </c>
-      <c r="C498" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10198,7 +10199,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10206,10 +10207,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>981</v>
+      </c>
+      <c r="C500" t="s">
         <v>982</v>
-      </c>
-      <c r="C500" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10217,10 +10218,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>983</v>
+      </c>
+      <c r="C501" t="s">
         <v>984</v>
-      </c>
-      <c r="C501" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10228,10 +10229,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>985</v>
+      </c>
+      <c r="C502" t="s">
         <v>986</v>
-      </c>
-      <c r="C502" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10239,10 +10240,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10250,10 +10251,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>988</v>
+      </c>
+      <c r="C504" t="s">
         <v>989</v>
-      </c>
-      <c r="C504" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10261,10 +10262,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>990</v>
+      </c>
+      <c r="C505" t="s">
         <v>991</v>
-      </c>
-      <c r="C505" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10272,10 +10273,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>992</v>
+      </c>
+      <c r="C506" t="s">
         <v>993</v>
-      </c>
-      <c r="C506" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10283,10 +10284,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>994</v>
+      </c>
+      <c r="C507" t="s">
         <v>995</v>
-      </c>
-      <c r="C507" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10294,10 +10295,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>996</v>
+      </c>
+      <c r="C508" t="s">
         <v>997</v>
-      </c>
-      <c r="C508" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10305,10 +10306,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>998</v>
+      </c>
+      <c r="C509" t="s">
         <v>999</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10316,10 +10317,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C510" t="s">
         <v>1001</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10327,10 +10328,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C511" t="s">
         <v>1003</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10338,10 +10339,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C512" t="s">
         <v>1005</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10349,10 +10350,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C513" t="s">
         <v>1007</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10360,10 +10361,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C514" t="s">
         <v>1009</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10371,10 +10372,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C515" t="s">
         <v>1011</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10382,10 +10383,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C516" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10393,10 +10394,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C517" t="s">
         <v>1014</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10404,7 +10405,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10412,10 +10413,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C519" t="s">
         <v>1017</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10423,10 +10424,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C520" t="s">
         <v>1019</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10434,10 +10435,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C521" t="s">
         <v>1021</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10445,10 +10446,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C522" t="s">
         <v>1023</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10456,10 +10457,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C523" t="s">
         <v>1025</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10467,10 +10468,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C524" t="s">
         <v>1027</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10478,10 +10479,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10489,10 +10490,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C526" t="s">
         <v>1030</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10500,10 +10501,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C527" t="s">
         <v>1032</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10511,10 +10512,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C528" t="s">
         <v>1034</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10522,10 +10523,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C529" t="s">
         <v>1036</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10533,10 +10534,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10544,10 +10545,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C531" t="s">
         <v>1039</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10555,10 +10556,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C532" t="s">
         <v>1041</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10566,10 +10567,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C533" t="s">
         <v>1043</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10577,10 +10578,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C534" t="s">
         <v>1045</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10588,10 +10589,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C535" t="s">
         <v>1047</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10599,10 +10600,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C536" t="s">
         <v>1049</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10610,10 +10611,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C537" t="s">
         <v>1051</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10621,10 +10622,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C538" t="s">
         <v>1053</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10632,10 +10633,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C539" t="s">
         <v>1055</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10643,10 +10644,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C540" t="s">
         <v>1057</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10654,10 +10655,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C541" t="s">
         <v>1059</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10665,10 +10666,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C542" t="s">
         <v>1061</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10676,10 +10677,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C543" t="s">
         <v>1063</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10687,10 +10688,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C544" t="s">
         <v>1065</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10698,10 +10699,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C545" t="s">
         <v>1067</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10709,10 +10710,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C546" t="s">
         <v>1069</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10720,7 +10721,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10728,10 +10729,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C548" t="s">
         <v>1072</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10739,10 +10740,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C549" t="s">
         <v>1074</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10750,10 +10751,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C550" t="s">
         <v>1076</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10761,10 +10762,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C551" t="s">
         <v>1078</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10772,10 +10773,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C552" t="s">
         <v>1080</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10783,10 +10784,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C553" t="s">
         <v>1082</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10794,10 +10795,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C554" t="s">
         <v>1084</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10805,10 +10806,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C555" t="s">
         <v>1086</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10816,10 +10817,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C556" t="s">
         <v>1088</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10827,10 +10828,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C557" t="s">
         <v>1090</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10838,10 +10839,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C558" t="s">
         <v>1092</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10849,7 +10850,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10857,10 +10858,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C560" t="s">
         <v>1095</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10868,10 +10869,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C561" t="s">
         <v>1097</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10879,10 +10880,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C562" t="s">
         <v>1099</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10890,10 +10891,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C563" t="s">
         <v>1101</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10901,10 +10902,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C564" t="s">
         <v>1103</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10912,10 +10913,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C565" t="s">
         <v>1105</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10923,10 +10924,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C566" t="s">
         <v>1107</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10934,10 +10935,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C567" t="s">
         <v>1109</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10945,10 +10946,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C568" t="s">
         <v>1111</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10956,10 +10957,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C569" t="s">
         <v>1113</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10967,10 +10968,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C570" t="s">
         <v>1115</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10978,10 +10979,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C571" t="s">
         <v>1117</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10989,10 +10990,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C572" t="s">
         <v>1119</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -11000,10 +11001,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C573" t="s">
         <v>1121</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11011,10 +11012,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C574" t="s">
         <v>1123</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11022,10 +11023,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11033,10 +11034,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C576" t="s">
         <v>1126</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11044,10 +11045,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11055,10 +11056,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11066,10 +11067,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C579" t="s">
         <v>1128</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11077,10 +11078,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C580" t="s">
         <v>1130</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11088,10 +11089,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C581" t="s">
         <v>1132</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11099,10 +11100,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C582" t="s">
         <v>1134</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11110,10 +11111,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11121,7 +11122,7 @@
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11129,10 +11130,10 @@
         <v>612</v>
       </c>
       <c r="B585" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C585" t="s">
         <v>1137</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11140,10 +11141,10 @@
         <v>615</v>
       </c>
       <c r="B586" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C586" t="s">
         <v>1139</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11151,10 +11152,10 @@
         <v>617</v>
       </c>
       <c r="B587" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C587" t="s">
         <v>1141</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11162,10 +11163,10 @@
         <v>618</v>
       </c>
       <c r="B588" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C588" t="s">
         <v>1143</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11173,10 +11174,10 @@
         <v>625</v>
       </c>
       <c r="B589" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C589" t="s">
         <v>1145</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11184,10 +11185,10 @@
         <v>624</v>
       </c>
       <c r="B590" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C590" t="s">
         <v>1147</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11195,10 +11196,10 @@
         <v>626</v>
       </c>
       <c r="B591" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C591" t="s">
         <v>1149</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11206,10 +11207,10 @@
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C592" t="s">
         <v>1151</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11217,10 +11218,10 @@
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C593" t="s">
         <v>1153</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11228,7 +11229,7 @@
         <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11236,10 +11237,10 @@
         <v>633</v>
       </c>
       <c r="B595" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C595" t="s">
         <v>1156</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11247,10 +11248,10 @@
         <v>635</v>
       </c>
       <c r="B596" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C596" t="s">
         <v>1158</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11258,10 +11259,10 @@
         <v>636</v>
       </c>
       <c r="B597" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C597" t="s">
         <v>1160</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11269,10 +11270,10 @@
         <v>642</v>
       </c>
       <c r="B598" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C598" t="s">
         <v>1162</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11280,10 +11281,10 @@
         <v>644</v>
       </c>
       <c r="B599" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C599" t="s">
         <v>1164</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11291,10 +11292,10 @@
         <v>646</v>
       </c>
       <c r="B600" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C600" t="s">
         <v>1166</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11302,10 +11303,10 @@
         <v>649</v>
       </c>
       <c r="B601" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C601" t="s">
         <v>1168</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11313,10 +11314,10 @@
         <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11324,10 +11325,10 @@
         <v>651</v>
       </c>
       <c r="B603" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C603" t="s">
         <v>1171</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11335,10 +11336,10 @@
         <v>653</v>
       </c>
       <c r="B604" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C604" t="s">
         <v>1173</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11346,10 +11347,10 @@
         <v>654</v>
       </c>
       <c r="B605" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C605" t="s">
         <v>1175</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11357,10 +11358,10 @@
         <v>655</v>
       </c>
       <c r="B606" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C606" t="s">
         <v>1177</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11368,10 +11369,10 @@
         <v>659</v>
       </c>
       <c r="B607" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C607" t="s">
         <v>1179</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11379,10 +11380,10 @@
         <v>660</v>
       </c>
       <c r="B608" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C608" t="s">
         <v>1181</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11390,10 +11391,10 @@
         <v>661</v>
       </c>
       <c r="B609" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C609" t="s">
         <v>1183</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11401,10 +11402,10 @@
         <v>663</v>
       </c>
       <c r="B610" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C610" t="s">
         <v>1185</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11412,10 +11413,10 @@
         <v>667</v>
       </c>
       <c r="B611" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C611" t="s">
         <v>1187</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11423,10 +11424,10 @@
         <v>670</v>
       </c>
       <c r="B612" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C612" t="s">
         <v>1189</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11434,10 +11435,10 @@
         <v>673</v>
       </c>
       <c r="B613" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C613" t="s">
         <v>1191</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11445,10 +11446,10 @@
         <v>674</v>
       </c>
       <c r="B614" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C614" t="s">
         <v>1193</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11456,10 +11457,10 @@
         <v>675</v>
       </c>
       <c r="B615" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C615" t="s">
         <v>1195</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11467,10 +11468,10 @@
         <v>680</v>
       </c>
       <c r="B616" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C616" t="s">
         <v>1197</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11478,10 +11479,10 @@
         <v>681</v>
       </c>
       <c r="B617" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C617" t="s">
         <v>1199</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11489,10 +11490,10 @@
         <v>682</v>
       </c>
       <c r="B618" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C618" t="s">
         <v>1201</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11500,10 +11501,10 @@
         <v>683</v>
       </c>
       <c r="B619" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C619" t="s">
         <v>1203</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11511,10 +11512,10 @@
         <v>684</v>
       </c>
       <c r="B620" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C620" t="s">
         <v>1205</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11522,10 +11523,10 @@
         <v>685</v>
       </c>
       <c r="B621" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C621" t="s">
         <v>1207</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11533,10 +11534,10 @@
         <v>686</v>
       </c>
       <c r="B622" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C622" t="s">
         <v>1209</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11544,10 +11545,10 @@
         <v>689</v>
       </c>
       <c r="B623" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C623" t="s">
         <v>1211</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11555,10 +11556,10 @@
         <v>697</v>
       </c>
       <c r="B624" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C624" t="s">
         <v>1213</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11566,10 +11567,10 @@
         <v>701</v>
       </c>
       <c r="B625" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C625" t="s">
         <v>1215</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11577,10 +11578,10 @@
         <v>702</v>
       </c>
       <c r="B626" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C626" t="s">
         <v>1217</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11588,10 +11589,10 @@
         <v>704</v>
       </c>
       <c r="B627" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C627" t="s">
         <v>1219</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11599,10 +11600,10 @@
         <v>705</v>
       </c>
       <c r="B628" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C628" t="s">
         <v>1221</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11610,10 +11611,10 @@
         <v>710</v>
       </c>
       <c r="B629" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C629" t="s">
         <v>1223</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11621,10 +11622,10 @@
         <v>711</v>
       </c>
       <c r="B630" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C630" t="s">
         <v>1225</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11632,10 +11633,10 @@
         <v>712</v>
       </c>
       <c r="B631" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C631" t="s">
         <v>1227</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11643,10 +11644,10 @@
         <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11654,10 +11655,10 @@
         <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11665,10 +11666,10 @@
         <v>718</v>
       </c>
       <c r="B634" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C634" t="s">
         <v>1231</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11676,10 +11677,10 @@
         <v>719</v>
       </c>
       <c r="B635" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C635" t="s">
         <v>1233</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11687,10 +11688,10 @@
         <v>721</v>
       </c>
       <c r="B636" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C636" t="s">
         <v>1235</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11698,10 +11699,10 @@
         <v>722</v>
       </c>
       <c r="B637" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C637" t="s">
         <v>1237</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11709,10 +11710,10 @@
         <v>723</v>
       </c>
       <c r="B638" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C638" t="s">
         <v>1239</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11720,7 +11721,7 @@
         <v>724</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11728,10 +11729,10 @@
         <v>725</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C640" t="s">
         <v>1241</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11739,10 +11740,10 @@
         <v>726</v>
       </c>
       <c r="B641" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C641" t="s">
         <v>1243</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11750,10 +11751,10 @@
         <v>727</v>
       </c>
       <c r="B642" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C642" t="s">
         <v>1245</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11761,10 +11762,10 @@
         <v>728</v>
       </c>
       <c r="B643" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C643" t="s">
         <v>1247</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11772,10 +11773,10 @@
         <v>729</v>
       </c>
       <c r="B644" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C644" t="s">
         <v>1249</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11783,10 +11784,10 @@
         <v>730</v>
       </c>
       <c r="B645" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C645" t="s">
         <v>1251</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11794,10 +11795,10 @@
         <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11805,10 +11806,10 @@
         <v>733</v>
       </c>
       <c r="B647" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C647" t="s">
         <v>1254</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11816,10 +11817,10 @@
         <v>735</v>
       </c>
       <c r="B648" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C648" t="s">
         <v>1256</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11827,10 +11828,10 @@
         <v>736</v>
       </c>
       <c r="B649" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C649" t="s">
         <v>1258</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11838,10 +11839,10 @@
         <v>737</v>
       </c>
       <c r="B650" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C650" t="s">
         <v>1260</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11849,10 +11850,10 @@
         <v>738</v>
       </c>
       <c r="B651" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C651" t="s">
         <v>1262</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11860,10 +11861,10 @@
         <v>739</v>
       </c>
       <c r="B652" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C652" t="s">
         <v>1264</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11871,10 +11872,10 @@
         <v>740</v>
       </c>
       <c r="B653" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C653" t="s">
         <v>1266</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11882,10 +11883,10 @@
         <v>741</v>
       </c>
       <c r="B654" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C654" t="s">
         <v>1268</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11893,10 +11894,10 @@
         <v>742</v>
       </c>
       <c r="B655" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C655" t="s">
         <v>1270</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11904,10 +11905,10 @@
         <v>743</v>
       </c>
       <c r="B656" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C656" t="s">
         <v>1272</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11915,10 +11916,10 @@
         <v>744</v>
       </c>
       <c r="B657" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C657" t="s">
         <v>1274</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11926,10 +11927,10 @@
         <v>745</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C658" t="s">
         <v>1276</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11937,10 +11938,10 @@
         <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C659" t="s">
         <v>1278</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11948,10 +11949,10 @@
         <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C660" t="s">
         <v>1280</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11959,10 +11960,10 @@
         <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C661" t="s">
         <v>1282</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11970,10 +11971,10 @@
         <v>749</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C662" t="s">
         <v>1284</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11982,7 +11983,7 @@
       </c>
       <c r="B663" s="1"/>
       <c r="C663" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11990,10 +11991,10 @@
         <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C664" t="s">
         <v>1286</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -12001,10 +12002,10 @@
         <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12012,10 +12013,10 @@
         <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C666" t="s">
         <v>1289</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12023,10 +12024,10 @@
         <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C667" t="s">
         <v>1291</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12034,10 +12035,10 @@
         <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C668" t="s">
         <v>1293</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12045,10 +12046,10 @@
         <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12056,10 +12057,10 @@
         <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C670" t="s">
         <v>1296</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12067,10 +12068,10 @@
         <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C671" t="s">
         <v>1298</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12078,10 +12079,10 @@
         <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C672" t="s">
         <v>1300</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12089,10 +12090,10 @@
         <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C673" t="s">
         <v>1302</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -12100,10 +12101,10 @@
         <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C674" t="s">
         <v>1304</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12111,10 +12112,10 @@
         <v>765</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C675" t="s">
         <v>1306</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12128,10 +12129,10 @@
         <v>767</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C677" t="s">
         <v>1308</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12140,7 +12141,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12148,10 +12149,10 @@
         <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C679" t="s">
         <v>1311</v>
-      </c>
-      <c r="C679" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12159,10 +12160,10 @@
         <v>772</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C680" s="3" t="s">
         <v>1316</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12171,7 +12172,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12180,7 +12181,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12189,7 +12190,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12198,7 +12199,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12207,7 +12208,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12216,7 +12217,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12225,7 +12226,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -12234,7 +12235,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
@@ -12243,7 +12244,7 @@
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -12251,10 +12252,10 @@
         <v>10001</v>
       </c>
       <c r="B690" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
@@ -12262,10 +12263,10 @@
         <v>10003</v>
       </c>
       <c r="B691" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C691" t="s">
         <v>1311</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1312</v>
       </c>
     </row>
   </sheetData>
@@ -12273,7 +12274,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA137AAE-FE2F-4AB2-BCE3-087BCF2FAAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D346E4-3EEA-4958-A602-D42EA28B5271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24480" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4155" yWindow="2010" windowWidth="24855" windowHeight="10020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -1058,9 +1058,6 @@
     <t>Ringing Bloom</t>
   </si>
   <si>
-    <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花,00开花,00 开花</t>
-  </si>
-  <si>
     <t>Baby Sweet Berry Love</t>
   </si>
   <si>
@@ -4289,6 +4286,10 @@
   </si>
   <si>
     <t>彩千圣,情歌对唱,摇摇曳曳圆舞曲,摇曳摇曳圆舞曲</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花,00开花,00 开花,磷磷开花,ringring bloom,rinrin bloom,rin rin bomm,ring ring boom</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5343,7 +5344,7 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -5959,7 +5960,7 @@
         <v>224</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -6146,7 +6147,7 @@
         <v>257</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -6552,8 +6553,8 @@
       <c r="B167" t="s">
         <v>330</v>
       </c>
-      <c r="C167" t="s">
-        <v>331</v>
+      <c r="C167" s="3" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6561,10 +6562,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
+        <v>331</v>
+      </c>
+      <c r="C168" t="s">
         <v>332</v>
-      </c>
-      <c r="C168" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -6572,10 +6573,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
+        <v>333</v>
+      </c>
+      <c r="C169" t="s">
         <v>334</v>
-      </c>
-      <c r="C169" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -6583,10 +6584,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
+        <v>335</v>
+      </c>
+      <c r="C170" t="s">
         <v>336</v>
-      </c>
-      <c r="C170" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -6594,10 +6595,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
+        <v>337</v>
+      </c>
+      <c r="C171" t="s">
         <v>338</v>
-      </c>
-      <c r="C171" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -6605,10 +6606,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
+        <v>339</v>
+      </c>
+      <c r="C172" t="s">
         <v>340</v>
-      </c>
-      <c r="C172" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -6616,10 +6617,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
+        <v>341</v>
+      </c>
+      <c r="C173" t="s">
         <v>342</v>
-      </c>
-      <c r="C173" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -6627,10 +6628,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
+        <v>343</v>
+      </c>
+      <c r="C174" t="s">
         <v>344</v>
-      </c>
-      <c r="C174" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -6638,10 +6639,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
+        <v>345</v>
+      </c>
+      <c r="C175" t="s">
         <v>346</v>
-      </c>
-      <c r="C175" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -6649,10 +6650,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
+        <v>347</v>
+      </c>
+      <c r="C176" t="s">
         <v>348</v>
-      </c>
-      <c r="C176" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -6660,10 +6661,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
+        <v>349</v>
+      </c>
+      <c r="C177" t="s">
         <v>350</v>
-      </c>
-      <c r="C177" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -6671,10 +6672,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
+        <v>351</v>
+      </c>
+      <c r="C178" t="s">
         <v>352</v>
-      </c>
-      <c r="C178" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -6682,10 +6683,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
+        <v>353</v>
+      </c>
+      <c r="C179" t="s">
         <v>354</v>
-      </c>
-      <c r="C179" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -6693,10 +6694,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
+        <v>355</v>
+      </c>
+      <c r="C180" t="s">
         <v>356</v>
-      </c>
-      <c r="C180" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -6704,10 +6705,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
+        <v>357</v>
+      </c>
+      <c r="C181" t="s">
         <v>358</v>
-      </c>
-      <c r="C181" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -6715,10 +6716,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>359</v>
+      </c>
+      <c r="C182" t="s">
         <v>360</v>
-      </c>
-      <c r="C182" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -6726,10 +6727,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
+        <v>361</v>
+      </c>
+      <c r="C183" t="s">
         <v>362</v>
-      </c>
-      <c r="C183" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -6737,10 +6738,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>363</v>
+      </c>
+      <c r="C184" t="s">
         <v>364</v>
-      </c>
-      <c r="C184" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -6748,10 +6749,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
+        <v>365</v>
+      </c>
+      <c r="C185" t="s">
         <v>366</v>
-      </c>
-      <c r="C185" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -6759,10 +6760,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
+        <v>367</v>
+      </c>
+      <c r="C186" t="s">
         <v>368</v>
-      </c>
-      <c r="C186" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -6770,10 +6771,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
+        <v>369</v>
+      </c>
+      <c r="C187" t="s">
         <v>370</v>
-      </c>
-      <c r="C187" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -6781,10 +6782,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
+        <v>371</v>
+      </c>
+      <c r="C188" t="s">
         <v>372</v>
-      </c>
-      <c r="C188" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -6792,10 +6793,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
+        <v>373</v>
+      </c>
+      <c r="C189" t="s">
         <v>374</v>
-      </c>
-      <c r="C189" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -6803,10 +6804,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
+        <v>375</v>
+      </c>
+      <c r="C190" t="s">
         <v>376</v>
-      </c>
-      <c r="C190" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -6814,10 +6815,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
+        <v>377</v>
+      </c>
+      <c r="C191" t="s">
         <v>378</v>
-      </c>
-      <c r="C191" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -6825,10 +6826,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
+        <v>379</v>
+      </c>
+      <c r="C192" t="s">
         <v>380</v>
-      </c>
-      <c r="C192" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -6836,10 +6837,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>381</v>
+      </c>
+      <c r="C193" t="s">
         <v>382</v>
-      </c>
-      <c r="C193" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -6847,10 +6848,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
+        <v>383</v>
+      </c>
+      <c r="C194" t="s">
         <v>384</v>
-      </c>
-      <c r="C194" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -6858,10 +6859,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
+        <v>385</v>
+      </c>
+      <c r="C195" t="s">
         <v>386</v>
-      </c>
-      <c r="C195" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -6869,10 +6870,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
+        <v>387</v>
+      </c>
+      <c r="C196" t="s">
         <v>388</v>
-      </c>
-      <c r="C196" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -6880,10 +6881,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
+        <v>389</v>
+      </c>
+      <c r="C197" t="s">
         <v>390</v>
-      </c>
-      <c r="C197" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -6891,10 +6892,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
+        <v>391</v>
+      </c>
+      <c r="C198" t="s">
         <v>392</v>
-      </c>
-      <c r="C198" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -6902,10 +6903,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
+        <v>393</v>
+      </c>
+      <c r="C199" t="s">
         <v>394</v>
-      </c>
-      <c r="C199" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -6913,10 +6914,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
+        <v>395</v>
+      </c>
+      <c r="C200" t="s">
         <v>396</v>
-      </c>
-      <c r="C200" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -6924,10 +6925,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
+        <v>397</v>
+      </c>
+      <c r="C201" t="s">
         <v>398</v>
-      </c>
-      <c r="C201" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -6935,10 +6936,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
+        <v>399</v>
+      </c>
+      <c r="C202" t="s">
         <v>400</v>
-      </c>
-      <c r="C202" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -6946,10 +6947,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
+        <v>401</v>
+      </c>
+      <c r="C203" t="s">
         <v>402</v>
-      </c>
-      <c r="C203" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -6957,10 +6958,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
+        <v>403</v>
+      </c>
+      <c r="C204" t="s">
         <v>404</v>
-      </c>
-      <c r="C204" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -6968,10 +6969,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
+        <v>405</v>
+      </c>
+      <c r="C205" t="s">
         <v>406</v>
-      </c>
-      <c r="C205" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -6979,10 +6980,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
+        <v>407</v>
+      </c>
+      <c r="C206" t="s">
         <v>408</v>
-      </c>
-      <c r="C206" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -6990,10 +6991,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
+        <v>409</v>
+      </c>
+      <c r="C207" t="s">
         <v>410</v>
-      </c>
-      <c r="C207" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -7001,10 +7002,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
+        <v>411</v>
+      </c>
+      <c r="C208" t="s">
         <v>412</v>
-      </c>
-      <c r="C208" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7012,10 +7013,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
+        <v>413</v>
+      </c>
+      <c r="C209" t="s">
         <v>414</v>
-      </c>
-      <c r="C209" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -7023,10 +7024,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
+        <v>415</v>
+      </c>
+      <c r="C210" t="s">
         <v>416</v>
-      </c>
-      <c r="C210" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -7034,10 +7035,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
+        <v>417</v>
+      </c>
+      <c r="C211" t="s">
         <v>418</v>
-      </c>
-      <c r="C211" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -7045,10 +7046,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
+        <v>419</v>
+      </c>
+      <c r="C212" t="s">
         <v>420</v>
-      </c>
-      <c r="C212" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -7056,10 +7057,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
+        <v>421</v>
+      </c>
+      <c r="C213" t="s">
         <v>422</v>
-      </c>
-      <c r="C213" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -7067,10 +7068,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
+        <v>423</v>
+      </c>
+      <c r="C214" t="s">
         <v>424</v>
-      </c>
-      <c r="C214" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -7078,10 +7079,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
+        <v>425</v>
+      </c>
+      <c r="C215" t="s">
         <v>426</v>
-      </c>
-      <c r="C215" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -7089,10 +7090,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
+        <v>427</v>
+      </c>
+      <c r="C216" t="s">
         <v>428</v>
-      </c>
-      <c r="C216" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -7100,10 +7101,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
+        <v>429</v>
+      </c>
+      <c r="C217" t="s">
         <v>430</v>
-      </c>
-      <c r="C217" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -7111,10 +7112,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
+        <v>431</v>
+      </c>
+      <c r="C218" t="s">
         <v>432</v>
-      </c>
-      <c r="C218" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -7122,10 +7123,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
+        <v>433</v>
+      </c>
+      <c r="C219" t="s">
         <v>434</v>
-      </c>
-      <c r="C219" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -7133,10 +7134,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
+        <v>435</v>
+      </c>
+      <c r="C220" t="s">
         <v>436</v>
-      </c>
-      <c r="C220" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -7144,10 +7145,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
+        <v>437</v>
+      </c>
+      <c r="C221" t="s">
         <v>438</v>
-      </c>
-      <c r="C221" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -7155,10 +7156,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
+        <v>439</v>
+      </c>
+      <c r="C222" t="s">
         <v>440</v>
-      </c>
-      <c r="C222" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -7166,10 +7167,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
+        <v>441</v>
+      </c>
+      <c r="C223" t="s">
         <v>442</v>
-      </c>
-      <c r="C223" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -7177,10 +7178,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7188,10 +7189,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>444</v>
+      </c>
+      <c r="C225" t="s">
         <v>445</v>
-      </c>
-      <c r="C225" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -7199,10 +7200,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>446</v>
+      </c>
+      <c r="C226" t="s">
         <v>447</v>
-      </c>
-      <c r="C226" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -7210,10 +7211,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>448</v>
+      </c>
+      <c r="C227" t="s">
         <v>449</v>
-      </c>
-      <c r="C227" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -7221,10 +7222,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>450</v>
+      </c>
+      <c r="C228" t="s">
         <v>451</v>
-      </c>
-      <c r="C228" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -7232,10 +7233,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
+        <v>452</v>
+      </c>
+      <c r="C229" t="s">
         <v>453</v>
-      </c>
-      <c r="C229" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7243,10 +7244,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
+        <v>454</v>
+      </c>
+      <c r="C230" t="s">
         <v>455</v>
-      </c>
-      <c r="C230" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7254,10 +7255,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>456</v>
+      </c>
+      <c r="C231" t="s">
         <v>457</v>
-      </c>
-      <c r="C231" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -7265,10 +7266,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>458</v>
+      </c>
+      <c r="C232" t="s">
         <v>459</v>
-      </c>
-      <c r="C232" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -7276,10 +7277,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>460</v>
+      </c>
+      <c r="C233" t="s">
         <v>461</v>
-      </c>
-      <c r="C233" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -7287,10 +7288,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
+        <v>462</v>
+      </c>
+      <c r="C234" t="s">
         <v>463</v>
-      </c>
-      <c r="C234" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7298,10 +7299,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>464</v>
+      </c>
+      <c r="C235" t="s">
         <v>465</v>
-      </c>
-      <c r="C235" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -7309,10 +7310,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>466</v>
+      </c>
+      <c r="C236" t="s">
         <v>467</v>
-      </c>
-      <c r="C236" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -7320,10 +7321,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>468</v>
+      </c>
+      <c r="C237" t="s">
         <v>469</v>
-      </c>
-      <c r="C237" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -7331,10 +7332,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>470</v>
+      </c>
+      <c r="C238" t="s">
         <v>471</v>
-      </c>
-      <c r="C238" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -7342,10 +7343,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>472</v>
+      </c>
+      <c r="C239" t="s">
         <v>473</v>
-      </c>
-      <c r="C239" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -7353,10 +7354,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>474</v>
+      </c>
+      <c r="C240" t="s">
         <v>475</v>
-      </c>
-      <c r="C240" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -7364,10 +7365,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>476</v>
+      </c>
+      <c r="C241" t="s">
         <v>477</v>
-      </c>
-      <c r="C241" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -7375,10 +7376,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>478</v>
+      </c>
+      <c r="C242" t="s">
         <v>479</v>
-      </c>
-      <c r="C242" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -7386,10 +7387,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>480</v>
+      </c>
+      <c r="C243" t="s">
         <v>481</v>
-      </c>
-      <c r="C243" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -7397,10 +7398,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>482</v>
+      </c>
+      <c r="C244" t="s">
         <v>483</v>
-      </c>
-      <c r="C244" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -7408,10 +7409,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>484</v>
+      </c>
+      <c r="C245" t="s">
         <v>485</v>
-      </c>
-      <c r="C245" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -7419,10 +7420,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>486</v>
+      </c>
+      <c r="C246" t="s">
         <v>487</v>
-      </c>
-      <c r="C246" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -7430,10 +7431,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>488</v>
+      </c>
+      <c r="C247" t="s">
         <v>489</v>
-      </c>
-      <c r="C247" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -7441,10 +7442,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>490</v>
+      </c>
+      <c r="C248" t="s">
         <v>491</v>
-      </c>
-      <c r="C248" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -7452,10 +7453,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>492</v>
+      </c>
+      <c r="C249" t="s">
         <v>493</v>
-      </c>
-      <c r="C249" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -7463,10 +7464,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
+        <v>494</v>
+      </c>
+      <c r="C250" t="s">
         <v>495</v>
-      </c>
-      <c r="C250" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7474,10 +7475,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7485,10 +7486,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C252" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7496,10 +7497,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>498</v>
+      </c>
+      <c r="C253" t="s">
         <v>499</v>
-      </c>
-      <c r="C253" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7507,10 +7508,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
+        <v>500</v>
+      </c>
+      <c r="C254" t="s">
         <v>501</v>
-      </c>
-      <c r="C254" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7518,10 +7519,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>502</v>
+      </c>
+      <c r="C255" t="s">
         <v>503</v>
-      </c>
-      <c r="C255" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7529,10 +7530,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>504</v>
+      </c>
+      <c r="C256" t="s">
         <v>505</v>
-      </c>
-      <c r="C256" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7540,10 +7541,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>506</v>
+      </c>
+      <c r="C257" t="s">
         <v>507</v>
-      </c>
-      <c r="C257" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7551,10 +7552,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>508</v>
+      </c>
+      <c r="C258" t="s">
         <v>509</v>
-      </c>
-      <c r="C258" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7562,10 +7563,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>510</v>
+      </c>
+      <c r="C259" t="s">
         <v>511</v>
-      </c>
-      <c r="C259" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7573,10 +7574,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>512</v>
+      </c>
+      <c r="C260" t="s">
         <v>513</v>
-      </c>
-      <c r="C260" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7584,10 +7585,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>514</v>
+      </c>
+      <c r="C261" t="s">
         <v>515</v>
-      </c>
-      <c r="C261" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7595,10 +7596,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>516</v>
+      </c>
+      <c r="C262" t="s">
         <v>517</v>
-      </c>
-      <c r="C262" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7606,10 +7607,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>518</v>
+      </c>
+      <c r="C263" t="s">
         <v>519</v>
-      </c>
-      <c r="C263" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7617,10 +7618,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>520</v>
+      </c>
+      <c r="C264" t="s">
         <v>521</v>
-      </c>
-      <c r="C264" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7628,10 +7629,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>522</v>
+      </c>
+      <c r="C265" t="s">
         <v>523</v>
-      </c>
-      <c r="C265" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7639,10 +7640,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>524</v>
+      </c>
+      <c r="C266" t="s">
         <v>525</v>
-      </c>
-      <c r="C266" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7650,10 +7651,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>526</v>
+      </c>
+      <c r="C267" t="s">
         <v>527</v>
-      </c>
-      <c r="C267" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7661,10 +7662,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>528</v>
+      </c>
+      <c r="C268" t="s">
         <v>529</v>
-      </c>
-      <c r="C268" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7672,10 +7673,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>530</v>
+      </c>
+      <c r="C269" t="s">
         <v>531</v>
-      </c>
-      <c r="C269" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7683,10 +7684,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>532</v>
+      </c>
+      <c r="C270" t="s">
         <v>533</v>
-      </c>
-      <c r="C270" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7694,10 +7695,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7705,10 +7706,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>535</v>
+      </c>
+      <c r="C272" t="s">
         <v>536</v>
-      </c>
-      <c r="C272" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7716,10 +7717,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>537</v>
+      </c>
+      <c r="C273" t="s">
         <v>538</v>
-      </c>
-      <c r="C273" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7727,10 +7728,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>539</v>
+      </c>
+      <c r="C274" t="s">
         <v>540</v>
-      </c>
-      <c r="C274" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7738,10 +7739,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>541</v>
+      </c>
+      <c r="C275" t="s">
         <v>542</v>
-      </c>
-      <c r="C275" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7749,10 +7750,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>543</v>
+      </c>
+      <c r="C276" t="s">
         <v>544</v>
-      </c>
-      <c r="C276" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7760,10 +7761,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>545</v>
+      </c>
+      <c r="C277" t="s">
         <v>546</v>
-      </c>
-      <c r="C277" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7771,10 +7772,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>547</v>
+      </c>
+      <c r="C278" t="s">
         <v>548</v>
-      </c>
-      <c r="C278" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7782,10 +7783,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>549</v>
+      </c>
+      <c r="C279" t="s">
         <v>550</v>
-      </c>
-      <c r="C279" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7793,10 +7794,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>551</v>
+      </c>
+      <c r="C280" t="s">
         <v>552</v>
-      </c>
-      <c r="C280" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7804,10 +7805,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>553</v>
+      </c>
+      <c r="C281" t="s">
         <v>554</v>
-      </c>
-      <c r="C281" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -7815,10 +7816,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>555</v>
+      </c>
+      <c r="C282" t="s">
         <v>556</v>
-      </c>
-      <c r="C282" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -7826,10 +7827,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>557</v>
+      </c>
+      <c r="C283" t="s">
         <v>558</v>
-      </c>
-      <c r="C283" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -7837,10 +7838,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>559</v>
+      </c>
+      <c r="C284" t="s">
         <v>560</v>
-      </c>
-      <c r="C284" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -7848,10 +7849,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>561</v>
+      </c>
+      <c r="C285" t="s">
         <v>562</v>
-      </c>
-      <c r="C285" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -7859,10 +7860,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>563</v>
+      </c>
+      <c r="C286" t="s">
         <v>564</v>
-      </c>
-      <c r="C286" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7870,10 +7871,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>565</v>
+      </c>
+      <c r="C287" t="s">
         <v>566</v>
-      </c>
-      <c r="C287" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -7881,10 +7882,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>567</v>
+      </c>
+      <c r="C288" t="s">
         <v>568</v>
-      </c>
-      <c r="C288" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -7892,10 +7893,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>569</v>
+      </c>
+      <c r="C289" t="s">
         <v>570</v>
-      </c>
-      <c r="C289" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -7903,10 +7904,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>571</v>
+      </c>
+      <c r="C290" t="s">
         <v>572</v>
-      </c>
-      <c r="C290" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -7914,10 +7915,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>573</v>
+      </c>
+      <c r="C291" t="s">
         <v>574</v>
-      </c>
-      <c r="C291" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -7925,10 +7926,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>575</v>
+      </c>
+      <c r="C292" t="s">
         <v>576</v>
-      </c>
-      <c r="C292" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -7936,10 +7937,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>577</v>
+      </c>
+      <c r="C293" t="s">
         <v>578</v>
-      </c>
-      <c r="C293" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -7947,10 +7948,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>579</v>
+      </c>
+      <c r="C294" t="s">
         <v>580</v>
-      </c>
-      <c r="C294" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -7958,10 +7959,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>581</v>
+      </c>
+      <c r="C295" t="s">
         <v>582</v>
-      </c>
-      <c r="C295" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -7969,10 +7970,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -7980,10 +7981,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>584</v>
+      </c>
+      <c r="C297" t="s">
         <v>585</v>
-      </c>
-      <c r="C297" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -7991,10 +7992,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>586</v>
+      </c>
+      <c r="C298" t="s">
         <v>587</v>
-      </c>
-      <c r="C298" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -8002,10 +8003,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>588</v>
+      </c>
+      <c r="C299" t="s">
         <v>589</v>
-      </c>
-      <c r="C299" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -8013,10 +8014,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>590</v>
+      </c>
+      <c r="C300" t="s">
         <v>591</v>
-      </c>
-      <c r="C300" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -8024,10 +8025,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>592</v>
+      </c>
+      <c r="C301" t="s">
         <v>593</v>
-      </c>
-      <c r="C301" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8035,10 +8036,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>594</v>
+      </c>
+      <c r="C302" t="s">
         <v>595</v>
-      </c>
-      <c r="C302" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8046,10 +8047,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>596</v>
+      </c>
+      <c r="C303" t="s">
         <v>597</v>
-      </c>
-      <c r="C303" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8057,10 +8058,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>598</v>
+      </c>
+      <c r="C304" t="s">
         <v>599</v>
-      </c>
-      <c r="C304" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8068,10 +8069,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>600</v>
+      </c>
+      <c r="C305" t="s">
         <v>601</v>
-      </c>
-      <c r="C305" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8079,10 +8080,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>602</v>
+      </c>
+      <c r="C306" t="s">
         <v>603</v>
-      </c>
-      <c r="C306" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8090,10 +8091,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>604</v>
+      </c>
+      <c r="C307" t="s">
         <v>605</v>
-      </c>
-      <c r="C307" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8101,10 +8102,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>606</v>
+      </c>
+      <c r="C308" t="s">
         <v>607</v>
-      </c>
-      <c r="C308" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8112,10 +8113,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>608</v>
+      </c>
+      <c r="C309" t="s">
         <v>609</v>
-      </c>
-      <c r="C309" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8123,10 +8124,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>610</v>
+      </c>
+      <c r="C310" t="s">
         <v>611</v>
-      </c>
-      <c r="C310" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8134,10 +8135,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>612</v>
+      </c>
+      <c r="C311" t="s">
         <v>613</v>
-      </c>
-      <c r="C311" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8145,10 +8146,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>614</v>
+      </c>
+      <c r="C312" t="s">
         <v>615</v>
-      </c>
-      <c r="C312" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8156,10 +8157,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>616</v>
+      </c>
+      <c r="C313" t="s">
         <v>617</v>
-      </c>
-      <c r="C313" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8167,10 +8168,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>618</v>
+      </c>
+      <c r="C314" t="s">
         <v>619</v>
-      </c>
-      <c r="C314" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8178,10 +8179,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>620</v>
+      </c>
+      <c r="C315" t="s">
         <v>621</v>
-      </c>
-      <c r="C315" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8189,10 +8190,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>622</v>
+      </c>
+      <c r="C316" t="s">
         <v>623</v>
-      </c>
-      <c r="C316" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8200,10 +8201,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>624</v>
+      </c>
+      <c r="C317" t="s">
         <v>625</v>
-      </c>
-      <c r="C317" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8211,10 +8212,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>626</v>
+      </c>
+      <c r="C318" t="s">
         <v>627</v>
-      </c>
-      <c r="C318" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8222,10 +8223,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>628</v>
+      </c>
+      <c r="C319" t="s">
         <v>629</v>
-      </c>
-      <c r="C319" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8233,10 +8234,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>630</v>
+      </c>
+      <c r="C320" t="s">
         <v>631</v>
-      </c>
-      <c r="C320" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8244,10 +8245,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>632</v>
+      </c>
+      <c r="C321" t="s">
         <v>633</v>
-      </c>
-      <c r="C321" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8255,10 +8256,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>634</v>
+      </c>
+      <c r="C322" t="s">
         <v>635</v>
-      </c>
-      <c r="C322" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8266,10 +8267,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>636</v>
+      </c>
+      <c r="C323" t="s">
         <v>637</v>
-      </c>
-      <c r="C323" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8277,10 +8278,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>638</v>
+      </c>
+      <c r="C324" t="s">
         <v>639</v>
-      </c>
-      <c r="C324" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8288,10 +8289,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>640</v>
+      </c>
+      <c r="C325" t="s">
         <v>641</v>
-      </c>
-      <c r="C325" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8299,10 +8300,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>642</v>
+      </c>
+      <c r="C326" t="s">
         <v>643</v>
-      </c>
-      <c r="C326" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8310,10 +8311,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>644</v>
+      </c>
+      <c r="C327" t="s">
         <v>645</v>
-      </c>
-      <c r="C327" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8321,10 +8322,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>646</v>
+      </c>
+      <c r="C328" t="s">
         <v>647</v>
-      </c>
-      <c r="C328" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8332,10 +8333,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>648</v>
+      </c>
+      <c r="C329" t="s">
         <v>649</v>
-      </c>
-      <c r="C329" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8343,10 +8344,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>650</v>
+      </c>
+      <c r="C330" t="s">
         <v>651</v>
-      </c>
-      <c r="C330" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8354,10 +8355,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>652</v>
+      </c>
+      <c r="C331" t="s">
         <v>653</v>
-      </c>
-      <c r="C331" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8365,10 +8366,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>654</v>
+      </c>
+      <c r="C332" t="s">
         <v>655</v>
-      </c>
-      <c r="C332" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8376,10 +8377,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>656</v>
+      </c>
+      <c r="C333" t="s">
         <v>657</v>
-      </c>
-      <c r="C333" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8387,10 +8388,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>658</v>
+      </c>
+      <c r="C334" t="s">
         <v>659</v>
-      </c>
-      <c r="C334" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8398,10 +8399,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>660</v>
+      </c>
+      <c r="C335" t="s">
         <v>661</v>
-      </c>
-      <c r="C335" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8409,10 +8410,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>662</v>
+      </c>
+      <c r="C336" t="s">
         <v>663</v>
-      </c>
-      <c r="C336" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8420,10 +8421,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>664</v>
+      </c>
+      <c r="C337" t="s">
         <v>665</v>
-      </c>
-      <c r="C337" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8431,10 +8432,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8442,10 +8443,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8453,10 +8454,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>668</v>
+      </c>
+      <c r="C340" t="s">
         <v>669</v>
-      </c>
-      <c r="C340" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8464,10 +8465,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>670</v>
+      </c>
+      <c r="C341" t="s">
         <v>671</v>
-      </c>
-      <c r="C341" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8475,10 +8476,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>672</v>
+      </c>
+      <c r="C342" t="s">
         <v>673</v>
-      </c>
-      <c r="C342" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8486,10 +8487,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>674</v>
+      </c>
+      <c r="C343" t="s">
         <v>675</v>
-      </c>
-      <c r="C343" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8497,10 +8498,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>676</v>
+      </c>
+      <c r="C344" t="s">
         <v>677</v>
-      </c>
-      <c r="C344" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8508,10 +8509,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>678</v>
+      </c>
+      <c r="C345" t="s">
         <v>679</v>
-      </c>
-      <c r="C345" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8519,10 +8520,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>680</v>
+      </c>
+      <c r="C346" t="s">
         <v>681</v>
-      </c>
-      <c r="C346" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8530,10 +8531,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>682</v>
+      </c>
+      <c r="C347" t="s">
         <v>683</v>
-      </c>
-      <c r="C347" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8541,10 +8542,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>684</v>
+      </c>
+      <c r="C348" t="s">
         <v>685</v>
-      </c>
-      <c r="C348" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8552,10 +8553,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>686</v>
+      </c>
+      <c r="C349" t="s">
         <v>687</v>
-      </c>
-      <c r="C349" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8563,10 +8564,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>688</v>
+      </c>
+      <c r="C350" t="s">
         <v>689</v>
-      </c>
-      <c r="C350" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8574,10 +8575,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>690</v>
+      </c>
+      <c r="C351" t="s">
         <v>691</v>
-      </c>
-      <c r="C351" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8585,10 +8586,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>692</v>
+      </c>
+      <c r="C352" t="s">
         <v>693</v>
-      </c>
-      <c r="C352" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8596,10 +8597,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>694</v>
+      </c>
+      <c r="C353" t="s">
         <v>695</v>
-      </c>
-      <c r="C353" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8607,10 +8608,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>696</v>
+      </c>
+      <c r="C354" t="s">
         <v>697</v>
-      </c>
-      <c r="C354" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8618,10 +8619,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>698</v>
+      </c>
+      <c r="C355" t="s">
         <v>699</v>
-      </c>
-      <c r="C355" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8629,10 +8630,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>700</v>
+      </c>
+      <c r="C356" t="s">
         <v>701</v>
-      </c>
-      <c r="C356" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8640,10 +8641,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>702</v>
+      </c>
+      <c r="C357" t="s">
         <v>703</v>
-      </c>
-      <c r="C357" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8651,10 +8652,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>704</v>
+      </c>
+      <c r="C358" t="s">
         <v>705</v>
-      </c>
-      <c r="C358" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8662,10 +8663,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>706</v>
+      </c>
+      <c r="C359" t="s">
         <v>707</v>
-      </c>
-      <c r="C359" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8673,10 +8674,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>708</v>
+      </c>
+      <c r="C360" t="s">
         <v>709</v>
-      </c>
-      <c r="C360" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8684,10 +8685,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>710</v>
+      </c>
+      <c r="C361" t="s">
         <v>711</v>
-      </c>
-      <c r="C361" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8695,10 +8696,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>712</v>
+      </c>
+      <c r="C362" t="s">
         <v>713</v>
-      </c>
-      <c r="C362" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8706,10 +8707,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>714</v>
+      </c>
+      <c r="C363" t="s">
         <v>715</v>
-      </c>
-      <c r="C363" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8717,10 +8718,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>716</v>
+      </c>
+      <c r="C364" t="s">
         <v>717</v>
-      </c>
-      <c r="C364" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8728,10 +8729,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>718</v>
+      </c>
+      <c r="C365" t="s">
         <v>719</v>
-      </c>
-      <c r="C365" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8739,10 +8740,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>720</v>
+      </c>
+      <c r="C366" t="s">
         <v>721</v>
-      </c>
-      <c r="C366" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8750,10 +8751,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>722</v>
+      </c>
+      <c r="C367" t="s">
         <v>723</v>
-      </c>
-      <c r="C367" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8761,10 +8762,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>724</v>
+      </c>
+      <c r="C368" t="s">
         <v>725</v>
-      </c>
-      <c r="C368" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8772,10 +8773,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>726</v>
+      </c>
+      <c r="C369" t="s">
         <v>727</v>
-      </c>
-      <c r="C369" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8783,10 +8784,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>728</v>
+      </c>
+      <c r="C370" t="s">
         <v>729</v>
-      </c>
-      <c r="C370" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -8794,10 +8795,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>730</v>
+      </c>
+      <c r="C371" t="s">
         <v>731</v>
-      </c>
-      <c r="C371" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -8805,10 +8806,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>732</v>
+      </c>
+      <c r="C372" t="s">
         <v>733</v>
-      </c>
-      <c r="C372" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -8816,10 +8817,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>734</v>
+      </c>
+      <c r="C373" t="s">
         <v>735</v>
-      </c>
-      <c r="C373" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -8827,10 +8828,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>736</v>
+      </c>
+      <c r="C374" t="s">
         <v>737</v>
-      </c>
-      <c r="C374" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8838,10 +8839,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>738</v>
+      </c>
+      <c r="C375" t="s">
         <v>739</v>
-      </c>
-      <c r="C375" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -8849,10 +8850,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>740</v>
+      </c>
+      <c r="C376" t="s">
         <v>741</v>
-      </c>
-      <c r="C376" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -8860,10 +8861,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>742</v>
+      </c>
+      <c r="C377" t="s">
         <v>743</v>
-      </c>
-      <c r="C377" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8871,10 +8872,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>744</v>
+      </c>
+      <c r="C378" t="s">
         <v>745</v>
-      </c>
-      <c r="C378" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -8882,10 +8883,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>746</v>
+      </c>
+      <c r="C379" t="s">
         <v>747</v>
-      </c>
-      <c r="C379" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8893,10 +8894,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>748</v>
+      </c>
+      <c r="C380" t="s">
         <v>749</v>
-      </c>
-      <c r="C380" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -8904,10 +8905,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>750</v>
+      </c>
+      <c r="C381" t="s">
         <v>751</v>
-      </c>
-      <c r="C381" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -8915,10 +8916,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>752</v>
+      </c>
+      <c r="C382" t="s">
         <v>753</v>
-      </c>
-      <c r="C382" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -8926,10 +8927,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>754</v>
+      </c>
+      <c r="C383" t="s">
         <v>755</v>
-      </c>
-      <c r="C383" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -8937,10 +8938,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>756</v>
+      </c>
+      <c r="C384" t="s">
         <v>757</v>
-      </c>
-      <c r="C384" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -8948,10 +8949,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>758</v>
+      </c>
+      <c r="C385" t="s">
         <v>759</v>
-      </c>
-      <c r="C385" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -8959,10 +8960,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>760</v>
+      </c>
+      <c r="C386" t="s">
         <v>761</v>
-      </c>
-      <c r="C386" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -8970,10 +8971,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>762</v>
+      </c>
+      <c r="C387" t="s">
         <v>763</v>
-      </c>
-      <c r="C387" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -8981,10 +8982,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>764</v>
+      </c>
+      <c r="C388" t="s">
         <v>765</v>
-      </c>
-      <c r="C388" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -8992,10 +8993,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>766</v>
+      </c>
+      <c r="C389" t="s">
         <v>767</v>
-      </c>
-      <c r="C389" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -9003,10 +9004,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>768</v>
+      </c>
+      <c r="C390" t="s">
         <v>769</v>
-      </c>
-      <c r="C390" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9014,10 +9015,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>770</v>
+      </c>
+      <c r="C391" t="s">
         <v>771</v>
-      </c>
-      <c r="C391" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9025,10 +9026,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>772</v>
+      </c>
+      <c r="C392" t="s">
         <v>773</v>
-      </c>
-      <c r="C392" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9036,10 +9037,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>774</v>
+      </c>
+      <c r="C393" t="s">
         <v>775</v>
-      </c>
-      <c r="C393" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9047,10 +9048,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>776</v>
+      </c>
+      <c r="C394" t="s">
         <v>777</v>
-      </c>
-      <c r="C394" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9058,10 +9059,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>778</v>
+      </c>
+      <c r="C395" t="s">
         <v>779</v>
-      </c>
-      <c r="C395" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9069,10 +9070,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>780</v>
+      </c>
+      <c r="C396" t="s">
         <v>781</v>
-      </c>
-      <c r="C396" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9080,10 +9081,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>782</v>
+      </c>
+      <c r="C397" t="s">
         <v>783</v>
-      </c>
-      <c r="C397" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9091,10 +9092,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>784</v>
+      </c>
+      <c r="C398" t="s">
         <v>785</v>
-      </c>
-      <c r="C398" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9102,10 +9103,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>786</v>
+      </c>
+      <c r="C399" t="s">
         <v>787</v>
-      </c>
-      <c r="C399" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9113,10 +9114,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>788</v>
+      </c>
+      <c r="C400" t="s">
         <v>789</v>
-      </c>
-      <c r="C400" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9124,10 +9125,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>790</v>
+      </c>
+      <c r="C401" t="s">
         <v>791</v>
-      </c>
-      <c r="C401" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9135,10 +9136,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>792</v>
+      </c>
+      <c r="C402" t="s">
         <v>793</v>
-      </c>
-      <c r="C402" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9146,10 +9147,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>794</v>
+      </c>
+      <c r="C403" t="s">
         <v>795</v>
-      </c>
-      <c r="C403" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9157,10 +9158,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>796</v>
+      </c>
+      <c r="C404" t="s">
         <v>797</v>
-      </c>
-      <c r="C404" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9168,10 +9169,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>798</v>
+      </c>
+      <c r="C405" t="s">
         <v>799</v>
-      </c>
-      <c r="C405" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9179,10 +9180,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>800</v>
+      </c>
+      <c r="C406" t="s">
         <v>801</v>
-      </c>
-      <c r="C406" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9190,10 +9191,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>802</v>
+      </c>
+      <c r="C407" t="s">
         <v>803</v>
-      </c>
-      <c r="C407" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9201,10 +9202,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>804</v>
+      </c>
+      <c r="C408" t="s">
         <v>805</v>
-      </c>
-      <c r="C408" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9212,10 +9213,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>806</v>
+      </c>
+      <c r="C409" t="s">
         <v>807</v>
-      </c>
-      <c r="C409" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9223,10 +9224,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>808</v>
+      </c>
+      <c r="C410" t="s">
         <v>809</v>
-      </c>
-      <c r="C410" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9234,10 +9235,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>810</v>
+      </c>
+      <c r="C411" t="s">
         <v>811</v>
-      </c>
-      <c r="C411" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9245,10 +9246,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>812</v>
+      </c>
+      <c r="C412" t="s">
         <v>813</v>
-      </c>
-      <c r="C412" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9256,10 +9257,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>814</v>
+      </c>
+      <c r="C413" t="s">
         <v>815</v>
-      </c>
-      <c r="C413" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9267,10 +9268,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>816</v>
+      </c>
+      <c r="C414" t="s">
         <v>817</v>
-      </c>
-      <c r="C414" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9278,10 +9279,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>818</v>
+      </c>
+      <c r="C415" t="s">
         <v>819</v>
-      </c>
-      <c r="C415" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9289,10 +9290,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>820</v>
+      </c>
+      <c r="C416" t="s">
         <v>821</v>
-      </c>
-      <c r="C416" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9300,10 +9301,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>822</v>
+      </c>
+      <c r="C417" t="s">
         <v>823</v>
-      </c>
-      <c r="C417" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9311,10 +9312,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>824</v>
+      </c>
+      <c r="C418" t="s">
         <v>825</v>
-      </c>
-      <c r="C418" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9322,10 +9323,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>826</v>
+      </c>
+      <c r="C419" t="s">
         <v>827</v>
-      </c>
-      <c r="C419" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9333,10 +9334,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>828</v>
+      </c>
+      <c r="C420" t="s">
         <v>829</v>
-      </c>
-      <c r="C420" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9344,10 +9345,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>830</v>
+      </c>
+      <c r="C421" t="s">
         <v>831</v>
-      </c>
-      <c r="C421" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9355,10 +9356,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>832</v>
+      </c>
+      <c r="C422" t="s">
         <v>833</v>
-      </c>
-      <c r="C422" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9366,10 +9367,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>834</v>
+      </c>
+      <c r="C423" t="s">
         <v>835</v>
-      </c>
-      <c r="C423" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9377,10 +9378,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>836</v>
+      </c>
+      <c r="C424" t="s">
         <v>837</v>
-      </c>
-      <c r="C424" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9388,10 +9389,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>838</v>
+      </c>
+      <c r="C425" t="s">
         <v>839</v>
-      </c>
-      <c r="C425" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9399,10 +9400,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>840</v>
+      </c>
+      <c r="C426" t="s">
         <v>841</v>
-      </c>
-      <c r="C426" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9410,10 +9411,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>842</v>
+      </c>
+      <c r="C427" t="s">
         <v>843</v>
-      </c>
-      <c r="C427" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9421,10 +9422,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C428" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9432,10 +9433,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C429" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9443,10 +9444,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>846</v>
+      </c>
+      <c r="C430" t="s">
         <v>847</v>
-      </c>
-      <c r="C430" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9454,10 +9455,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>848</v>
+      </c>
+      <c r="C431" t="s">
         <v>849</v>
-      </c>
-      <c r="C431" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9465,10 +9466,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>850</v>
+      </c>
+      <c r="C432" t="s">
         <v>851</v>
-      </c>
-      <c r="C432" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9476,10 +9477,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>852</v>
+      </c>
+      <c r="C433" t="s">
         <v>853</v>
-      </c>
-      <c r="C433" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9487,10 +9488,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>854</v>
+      </c>
+      <c r="C434" t="s">
         <v>855</v>
-      </c>
-      <c r="C434" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9498,10 +9499,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>856</v>
+      </c>
+      <c r="C435" t="s">
         <v>857</v>
-      </c>
-      <c r="C435" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9509,10 +9510,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>858</v>
+      </c>
+      <c r="C436" t="s">
         <v>859</v>
-      </c>
-      <c r="C436" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9520,10 +9521,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>860</v>
+      </c>
+      <c r="C437" t="s">
         <v>861</v>
-      </c>
-      <c r="C437" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9531,10 +9532,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>862</v>
+      </c>
+      <c r="C438" t="s">
         <v>863</v>
-      </c>
-      <c r="C438" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9542,10 +9543,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>864</v>
+      </c>
+      <c r="C439" t="s">
         <v>865</v>
-      </c>
-      <c r="C439" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9553,10 +9554,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>866</v>
+      </c>
+      <c r="C440" t="s">
         <v>867</v>
-      </c>
-      <c r="C440" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9564,10 +9565,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>868</v>
+      </c>
+      <c r="C441" t="s">
         <v>869</v>
-      </c>
-      <c r="C441" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9575,10 +9576,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>870</v>
+      </c>
+      <c r="C442" t="s">
         <v>871</v>
-      </c>
-      <c r="C442" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9586,10 +9587,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>872</v>
+      </c>
+      <c r="C443" t="s">
         <v>873</v>
-      </c>
-      <c r="C443" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9597,10 +9598,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>874</v>
+      </c>
+      <c r="C444" t="s">
         <v>875</v>
-      </c>
-      <c r="C444" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9608,10 +9609,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>876</v>
+      </c>
+      <c r="C445" t="s">
         <v>877</v>
-      </c>
-      <c r="C445" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9619,10 +9620,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>878</v>
+      </c>
+      <c r="C446" t="s">
         <v>879</v>
-      </c>
-      <c r="C446" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9630,10 +9631,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>880</v>
+      </c>
+      <c r="C447" t="s">
         <v>881</v>
-      </c>
-      <c r="C447" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9641,10 +9642,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>882</v>
+      </c>
+      <c r="C448" t="s">
         <v>883</v>
-      </c>
-      <c r="C448" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9652,10 +9653,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>884</v>
+      </c>
+      <c r="C449" t="s">
         <v>885</v>
-      </c>
-      <c r="C449" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9663,10 +9664,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>886</v>
+      </c>
+      <c r="C450" t="s">
         <v>887</v>
-      </c>
-      <c r="C450" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9674,10 +9675,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C451" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9685,10 +9686,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>889</v>
+      </c>
+      <c r="C452" t="s">
         <v>890</v>
-      </c>
-      <c r="C452" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9696,10 +9697,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>891</v>
+      </c>
+      <c r="C453" t="s">
         <v>892</v>
-      </c>
-      <c r="C453" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9707,10 +9708,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>893</v>
+      </c>
+      <c r="C454" t="s">
         <v>894</v>
-      </c>
-      <c r="C454" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9718,10 +9719,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>895</v>
+      </c>
+      <c r="C455" t="s">
         <v>896</v>
-      </c>
-      <c r="C455" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9729,10 +9730,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C456" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9740,10 +9741,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>898</v>
+      </c>
+      <c r="C457" t="s">
         <v>899</v>
-      </c>
-      <c r="C457" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9751,10 +9752,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>900</v>
+      </c>
+      <c r="C458" t="s">
         <v>901</v>
-      </c>
-      <c r="C458" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9762,10 +9763,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>902</v>
+      </c>
+      <c r="C459" t="s">
         <v>903</v>
-      </c>
-      <c r="C459" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9773,7 +9774,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9781,10 +9782,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>905</v>
+      </c>
+      <c r="C461" t="s">
         <v>906</v>
-      </c>
-      <c r="C461" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9792,10 +9793,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>907</v>
+      </c>
+      <c r="C462" t="s">
         <v>908</v>
-      </c>
-      <c r="C462" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9803,10 +9804,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>909</v>
+      </c>
+      <c r="C463" t="s">
         <v>910</v>
-      </c>
-      <c r="C463" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9814,10 +9815,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>911</v>
+      </c>
+      <c r="C464" t="s">
         <v>912</v>
-      </c>
-      <c r="C464" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9825,10 +9826,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>913</v>
+      </c>
+      <c r="C465" t="s">
         <v>914</v>
-      </c>
-      <c r="C465" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9836,10 +9837,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>915</v>
+      </c>
+      <c r="C466" t="s">
         <v>916</v>
-      </c>
-      <c r="C466" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9847,10 +9848,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9858,10 +9859,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>918</v>
+      </c>
+      <c r="C468" t="s">
         <v>919</v>
-      </c>
-      <c r="C468" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9869,10 +9870,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>920</v>
+      </c>
+      <c r="C469" t="s">
         <v>921</v>
-      </c>
-      <c r="C469" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9880,10 +9881,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>922</v>
+      </c>
+      <c r="C470" t="s">
         <v>923</v>
-      </c>
-      <c r="C470" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9891,10 +9892,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>924</v>
+      </c>
+      <c r="C471" t="s">
         <v>925</v>
-      </c>
-      <c r="C471" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9902,10 +9903,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>926</v>
+      </c>
+      <c r="C472" t="s">
         <v>927</v>
-      </c>
-      <c r="C472" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9913,10 +9914,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>928</v>
+      </c>
+      <c r="C473" t="s">
         <v>929</v>
-      </c>
-      <c r="C473" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9924,10 +9925,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>930</v>
+      </c>
+      <c r="C474" t="s">
         <v>931</v>
-      </c>
-      <c r="C474" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9935,10 +9936,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>932</v>
+      </c>
+      <c r="C475" t="s">
         <v>933</v>
-      </c>
-      <c r="C475" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9946,10 +9947,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>934</v>
+      </c>
+      <c r="C476" t="s">
         <v>935</v>
-      </c>
-      <c r="C476" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9957,10 +9958,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>936</v>
+      </c>
+      <c r="C477" t="s">
         <v>937</v>
-      </c>
-      <c r="C477" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9968,10 +9969,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C478" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9979,10 +9980,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>939</v>
+      </c>
+      <c r="C479" t="s">
         <v>940</v>
-      </c>
-      <c r="C479" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9990,10 +9991,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>941</v>
+      </c>
+      <c r="C480" t="s">
         <v>942</v>
-      </c>
-      <c r="C480" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -10001,10 +10002,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>943</v>
+      </c>
+      <c r="C481" t="s">
         <v>944</v>
-      </c>
-      <c r="C481" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -10012,10 +10013,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>945</v>
+      </c>
+      <c r="C482" t="s">
         <v>946</v>
-      </c>
-      <c r="C482" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10023,10 +10024,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>947</v>
+      </c>
+      <c r="C483" t="s">
         <v>948</v>
-      </c>
-      <c r="C483" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10034,10 +10035,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>949</v>
+      </c>
+      <c r="C484" t="s">
         <v>950</v>
-      </c>
-      <c r="C484" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10045,10 +10046,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>951</v>
+      </c>
+      <c r="C485" t="s">
         <v>952</v>
-      </c>
-      <c r="C485" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10056,10 +10057,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>953</v>
+      </c>
+      <c r="C486" t="s">
         <v>954</v>
-      </c>
-      <c r="C486" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10067,10 +10068,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>955</v>
+      </c>
+      <c r="C487" t="s">
         <v>956</v>
-      </c>
-      <c r="C487" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10078,10 +10079,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>957</v>
+      </c>
+      <c r="C488" t="s">
         <v>958</v>
-      </c>
-      <c r="C488" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10089,10 +10090,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>959</v>
+      </c>
+      <c r="C489" t="s">
         <v>960</v>
-      </c>
-      <c r="C489" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10100,10 +10101,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>961</v>
+      </c>
+      <c r="C490" t="s">
         <v>962</v>
-      </c>
-      <c r="C490" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10111,10 +10112,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>963</v>
+      </c>
+      <c r="C491" t="s">
         <v>964</v>
-      </c>
-      <c r="C491" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10122,10 +10123,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>965</v>
+      </c>
+      <c r="C492" t="s">
         <v>966</v>
-      </c>
-      <c r="C492" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10133,10 +10134,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>967</v>
+      </c>
+      <c r="C493" t="s">
         <v>968</v>
-      </c>
-      <c r="C493" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10144,10 +10145,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>969</v>
+      </c>
+      <c r="C494" t="s">
         <v>970</v>
-      </c>
-      <c r="C494" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10155,10 +10156,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>971</v>
+      </c>
+      <c r="C495" t="s">
         <v>972</v>
-      </c>
-      <c r="C495" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10166,10 +10167,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>973</v>
+      </c>
+      <c r="C496" t="s">
         <v>974</v>
-      </c>
-      <c r="C496" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10177,10 +10178,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>975</v>
+      </c>
+      <c r="C497" t="s">
         <v>976</v>
-      </c>
-      <c r="C497" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10188,10 +10189,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>977</v>
+      </c>
+      <c r="C498" t="s">
         <v>978</v>
-      </c>
-      <c r="C498" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10199,7 +10200,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10207,10 +10208,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>980</v>
+      </c>
+      <c r="C500" t="s">
         <v>981</v>
-      </c>
-      <c r="C500" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10218,10 +10219,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>982</v>
+      </c>
+      <c r="C501" t="s">
         <v>983</v>
-      </c>
-      <c r="C501" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10229,10 +10230,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>984</v>
+      </c>
+      <c r="C502" t="s">
         <v>985</v>
-      </c>
-      <c r="C502" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10240,10 +10241,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10251,10 +10252,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>987</v>
+      </c>
+      <c r="C504" t="s">
         <v>988</v>
-      </c>
-      <c r="C504" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10262,10 +10263,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>989</v>
+      </c>
+      <c r="C505" t="s">
         <v>990</v>
-      </c>
-      <c r="C505" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10273,10 +10274,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>991</v>
+      </c>
+      <c r="C506" t="s">
         <v>992</v>
-      </c>
-      <c r="C506" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10284,10 +10285,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>993</v>
+      </c>
+      <c r="C507" t="s">
         <v>994</v>
-      </c>
-      <c r="C507" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10295,10 +10296,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>995</v>
+      </c>
+      <c r="C508" t="s">
         <v>996</v>
-      </c>
-      <c r="C508" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10306,10 +10307,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>997</v>
+      </c>
+      <c r="C509" t="s">
         <v>998</v>
-      </c>
-      <c r="C509" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10317,10 +10318,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>999</v>
+      </c>
+      <c r="C510" t="s">
         <v>1000</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10328,10 +10329,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C511" t="s">
         <v>1002</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10339,10 +10340,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C512" t="s">
         <v>1004</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10350,10 +10351,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C513" t="s">
         <v>1006</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10361,10 +10362,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C514" t="s">
         <v>1008</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10372,10 +10373,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C515" t="s">
         <v>1010</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10383,10 +10384,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C516" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10394,10 +10395,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C517" t="s">
         <v>1013</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10405,7 +10406,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10413,10 +10414,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C519" t="s">
         <v>1016</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10424,10 +10425,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C520" t="s">
         <v>1018</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10435,10 +10436,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C521" t="s">
         <v>1020</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10446,10 +10447,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C522" t="s">
         <v>1022</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10457,10 +10458,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C523" t="s">
         <v>1024</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10468,10 +10469,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C524" t="s">
         <v>1026</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10479,10 +10480,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10490,10 +10491,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C526" t="s">
         <v>1029</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10501,10 +10502,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C527" t="s">
         <v>1031</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10512,10 +10513,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C528" t="s">
         <v>1033</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10523,10 +10524,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C529" t="s">
         <v>1035</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10534,10 +10535,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10545,10 +10546,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C531" t="s">
         <v>1038</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10556,10 +10557,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C532" t="s">
         <v>1040</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10567,10 +10568,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C533" t="s">
         <v>1042</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10578,10 +10579,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C534" t="s">
         <v>1044</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10589,10 +10590,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C535" t="s">
         <v>1046</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10600,10 +10601,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C536" t="s">
         <v>1048</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10611,10 +10612,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C537" t="s">
         <v>1050</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10622,10 +10623,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C538" t="s">
         <v>1052</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10633,10 +10634,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C539" t="s">
         <v>1054</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10644,10 +10645,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C540" t="s">
         <v>1056</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10655,10 +10656,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C541" t="s">
         <v>1058</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10666,10 +10667,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C542" t="s">
         <v>1060</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10677,10 +10678,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C543" t="s">
         <v>1062</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10688,10 +10689,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C544" t="s">
         <v>1064</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10699,10 +10700,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C545" t="s">
         <v>1066</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10710,10 +10711,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C546" t="s">
         <v>1068</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10721,7 +10722,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10729,10 +10730,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C548" t="s">
         <v>1071</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10740,10 +10741,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C549" t="s">
         <v>1073</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10751,10 +10752,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C550" t="s">
         <v>1075</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10762,10 +10763,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C551" t="s">
         <v>1077</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10773,10 +10774,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C552" t="s">
         <v>1079</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10784,10 +10785,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C553" t="s">
         <v>1081</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10795,10 +10796,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C554" t="s">
         <v>1083</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10806,10 +10807,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C555" t="s">
         <v>1085</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10817,10 +10818,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C556" t="s">
         <v>1087</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10828,10 +10829,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C557" t="s">
         <v>1089</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10839,10 +10840,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C558" t="s">
         <v>1091</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10850,7 +10851,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10858,10 +10859,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C560" t="s">
         <v>1094</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10869,10 +10870,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C561" t="s">
         <v>1096</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10880,10 +10881,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C562" t="s">
         <v>1098</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10891,10 +10892,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C563" t="s">
         <v>1100</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10902,10 +10903,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C564" t="s">
         <v>1102</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10913,10 +10914,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C565" t="s">
         <v>1104</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10924,10 +10925,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C566" t="s">
         <v>1106</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10935,10 +10936,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C567" t="s">
         <v>1108</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10946,10 +10947,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C568" t="s">
         <v>1110</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10957,10 +10958,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C569" t="s">
         <v>1112</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10968,10 +10969,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C570" t="s">
         <v>1114</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10979,10 +10980,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C571" t="s">
         <v>1116</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10990,10 +10991,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C572" t="s">
         <v>1118</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -11001,10 +11002,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C573" t="s">
         <v>1120</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11012,10 +11013,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C574" t="s">
         <v>1122</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11023,10 +11024,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11034,10 +11035,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C576" t="s">
         <v>1125</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11045,10 +11046,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11056,10 +11057,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11067,10 +11068,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C579" t="s">
         <v>1127</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11078,10 +11079,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C580" t="s">
         <v>1129</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11089,10 +11090,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C581" t="s">
         <v>1131</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11100,10 +11101,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C582" t="s">
         <v>1133</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11111,10 +11112,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11122,7 +11123,7 @@
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11130,10 +11131,10 @@
         <v>612</v>
       </c>
       <c r="B585" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C585" t="s">
         <v>1136</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11141,10 +11142,10 @@
         <v>615</v>
       </c>
       <c r="B586" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C586" t="s">
         <v>1138</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11152,10 +11153,10 @@
         <v>617</v>
       </c>
       <c r="B587" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C587" t="s">
         <v>1140</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11163,10 +11164,10 @@
         <v>618</v>
       </c>
       <c r="B588" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C588" t="s">
         <v>1142</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11174,10 +11175,10 @@
         <v>625</v>
       </c>
       <c r="B589" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C589" t="s">
         <v>1144</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11185,10 +11186,10 @@
         <v>624</v>
       </c>
       <c r="B590" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C590" t="s">
         <v>1146</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11196,10 +11197,10 @@
         <v>626</v>
       </c>
       <c r="B591" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C591" t="s">
         <v>1148</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11207,10 +11208,10 @@
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C592" t="s">
         <v>1150</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11218,10 +11219,10 @@
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C593" t="s">
         <v>1152</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11229,7 +11230,7 @@
         <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11237,10 +11238,10 @@
         <v>633</v>
       </c>
       <c r="B595" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C595" t="s">
         <v>1155</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11248,10 +11249,10 @@
         <v>635</v>
       </c>
       <c r="B596" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C596" t="s">
         <v>1157</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11259,10 +11260,10 @@
         <v>636</v>
       </c>
       <c r="B597" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C597" t="s">
         <v>1159</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11270,10 +11271,10 @@
         <v>642</v>
       </c>
       <c r="B598" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C598" t="s">
         <v>1161</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11281,10 +11282,10 @@
         <v>644</v>
       </c>
       <c r="B599" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C599" t="s">
         <v>1163</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11292,10 +11293,10 @@
         <v>646</v>
       </c>
       <c r="B600" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C600" t="s">
         <v>1165</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11303,10 +11304,10 @@
         <v>649</v>
       </c>
       <c r="B601" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C601" t="s">
         <v>1167</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11314,10 +11315,10 @@
         <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11325,10 +11326,10 @@
         <v>651</v>
       </c>
       <c r="B603" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C603" t="s">
         <v>1170</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11336,10 +11337,10 @@
         <v>653</v>
       </c>
       <c r="B604" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C604" t="s">
         <v>1172</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11347,10 +11348,10 @@
         <v>654</v>
       </c>
       <c r="B605" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C605" t="s">
         <v>1174</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11358,10 +11359,10 @@
         <v>655</v>
       </c>
       <c r="B606" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C606" t="s">
         <v>1176</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11369,10 +11370,10 @@
         <v>659</v>
       </c>
       <c r="B607" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C607" t="s">
         <v>1178</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11380,10 +11381,10 @@
         <v>660</v>
       </c>
       <c r="B608" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C608" t="s">
         <v>1180</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11391,10 +11392,10 @@
         <v>661</v>
       </c>
       <c r="B609" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C609" t="s">
         <v>1182</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11402,10 +11403,10 @@
         <v>663</v>
       </c>
       <c r="B610" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C610" t="s">
         <v>1184</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11413,10 +11414,10 @@
         <v>667</v>
       </c>
       <c r="B611" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C611" t="s">
         <v>1186</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11424,10 +11425,10 @@
         <v>670</v>
       </c>
       <c r="B612" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C612" t="s">
         <v>1188</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11435,10 +11436,10 @@
         <v>673</v>
       </c>
       <c r="B613" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C613" t="s">
         <v>1190</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11446,10 +11447,10 @@
         <v>674</v>
       </c>
       <c r="B614" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C614" t="s">
         <v>1192</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11457,10 +11458,10 @@
         <v>675</v>
       </c>
       <c r="B615" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C615" t="s">
         <v>1194</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11468,10 +11469,10 @@
         <v>680</v>
       </c>
       <c r="B616" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C616" t="s">
         <v>1196</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11479,10 +11480,10 @@
         <v>681</v>
       </c>
       <c r="B617" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C617" t="s">
         <v>1198</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11490,10 +11491,10 @@
         <v>682</v>
       </c>
       <c r="B618" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C618" t="s">
         <v>1200</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11501,10 +11502,10 @@
         <v>683</v>
       </c>
       <c r="B619" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C619" t="s">
         <v>1202</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11512,10 +11513,10 @@
         <v>684</v>
       </c>
       <c r="B620" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C620" t="s">
         <v>1204</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11523,10 +11524,10 @@
         <v>685</v>
       </c>
       <c r="B621" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C621" t="s">
         <v>1206</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11534,10 +11535,10 @@
         <v>686</v>
       </c>
       <c r="B622" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C622" t="s">
         <v>1208</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11545,10 +11546,10 @@
         <v>689</v>
       </c>
       <c r="B623" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C623" t="s">
         <v>1210</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11556,10 +11557,10 @@
         <v>697</v>
       </c>
       <c r="B624" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C624" t="s">
         <v>1212</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11567,10 +11568,10 @@
         <v>701</v>
       </c>
       <c r="B625" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C625" t="s">
         <v>1214</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11578,10 +11579,10 @@
         <v>702</v>
       </c>
       <c r="B626" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C626" t="s">
         <v>1216</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11589,10 +11590,10 @@
         <v>704</v>
       </c>
       <c r="B627" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C627" t="s">
         <v>1218</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11600,10 +11601,10 @@
         <v>705</v>
       </c>
       <c r="B628" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C628" t="s">
         <v>1220</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11611,10 +11612,10 @@
         <v>710</v>
       </c>
       <c r="B629" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C629" t="s">
         <v>1222</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11622,10 +11623,10 @@
         <v>711</v>
       </c>
       <c r="B630" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C630" t="s">
         <v>1224</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11633,10 +11634,10 @@
         <v>712</v>
       </c>
       <c r="B631" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C631" t="s">
         <v>1226</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11644,10 +11645,10 @@
         <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11655,10 +11656,10 @@
         <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11666,10 +11667,10 @@
         <v>718</v>
       </c>
       <c r="B634" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C634" t="s">
         <v>1230</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11677,10 +11678,10 @@
         <v>719</v>
       </c>
       <c r="B635" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C635" t="s">
         <v>1232</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11688,10 +11689,10 @@
         <v>721</v>
       </c>
       <c r="B636" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C636" t="s">
         <v>1234</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11699,10 +11700,10 @@
         <v>722</v>
       </c>
       <c r="B637" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C637" t="s">
         <v>1236</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11710,10 +11711,10 @@
         <v>723</v>
       </c>
       <c r="B638" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C638" t="s">
         <v>1238</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11721,7 +11722,7 @@
         <v>724</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11729,10 +11730,10 @@
         <v>725</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C640" t="s">
         <v>1240</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11740,10 +11741,10 @@
         <v>726</v>
       </c>
       <c r="B641" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C641" t="s">
         <v>1242</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11751,10 +11752,10 @@
         <v>727</v>
       </c>
       <c r="B642" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C642" t="s">
         <v>1244</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11762,10 +11763,10 @@
         <v>728</v>
       </c>
       <c r="B643" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C643" t="s">
         <v>1246</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11773,10 +11774,10 @@
         <v>729</v>
       </c>
       <c r="B644" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C644" t="s">
         <v>1248</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11784,10 +11785,10 @@
         <v>730</v>
       </c>
       <c r="B645" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C645" t="s">
         <v>1250</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11795,10 +11796,10 @@
         <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11806,10 +11807,10 @@
         <v>733</v>
       </c>
       <c r="B647" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C647" t="s">
         <v>1253</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11817,10 +11818,10 @@
         <v>735</v>
       </c>
       <c r="B648" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C648" t="s">
         <v>1255</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11828,10 +11829,10 @@
         <v>736</v>
       </c>
       <c r="B649" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C649" t="s">
         <v>1257</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11839,10 +11840,10 @@
         <v>737</v>
       </c>
       <c r="B650" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C650" t="s">
         <v>1259</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11850,10 +11851,10 @@
         <v>738</v>
       </c>
       <c r="B651" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C651" t="s">
         <v>1261</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11861,10 +11862,10 @@
         <v>739</v>
       </c>
       <c r="B652" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C652" t="s">
         <v>1263</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11872,10 +11873,10 @@
         <v>740</v>
       </c>
       <c r="B653" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C653" t="s">
         <v>1265</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11883,10 +11884,10 @@
         <v>741</v>
       </c>
       <c r="B654" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C654" t="s">
         <v>1267</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11894,10 +11895,10 @@
         <v>742</v>
       </c>
       <c r="B655" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C655" t="s">
         <v>1269</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11905,10 +11906,10 @@
         <v>743</v>
       </c>
       <c r="B656" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C656" t="s">
         <v>1271</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11916,10 +11917,10 @@
         <v>744</v>
       </c>
       <c r="B657" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C657" t="s">
         <v>1273</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11927,10 +11928,10 @@
         <v>745</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C658" t="s">
         <v>1275</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11938,10 +11939,10 @@
         <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C659" t="s">
         <v>1277</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11949,10 +11950,10 @@
         <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C660" t="s">
         <v>1279</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11960,10 +11961,10 @@
         <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C661" t="s">
         <v>1281</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11971,10 +11972,10 @@
         <v>749</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C662" t="s">
         <v>1283</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11983,7 +11984,7 @@
       </c>
       <c r="B663" s="1"/>
       <c r="C663" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11991,10 +11992,10 @@
         <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C664" t="s">
         <v>1285</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -12002,10 +12003,10 @@
         <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12013,10 +12014,10 @@
         <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C666" t="s">
         <v>1288</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12024,10 +12025,10 @@
         <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C667" t="s">
         <v>1290</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12035,10 +12036,10 @@
         <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C668" t="s">
         <v>1292</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12046,10 +12047,10 @@
         <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12057,10 +12058,10 @@
         <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C670" t="s">
         <v>1295</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12068,10 +12069,10 @@
         <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C671" t="s">
         <v>1297</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12079,10 +12080,10 @@
         <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C672" t="s">
         <v>1299</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12090,10 +12091,10 @@
         <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C673" t="s">
         <v>1301</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -12101,10 +12102,10 @@
         <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C674" t="s">
         <v>1303</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12112,10 +12113,10 @@
         <v>765</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C675" t="s">
         <v>1305</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12129,10 +12130,10 @@
         <v>767</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C677" t="s">
         <v>1307</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12141,7 +12142,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12149,10 +12150,10 @@
         <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C679" t="s">
         <v>1310</v>
-      </c>
-      <c r="C679" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12160,10 +12161,10 @@
         <v>772</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C680" s="3" t="s">
         <v>1315</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12172,7 +12173,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12181,7 +12182,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12190,7 +12191,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12199,7 +12200,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12208,7 +12209,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12217,7 +12218,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12226,7 +12227,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -12235,7 +12236,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
@@ -12244,7 +12245,7 @@
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -12252,10 +12253,10 @@
         <v>10001</v>
       </c>
       <c r="B690" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
@@ -12263,10 +12264,10 @@
         <v>10003</v>
       </c>
       <c r="B691" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C691" t="s">
         <v>1310</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1311</v>
       </c>
     </row>
   </sheetData>

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D346E4-3EEA-4958-A602-D42EA28B5271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F40BEC5-8BE5-45F6-9BC2-09F20CE83774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="2010" windowWidth="24855" windowHeight="10020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -4289,7 +4289,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花,00开花,00 开花,磷磷开花,ringring bloom,rinrin bloom,rin rin bomm,ring ring boom</t>
+    <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花,00开花,00 开花,磷磷开花,ringring bloom,rinrin bloom,rin rin boom,ring ring boom</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F40BEC5-8BE5-45F6-9BC2-09F20CE83774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAAF842-5C05-4C25-9821-5A05375867D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4289,7 +4289,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花,00开花,00 开花,磷磷开花,ringring bloom,rinrin bloom,rin rin boom,ring ring boom</t>
+    <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花,00开花,00 开花,磷磷开花,ringring bloom,rinrin bloom,rin rin boom,ring ring boom,ringing boom</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAAF842-5C05-4C25-9821-5A05375867D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12FD81B-5F6B-44CC-A6E7-4ABB4D91D14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1568,9 +1568,6 @@
     <t>ブルームブルーム</t>
   </si>
   <si>
-    <t>bloombloom</t>
-  </si>
-  <si>
     <t>Winking☆Cheer</t>
   </si>
   <si>
@@ -4290,6 +4287,10 @@
   </si>
   <si>
     <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花,00开花,00 开花,磷磷开花,ringring bloom,rinrin bloom,rin rin boom,ring ring boom,ringing boom</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bloombloom,生长,boomboom</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4712,15 +4713,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C691"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.69921875" customWidth="1"/>
-    <col min="2" max="2" width="50.69921875" customWidth="1"/>
-    <col min="3" max="3" width="65.69921875" customWidth="1"/>
-    <col min="4" max="4" width="55.69921875" customWidth="1"/>
+    <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="50.75" customWidth="1"/>
+    <col min="3" max="3" width="65.75" customWidth="1"/>
+    <col min="4" max="4" width="55.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4731,7 +4732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4742,7 +4743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4753,7 +4754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4764,7 +4765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4775,7 +4776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4786,7 +4787,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4797,7 +4798,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4808,7 +4809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4819,7 +4820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4830,7 +4831,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4841,7 +4842,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4852,7 +4853,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4863,7 +4864,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4874,7 +4875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4918,7 +4919,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4929,7 +4930,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4940,7 +4941,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4951,7 +4952,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4962,7 +4963,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>24</v>
       </c>
@@ -4973,7 +4974,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>25</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>26</v>
       </c>
@@ -4995,7 +4996,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>27</v>
       </c>
@@ -5006,7 +5007,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>28</v>
       </c>
@@ -5017,7 +5018,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5028,7 +5029,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>30</v>
       </c>
@@ -5039,7 +5040,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5050,7 +5051,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5061,7 +5062,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5072,7 +5073,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5083,7 +5084,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>35</v>
       </c>
@@ -5094,7 +5095,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5105,7 +5106,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5116,7 +5117,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>40</v>
       </c>
@@ -5127,7 +5128,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5138,7 +5139,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5149,7 +5150,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5160,7 +5161,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5171,7 +5172,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5182,7 +5183,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5193,7 +5194,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5204,7 +5205,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5215,7 +5216,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5226,7 +5227,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5237,7 +5238,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5270,7 +5271,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5281,7 +5282,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5292,7 +5293,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5303,7 +5304,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5314,7 +5315,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5325,7 +5326,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5336,7 +5337,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5344,10 +5345,10 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5358,7 +5359,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5369,7 +5370,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5380,7 +5381,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5391,7 +5392,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5402,7 +5403,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5413,7 +5414,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5424,7 +5425,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5435,7 +5436,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5446,7 +5447,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5457,7 +5458,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5468,7 +5469,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5479,7 +5480,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>73</v>
       </c>
@@ -5490,7 +5491,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>74</v>
       </c>
@@ -5501,7 +5502,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>75</v>
       </c>
@@ -5512,7 +5513,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>76</v>
       </c>
@@ -5523,7 +5524,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>77</v>
       </c>
@@ -5534,7 +5535,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>78</v>
       </c>
@@ -5545,7 +5546,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>79</v>
       </c>
@@ -5556,7 +5557,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>80</v>
       </c>
@@ -5567,7 +5568,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>81</v>
       </c>
@@ -5578,7 +5579,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>82</v>
       </c>
@@ -5589,7 +5590,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>83</v>
       </c>
@@ -5600,7 +5601,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>84</v>
       </c>
@@ -5611,7 +5612,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>85</v>
       </c>
@@ -5622,7 +5623,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>86</v>
       </c>
@@ -5633,7 +5634,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>87</v>
       </c>
@@ -5644,7 +5645,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>88</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>89</v>
       </c>
@@ -5666,7 +5667,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>90</v>
       </c>
@@ -5677,7 +5678,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>91</v>
       </c>
@@ -5688,7 +5689,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>92</v>
       </c>
@@ -5699,7 +5700,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5710,7 +5711,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5721,7 +5722,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5732,7 +5733,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5743,7 +5744,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5765,7 +5766,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5776,7 +5777,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5787,7 +5788,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5798,7 +5799,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5809,7 +5810,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5820,7 +5821,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5831,7 +5832,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5842,7 +5843,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5853,7 +5854,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5864,7 +5865,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5886,7 +5887,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5897,7 +5898,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5919,7 +5920,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5930,7 +5931,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5941,7 +5942,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5952,7 +5953,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5960,10 +5961,10 @@
         <v>224</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114">
         <v>122</v>
       </c>
@@ -5974,7 +5975,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115">
         <v>123</v>
       </c>
@@ -5985,7 +5986,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116">
         <v>124</v>
       </c>
@@ -5996,7 +5997,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117">
         <v>125</v>
       </c>
@@ -6007,7 +6008,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118">
         <v>126</v>
       </c>
@@ -6018,7 +6019,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119">
         <v>127</v>
       </c>
@@ -6029,7 +6030,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120">
         <v>128</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121">
         <v>129</v>
       </c>
@@ -6051,7 +6052,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122">
         <v>130</v>
       </c>
@@ -6062,7 +6063,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123">
         <v>131</v>
       </c>
@@ -6073,7 +6074,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124">
         <v>132</v>
       </c>
@@ -6084,7 +6085,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125">
         <v>133</v>
       </c>
@@ -6095,7 +6096,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126">
         <v>134</v>
       </c>
@@ -6106,7 +6107,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127">
         <v>135</v>
       </c>
@@ -6117,7 +6118,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6128,7 +6129,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6139,7 +6140,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6147,10 +6148,10 @@
         <v>257</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6161,7 +6162,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6172,7 +6173,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6183,7 +6184,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6194,7 +6195,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6205,7 +6206,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6216,7 +6217,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6227,7 +6228,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6249,7 +6250,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6260,7 +6261,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6271,7 +6272,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6282,7 +6283,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6293,7 +6294,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6304,7 +6305,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6315,7 +6316,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6326,7 +6327,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6337,7 +6338,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6348,7 +6349,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6359,7 +6360,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6370,7 +6371,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6381,7 +6382,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6392,7 +6393,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6403,7 +6404,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6414,7 +6415,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6425,7 +6426,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6436,7 +6437,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6447,7 +6448,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6458,7 +6459,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6469,7 +6470,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6480,7 +6481,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A161">
         <v>169</v>
       </c>
@@ -6491,7 +6492,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A162">
         <v>170</v>
       </c>
@@ -6502,7 +6503,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A163">
         <v>171</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A164">
         <v>172</v>
       </c>
@@ -6524,7 +6525,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A165">
         <v>173</v>
       </c>
@@ -6535,7 +6536,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A166">
         <v>174</v>
       </c>
@@ -6546,7 +6547,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A167">
         <v>175</v>
       </c>
@@ -6554,10 +6555,10 @@
         <v>330</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A168">
         <v>176</v>
       </c>
@@ -6568,7 +6569,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A169">
         <v>177</v>
       </c>
@@ -6579,7 +6580,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A170">
         <v>178</v>
       </c>
@@ -6590,7 +6591,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A171">
         <v>179</v>
       </c>
@@ -6601,7 +6602,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A172">
         <v>180</v>
       </c>
@@ -6612,7 +6613,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A173">
         <v>181</v>
       </c>
@@ -6623,7 +6624,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A174">
         <v>182</v>
       </c>
@@ -6634,7 +6635,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A175">
         <v>183</v>
       </c>
@@ -6645,7 +6646,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A176">
         <v>184</v>
       </c>
@@ -6656,7 +6657,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A177">
         <v>185</v>
       </c>
@@ -6667,7 +6668,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A178">
         <v>186</v>
       </c>
@@ -6678,7 +6679,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A179">
         <v>187</v>
       </c>
@@ -6689,7 +6690,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A180">
         <v>188</v>
       </c>
@@ -6700,7 +6701,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A181">
         <v>189</v>
       </c>
@@ -6711,7 +6712,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A182">
         <v>190</v>
       </c>
@@ -6722,7 +6723,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A183">
         <v>191</v>
       </c>
@@ -6733,7 +6734,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A184">
         <v>192</v>
       </c>
@@ -6744,7 +6745,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6755,7 +6756,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6766,7 +6767,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6777,7 +6778,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6788,7 +6789,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6799,7 +6800,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6810,7 +6811,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6821,7 +6822,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6832,7 +6833,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6843,7 +6844,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6854,7 +6855,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6865,7 +6866,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6876,7 +6877,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6887,7 +6888,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6898,7 +6899,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6909,7 +6910,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6920,7 +6921,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6931,7 +6932,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6942,7 +6943,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6953,7 +6954,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6964,7 +6965,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A205">
         <v>213</v>
       </c>
@@ -6975,7 +6976,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A206">
         <v>214</v>
       </c>
@@ -6986,7 +6987,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A207">
         <v>215</v>
       </c>
@@ -6997,7 +6998,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A208">
         <v>217</v>
       </c>
@@ -7008,7 +7009,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A209">
         <v>218</v>
       </c>
@@ -7019,7 +7020,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A210">
         <v>219</v>
       </c>
@@ -7030,7 +7031,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A211">
         <v>220</v>
       </c>
@@ -7041,7 +7042,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A212">
         <v>221</v>
       </c>
@@ -7052,7 +7053,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A213">
         <v>222</v>
       </c>
@@ -7063,7 +7064,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A214">
         <v>223</v>
       </c>
@@ -7074,7 +7075,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A215">
         <v>224</v>
       </c>
@@ -7085,7 +7086,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A216">
         <v>225</v>
       </c>
@@ -7096,7 +7097,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A217">
         <v>226</v>
       </c>
@@ -7107,7 +7108,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A218">
         <v>227</v>
       </c>
@@ -7118,7 +7119,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7129,7 +7130,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7140,7 +7141,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7151,7 +7152,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7162,7 +7163,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7173,7 +7174,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A224">
         <v>233</v>
       </c>
@@ -7181,10 +7182,10 @@
         <v>443</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A225">
         <v>234</v>
       </c>
@@ -7195,7 +7196,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A226">
         <v>235</v>
       </c>
@@ -7206,7 +7207,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A227">
         <v>236</v>
       </c>
@@ -7217,7 +7218,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A228">
         <v>237</v>
       </c>
@@ -7228,7 +7229,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A229">
         <v>238</v>
       </c>
@@ -7239,7 +7240,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A230">
         <v>239</v>
       </c>
@@ -7250,7 +7251,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A231">
         <v>240</v>
       </c>
@@ -7261,7 +7262,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A232">
         <v>241</v>
       </c>
@@ -7272,7 +7273,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A233">
         <v>242</v>
       </c>
@@ -7283,7 +7284,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A234">
         <v>243</v>
       </c>
@@ -7294,7 +7295,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A235">
         <v>244</v>
       </c>
@@ -7305,7 +7306,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A236">
         <v>245</v>
       </c>
@@ -7316,7 +7317,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A237">
         <v>246</v>
       </c>
@@ -7327,7 +7328,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A238">
         <v>247</v>
       </c>
@@ -7338,7 +7339,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A239">
         <v>248</v>
       </c>
@@ -7349,7 +7350,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A240">
         <v>249</v>
       </c>
@@ -7360,7 +7361,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A241">
         <v>250</v>
       </c>
@@ -7371,7 +7372,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A242">
         <v>251</v>
       </c>
@@ -7382,7 +7383,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A243">
         <v>252</v>
       </c>
@@ -7393,7 +7394,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A244">
         <v>253</v>
       </c>
@@ -7404,7 +7405,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A245">
         <v>254</v>
       </c>
@@ -7415,7 +7416,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A246">
         <v>255</v>
       </c>
@@ -7426,7 +7427,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A247">
         <v>256</v>
       </c>
@@ -7437,7 +7438,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A248">
         <v>257</v>
       </c>
@@ -7448,7 +7449,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A249">
         <v>258</v>
       </c>
@@ -7459,7 +7460,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A250">
         <v>259</v>
       </c>
@@ -7470,7 +7471,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A251">
         <v>260</v>
       </c>
@@ -7478,10 +7479,10 @@
         <v>496</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A252">
         <v>261</v>
       </c>
@@ -7492,7 +7493,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A253">
         <v>262</v>
       </c>
@@ -7503,4771 +7504,4771 @@
         <v>499</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A254">
         <v>263</v>
       </c>
       <c r="B254" t="s">
         <v>500</v>
       </c>
-      <c r="C254" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C254" s="3" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A255">
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>501</v>
+      </c>
+      <c r="C255" t="s">
         <v>502</v>
       </c>
-      <c r="C255" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A256">
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>503</v>
+      </c>
+      <c r="C256" t="s">
         <v>504</v>
       </c>
-      <c r="C256" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A257">
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>505</v>
+      </c>
+      <c r="C257" t="s">
         <v>506</v>
       </c>
-      <c r="C257" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A258">
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>507</v>
+      </c>
+      <c r="C258" t="s">
         <v>508</v>
       </c>
-      <c r="C258" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A259">
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>509</v>
+      </c>
+      <c r="C259" t="s">
         <v>510</v>
       </c>
-      <c r="C259" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A260">
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>511</v>
+      </c>
+      <c r="C260" t="s">
         <v>512</v>
       </c>
-      <c r="C260" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A261">
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>513</v>
+      </c>
+      <c r="C261" t="s">
         <v>514</v>
       </c>
-      <c r="C261" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A262">
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>515</v>
+      </c>
+      <c r="C262" t="s">
         <v>516</v>
       </c>
-      <c r="C262" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A263">
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>517</v>
+      </c>
+      <c r="C263" t="s">
         <v>518</v>
       </c>
-      <c r="C263" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A264">
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>519</v>
+      </c>
+      <c r="C264" t="s">
         <v>520</v>
       </c>
-      <c r="C264" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A265">
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>521</v>
+      </c>
+      <c r="C265" t="s">
         <v>522</v>
       </c>
-      <c r="C265" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A266">
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>523</v>
+      </c>
+      <c r="C266" t="s">
         <v>524</v>
       </c>
-      <c r="C266" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A267">
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>525</v>
+      </c>
+      <c r="C267" t="s">
         <v>526</v>
       </c>
-      <c r="C267" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A268">
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>527</v>
+      </c>
+      <c r="C268" t="s">
         <v>528</v>
       </c>
-      <c r="C268" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A269">
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>529</v>
+      </c>
+      <c r="C269" t="s">
         <v>530</v>
       </c>
-      <c r="C269" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A270">
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>531</v>
+      </c>
+      <c r="C270" t="s">
         <v>532</v>
       </c>
-      <c r="C270" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A271">
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A272">
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>534</v>
+      </c>
+      <c r="C272" t="s">
         <v>535</v>
       </c>
-      <c r="C272" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A273">
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>536</v>
+      </c>
+      <c r="C273" t="s">
         <v>537</v>
       </c>
-      <c r="C273" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A274">
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>538</v>
+      </c>
+      <c r="C274" t="s">
         <v>539</v>
       </c>
-      <c r="C274" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A275">
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>540</v>
+      </c>
+      <c r="C275" t="s">
         <v>541</v>
       </c>
-      <c r="C275" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A276">
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>542</v>
+      </c>
+      <c r="C276" t="s">
         <v>543</v>
       </c>
-      <c r="C276" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A277">
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>544</v>
+      </c>
+      <c r="C277" t="s">
         <v>545</v>
       </c>
-      <c r="C277" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A278">
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>546</v>
+      </c>
+      <c r="C278" t="s">
         <v>547</v>
       </c>
-      <c r="C278" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A279">
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>548</v>
+      </c>
+      <c r="C279" t="s">
         <v>549</v>
       </c>
-      <c r="C279" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A280">
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>550</v>
+      </c>
+      <c r="C280" t="s">
         <v>551</v>
       </c>
-      <c r="C280" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A281">
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>552</v>
+      </c>
+      <c r="C281" t="s">
         <v>553</v>
       </c>
-      <c r="C281" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A282">
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>554</v>
+      </c>
+      <c r="C282" t="s">
         <v>555</v>
       </c>
-      <c r="C282" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A283">
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>556</v>
+      </c>
+      <c r="C283" t="s">
         <v>557</v>
       </c>
-      <c r="C283" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A284">
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>558</v>
+      </c>
+      <c r="C284" t="s">
         <v>559</v>
       </c>
-      <c r="C284" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A285">
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>560</v>
+      </c>
+      <c r="C285" t="s">
         <v>561</v>
       </c>
-      <c r="C285" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A286">
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>562</v>
+      </c>
+      <c r="C286" t="s">
         <v>563</v>
       </c>
-      <c r="C286" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A287">
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>564</v>
+      </c>
+      <c r="C287" t="s">
         <v>565</v>
       </c>
-      <c r="C287" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A288">
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>566</v>
+      </c>
+      <c r="C288" t="s">
         <v>567</v>
       </c>
-      <c r="C288" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A289">
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>568</v>
+      </c>
+      <c r="C289" t="s">
         <v>569</v>
       </c>
-      <c r="C289" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A290">
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>570</v>
+      </c>
+      <c r="C290" t="s">
         <v>571</v>
       </c>
-      <c r="C290" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A291">
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>572</v>
+      </c>
+      <c r="C291" t="s">
         <v>573</v>
       </c>
-      <c r="C291" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A292">
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>574</v>
+      </c>
+      <c r="C292" t="s">
         <v>575</v>
       </c>
-      <c r="C292" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A293">
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>576</v>
+      </c>
+      <c r="C293" t="s">
         <v>577</v>
       </c>
-      <c r="C293" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A294">
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>578</v>
+      </c>
+      <c r="C294" t="s">
         <v>579</v>
       </c>
-      <c r="C294" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A295">
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>580</v>
+      </c>
+      <c r="C295" t="s">
         <v>581</v>
       </c>
-      <c r="C295" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A296">
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A297">
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>583</v>
+      </c>
+      <c r="C297" t="s">
         <v>584</v>
       </c>
-      <c r="C297" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A298">
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>585</v>
+      </c>
+      <c r="C298" t="s">
         <v>586</v>
       </c>
-      <c r="C298" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A299">
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>587</v>
+      </c>
+      <c r="C299" t="s">
         <v>588</v>
       </c>
-      <c r="C299" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A300">
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>589</v>
+      </c>
+      <c r="C300" t="s">
         <v>590</v>
       </c>
-      <c r="C300" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A301">
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>591</v>
+      </c>
+      <c r="C301" t="s">
         <v>592</v>
       </c>
-      <c r="C301" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A302">
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>593</v>
+      </c>
+      <c r="C302" t="s">
         <v>594</v>
       </c>
-      <c r="C302" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A303">
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>595</v>
+      </c>
+      <c r="C303" t="s">
         <v>596</v>
       </c>
-      <c r="C303" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A304">
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>597</v>
+      </c>
+      <c r="C304" t="s">
         <v>598</v>
       </c>
-      <c r="C304" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A305">
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>599</v>
+      </c>
+      <c r="C305" t="s">
         <v>600</v>
       </c>
-      <c r="C305" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A306">
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>601</v>
+      </c>
+      <c r="C306" t="s">
         <v>602</v>
       </c>
-      <c r="C306" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A307">
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>603</v>
+      </c>
+      <c r="C307" t="s">
         <v>604</v>
       </c>
-      <c r="C307" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A308">
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>605</v>
+      </c>
+      <c r="C308" t="s">
         <v>606</v>
       </c>
-      <c r="C308" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A309">
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>607</v>
+      </c>
+      <c r="C309" t="s">
         <v>608</v>
       </c>
-      <c r="C309" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A310">
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>609</v>
+      </c>
+      <c r="C310" t="s">
         <v>610</v>
       </c>
-      <c r="C310" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A311">
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>611</v>
+      </c>
+      <c r="C311" t="s">
         <v>612</v>
       </c>
-      <c r="C311" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A312">
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>613</v>
+      </c>
+      <c r="C312" t="s">
         <v>614</v>
       </c>
-      <c r="C312" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A313">
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>615</v>
+      </c>
+      <c r="C313" t="s">
         <v>616</v>
       </c>
-      <c r="C313" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A314">
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>617</v>
+      </c>
+      <c r="C314" t="s">
         <v>618</v>
       </c>
-      <c r="C314" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A315">
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>619</v>
+      </c>
+      <c r="C315" t="s">
         <v>620</v>
       </c>
-      <c r="C315" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A316">
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>621</v>
+      </c>
+      <c r="C316" t="s">
         <v>622</v>
       </c>
-      <c r="C316" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A317">
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>623</v>
+      </c>
+      <c r="C317" t="s">
         <v>624</v>
       </c>
-      <c r="C317" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A318">
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>625</v>
+      </c>
+      <c r="C318" t="s">
         <v>626</v>
       </c>
-      <c r="C318" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A319">
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>627</v>
+      </c>
+      <c r="C319" t="s">
         <v>628</v>
       </c>
-      <c r="C319" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A320">
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>629</v>
+      </c>
+      <c r="C320" t="s">
         <v>630</v>
       </c>
-      <c r="C320" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A321">
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>631</v>
+      </c>
+      <c r="C321" t="s">
         <v>632</v>
       </c>
-      <c r="C321" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A322">
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>633</v>
+      </c>
+      <c r="C322" t="s">
         <v>634</v>
       </c>
-      <c r="C322" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A323">
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>635</v>
+      </c>
+      <c r="C323" t="s">
         <v>636</v>
       </c>
-      <c r="C323" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A324">
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>637</v>
+      </c>
+      <c r="C324" t="s">
         <v>638</v>
       </c>
-      <c r="C324" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A325">
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>639</v>
+      </c>
+      <c r="C325" t="s">
         <v>640</v>
       </c>
-      <c r="C325" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A326">
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>641</v>
+      </c>
+      <c r="C326" t="s">
         <v>642</v>
       </c>
-      <c r="C326" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A327">
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>643</v>
+      </c>
+      <c r="C327" t="s">
         <v>644</v>
       </c>
-      <c r="C327" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A328">
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>645</v>
+      </c>
+      <c r="C328" t="s">
         <v>646</v>
       </c>
-      <c r="C328" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A329">
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>647</v>
+      </c>
+      <c r="C329" t="s">
         <v>648</v>
       </c>
-      <c r="C329" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A330">
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>649</v>
+      </c>
+      <c r="C330" t="s">
         <v>650</v>
       </c>
-      <c r="C330" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A331">
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>651</v>
+      </c>
+      <c r="C331" t="s">
         <v>652</v>
       </c>
-      <c r="C331" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A332">
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>653</v>
+      </c>
+      <c r="C332" t="s">
         <v>654</v>
       </c>
-      <c r="C332" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A333">
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>655</v>
+      </c>
+      <c r="C333" t="s">
         <v>656</v>
       </c>
-      <c r="C333" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A334">
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>657</v>
+      </c>
+      <c r="C334" t="s">
         <v>658</v>
       </c>
-      <c r="C334" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A335">
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>659</v>
+      </c>
+      <c r="C335" t="s">
         <v>660</v>
       </c>
-      <c r="C335" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A336">
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>661</v>
+      </c>
+      <c r="C336" t="s">
         <v>662</v>
       </c>
-      <c r="C336" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A337">
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>663</v>
+      </c>
+      <c r="C337" t="s">
         <v>664</v>
       </c>
-      <c r="C337" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A338">
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A339">
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A340">
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>667</v>
+      </c>
+      <c r="C340" t="s">
         <v>668</v>
       </c>
-      <c r="C340" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A341">
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>669</v>
+      </c>
+      <c r="C341" t="s">
         <v>670</v>
       </c>
-      <c r="C341" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A342">
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>671</v>
+      </c>
+      <c r="C342" t="s">
         <v>672</v>
       </c>
-      <c r="C342" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A343">
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>673</v>
+      </c>
+      <c r="C343" t="s">
         <v>674</v>
       </c>
-      <c r="C343" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A344">
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>675</v>
+      </c>
+      <c r="C344" t="s">
         <v>676</v>
       </c>
-      <c r="C344" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A345">
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>677</v>
+      </c>
+      <c r="C345" t="s">
         <v>678</v>
       </c>
-      <c r="C345" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A346">
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>679</v>
+      </c>
+      <c r="C346" t="s">
         <v>680</v>
       </c>
-      <c r="C346" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A347">
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>681</v>
+      </c>
+      <c r="C347" t="s">
         <v>682</v>
       </c>
-      <c r="C347" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A348">
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>683</v>
+      </c>
+      <c r="C348" t="s">
         <v>684</v>
       </c>
-      <c r="C348" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A349">
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>685</v>
+      </c>
+      <c r="C349" t="s">
         <v>686</v>
       </c>
-      <c r="C349" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A350">
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>687</v>
+      </c>
+      <c r="C350" t="s">
         <v>688</v>
       </c>
-      <c r="C350" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A351">
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>689</v>
+      </c>
+      <c r="C351" t="s">
         <v>690</v>
       </c>
-      <c r="C351" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A352">
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>691</v>
+      </c>
+      <c r="C352" t="s">
         <v>692</v>
       </c>
-      <c r="C352" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A353">
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>693</v>
+      </c>
+      <c r="C353" t="s">
         <v>694</v>
       </c>
-      <c r="C353" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A354">
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>695</v>
+      </c>
+      <c r="C354" t="s">
         <v>696</v>
       </c>
-      <c r="C354" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A355">
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>697</v>
+      </c>
+      <c r="C355" t="s">
         <v>698</v>
       </c>
-      <c r="C355" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A356">
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>699</v>
+      </c>
+      <c r="C356" t="s">
         <v>700</v>
       </c>
-      <c r="C356" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A357">
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>701</v>
+      </c>
+      <c r="C357" t="s">
         <v>702</v>
       </c>
-      <c r="C357" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A358">
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>703</v>
+      </c>
+      <c r="C358" t="s">
         <v>704</v>
       </c>
-      <c r="C358" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A359">
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>705</v>
+      </c>
+      <c r="C359" t="s">
         <v>706</v>
       </c>
-      <c r="C359" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A360">
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>707</v>
+      </c>
+      <c r="C360" t="s">
         <v>708</v>
       </c>
-      <c r="C360" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A361">
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>709</v>
+      </c>
+      <c r="C361" t="s">
         <v>710</v>
       </c>
-      <c r="C361" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A362">
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>711</v>
+      </c>
+      <c r="C362" t="s">
         <v>712</v>
       </c>
-      <c r="C362" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A363">
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>713</v>
+      </c>
+      <c r="C363" t="s">
         <v>714</v>
       </c>
-      <c r="C363" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A364">
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>715</v>
+      </c>
+      <c r="C364" t="s">
         <v>716</v>
       </c>
-      <c r="C364" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A365">
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>717</v>
+      </c>
+      <c r="C365" t="s">
         <v>718</v>
       </c>
-      <c r="C365" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A366">
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>719</v>
+      </c>
+      <c r="C366" t="s">
         <v>720</v>
       </c>
-      <c r="C366" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A367">
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>721</v>
+      </c>
+      <c r="C367" t="s">
         <v>722</v>
       </c>
-      <c r="C367" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A368">
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>723</v>
+      </c>
+      <c r="C368" t="s">
         <v>724</v>
       </c>
-      <c r="C368" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A369">
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>725</v>
+      </c>
+      <c r="C369" t="s">
         <v>726</v>
       </c>
-      <c r="C369" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A370">
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>727</v>
+      </c>
+      <c r="C370" t="s">
         <v>728</v>
       </c>
-      <c r="C370" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A371">
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>729</v>
+      </c>
+      <c r="C371" t="s">
         <v>730</v>
       </c>
-      <c r="C371" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A372">
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>731</v>
+      </c>
+      <c r="C372" t="s">
         <v>732</v>
       </c>
-      <c r="C372" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A373">
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>733</v>
+      </c>
+      <c r="C373" t="s">
         <v>734</v>
       </c>
-      <c r="C373" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A374">
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>735</v>
+      </c>
+      <c r="C374" t="s">
         <v>736</v>
       </c>
-      <c r="C374" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A375">
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>737</v>
+      </c>
+      <c r="C375" t="s">
         <v>738</v>
       </c>
-      <c r="C375" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A376">
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>739</v>
+      </c>
+      <c r="C376" t="s">
         <v>740</v>
       </c>
-      <c r="C376" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A377">
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>741</v>
+      </c>
+      <c r="C377" t="s">
         <v>742</v>
       </c>
-      <c r="C377" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A378">
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>743</v>
+      </c>
+      <c r="C378" t="s">
         <v>744</v>
       </c>
-      <c r="C378" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A379">
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>745</v>
+      </c>
+      <c r="C379" t="s">
         <v>746</v>
       </c>
-      <c r="C379" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A380">
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>747</v>
+      </c>
+      <c r="C380" t="s">
         <v>748</v>
       </c>
-      <c r="C380" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A381">
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>749</v>
+      </c>
+      <c r="C381" t="s">
         <v>750</v>
       </c>
-      <c r="C381" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A382">
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>751</v>
+      </c>
+      <c r="C382" t="s">
         <v>752</v>
       </c>
-      <c r="C382" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A383">
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>753</v>
+      </c>
+      <c r="C383" t="s">
         <v>754</v>
       </c>
-      <c r="C383" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A384">
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>755</v>
+      </c>
+      <c r="C384" t="s">
         <v>756</v>
       </c>
-      <c r="C384" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A385">
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>757</v>
+      </c>
+      <c r="C385" t="s">
         <v>758</v>
       </c>
-      <c r="C385" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A386">
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>759</v>
+      </c>
+      <c r="C386" t="s">
         <v>760</v>
       </c>
-      <c r="C386" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A387">
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>761</v>
+      </c>
+      <c r="C387" t="s">
         <v>762</v>
       </c>
-      <c r="C387" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A388">
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>763</v>
+      </c>
+      <c r="C388" t="s">
         <v>764</v>
       </c>
-      <c r="C388" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A389">
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>765</v>
+      </c>
+      <c r="C389" t="s">
         <v>766</v>
       </c>
-      <c r="C389" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A390">
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>767</v>
+      </c>
+      <c r="C390" t="s">
         <v>768</v>
       </c>
-      <c r="C390" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A391">
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>769</v>
+      </c>
+      <c r="C391" t="s">
         <v>770</v>
       </c>
-      <c r="C391" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
+    </row>
+    <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>771</v>
+      </c>
+      <c r="C392" t="s">
         <v>772</v>
       </c>
-      <c r="C392" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A393">
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>773</v>
+      </c>
+      <c r="C393" t="s">
         <v>774</v>
       </c>
-      <c r="C393" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A394">
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>775</v>
+      </c>
+      <c r="C394" t="s">
         <v>776</v>
       </c>
-      <c r="C394" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A395">
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>777</v>
+      </c>
+      <c r="C395" t="s">
         <v>778</v>
       </c>
-      <c r="C395" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A396">
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>779</v>
+      </c>
+      <c r="C396" t="s">
         <v>780</v>
       </c>
-      <c r="C396" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A397">
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>781</v>
+      </c>
+      <c r="C397" t="s">
         <v>782</v>
       </c>
-      <c r="C397" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A398">
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>783</v>
+      </c>
+      <c r="C398" t="s">
         <v>784</v>
       </c>
-      <c r="C398" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A399">
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>785</v>
+      </c>
+      <c r="C399" t="s">
         <v>786</v>
       </c>
-      <c r="C399" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A400">
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>787</v>
+      </c>
+      <c r="C400" t="s">
         <v>788</v>
       </c>
-      <c r="C400" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A401">
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>789</v>
+      </c>
+      <c r="C401" t="s">
         <v>790</v>
       </c>
-      <c r="C401" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A402">
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>791</v>
+      </c>
+      <c r="C402" t="s">
         <v>792</v>
       </c>
-      <c r="C402" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A403">
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>793</v>
+      </c>
+      <c r="C403" t="s">
         <v>794</v>
       </c>
-      <c r="C403" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A404">
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>795</v>
+      </c>
+      <c r="C404" t="s">
         <v>796</v>
       </c>
-      <c r="C404" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A405">
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>797</v>
+      </c>
+      <c r="C405" t="s">
         <v>798</v>
       </c>
-      <c r="C405" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A406">
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>799</v>
+      </c>
+      <c r="C406" t="s">
         <v>800</v>
       </c>
-      <c r="C406" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A407">
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>801</v>
+      </c>
+      <c r="C407" t="s">
         <v>802</v>
       </c>
-      <c r="C407" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A408">
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>803</v>
+      </c>
+      <c r="C408" t="s">
         <v>804</v>
       </c>
-      <c r="C408" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A409">
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>805</v>
+      </c>
+      <c r="C409" t="s">
         <v>806</v>
       </c>
-      <c r="C409" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A410">
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>807</v>
+      </c>
+      <c r="C410" t="s">
         <v>808</v>
       </c>
-      <c r="C410" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A411">
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>809</v>
+      </c>
+      <c r="C411" t="s">
         <v>810</v>
       </c>
-      <c r="C411" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A412">
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>811</v>
+      </c>
+      <c r="C412" t="s">
         <v>812</v>
       </c>
-      <c r="C412" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A413">
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>813</v>
+      </c>
+      <c r="C413" t="s">
         <v>814</v>
       </c>
-      <c r="C413" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A414">
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>815</v>
+      </c>
+      <c r="C414" t="s">
         <v>816</v>
       </c>
-      <c r="C414" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A415">
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>817</v>
+      </c>
+      <c r="C415" t="s">
         <v>818</v>
       </c>
-      <c r="C415" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A416">
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>819</v>
+      </c>
+      <c r="C416" t="s">
         <v>820</v>
       </c>
-      <c r="C416" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A417">
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>821</v>
+      </c>
+      <c r="C417" t="s">
         <v>822</v>
       </c>
-      <c r="C417" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A418">
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>823</v>
+      </c>
+      <c r="C418" t="s">
         <v>824</v>
       </c>
-      <c r="C418" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A419">
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>825</v>
+      </c>
+      <c r="C419" t="s">
         <v>826</v>
       </c>
-      <c r="C419" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A420">
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>827</v>
+      </c>
+      <c r="C420" t="s">
         <v>828</v>
       </c>
-      <c r="C420" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A421">
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>829</v>
+      </c>
+      <c r="C421" t="s">
         <v>830</v>
       </c>
-      <c r="C421" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A422">
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>831</v>
+      </c>
+      <c r="C422" t="s">
         <v>832</v>
       </c>
-      <c r="C422" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A423">
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>833</v>
+      </c>
+      <c r="C423" t="s">
         <v>834</v>
       </c>
-      <c r="C423" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A424">
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>835</v>
+      </c>
+      <c r="C424" t="s">
         <v>836</v>
       </c>
-      <c r="C424" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A425">
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>837</v>
+      </c>
+      <c r="C425" t="s">
         <v>838</v>
       </c>
-      <c r="C425" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A426">
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>839</v>
+      </c>
+      <c r="C426" t="s">
         <v>840</v>
       </c>
-      <c r="C426" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A427">
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>841</v>
+      </c>
+      <c r="C427" t="s">
         <v>842</v>
       </c>
-      <c r="C427" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A428">
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C428" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A429">
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C429" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A430">
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>845</v>
+      </c>
+      <c r="C430" t="s">
         <v>846</v>
       </c>
-      <c r="C430" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A431">
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>847</v>
+      </c>
+      <c r="C431" t="s">
         <v>848</v>
       </c>
-      <c r="C431" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A432">
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>849</v>
+      </c>
+      <c r="C432" t="s">
         <v>850</v>
       </c>
-      <c r="C432" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A433">
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>851</v>
+      </c>
+      <c r="C433" t="s">
         <v>852</v>
       </c>
-      <c r="C433" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A434">
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>853</v>
+      </c>
+      <c r="C434" t="s">
         <v>854</v>
       </c>
-      <c r="C434" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A435">
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>855</v>
+      </c>
+      <c r="C435" t="s">
         <v>856</v>
       </c>
-      <c r="C435" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A436">
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>857</v>
+      </c>
+      <c r="C436" t="s">
         <v>858</v>
       </c>
-      <c r="C436" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A437">
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>859</v>
+      </c>
+      <c r="C437" t="s">
         <v>860</v>
       </c>
-      <c r="C437" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A438">
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>861</v>
+      </c>
+      <c r="C438" t="s">
         <v>862</v>
       </c>
-      <c r="C438" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A439">
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>863</v>
+      </c>
+      <c r="C439" t="s">
         <v>864</v>
       </c>
-      <c r="C439" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A440">
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>865</v>
+      </c>
+      <c r="C440" t="s">
         <v>866</v>
       </c>
-      <c r="C440" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A441">
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>867</v>
+      </c>
+      <c r="C441" t="s">
         <v>868</v>
       </c>
-      <c r="C441" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A442">
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>869</v>
+      </c>
+      <c r="C442" t="s">
         <v>870</v>
       </c>
-      <c r="C442" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A443">
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>871</v>
+      </c>
+      <c r="C443" t="s">
         <v>872</v>
       </c>
-      <c r="C443" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A444">
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>873</v>
+      </c>
+      <c r="C444" t="s">
         <v>874</v>
       </c>
-      <c r="C444" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A445">
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>875</v>
+      </c>
+      <c r="C445" t="s">
         <v>876</v>
       </c>
-      <c r="C445" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A446">
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>877</v>
+      </c>
+      <c r="C446" t="s">
         <v>878</v>
       </c>
-      <c r="C446" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A447">
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>879</v>
+      </c>
+      <c r="C447" t="s">
         <v>880</v>
       </c>
-      <c r="C447" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A448">
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>881</v>
+      </c>
+      <c r="C448" t="s">
         <v>882</v>
       </c>
-      <c r="C448" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A449">
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>883</v>
+      </c>
+      <c r="C449" t="s">
         <v>884</v>
       </c>
-      <c r="C449" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A450">
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>885</v>
+      </c>
+      <c r="C450" t="s">
         <v>886</v>
       </c>
-      <c r="C450" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A451">
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C451" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A452">
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>888</v>
+      </c>
+      <c r="C452" t="s">
         <v>889</v>
       </c>
-      <c r="C452" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A453">
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>890</v>
+      </c>
+      <c r="C453" t="s">
         <v>891</v>
       </c>
-      <c r="C453" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A454">
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>892</v>
+      </c>
+      <c r="C454" t="s">
         <v>893</v>
       </c>
-      <c r="C454" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A455">
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>894</v>
+      </c>
+      <c r="C455" t="s">
         <v>895</v>
       </c>
-      <c r="C455" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A456">
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C456" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A457">
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>897</v>
+      </c>
+      <c r="C457" t="s">
         <v>898</v>
       </c>
-      <c r="C457" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A458">
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>899</v>
+      </c>
+      <c r="C458" t="s">
         <v>900</v>
       </c>
-      <c r="C458" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A459">
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>901</v>
+      </c>
+      <c r="C459" t="s">
         <v>902</v>
       </c>
-      <c r="C459" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A460">
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A461">
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>904</v>
+      </c>
+      <c r="C461" t="s">
         <v>905</v>
       </c>
-      <c r="C461" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A462">
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>906</v>
+      </c>
+      <c r="C462" t="s">
         <v>907</v>
       </c>
-      <c r="C462" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A463">
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>908</v>
+      </c>
+      <c r="C463" t="s">
         <v>909</v>
       </c>
-      <c r="C463" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A464">
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>910</v>
+      </c>
+      <c r="C464" t="s">
         <v>911</v>
       </c>
-      <c r="C464" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A465">
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>912</v>
+      </c>
+      <c r="C465" t="s">
         <v>913</v>
       </c>
-      <c r="C465" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A466">
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>914</v>
+      </c>
+      <c r="C466" t="s">
         <v>915</v>
       </c>
-      <c r="C466" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A467">
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A468">
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>917</v>
+      </c>
+      <c r="C468" t="s">
         <v>918</v>
       </c>
-      <c r="C468" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A469">
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>919</v>
+      </c>
+      <c r="C469" t="s">
         <v>920</v>
       </c>
-      <c r="C469" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A470">
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>921</v>
+      </c>
+      <c r="C470" t="s">
         <v>922</v>
       </c>
-      <c r="C470" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A471">
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>923</v>
+      </c>
+      <c r="C471" t="s">
         <v>924</v>
       </c>
-      <c r="C471" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A472">
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>925</v>
+      </c>
+      <c r="C472" t="s">
         <v>926</v>
       </c>
-      <c r="C472" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
+    </row>
+    <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>927</v>
+      </c>
+      <c r="C473" t="s">
         <v>928</v>
       </c>
-      <c r="C473" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A474">
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>929</v>
+      </c>
+      <c r="C474" t="s">
         <v>930</v>
       </c>
-      <c r="C474" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A475">
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>931</v>
+      </c>
+      <c r="C475" t="s">
         <v>932</v>
       </c>
-      <c r="C475" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A476">
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>933</v>
+      </c>
+      <c r="C476" t="s">
         <v>934</v>
       </c>
-      <c r="C476" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A477">
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>935</v>
+      </c>
+      <c r="C477" t="s">
         <v>936</v>
       </c>
-      <c r="C477" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A478">
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C478" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A479">
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>938</v>
+      </c>
+      <c r="C479" t="s">
         <v>939</v>
       </c>
-      <c r="C479" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A480">
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>940</v>
+      </c>
+      <c r="C480" t="s">
         <v>941</v>
       </c>
-      <c r="C480" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A481">
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>942</v>
+      </c>
+      <c r="C481" t="s">
         <v>943</v>
       </c>
-      <c r="C481" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A482">
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>944</v>
+      </c>
+      <c r="C482" t="s">
         <v>945</v>
       </c>
-      <c r="C482" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A483">
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>946</v>
+      </c>
+      <c r="C483" t="s">
         <v>947</v>
       </c>
-      <c r="C483" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A484">
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>948</v>
+      </c>
+      <c r="C484" t="s">
         <v>949</v>
       </c>
-      <c r="C484" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A485">
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>950</v>
+      </c>
+      <c r="C485" t="s">
         <v>951</v>
       </c>
-      <c r="C485" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A486">
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>952</v>
+      </c>
+      <c r="C486" t="s">
         <v>953</v>
       </c>
-      <c r="C486" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A487">
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>954</v>
+      </c>
+      <c r="C487" t="s">
         <v>955</v>
       </c>
-      <c r="C487" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A488">
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>956</v>
+      </c>
+      <c r="C488" t="s">
         <v>957</v>
       </c>
-      <c r="C488" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A489">
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>958</v>
+      </c>
+      <c r="C489" t="s">
         <v>959</v>
       </c>
-      <c r="C489" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A490">
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>960</v>
+      </c>
+      <c r="C490" t="s">
         <v>961</v>
       </c>
-      <c r="C490" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A491">
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>962</v>
+      </c>
+      <c r="C491" t="s">
         <v>963</v>
       </c>
-      <c r="C491" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A492">
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>964</v>
+      </c>
+      <c r="C492" t="s">
         <v>965</v>
       </c>
-      <c r="C492" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A493">
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>966</v>
+      </c>
+      <c r="C493" t="s">
         <v>967</v>
       </c>
-      <c r="C493" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A494">
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>968</v>
+      </c>
+      <c r="C494" t="s">
         <v>969</v>
       </c>
-      <c r="C494" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A495">
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>970</v>
+      </c>
+      <c r="C495" t="s">
         <v>971</v>
       </c>
-      <c r="C495" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A496">
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>972</v>
+      </c>
+      <c r="C496" t="s">
         <v>973</v>
       </c>
-      <c r="C496" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A497">
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>974</v>
+      </c>
+      <c r="C497" t="s">
         <v>975</v>
       </c>
-      <c r="C497" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A498">
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>976</v>
+      </c>
+      <c r="C498" t="s">
         <v>977</v>
       </c>
-      <c r="C498" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A499">
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A500">
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>979</v>
+      </c>
+      <c r="C500" t="s">
         <v>980</v>
       </c>
-      <c r="C500" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A501">
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>981</v>
+      </c>
+      <c r="C501" t="s">
         <v>982</v>
       </c>
-      <c r="C501" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A502">
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>983</v>
+      </c>
+      <c r="C502" t="s">
         <v>984</v>
       </c>
-      <c r="C502" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A503">
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A504">
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>986</v>
+      </c>
+      <c r="C504" t="s">
         <v>987</v>
       </c>
-      <c r="C504" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A505">
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>988</v>
+      </c>
+      <c r="C505" t="s">
         <v>989</v>
       </c>
-      <c r="C505" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A506">
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>990</v>
+      </c>
+      <c r="C506" t="s">
         <v>991</v>
       </c>
-      <c r="C506" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A507">
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>992</v>
+      </c>
+      <c r="C507" t="s">
         <v>993</v>
       </c>
-      <c r="C507" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A508">
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>994</v>
+      </c>
+      <c r="C508" t="s">
         <v>995</v>
       </c>
-      <c r="C508" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A509">
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>996</v>
+      </c>
+      <c r="C509" t="s">
         <v>997</v>
       </c>
-      <c r="C509" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A510">
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>998</v>
+      </c>
+      <c r="C510" t="s">
         <v>999</v>
       </c>
-      <c r="C510" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A511">
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C511" t="s">
         <v>1001</v>
       </c>
-      <c r="C511" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A512">
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C512" t="s">
         <v>1003</v>
       </c>
-      <c r="C512" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A513">
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C513" t="s">
         <v>1005</v>
       </c>
-      <c r="C513" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A514">
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C514" t="s">
         <v>1007</v>
       </c>
-      <c r="C514" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A515">
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C515" t="s">
         <v>1009</v>
       </c>
-      <c r="C515" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A516">
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C516" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A517">
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C517" t="s">
         <v>1012</v>
       </c>
-      <c r="C517" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A518">
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A519">
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C519" t="s">
         <v>1015</v>
       </c>
-      <c r="C519" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A520">
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C520" t="s">
         <v>1017</v>
       </c>
-      <c r="C520" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A521">
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C521" t="s">
         <v>1019</v>
       </c>
-      <c r="C521" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A522">
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C522" t="s">
         <v>1021</v>
       </c>
-      <c r="C522" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A523">
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C523" t="s">
         <v>1023</v>
       </c>
-      <c r="C523" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A524">
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C524" t="s">
         <v>1025</v>
       </c>
-      <c r="C524" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A525">
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A526">
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C526" t="s">
         <v>1028</v>
       </c>
-      <c r="C526" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A527">
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C527" t="s">
         <v>1030</v>
       </c>
-      <c r="C527" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A528">
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C528" t="s">
         <v>1032</v>
       </c>
-      <c r="C528" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A529">
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C529" t="s">
         <v>1034</v>
       </c>
-      <c r="C529" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A530">
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A531">
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C531" t="s">
         <v>1037</v>
       </c>
-      <c r="C531" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A532">
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C532" t="s">
         <v>1039</v>
       </c>
-      <c r="C532" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A533">
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C533" t="s">
         <v>1041</v>
       </c>
-      <c r="C533" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A534">
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C534" t="s">
         <v>1043</v>
       </c>
-      <c r="C534" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A535">
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C535" t="s">
         <v>1045</v>
       </c>
-      <c r="C535" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A536">
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C536" t="s">
         <v>1047</v>
       </c>
-      <c r="C536" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A537">
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C537" t="s">
         <v>1049</v>
       </c>
-      <c r="C537" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A538">
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C538" t="s">
         <v>1051</v>
       </c>
-      <c r="C538" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A539">
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C539" t="s">
         <v>1053</v>
       </c>
-      <c r="C539" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A540">
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C540" t="s">
         <v>1055</v>
       </c>
-      <c r="C540" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A541">
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C541" t="s">
         <v>1057</v>
       </c>
-      <c r="C541" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A542">
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C542" t="s">
         <v>1059</v>
       </c>
-      <c r="C542" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A543">
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C543" t="s">
         <v>1061</v>
       </c>
-      <c r="C543" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A544">
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C544" t="s">
         <v>1063</v>
       </c>
-      <c r="C544" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A545">
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C545" t="s">
         <v>1065</v>
       </c>
-      <c r="C545" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A546">
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C546" t="s">
         <v>1067</v>
       </c>
-      <c r="C546" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A547">
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A548">
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C548" t="s">
         <v>1070</v>
       </c>
-      <c r="C548" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A549">
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C549" t="s">
         <v>1072</v>
       </c>
-      <c r="C549" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A550">
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C550" t="s">
         <v>1074</v>
       </c>
-      <c r="C550" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A551">
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C551" t="s">
         <v>1076</v>
       </c>
-      <c r="C551" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A552">
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C552" t="s">
         <v>1078</v>
       </c>
-      <c r="C552" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A553">
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C553" t="s">
         <v>1080</v>
       </c>
-      <c r="C553" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A554">
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C554" t="s">
         <v>1082</v>
       </c>
-      <c r="C554" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A555">
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C555" t="s">
         <v>1084</v>
       </c>
-      <c r="C555" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A556">
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C556" t="s">
         <v>1086</v>
       </c>
-      <c r="C556" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A557">
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C557" t="s">
         <v>1088</v>
       </c>
-      <c r="C557" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A558">
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C558" t="s">
         <v>1090</v>
       </c>
-      <c r="C558" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A559">
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A560">
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C560" t="s">
         <v>1093</v>
       </c>
-      <c r="C560" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A561">
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C561" t="s">
         <v>1095</v>
       </c>
-      <c r="C561" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A562">
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C562" t="s">
         <v>1097</v>
       </c>
-      <c r="C562" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A563">
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C563" t="s">
         <v>1099</v>
       </c>
-      <c r="C563" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A564">
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C564" t="s">
         <v>1101</v>
       </c>
-      <c r="C564" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A565">
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C565" t="s">
         <v>1103</v>
       </c>
-      <c r="C565" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A566">
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C566" t="s">
         <v>1105</v>
       </c>
-      <c r="C566" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A567">
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C567" t="s">
         <v>1107</v>
       </c>
-      <c r="C567" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A568">
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C568" t="s">
         <v>1109</v>
       </c>
-      <c r="C568" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A569">
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C569" t="s">
         <v>1111</v>
       </c>
-      <c r="C569" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A570">
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C570" t="s">
         <v>1113</v>
       </c>
-      <c r="C570" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A571">
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C571" t="s">
         <v>1115</v>
       </c>
-      <c r="C571" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A572">
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C572" t="s">
         <v>1117</v>
       </c>
-      <c r="C572" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A573">
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C573" t="s">
         <v>1119</v>
       </c>
-      <c r="C573" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A574">
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C574" t="s">
         <v>1121</v>
       </c>
-      <c r="C574" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A575">
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A576">
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C576" t="s">
         <v>1124</v>
       </c>
-      <c r="C576" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A577">
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A578">
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A579">
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C579" t="s">
         <v>1126</v>
       </c>
-      <c r="C579" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A580">
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C580" t="s">
         <v>1128</v>
       </c>
-      <c r="C580" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A581">
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C581" t="s">
         <v>1130</v>
       </c>
-      <c r="C581" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A582">
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C582" t="s">
         <v>1132</v>
       </c>
-      <c r="C582" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A583">
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A584">
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A585">
         <v>612</v>
       </c>
       <c r="B585" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C585" t="s">
         <v>1135</v>
       </c>
-      <c r="C585" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A586">
         <v>615</v>
       </c>
       <c r="B586" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C586" t="s">
         <v>1137</v>
       </c>
-      <c r="C586" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A587">
         <v>617</v>
       </c>
       <c r="B587" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C587" t="s">
         <v>1139</v>
       </c>
-      <c r="C587" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A588">
         <v>618</v>
       </c>
       <c r="B588" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C588" t="s">
         <v>1141</v>
       </c>
-      <c r="C588" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A589">
         <v>625</v>
       </c>
       <c r="B589" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C589" t="s">
         <v>1143</v>
       </c>
-      <c r="C589" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A590">
         <v>624</v>
       </c>
       <c r="B590" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C590" t="s">
         <v>1145</v>
       </c>
-      <c r="C590" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A591">
         <v>626</v>
       </c>
       <c r="B591" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C591" t="s">
         <v>1147</v>
       </c>
-      <c r="C591" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A592">
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C592" t="s">
         <v>1149</v>
       </c>
-      <c r="C592" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A593">
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C593" t="s">
         <v>1151</v>
       </c>
-      <c r="C593" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A594">
         <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A595">
         <v>633</v>
       </c>
       <c r="B595" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C595" t="s">
         <v>1154</v>
       </c>
-      <c r="C595" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A596">
         <v>635</v>
       </c>
       <c r="B596" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C596" t="s">
         <v>1156</v>
       </c>
-      <c r="C596" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A597">
         <v>636</v>
       </c>
       <c r="B597" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C597" t="s">
         <v>1158</v>
       </c>
-      <c r="C597" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A598">
         <v>642</v>
       </c>
       <c r="B598" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C598" t="s">
         <v>1160</v>
       </c>
-      <c r="C598" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A599">
         <v>644</v>
       </c>
       <c r="B599" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C599" t="s">
         <v>1162</v>
       </c>
-      <c r="C599" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A600">
         <v>646</v>
       </c>
       <c r="B600" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C600" t="s">
         <v>1164</v>
       </c>
-      <c r="C600" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A601">
         <v>649</v>
       </c>
       <c r="B601" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C601" t="s">
         <v>1166</v>
       </c>
-      <c r="C601" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A602">
         <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A603">
         <v>651</v>
       </c>
       <c r="B603" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C603" t="s">
         <v>1169</v>
       </c>
-      <c r="C603" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A604">
         <v>653</v>
       </c>
       <c r="B604" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C604" t="s">
         <v>1171</v>
       </c>
-      <c r="C604" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A605">
         <v>654</v>
       </c>
       <c r="B605" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C605" t="s">
         <v>1173</v>
       </c>
-      <c r="C605" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A606">
         <v>655</v>
       </c>
       <c r="B606" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C606" t="s">
         <v>1175</v>
       </c>
-      <c r="C606" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A607">
         <v>659</v>
       </c>
       <c r="B607" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C607" t="s">
         <v>1177</v>
       </c>
-      <c r="C607" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A608">
         <v>660</v>
       </c>
       <c r="B608" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C608" t="s">
         <v>1179</v>
       </c>
-      <c r="C608" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A609">
         <v>661</v>
       </c>
       <c r="B609" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C609" t="s">
         <v>1181</v>
       </c>
-      <c r="C609" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A610">
         <v>663</v>
       </c>
       <c r="B610" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C610" t="s">
         <v>1183</v>
       </c>
-      <c r="C610" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A611">
         <v>667</v>
       </c>
       <c r="B611" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C611" t="s">
         <v>1185</v>
       </c>
-      <c r="C611" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A612">
         <v>670</v>
       </c>
       <c r="B612" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C612" t="s">
         <v>1187</v>
       </c>
-      <c r="C612" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A613">
         <v>673</v>
       </c>
       <c r="B613" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C613" t="s">
         <v>1189</v>
       </c>
-      <c r="C613" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A614">
         <v>674</v>
       </c>
       <c r="B614" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C614" t="s">
         <v>1191</v>
       </c>
-      <c r="C614" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A615">
         <v>675</v>
       </c>
       <c r="B615" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C615" t="s">
         <v>1193</v>
       </c>
-      <c r="C615" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A616">
         <v>680</v>
       </c>
       <c r="B616" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C616" t="s">
         <v>1195</v>
       </c>
-      <c r="C616" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A617">
         <v>681</v>
       </c>
       <c r="B617" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C617" t="s">
         <v>1197</v>
       </c>
-      <c r="C617" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A618">
         <v>682</v>
       </c>
       <c r="B618" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C618" t="s">
         <v>1199</v>
       </c>
-      <c r="C618" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A619">
         <v>683</v>
       </c>
       <c r="B619" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C619" t="s">
         <v>1201</v>
       </c>
-      <c r="C619" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A620">
         <v>684</v>
       </c>
       <c r="B620" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C620" t="s">
         <v>1203</v>
       </c>
-      <c r="C620" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A621">
         <v>685</v>
       </c>
       <c r="B621" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C621" t="s">
         <v>1205</v>
       </c>
-      <c r="C621" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A622">
         <v>686</v>
       </c>
       <c r="B622" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C622" t="s">
         <v>1207</v>
       </c>
-      <c r="C622" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A623">
         <v>689</v>
       </c>
       <c r="B623" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C623" t="s">
         <v>1209</v>
       </c>
-      <c r="C623" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A624">
         <v>697</v>
       </c>
       <c r="B624" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C624" t="s">
         <v>1211</v>
       </c>
-      <c r="C624" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A625">
         <v>701</v>
       </c>
       <c r="B625" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C625" t="s">
         <v>1213</v>
       </c>
-      <c r="C625" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A626">
         <v>702</v>
       </c>
       <c r="B626" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C626" t="s">
         <v>1215</v>
       </c>
-      <c r="C626" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A627">
         <v>704</v>
       </c>
       <c r="B627" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C627" t="s">
         <v>1217</v>
       </c>
-      <c r="C627" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A628">
         <v>705</v>
       </c>
       <c r="B628" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C628" t="s">
         <v>1219</v>
       </c>
-      <c r="C628" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A629">
         <v>710</v>
       </c>
       <c r="B629" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C629" t="s">
         <v>1221</v>
       </c>
-      <c r="C629" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A630">
         <v>711</v>
       </c>
       <c r="B630" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C630" t="s">
         <v>1223</v>
       </c>
-      <c r="C630" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A631">
         <v>712</v>
       </c>
       <c r="B631" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C631" t="s">
         <v>1225</v>
       </c>
-      <c r="C631" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A632">
         <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A633">
         <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A634">
         <v>718</v>
       </c>
       <c r="B634" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C634" t="s">
         <v>1229</v>
       </c>
-      <c r="C634" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A635">
         <v>719</v>
       </c>
       <c r="B635" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C635" t="s">
         <v>1231</v>
       </c>
-      <c r="C635" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    </row>
+    <row r="636" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A636">
         <v>721</v>
       </c>
       <c r="B636" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C636" t="s">
         <v>1233</v>
       </c>
-      <c r="C636" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A637">
         <v>722</v>
       </c>
       <c r="B637" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C637" t="s">
         <v>1235</v>
       </c>
-      <c r="C637" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A638">
         <v>723</v>
       </c>
       <c r="B638" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C638" t="s">
         <v>1237</v>
       </c>
-      <c r="C638" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A639">
         <v>724</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A640">
         <v>725</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C640" t="s">
         <v>1239</v>
       </c>
-      <c r="C640" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A641">
         <v>726</v>
       </c>
       <c r="B641" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C641" t="s">
         <v>1241</v>
       </c>
-      <c r="C641" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A642">
         <v>727</v>
       </c>
       <c r="B642" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C642" t="s">
         <v>1243</v>
       </c>
-      <c r="C642" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    </row>
+    <row r="643" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A643">
         <v>728</v>
       </c>
       <c r="B643" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C643" t="s">
         <v>1245</v>
       </c>
-      <c r="C643" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    </row>
+    <row r="644" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A644">
         <v>729</v>
       </c>
       <c r="B644" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C644" t="s">
         <v>1247</v>
       </c>
-      <c r="C644" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A645">
         <v>730</v>
       </c>
       <c r="B645" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C645" t="s">
         <v>1249</v>
       </c>
-      <c r="C645" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A646">
         <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A647">
         <v>733</v>
       </c>
       <c r="B647" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C647" t="s">
         <v>1252</v>
       </c>
-      <c r="C647" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A648">
         <v>735</v>
       </c>
       <c r="B648" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C648" t="s">
         <v>1254</v>
       </c>
-      <c r="C648" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A649">
         <v>736</v>
       </c>
       <c r="B649" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C649" t="s">
         <v>1256</v>
       </c>
-      <c r="C649" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A650">
         <v>737</v>
       </c>
       <c r="B650" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C650" t="s">
         <v>1258</v>
       </c>
-      <c r="C650" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A651">
         <v>738</v>
       </c>
       <c r="B651" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C651" t="s">
         <v>1260</v>
       </c>
-      <c r="C651" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A652">
         <v>739</v>
       </c>
       <c r="B652" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C652" t="s">
         <v>1262</v>
       </c>
-      <c r="C652" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A653">
         <v>740</v>
       </c>
       <c r="B653" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C653" t="s">
         <v>1264</v>
       </c>
-      <c r="C653" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A654">
         <v>741</v>
       </c>
       <c r="B654" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C654" t="s">
         <v>1266</v>
       </c>
-      <c r="C654" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A655">
         <v>742</v>
       </c>
       <c r="B655" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C655" t="s">
         <v>1268</v>
       </c>
-      <c r="C655" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A656">
         <v>743</v>
       </c>
       <c r="B656" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C656" t="s">
         <v>1270</v>
       </c>
-      <c r="C656" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A657">
         <v>744</v>
       </c>
       <c r="B657" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C657" t="s">
         <v>1272</v>
       </c>
-      <c r="C657" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    </row>
+    <row r="658" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A658">
         <v>745</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C658" t="s">
         <v>1274</v>
       </c>
-      <c r="C658" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A659">
         <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C659" t="s">
         <v>1276</v>
       </c>
-      <c r="C659" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A660">
         <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C660" t="s">
         <v>1278</v>
       </c>
-      <c r="C660" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A661">
         <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C661" t="s">
         <v>1280</v>
       </c>
-      <c r="C661" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A662">
         <v>749</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C662" t="s">
         <v>1282</v>
       </c>
-      <c r="C662" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A663">
         <v>750</v>
       </c>
       <c r="B663" s="1"/>
       <c r="C663" s="3" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A664">
         <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C664" t="s">
         <v>1284</v>
       </c>
-      <c r="C664" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A665">
         <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A666">
         <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C666" t="s">
         <v>1287</v>
       </c>
-      <c r="C666" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A667">
         <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C667" t="s">
         <v>1289</v>
       </c>
-      <c r="C667" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A668">
         <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C668" t="s">
         <v>1291</v>
       </c>
-      <c r="C668" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A669">
         <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A670">
         <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C670" t="s">
         <v>1294</v>
       </c>
-      <c r="C670" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A671">
         <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C671" t="s">
         <v>1296</v>
       </c>
-      <c r="C671" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A672">
         <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C672" t="s">
         <v>1298</v>
       </c>
-      <c r="C672" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A673">
         <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C673" t="s">
         <v>1300</v>
       </c>
-      <c r="C673" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A674">
         <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C674" t="s">
         <v>1302</v>
       </c>
-      <c r="C674" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A675">
         <v>765</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C675" t="s">
         <v>1304</v>
       </c>
-      <c r="C675" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A676">
         <v>766</v>
       </c>
       <c r="B676" s="1"/>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A677">
         <v>767</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C677" t="s">
         <v>1306</v>
       </c>
-      <c r="C677" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A678">
         <v>768</v>
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A679">
         <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C679" t="s">
         <v>1309</v>
       </c>
-      <c r="C679" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A680">
         <v>772</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C680" s="3" t="s">
         <v>1314</v>
       </c>
-      <c r="C680" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A681">
         <v>773</v>
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A682">
         <v>774</v>
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A683">
         <v>776</v>
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A684">
         <v>779</v>
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A685">
         <v>780</v>
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A686">
         <v>781</v>
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A687">
         <v>783</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A688">
         <v>784</v>
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A689">
         <v>782</v>
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A690">
         <v>10001</v>
       </c>
       <c r="B690" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A691">
         <v>10003</v>
       </c>
       <c r="B691" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C691" t="s">
         <v>1309</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1310</v>
       </c>
     </row>
   </sheetData>
@@ -12275,7 +12276,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12FD81B-5F6B-44CC-A6E7-4ABB4D91D14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154764E1-0675-46E7-8DBC-4A9BC5551E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -968,9 +968,6 @@
     <t>R·I·O·T</t>
   </si>
   <si>
-    <t>riot,come in</t>
-  </si>
-  <si>
     <t>ツキアカリのミチシルベ</t>
   </si>
   <si>
@@ -4291,6 +4288,10 @@
   </si>
   <si>
     <t>bloombloom,生长,boomboom</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>riot,come in,暴乱,骚乱,暴动</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5345,7 +5346,7 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
@@ -5961,7 +5962,7 @@
         <v>224</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
@@ -6148,7 +6149,7 @@
         <v>257</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.15">
@@ -6389,8 +6390,8 @@
       <c r="B152" t="s">
         <v>300</v>
       </c>
-      <c r="C152" t="s">
-        <v>301</v>
+      <c r="C152" s="3" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.15">
@@ -6398,10 +6399,10 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
+        <v>301</v>
+      </c>
+      <c r="C153" t="s">
         <v>302</v>
-      </c>
-      <c r="C153" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.15">
@@ -6409,10 +6410,10 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
+        <v>303</v>
+      </c>
+      <c r="C154" t="s">
         <v>304</v>
-      </c>
-      <c r="C154" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.15">
@@ -6420,10 +6421,10 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
+        <v>305</v>
+      </c>
+      <c r="C155" t="s">
         <v>306</v>
-      </c>
-      <c r="C155" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.15">
@@ -6431,10 +6432,10 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
+        <v>307</v>
+      </c>
+      <c r="C156" t="s">
         <v>308</v>
-      </c>
-      <c r="C156" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.15">
@@ -6442,10 +6443,10 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
+        <v>309</v>
+      </c>
+      <c r="C157" t="s">
         <v>310</v>
-      </c>
-      <c r="C157" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.15">
@@ -6453,10 +6454,10 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
+        <v>311</v>
+      </c>
+      <c r="C158" t="s">
         <v>312</v>
-      </c>
-      <c r="C158" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.15">
@@ -6464,10 +6465,10 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
+        <v>313</v>
+      </c>
+      <c r="C159" t="s">
         <v>314</v>
-      </c>
-      <c r="C159" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.15">
@@ -6475,10 +6476,10 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
+        <v>315</v>
+      </c>
+      <c r="C160" t="s">
         <v>316</v>
-      </c>
-      <c r="C160" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.15">
@@ -6486,10 +6487,10 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
+        <v>317</v>
+      </c>
+      <c r="C161" t="s">
         <v>318</v>
-      </c>
-      <c r="C161" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.15">
@@ -6497,10 +6498,10 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
+        <v>319</v>
+      </c>
+      <c r="C162" t="s">
         <v>320</v>
-      </c>
-      <c r="C162" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.15">
@@ -6508,10 +6509,10 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
+        <v>321</v>
+      </c>
+      <c r="C163" t="s">
         <v>322</v>
-      </c>
-      <c r="C163" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.15">
@@ -6519,10 +6520,10 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
+        <v>323</v>
+      </c>
+      <c r="C164" t="s">
         <v>324</v>
-      </c>
-      <c r="C164" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.15">
@@ -6530,10 +6531,10 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
+        <v>325</v>
+      </c>
+      <c r="C165" t="s">
         <v>326</v>
-      </c>
-      <c r="C165" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.15">
@@ -6541,10 +6542,10 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
+        <v>327</v>
+      </c>
+      <c r="C166" t="s">
         <v>328</v>
-      </c>
-      <c r="C166" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.15">
@@ -6552,10 +6553,10 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.15">
@@ -6563,10 +6564,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
+        <v>330</v>
+      </c>
+      <c r="C168" t="s">
         <v>331</v>
-      </c>
-      <c r="C168" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.15">
@@ -6574,10 +6575,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
+        <v>332</v>
+      </c>
+      <c r="C169" t="s">
         <v>333</v>
-      </c>
-      <c r="C169" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.15">
@@ -6585,10 +6586,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
+        <v>334</v>
+      </c>
+      <c r="C170" t="s">
         <v>335</v>
-      </c>
-      <c r="C170" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.15">
@@ -6596,10 +6597,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
+        <v>336</v>
+      </c>
+      <c r="C171" t="s">
         <v>337</v>
-      </c>
-      <c r="C171" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.15">
@@ -6607,10 +6608,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
+        <v>338</v>
+      </c>
+      <c r="C172" t="s">
         <v>339</v>
-      </c>
-      <c r="C172" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.15">
@@ -6618,10 +6619,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
+        <v>340</v>
+      </c>
+      <c r="C173" t="s">
         <v>341</v>
-      </c>
-      <c r="C173" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.15">
@@ -6629,10 +6630,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
+        <v>342</v>
+      </c>
+      <c r="C174" t="s">
         <v>343</v>
-      </c>
-      <c r="C174" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.15">
@@ -6640,10 +6641,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
+        <v>344</v>
+      </c>
+      <c r="C175" t="s">
         <v>345</v>
-      </c>
-      <c r="C175" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.15">
@@ -6651,10 +6652,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
+        <v>346</v>
+      </c>
+      <c r="C176" t="s">
         <v>347</v>
-      </c>
-      <c r="C176" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.15">
@@ -6662,10 +6663,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
+        <v>348</v>
+      </c>
+      <c r="C177" t="s">
         <v>349</v>
-      </c>
-      <c r="C177" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.15">
@@ -6673,10 +6674,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
+        <v>350</v>
+      </c>
+      <c r="C178" t="s">
         <v>351</v>
-      </c>
-      <c r="C178" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.15">
@@ -6684,10 +6685,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
+        <v>352</v>
+      </c>
+      <c r="C179" t="s">
         <v>353</v>
-      </c>
-      <c r="C179" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.15">
@@ -6695,10 +6696,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
+        <v>354</v>
+      </c>
+      <c r="C180" t="s">
         <v>355</v>
-      </c>
-      <c r="C180" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.15">
@@ -6706,10 +6707,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
+        <v>356</v>
+      </c>
+      <c r="C181" t="s">
         <v>357</v>
-      </c>
-      <c r="C181" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.15">
@@ -6717,10 +6718,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>358</v>
+      </c>
+      <c r="C182" t="s">
         <v>359</v>
-      </c>
-      <c r="C182" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.15">
@@ -6728,10 +6729,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
+        <v>360</v>
+      </c>
+      <c r="C183" t="s">
         <v>361</v>
-      </c>
-      <c r="C183" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.15">
@@ -6739,10 +6740,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>362</v>
+      </c>
+      <c r="C184" t="s">
         <v>363</v>
-      </c>
-      <c r="C184" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.15">
@@ -6750,10 +6751,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
+        <v>364</v>
+      </c>
+      <c r="C185" t="s">
         <v>365</v>
-      </c>
-      <c r="C185" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.15">
@@ -6761,10 +6762,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
+        <v>366</v>
+      </c>
+      <c r="C186" t="s">
         <v>367</v>
-      </c>
-      <c r="C186" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.15">
@@ -6772,10 +6773,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
+        <v>368</v>
+      </c>
+      <c r="C187" t="s">
         <v>369</v>
-      </c>
-      <c r="C187" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.15">
@@ -6783,10 +6784,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
+        <v>370</v>
+      </c>
+      <c r="C188" t="s">
         <v>371</v>
-      </c>
-      <c r="C188" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.15">
@@ -6794,10 +6795,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
+        <v>372</v>
+      </c>
+      <c r="C189" t="s">
         <v>373</v>
-      </c>
-      <c r="C189" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.15">
@@ -6805,10 +6806,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
+        <v>374</v>
+      </c>
+      <c r="C190" t="s">
         <v>375</v>
-      </c>
-      <c r="C190" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.15">
@@ -6816,10 +6817,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
+        <v>376</v>
+      </c>
+      <c r="C191" t="s">
         <v>377</v>
-      </c>
-      <c r="C191" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.15">
@@ -6827,10 +6828,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
+        <v>378</v>
+      </c>
+      <c r="C192" t="s">
         <v>379</v>
-      </c>
-      <c r="C192" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.15">
@@ -6838,10 +6839,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>380</v>
+      </c>
+      <c r="C193" t="s">
         <v>381</v>
-      </c>
-      <c r="C193" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.15">
@@ -6849,10 +6850,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
+        <v>382</v>
+      </c>
+      <c r="C194" t="s">
         <v>383</v>
-      </c>
-      <c r="C194" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.15">
@@ -6860,10 +6861,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
+        <v>384</v>
+      </c>
+      <c r="C195" t="s">
         <v>385</v>
-      </c>
-      <c r="C195" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.15">
@@ -6871,10 +6872,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
+        <v>386</v>
+      </c>
+      <c r="C196" t="s">
         <v>387</v>
-      </c>
-      <c r="C196" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.15">
@@ -6882,10 +6883,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
+        <v>388</v>
+      </c>
+      <c r="C197" t="s">
         <v>389</v>
-      </c>
-      <c r="C197" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.15">
@@ -6893,10 +6894,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
+        <v>390</v>
+      </c>
+      <c r="C198" t="s">
         <v>391</v>
-      </c>
-      <c r="C198" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.15">
@@ -6904,10 +6905,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
+        <v>392</v>
+      </c>
+      <c r="C199" t="s">
         <v>393</v>
-      </c>
-      <c r="C199" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.15">
@@ -6915,10 +6916,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
+        <v>394</v>
+      </c>
+      <c r="C200" t="s">
         <v>395</v>
-      </c>
-      <c r="C200" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.15">
@@ -6926,10 +6927,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
+        <v>396</v>
+      </c>
+      <c r="C201" t="s">
         <v>397</v>
-      </c>
-      <c r="C201" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.15">
@@ -6937,10 +6938,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
+        <v>398</v>
+      </c>
+      <c r="C202" t="s">
         <v>399</v>
-      </c>
-      <c r="C202" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.15">
@@ -6948,10 +6949,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
+        <v>400</v>
+      </c>
+      <c r="C203" t="s">
         <v>401</v>
-      </c>
-      <c r="C203" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.15">
@@ -6959,10 +6960,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
+        <v>402</v>
+      </c>
+      <c r="C204" t="s">
         <v>403</v>
-      </c>
-      <c r="C204" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.15">
@@ -6970,10 +6971,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
+        <v>404</v>
+      </c>
+      <c r="C205" t="s">
         <v>405</v>
-      </c>
-      <c r="C205" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.15">
@@ -6981,10 +6982,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
+        <v>406</v>
+      </c>
+      <c r="C206" t="s">
         <v>407</v>
-      </c>
-      <c r="C206" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.15">
@@ -6992,10 +6993,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
+        <v>408</v>
+      </c>
+      <c r="C207" t="s">
         <v>409</v>
-      </c>
-      <c r="C207" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.15">
@@ -7003,10 +7004,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
+        <v>410</v>
+      </c>
+      <c r="C208" t="s">
         <v>411</v>
-      </c>
-      <c r="C208" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.15">
@@ -7014,10 +7015,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
+        <v>412</v>
+      </c>
+      <c r="C209" t="s">
         <v>413</v>
-      </c>
-      <c r="C209" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.15">
@@ -7025,10 +7026,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
+        <v>414</v>
+      </c>
+      <c r="C210" t="s">
         <v>415</v>
-      </c>
-      <c r="C210" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.15">
@@ -7036,10 +7037,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
+        <v>416</v>
+      </c>
+      <c r="C211" t="s">
         <v>417</v>
-      </c>
-      <c r="C211" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.15">
@@ -7047,10 +7048,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
+        <v>418</v>
+      </c>
+      <c r="C212" t="s">
         <v>419</v>
-      </c>
-      <c r="C212" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.15">
@@ -7058,10 +7059,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
+        <v>420</v>
+      </c>
+      <c r="C213" t="s">
         <v>421</v>
-      </c>
-      <c r="C213" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.15">
@@ -7069,10 +7070,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
+        <v>422</v>
+      </c>
+      <c r="C214" t="s">
         <v>423</v>
-      </c>
-      <c r="C214" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.15">
@@ -7080,10 +7081,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
+        <v>424</v>
+      </c>
+      <c r="C215" t="s">
         <v>425</v>
-      </c>
-      <c r="C215" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.15">
@@ -7091,10 +7092,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
+        <v>426</v>
+      </c>
+      <c r="C216" t="s">
         <v>427</v>
-      </c>
-      <c r="C216" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.15">
@@ -7102,10 +7103,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
+        <v>428</v>
+      </c>
+      <c r="C217" t="s">
         <v>429</v>
-      </c>
-      <c r="C217" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.15">
@@ -7113,10 +7114,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
+        <v>430</v>
+      </c>
+      <c r="C218" t="s">
         <v>431</v>
-      </c>
-      <c r="C218" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.15">
@@ -7124,10 +7125,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
+        <v>432</v>
+      </c>
+      <c r="C219" t="s">
         <v>433</v>
-      </c>
-      <c r="C219" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.15">
@@ -7135,10 +7136,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
+        <v>434</v>
+      </c>
+      <c r="C220" t="s">
         <v>435</v>
-      </c>
-      <c r="C220" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.15">
@@ -7146,10 +7147,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
+        <v>436</v>
+      </c>
+      <c r="C221" t="s">
         <v>437</v>
-      </c>
-      <c r="C221" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.15">
@@ -7157,10 +7158,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
+        <v>438</v>
+      </c>
+      <c r="C222" t="s">
         <v>439</v>
-      </c>
-      <c r="C222" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.15">
@@ -7168,10 +7169,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
+        <v>440</v>
+      </c>
+      <c r="C223" t="s">
         <v>441</v>
-      </c>
-      <c r="C223" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.15">
@@ -7179,10 +7180,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.15">
@@ -7190,10 +7191,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>443</v>
+      </c>
+      <c r="C225" t="s">
         <v>444</v>
-      </c>
-      <c r="C225" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.15">
@@ -7201,10 +7202,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>445</v>
+      </c>
+      <c r="C226" t="s">
         <v>446</v>
-      </c>
-      <c r="C226" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.15">
@@ -7212,10 +7213,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>447</v>
+      </c>
+      <c r="C227" t="s">
         <v>448</v>
-      </c>
-      <c r="C227" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.15">
@@ -7223,10 +7224,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>449</v>
+      </c>
+      <c r="C228" t="s">
         <v>450</v>
-      </c>
-      <c r="C228" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.15">
@@ -7234,10 +7235,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
+        <v>451</v>
+      </c>
+      <c r="C229" t="s">
         <v>452</v>
-      </c>
-      <c r="C229" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.15">
@@ -7245,10 +7246,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
+        <v>453</v>
+      </c>
+      <c r="C230" t="s">
         <v>454</v>
-      </c>
-      <c r="C230" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.15">
@@ -7256,10 +7257,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>455</v>
+      </c>
+      <c r="C231" t="s">
         <v>456</v>
-      </c>
-      <c r="C231" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.15">
@@ -7267,10 +7268,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>457</v>
+      </c>
+      <c r="C232" t="s">
         <v>458</v>
-      </c>
-      <c r="C232" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.15">
@@ -7278,10 +7279,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>459</v>
+      </c>
+      <c r="C233" t="s">
         <v>460</v>
-      </c>
-      <c r="C233" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.15">
@@ -7289,10 +7290,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
+        <v>461</v>
+      </c>
+      <c r="C234" t="s">
         <v>462</v>
-      </c>
-      <c r="C234" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.15">
@@ -7300,10 +7301,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>463</v>
+      </c>
+      <c r="C235" t="s">
         <v>464</v>
-      </c>
-      <c r="C235" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.15">
@@ -7311,10 +7312,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>465</v>
+      </c>
+      <c r="C236" t="s">
         <v>466</v>
-      </c>
-      <c r="C236" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.15">
@@ -7322,10 +7323,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>467</v>
+      </c>
+      <c r="C237" t="s">
         <v>468</v>
-      </c>
-      <c r="C237" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.15">
@@ -7333,10 +7334,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>469</v>
+      </c>
+      <c r="C238" t="s">
         <v>470</v>
-      </c>
-      <c r="C238" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.15">
@@ -7344,10 +7345,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>471</v>
+      </c>
+      <c r="C239" t="s">
         <v>472</v>
-      </c>
-      <c r="C239" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.15">
@@ -7355,10 +7356,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>473</v>
+      </c>
+      <c r="C240" t="s">
         <v>474</v>
-      </c>
-      <c r="C240" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.15">
@@ -7366,10 +7367,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>475</v>
+      </c>
+      <c r="C241" t="s">
         <v>476</v>
-      </c>
-      <c r="C241" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.15">
@@ -7377,10 +7378,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>477</v>
+      </c>
+      <c r="C242" t="s">
         <v>478</v>
-      </c>
-      <c r="C242" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.15">
@@ -7388,10 +7389,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>479</v>
+      </c>
+      <c r="C243" t="s">
         <v>480</v>
-      </c>
-      <c r="C243" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.15">
@@ -7399,10 +7400,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>481</v>
+      </c>
+      <c r="C244" t="s">
         <v>482</v>
-      </c>
-      <c r="C244" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.15">
@@ -7410,10 +7411,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>483</v>
+      </c>
+      <c r="C245" t="s">
         <v>484</v>
-      </c>
-      <c r="C245" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.15">
@@ -7421,10 +7422,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>485</v>
+      </c>
+      <c r="C246" t="s">
         <v>486</v>
-      </c>
-      <c r="C246" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.15">
@@ -7432,10 +7433,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>487</v>
+      </c>
+      <c r="C247" t="s">
         <v>488</v>
-      </c>
-      <c r="C247" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.15">
@@ -7443,10 +7444,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>489</v>
+      </c>
+      <c r="C248" t="s">
         <v>490</v>
-      </c>
-      <c r="C248" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.15">
@@ -7454,10 +7455,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>491</v>
+      </c>
+      <c r="C249" t="s">
         <v>492</v>
-      </c>
-      <c r="C249" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.15">
@@ -7465,10 +7466,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
+        <v>493</v>
+      </c>
+      <c r="C250" t="s">
         <v>494</v>
-      </c>
-      <c r="C250" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.15">
@@ -7476,10 +7477,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.15">
@@ -7487,10 +7488,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C252" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.15">
@@ -7498,10 +7499,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>497</v>
+      </c>
+      <c r="C253" t="s">
         <v>498</v>
-      </c>
-      <c r="C253" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.15">
@@ -7509,10 +7510,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.15">
@@ -7520,10 +7521,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>500</v>
+      </c>
+      <c r="C255" t="s">
         <v>501</v>
-      </c>
-      <c r="C255" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.15">
@@ -7531,10 +7532,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>502</v>
+      </c>
+      <c r="C256" t="s">
         <v>503</v>
-      </c>
-      <c r="C256" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.15">
@@ -7542,10 +7543,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>504</v>
+      </c>
+      <c r="C257" t="s">
         <v>505</v>
-      </c>
-      <c r="C257" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.15">
@@ -7553,10 +7554,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>506</v>
+      </c>
+      <c r="C258" t="s">
         <v>507</v>
-      </c>
-      <c r="C258" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.15">
@@ -7564,10 +7565,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>508</v>
+      </c>
+      <c r="C259" t="s">
         <v>509</v>
-      </c>
-      <c r="C259" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.15">
@@ -7575,10 +7576,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>510</v>
+      </c>
+      <c r="C260" t="s">
         <v>511</v>
-      </c>
-      <c r="C260" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.15">
@@ -7586,10 +7587,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>512</v>
+      </c>
+      <c r="C261" t="s">
         <v>513</v>
-      </c>
-      <c r="C261" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.15">
@@ -7597,10 +7598,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>514</v>
+      </c>
+      <c r="C262" t="s">
         <v>515</v>
-      </c>
-      <c r="C262" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.15">
@@ -7608,10 +7609,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>516</v>
+      </c>
+      <c r="C263" t="s">
         <v>517</v>
-      </c>
-      <c r="C263" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.15">
@@ -7619,10 +7620,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>518</v>
+      </c>
+      <c r="C264" t="s">
         <v>519</v>
-      </c>
-      <c r="C264" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.15">
@@ -7630,10 +7631,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>520</v>
+      </c>
+      <c r="C265" t="s">
         <v>521</v>
-      </c>
-      <c r="C265" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.15">
@@ -7641,10 +7642,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>522</v>
+      </c>
+      <c r="C266" t="s">
         <v>523</v>
-      </c>
-      <c r="C266" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.15">
@@ -7652,10 +7653,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>524</v>
+      </c>
+      <c r="C267" t="s">
         <v>525</v>
-      </c>
-      <c r="C267" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.15">
@@ -7663,10 +7664,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>526</v>
+      </c>
+      <c r="C268" t="s">
         <v>527</v>
-      </c>
-      <c r="C268" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.15">
@@ -7674,10 +7675,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>528</v>
+      </c>
+      <c r="C269" t="s">
         <v>529</v>
-      </c>
-      <c r="C269" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.15">
@@ -7685,10 +7686,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>530</v>
+      </c>
+      <c r="C270" t="s">
         <v>531</v>
-      </c>
-      <c r="C270" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.15">
@@ -7696,10 +7697,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.15">
@@ -7707,10 +7708,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>533</v>
+      </c>
+      <c r="C272" t="s">
         <v>534</v>
-      </c>
-      <c r="C272" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.15">
@@ -7718,10 +7719,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>535</v>
+      </c>
+      <c r="C273" t="s">
         <v>536</v>
-      </c>
-      <c r="C273" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.15">
@@ -7729,10 +7730,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>537</v>
+      </c>
+      <c r="C274" t="s">
         <v>538</v>
-      </c>
-      <c r="C274" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.15">
@@ -7740,10 +7741,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>539</v>
+      </c>
+      <c r="C275" t="s">
         <v>540</v>
-      </c>
-      <c r="C275" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.15">
@@ -7751,10 +7752,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>541</v>
+      </c>
+      <c r="C276" t="s">
         <v>542</v>
-      </c>
-      <c r="C276" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.15">
@@ -7762,10 +7763,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>543</v>
+      </c>
+      <c r="C277" t="s">
         <v>544</v>
-      </c>
-      <c r="C277" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.15">
@@ -7773,10 +7774,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>545</v>
+      </c>
+      <c r="C278" t="s">
         <v>546</v>
-      </c>
-      <c r="C278" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.15">
@@ -7784,10 +7785,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>547</v>
+      </c>
+      <c r="C279" t="s">
         <v>548</v>
-      </c>
-      <c r="C279" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.15">
@@ -7795,10 +7796,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>549</v>
+      </c>
+      <c r="C280" t="s">
         <v>550</v>
-      </c>
-      <c r="C280" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.15">
@@ -7806,10 +7807,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>551</v>
+      </c>
+      <c r="C281" t="s">
         <v>552</v>
-      </c>
-      <c r="C281" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.15">
@@ -7817,10 +7818,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>553</v>
+      </c>
+      <c r="C282" t="s">
         <v>554</v>
-      </c>
-      <c r="C282" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.15">
@@ -7828,10 +7829,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>555</v>
+      </c>
+      <c r="C283" t="s">
         <v>556</v>
-      </c>
-      <c r="C283" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.15">
@@ -7839,10 +7840,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>557</v>
+      </c>
+      <c r="C284" t="s">
         <v>558</v>
-      </c>
-      <c r="C284" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.15">
@@ -7850,10 +7851,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>559</v>
+      </c>
+      <c r="C285" t="s">
         <v>560</v>
-      </c>
-      <c r="C285" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.15">
@@ -7861,10 +7862,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>561</v>
+      </c>
+      <c r="C286" t="s">
         <v>562</v>
-      </c>
-      <c r="C286" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.15">
@@ -7872,10 +7873,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>563</v>
+      </c>
+      <c r="C287" t="s">
         <v>564</v>
-      </c>
-      <c r="C287" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.15">
@@ -7883,10 +7884,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>565</v>
+      </c>
+      <c r="C288" t="s">
         <v>566</v>
-      </c>
-      <c r="C288" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.15">
@@ -7894,10 +7895,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>567</v>
+      </c>
+      <c r="C289" t="s">
         <v>568</v>
-      </c>
-      <c r="C289" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.15">
@@ -7905,10 +7906,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>569</v>
+      </c>
+      <c r="C290" t="s">
         <v>570</v>
-      </c>
-      <c r="C290" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.15">
@@ -7916,10 +7917,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>571</v>
+      </c>
+      <c r="C291" t="s">
         <v>572</v>
-      </c>
-      <c r="C291" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.15">
@@ -7927,10 +7928,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>573</v>
+      </c>
+      <c r="C292" t="s">
         <v>574</v>
-      </c>
-      <c r="C292" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.15">
@@ -7938,10 +7939,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>575</v>
+      </c>
+      <c r="C293" t="s">
         <v>576</v>
-      </c>
-      <c r="C293" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.15">
@@ -7949,10 +7950,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>577</v>
+      </c>
+      <c r="C294" t="s">
         <v>578</v>
-      </c>
-      <c r="C294" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.15">
@@ -7960,10 +7961,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>579</v>
+      </c>
+      <c r="C295" t="s">
         <v>580</v>
-      </c>
-      <c r="C295" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.15">
@@ -7971,10 +7972,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.15">
@@ -7982,10 +7983,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>582</v>
+      </c>
+      <c r="C297" t="s">
         <v>583</v>
-      </c>
-      <c r="C297" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.15">
@@ -7993,10 +7994,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>584</v>
+      </c>
+      <c r="C298" t="s">
         <v>585</v>
-      </c>
-      <c r="C298" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.15">
@@ -8004,10 +8005,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>586</v>
+      </c>
+      <c r="C299" t="s">
         <v>587</v>
-      </c>
-      <c r="C299" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.15">
@@ -8015,10 +8016,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>588</v>
+      </c>
+      <c r="C300" t="s">
         <v>589</v>
-      </c>
-      <c r="C300" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.15">
@@ -8026,10 +8027,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>590</v>
+      </c>
+      <c r="C301" t="s">
         <v>591</v>
-      </c>
-      <c r="C301" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.15">
@@ -8037,10 +8038,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>592</v>
+      </c>
+      <c r="C302" t="s">
         <v>593</v>
-      </c>
-      <c r="C302" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.15">
@@ -8048,10 +8049,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>594</v>
+      </c>
+      <c r="C303" t="s">
         <v>595</v>
-      </c>
-      <c r="C303" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.15">
@@ -8059,10 +8060,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>596</v>
+      </c>
+      <c r="C304" t="s">
         <v>597</v>
-      </c>
-      <c r="C304" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.15">
@@ -8070,10 +8071,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>598</v>
+      </c>
+      <c r="C305" t="s">
         <v>599</v>
-      </c>
-      <c r="C305" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.15">
@@ -8081,10 +8082,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>600</v>
+      </c>
+      <c r="C306" t="s">
         <v>601</v>
-      </c>
-      <c r="C306" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.15">
@@ -8092,10 +8093,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>602</v>
+      </c>
+      <c r="C307" t="s">
         <v>603</v>
-      </c>
-      <c r="C307" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.15">
@@ -8103,10 +8104,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>604</v>
+      </c>
+      <c r="C308" t="s">
         <v>605</v>
-      </c>
-      <c r="C308" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.15">
@@ -8114,10 +8115,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>606</v>
+      </c>
+      <c r="C309" t="s">
         <v>607</v>
-      </c>
-      <c r="C309" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.15">
@@ -8125,10 +8126,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>608</v>
+      </c>
+      <c r="C310" t="s">
         <v>609</v>
-      </c>
-      <c r="C310" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.15">
@@ -8136,10 +8137,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>610</v>
+      </c>
+      <c r="C311" t="s">
         <v>611</v>
-      </c>
-      <c r="C311" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.15">
@@ -8147,10 +8148,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>612</v>
+      </c>
+      <c r="C312" t="s">
         <v>613</v>
-      </c>
-      <c r="C312" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.15">
@@ -8158,10 +8159,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>614</v>
+      </c>
+      <c r="C313" t="s">
         <v>615</v>
-      </c>
-      <c r="C313" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.15">
@@ -8169,10 +8170,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>616</v>
+      </c>
+      <c r="C314" t="s">
         <v>617</v>
-      </c>
-      <c r="C314" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.15">
@@ -8180,10 +8181,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>618</v>
+      </c>
+      <c r="C315" t="s">
         <v>619</v>
-      </c>
-      <c r="C315" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.15">
@@ -8191,10 +8192,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>620</v>
+      </c>
+      <c r="C316" t="s">
         <v>621</v>
-      </c>
-      <c r="C316" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.15">
@@ -8202,10 +8203,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>622</v>
+      </c>
+      <c r="C317" t="s">
         <v>623</v>
-      </c>
-      <c r="C317" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.15">
@@ -8213,10 +8214,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>624</v>
+      </c>
+      <c r="C318" t="s">
         <v>625</v>
-      </c>
-      <c r="C318" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.15">
@@ -8224,10 +8225,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>626</v>
+      </c>
+      <c r="C319" t="s">
         <v>627</v>
-      </c>
-      <c r="C319" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.15">
@@ -8235,10 +8236,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>628</v>
+      </c>
+      <c r="C320" t="s">
         <v>629</v>
-      </c>
-      <c r="C320" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.15">
@@ -8246,10 +8247,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>630</v>
+      </c>
+      <c r="C321" t="s">
         <v>631</v>
-      </c>
-      <c r="C321" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.15">
@@ -8257,10 +8258,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>632</v>
+      </c>
+      <c r="C322" t="s">
         <v>633</v>
-      </c>
-      <c r="C322" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.15">
@@ -8268,10 +8269,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>634</v>
+      </c>
+      <c r="C323" t="s">
         <v>635</v>
-      </c>
-      <c r="C323" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.15">
@@ -8279,10 +8280,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>636</v>
+      </c>
+      <c r="C324" t="s">
         <v>637</v>
-      </c>
-      <c r="C324" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.15">
@@ -8290,10 +8291,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>638</v>
+      </c>
+      <c r="C325" t="s">
         <v>639</v>
-      </c>
-      <c r="C325" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.15">
@@ -8301,10 +8302,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>640</v>
+      </c>
+      <c r="C326" t="s">
         <v>641</v>
-      </c>
-      <c r="C326" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.15">
@@ -8312,10 +8313,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>642</v>
+      </c>
+      <c r="C327" t="s">
         <v>643</v>
-      </c>
-      <c r="C327" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.15">
@@ -8323,10 +8324,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>644</v>
+      </c>
+      <c r="C328" t="s">
         <v>645</v>
-      </c>
-      <c r="C328" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.15">
@@ -8334,10 +8335,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>646</v>
+      </c>
+      <c r="C329" t="s">
         <v>647</v>
-      </c>
-      <c r="C329" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.15">
@@ -8345,10 +8346,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>648</v>
+      </c>
+      <c r="C330" t="s">
         <v>649</v>
-      </c>
-      <c r="C330" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.15">
@@ -8356,10 +8357,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>650</v>
+      </c>
+      <c r="C331" t="s">
         <v>651</v>
-      </c>
-      <c r="C331" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.15">
@@ -8367,10 +8368,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>652</v>
+      </c>
+      <c r="C332" t="s">
         <v>653</v>
-      </c>
-      <c r="C332" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.15">
@@ -8378,10 +8379,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>654</v>
+      </c>
+      <c r="C333" t="s">
         <v>655</v>
-      </c>
-      <c r="C333" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.15">
@@ -8389,10 +8390,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>656</v>
+      </c>
+      <c r="C334" t="s">
         <v>657</v>
-      </c>
-      <c r="C334" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.15">
@@ -8400,10 +8401,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>658</v>
+      </c>
+      <c r="C335" t="s">
         <v>659</v>
-      </c>
-      <c r="C335" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.15">
@@ -8411,10 +8412,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>660</v>
+      </c>
+      <c r="C336" t="s">
         <v>661</v>
-      </c>
-      <c r="C336" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.15">
@@ -8422,10 +8423,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>662</v>
+      </c>
+      <c r="C337" t="s">
         <v>663</v>
-      </c>
-      <c r="C337" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.15">
@@ -8433,10 +8434,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.15">
@@ -8444,10 +8445,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.15">
@@ -8455,10 +8456,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>666</v>
+      </c>
+      <c r="C340" t="s">
         <v>667</v>
-      </c>
-      <c r="C340" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.15">
@@ -8466,10 +8467,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>668</v>
+      </c>
+      <c r="C341" t="s">
         <v>669</v>
-      </c>
-      <c r="C341" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.15">
@@ -8477,10 +8478,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>670</v>
+      </c>
+      <c r="C342" t="s">
         <v>671</v>
-      </c>
-      <c r="C342" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.15">
@@ -8488,10 +8489,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>672</v>
+      </c>
+      <c r="C343" t="s">
         <v>673</v>
-      </c>
-      <c r="C343" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.15">
@@ -8499,10 +8500,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>674</v>
+      </c>
+      <c r="C344" t="s">
         <v>675</v>
-      </c>
-      <c r="C344" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.15">
@@ -8510,10 +8511,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>676</v>
+      </c>
+      <c r="C345" t="s">
         <v>677</v>
-      </c>
-      <c r="C345" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.15">
@@ -8521,10 +8522,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>678</v>
+      </c>
+      <c r="C346" t="s">
         <v>679</v>
-      </c>
-      <c r="C346" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.15">
@@ -8532,10 +8533,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>680</v>
+      </c>
+      <c r="C347" t="s">
         <v>681</v>
-      </c>
-      <c r="C347" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.15">
@@ -8543,10 +8544,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>682</v>
+      </c>
+      <c r="C348" t="s">
         <v>683</v>
-      </c>
-      <c r="C348" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.15">
@@ -8554,10 +8555,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>684</v>
+      </c>
+      <c r="C349" t="s">
         <v>685</v>
-      </c>
-      <c r="C349" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.15">
@@ -8565,10 +8566,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>686</v>
+      </c>
+      <c r="C350" t="s">
         <v>687</v>
-      </c>
-      <c r="C350" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.15">
@@ -8576,10 +8577,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>688</v>
+      </c>
+      <c r="C351" t="s">
         <v>689</v>
-      </c>
-      <c r="C351" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.15">
@@ -8587,10 +8588,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>690</v>
+      </c>
+      <c r="C352" t="s">
         <v>691</v>
-      </c>
-      <c r="C352" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.15">
@@ -8598,10 +8599,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>692</v>
+      </c>
+      <c r="C353" t="s">
         <v>693</v>
-      </c>
-      <c r="C353" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.15">
@@ -8609,10 +8610,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>694</v>
+      </c>
+      <c r="C354" t="s">
         <v>695</v>
-      </c>
-      <c r="C354" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.15">
@@ -8620,10 +8621,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>696</v>
+      </c>
+      <c r="C355" t="s">
         <v>697</v>
-      </c>
-      <c r="C355" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.15">
@@ -8631,10 +8632,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>698</v>
+      </c>
+      <c r="C356" t="s">
         <v>699</v>
-      </c>
-      <c r="C356" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.15">
@@ -8642,10 +8643,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>700</v>
+      </c>
+      <c r="C357" t="s">
         <v>701</v>
-      </c>
-      <c r="C357" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.15">
@@ -8653,10 +8654,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>702</v>
+      </c>
+      <c r="C358" t="s">
         <v>703</v>
-      </c>
-      <c r="C358" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.15">
@@ -8664,10 +8665,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>704</v>
+      </c>
+      <c r="C359" t="s">
         <v>705</v>
-      </c>
-      <c r="C359" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.15">
@@ -8675,10 +8676,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>706</v>
+      </c>
+      <c r="C360" t="s">
         <v>707</v>
-      </c>
-      <c r="C360" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.15">
@@ -8686,10 +8687,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>708</v>
+      </c>
+      <c r="C361" t="s">
         <v>709</v>
-      </c>
-      <c r="C361" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.15">
@@ -8697,10 +8698,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>710</v>
+      </c>
+      <c r="C362" t="s">
         <v>711</v>
-      </c>
-      <c r="C362" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.15">
@@ -8708,10 +8709,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>712</v>
+      </c>
+      <c r="C363" t="s">
         <v>713</v>
-      </c>
-      <c r="C363" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.15">
@@ -8719,10 +8720,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>714</v>
+      </c>
+      <c r="C364" t="s">
         <v>715</v>
-      </c>
-      <c r="C364" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.15">
@@ -8730,10 +8731,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>716</v>
+      </c>
+      <c r="C365" t="s">
         <v>717</v>
-      </c>
-      <c r="C365" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.15">
@@ -8741,10 +8742,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>718</v>
+      </c>
+      <c r="C366" t="s">
         <v>719</v>
-      </c>
-      <c r="C366" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.15">
@@ -8752,10 +8753,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>720</v>
+      </c>
+      <c r="C367" t="s">
         <v>721</v>
-      </c>
-      <c r="C367" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.15">
@@ -8763,10 +8764,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>722</v>
+      </c>
+      <c r="C368" t="s">
         <v>723</v>
-      </c>
-      <c r="C368" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.15">
@@ -8774,10 +8775,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>724</v>
+      </c>
+      <c r="C369" t="s">
         <v>725</v>
-      </c>
-      <c r="C369" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.15">
@@ -8785,10 +8786,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>726</v>
+      </c>
+      <c r="C370" t="s">
         <v>727</v>
-      </c>
-      <c r="C370" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.15">
@@ -8796,10 +8797,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>728</v>
+      </c>
+      <c r="C371" t="s">
         <v>729</v>
-      </c>
-      <c r="C371" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.15">
@@ -8807,10 +8808,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>730</v>
+      </c>
+      <c r="C372" t="s">
         <v>731</v>
-      </c>
-      <c r="C372" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.15">
@@ -8818,10 +8819,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>732</v>
+      </c>
+      <c r="C373" t="s">
         <v>733</v>
-      </c>
-      <c r="C373" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.15">
@@ -8829,10 +8830,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>734</v>
+      </c>
+      <c r="C374" t="s">
         <v>735</v>
-      </c>
-      <c r="C374" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.15">
@@ -8840,10 +8841,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>736</v>
+      </c>
+      <c r="C375" t="s">
         <v>737</v>
-      </c>
-      <c r="C375" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.15">
@@ -8851,10 +8852,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>738</v>
+      </c>
+      <c r="C376" t="s">
         <v>739</v>
-      </c>
-      <c r="C376" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.15">
@@ -8862,10 +8863,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>740</v>
+      </c>
+      <c r="C377" t="s">
         <v>741</v>
-      </c>
-      <c r="C377" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.15">
@@ -8873,10 +8874,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>742</v>
+      </c>
+      <c r="C378" t="s">
         <v>743</v>
-      </c>
-      <c r="C378" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.15">
@@ -8884,10 +8885,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>744</v>
+      </c>
+      <c r="C379" t="s">
         <v>745</v>
-      </c>
-      <c r="C379" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.15">
@@ -8895,10 +8896,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>746</v>
+      </c>
+      <c r="C380" t="s">
         <v>747</v>
-      </c>
-      <c r="C380" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.15">
@@ -8906,10 +8907,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>748</v>
+      </c>
+      <c r="C381" t="s">
         <v>749</v>
-      </c>
-      <c r="C381" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.15">
@@ -8917,10 +8918,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>750</v>
+      </c>
+      <c r="C382" t="s">
         <v>751</v>
-      </c>
-      <c r="C382" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.15">
@@ -8928,10 +8929,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>752</v>
+      </c>
+      <c r="C383" t="s">
         <v>753</v>
-      </c>
-      <c r="C383" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.15">
@@ -8939,10 +8940,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>754</v>
+      </c>
+      <c r="C384" t="s">
         <v>755</v>
-      </c>
-      <c r="C384" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.15">
@@ -8950,10 +8951,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>756</v>
+      </c>
+      <c r="C385" t="s">
         <v>757</v>
-      </c>
-      <c r="C385" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.15">
@@ -8961,10 +8962,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>758</v>
+      </c>
+      <c r="C386" t="s">
         <v>759</v>
-      </c>
-      <c r="C386" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.15">
@@ -8972,10 +8973,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>760</v>
+      </c>
+      <c r="C387" t="s">
         <v>761</v>
-      </c>
-      <c r="C387" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.15">
@@ -8983,10 +8984,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>762</v>
+      </c>
+      <c r="C388" t="s">
         <v>763</v>
-      </c>
-      <c r="C388" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.15">
@@ -8994,10 +8995,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>764</v>
+      </c>
+      <c r="C389" t="s">
         <v>765</v>
-      </c>
-      <c r="C389" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.15">
@@ -9005,10 +9006,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>766</v>
+      </c>
+      <c r="C390" t="s">
         <v>767</v>
-      </c>
-      <c r="C390" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.15">
@@ -9016,10 +9017,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>768</v>
+      </c>
+      <c r="C391" t="s">
         <v>769</v>
-      </c>
-      <c r="C391" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
@@ -9027,10 +9028,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>770</v>
+      </c>
+      <c r="C392" t="s">
         <v>771</v>
-      </c>
-      <c r="C392" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.15">
@@ -9038,10 +9039,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>772</v>
+      </c>
+      <c r="C393" t="s">
         <v>773</v>
-      </c>
-      <c r="C393" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.15">
@@ -9049,10 +9050,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>774</v>
+      </c>
+      <c r="C394" t="s">
         <v>775</v>
-      </c>
-      <c r="C394" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.15">
@@ -9060,10 +9061,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>776</v>
+      </c>
+      <c r="C395" t="s">
         <v>777</v>
-      </c>
-      <c r="C395" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.15">
@@ -9071,10 +9072,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>778</v>
+      </c>
+      <c r="C396" t="s">
         <v>779</v>
-      </c>
-      <c r="C396" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.15">
@@ -9082,10 +9083,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>780</v>
+      </c>
+      <c r="C397" t="s">
         <v>781</v>
-      </c>
-      <c r="C397" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.15">
@@ -9093,10 +9094,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>782</v>
+      </c>
+      <c r="C398" t="s">
         <v>783</v>
-      </c>
-      <c r="C398" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.15">
@@ -9104,10 +9105,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>784</v>
+      </c>
+      <c r="C399" t="s">
         <v>785</v>
-      </c>
-      <c r="C399" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.15">
@@ -9115,10 +9116,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>786</v>
+      </c>
+      <c r="C400" t="s">
         <v>787</v>
-      </c>
-      <c r="C400" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.15">
@@ -9126,10 +9127,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>788</v>
+      </c>
+      <c r="C401" t="s">
         <v>789</v>
-      </c>
-      <c r="C401" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.15">
@@ -9137,10 +9138,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>790</v>
+      </c>
+      <c r="C402" t="s">
         <v>791</v>
-      </c>
-      <c r="C402" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.15">
@@ -9148,10 +9149,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>792</v>
+      </c>
+      <c r="C403" t="s">
         <v>793</v>
-      </c>
-      <c r="C403" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.15">
@@ -9159,10 +9160,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>794</v>
+      </c>
+      <c r="C404" t="s">
         <v>795</v>
-      </c>
-      <c r="C404" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.15">
@@ -9170,10 +9171,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>796</v>
+      </c>
+      <c r="C405" t="s">
         <v>797</v>
-      </c>
-      <c r="C405" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.15">
@@ -9181,10 +9182,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>798</v>
+      </c>
+      <c r="C406" t="s">
         <v>799</v>
-      </c>
-      <c r="C406" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.15">
@@ -9192,10 +9193,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>800</v>
+      </c>
+      <c r="C407" t="s">
         <v>801</v>
-      </c>
-      <c r="C407" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.15">
@@ -9203,10 +9204,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>802</v>
+      </c>
+      <c r="C408" t="s">
         <v>803</v>
-      </c>
-      <c r="C408" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.15">
@@ -9214,10 +9215,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>804</v>
+      </c>
+      <c r="C409" t="s">
         <v>805</v>
-      </c>
-      <c r="C409" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.15">
@@ -9225,10 +9226,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>806</v>
+      </c>
+      <c r="C410" t="s">
         <v>807</v>
-      </c>
-      <c r="C410" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.15">
@@ -9236,10 +9237,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>808</v>
+      </c>
+      <c r="C411" t="s">
         <v>809</v>
-      </c>
-      <c r="C411" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.15">
@@ -9247,10 +9248,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>810</v>
+      </c>
+      <c r="C412" t="s">
         <v>811</v>
-      </c>
-      <c r="C412" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.15">
@@ -9258,10 +9259,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>812</v>
+      </c>
+      <c r="C413" t="s">
         <v>813</v>
-      </c>
-      <c r="C413" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.15">
@@ -9269,10 +9270,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>814</v>
+      </c>
+      <c r="C414" t="s">
         <v>815</v>
-      </c>
-      <c r="C414" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.15">
@@ -9280,10 +9281,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>816</v>
+      </c>
+      <c r="C415" t="s">
         <v>817</v>
-      </c>
-      <c r="C415" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.15">
@@ -9291,10 +9292,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>818</v>
+      </c>
+      <c r="C416" t="s">
         <v>819</v>
-      </c>
-      <c r="C416" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.15">
@@ -9302,10 +9303,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>820</v>
+      </c>
+      <c r="C417" t="s">
         <v>821</v>
-      </c>
-      <c r="C417" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.15">
@@ -9313,10 +9314,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>822</v>
+      </c>
+      <c r="C418" t="s">
         <v>823</v>
-      </c>
-      <c r="C418" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.15">
@@ -9324,10 +9325,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>824</v>
+      </c>
+      <c r="C419" t="s">
         <v>825</v>
-      </c>
-      <c r="C419" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.15">
@@ -9335,10 +9336,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>826</v>
+      </c>
+      <c r="C420" t="s">
         <v>827</v>
-      </c>
-      <c r="C420" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.15">
@@ -9346,10 +9347,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>828</v>
+      </c>
+      <c r="C421" t="s">
         <v>829</v>
-      </c>
-      <c r="C421" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.15">
@@ -9357,10 +9358,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>830</v>
+      </c>
+      <c r="C422" t="s">
         <v>831</v>
-      </c>
-      <c r="C422" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.15">
@@ -9368,10 +9369,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>832</v>
+      </c>
+      <c r="C423" t="s">
         <v>833</v>
-      </c>
-      <c r="C423" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.15">
@@ -9379,10 +9380,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>834</v>
+      </c>
+      <c r="C424" t="s">
         <v>835</v>
-      </c>
-      <c r="C424" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.15">
@@ -9390,10 +9391,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>836</v>
+      </c>
+      <c r="C425" t="s">
         <v>837</v>
-      </c>
-      <c r="C425" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.15">
@@ -9401,10 +9402,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>838</v>
+      </c>
+      <c r="C426" t="s">
         <v>839</v>
-      </c>
-      <c r="C426" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.15">
@@ -9412,10 +9413,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>840</v>
+      </c>
+      <c r="C427" t="s">
         <v>841</v>
-      </c>
-      <c r="C427" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.15">
@@ -9423,10 +9424,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C428" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.15">
@@ -9434,10 +9435,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C429" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.15">
@@ -9445,10 +9446,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>844</v>
+      </c>
+      <c r="C430" t="s">
         <v>845</v>
-      </c>
-      <c r="C430" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.15">
@@ -9456,10 +9457,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>846</v>
+      </c>
+      <c r="C431" t="s">
         <v>847</v>
-      </c>
-      <c r="C431" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.15">
@@ -9467,10 +9468,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>848</v>
+      </c>
+      <c r="C432" t="s">
         <v>849</v>
-      </c>
-      <c r="C432" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.15">
@@ -9478,10 +9479,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>850</v>
+      </c>
+      <c r="C433" t="s">
         <v>851</v>
-      </c>
-      <c r="C433" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.15">
@@ -9489,10 +9490,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>852</v>
+      </c>
+      <c r="C434" t="s">
         <v>853</v>
-      </c>
-      <c r="C434" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.15">
@@ -9500,10 +9501,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>854</v>
+      </c>
+      <c r="C435" t="s">
         <v>855</v>
-      </c>
-      <c r="C435" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.15">
@@ -9511,10 +9512,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>856</v>
+      </c>
+      <c r="C436" t="s">
         <v>857</v>
-      </c>
-      <c r="C436" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.15">
@@ -9522,10 +9523,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>858</v>
+      </c>
+      <c r="C437" t="s">
         <v>859</v>
-      </c>
-      <c r="C437" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.15">
@@ -9533,10 +9534,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>860</v>
+      </c>
+      <c r="C438" t="s">
         <v>861</v>
-      </c>
-      <c r="C438" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.15">
@@ -9544,10 +9545,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>862</v>
+      </c>
+      <c r="C439" t="s">
         <v>863</v>
-      </c>
-      <c r="C439" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.15">
@@ -9555,10 +9556,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>864</v>
+      </c>
+      <c r="C440" t="s">
         <v>865</v>
-      </c>
-      <c r="C440" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.15">
@@ -9566,10 +9567,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>866</v>
+      </c>
+      <c r="C441" t="s">
         <v>867</v>
-      </c>
-      <c r="C441" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.15">
@@ -9577,10 +9578,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>868</v>
+      </c>
+      <c r="C442" t="s">
         <v>869</v>
-      </c>
-      <c r="C442" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.15">
@@ -9588,10 +9589,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>870</v>
+      </c>
+      <c r="C443" t="s">
         <v>871</v>
-      </c>
-      <c r="C443" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.15">
@@ -9599,10 +9600,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>872</v>
+      </c>
+      <c r="C444" t="s">
         <v>873</v>
-      </c>
-      <c r="C444" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.15">
@@ -9610,10 +9611,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>874</v>
+      </c>
+      <c r="C445" t="s">
         <v>875</v>
-      </c>
-      <c r="C445" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.15">
@@ -9621,10 +9622,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>876</v>
+      </c>
+      <c r="C446" t="s">
         <v>877</v>
-      </c>
-      <c r="C446" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.15">
@@ -9632,10 +9633,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>878</v>
+      </c>
+      <c r="C447" t="s">
         <v>879</v>
-      </c>
-      <c r="C447" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.15">
@@ -9643,10 +9644,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>880</v>
+      </c>
+      <c r="C448" t="s">
         <v>881</v>
-      </c>
-      <c r="C448" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.15">
@@ -9654,10 +9655,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>882</v>
+      </c>
+      <c r="C449" t="s">
         <v>883</v>
-      </c>
-      <c r="C449" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.15">
@@ -9665,10 +9666,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>884</v>
+      </c>
+      <c r="C450" t="s">
         <v>885</v>
-      </c>
-      <c r="C450" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.15">
@@ -9676,10 +9677,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C451" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.15">
@@ -9687,10 +9688,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>887</v>
+      </c>
+      <c r="C452" t="s">
         <v>888</v>
-      </c>
-      <c r="C452" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.15">
@@ -9698,10 +9699,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>889</v>
+      </c>
+      <c r="C453" t="s">
         <v>890</v>
-      </c>
-      <c r="C453" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.15">
@@ -9709,10 +9710,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>891</v>
+      </c>
+      <c r="C454" t="s">
         <v>892</v>
-      </c>
-      <c r="C454" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.15">
@@ -9720,10 +9721,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>893</v>
+      </c>
+      <c r="C455" t="s">
         <v>894</v>
-      </c>
-      <c r="C455" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.15">
@@ -9731,10 +9732,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C456" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.15">
@@ -9742,10 +9743,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>896</v>
+      </c>
+      <c r="C457" t="s">
         <v>897</v>
-      </c>
-      <c r="C457" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.15">
@@ -9753,10 +9754,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>898</v>
+      </c>
+      <c r="C458" t="s">
         <v>899</v>
-      </c>
-      <c r="C458" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.15">
@@ -9764,10 +9765,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>900</v>
+      </c>
+      <c r="C459" t="s">
         <v>901</v>
-      </c>
-      <c r="C459" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.15">
@@ -9775,7 +9776,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.15">
@@ -9783,10 +9784,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>903</v>
+      </c>
+      <c r="C461" t="s">
         <v>904</v>
-      </c>
-      <c r="C461" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.15">
@@ -9794,10 +9795,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>905</v>
+      </c>
+      <c r="C462" t="s">
         <v>906</v>
-      </c>
-      <c r="C462" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.15">
@@ -9805,10 +9806,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>907</v>
+      </c>
+      <c r="C463" t="s">
         <v>908</v>
-      </c>
-      <c r="C463" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.15">
@@ -9816,10 +9817,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>909</v>
+      </c>
+      <c r="C464" t="s">
         <v>910</v>
-      </c>
-      <c r="C464" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.15">
@@ -9827,10 +9828,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>911</v>
+      </c>
+      <c r="C465" t="s">
         <v>912</v>
-      </c>
-      <c r="C465" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.15">
@@ -9838,10 +9839,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>913</v>
+      </c>
+      <c r="C466" t="s">
         <v>914</v>
-      </c>
-      <c r="C466" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.15">
@@ -9849,10 +9850,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.15">
@@ -9860,10 +9861,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>916</v>
+      </c>
+      <c r="C468" t="s">
         <v>917</v>
-      </c>
-      <c r="C468" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.15">
@@ -9871,10 +9872,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>918</v>
+      </c>
+      <c r="C469" t="s">
         <v>919</v>
-      </c>
-      <c r="C469" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.15">
@@ -9882,10 +9883,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>920</v>
+      </c>
+      <c r="C470" t="s">
         <v>921</v>
-      </c>
-      <c r="C470" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.15">
@@ -9893,10 +9894,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>922</v>
+      </c>
+      <c r="C471" t="s">
         <v>923</v>
-      </c>
-      <c r="C471" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.15">
@@ -9904,10 +9905,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>924</v>
+      </c>
+      <c r="C472" t="s">
         <v>925</v>
-      </c>
-      <c r="C472" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
@@ -9915,10 +9916,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>926</v>
+      </c>
+      <c r="C473" t="s">
         <v>927</v>
-      </c>
-      <c r="C473" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.15">
@@ -9926,10 +9927,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>928</v>
+      </c>
+      <c r="C474" t="s">
         <v>929</v>
-      </c>
-      <c r="C474" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.15">
@@ -9937,10 +9938,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>930</v>
+      </c>
+      <c r="C475" t="s">
         <v>931</v>
-      </c>
-      <c r="C475" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.15">
@@ -9948,10 +9949,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>932</v>
+      </c>
+      <c r="C476" t="s">
         <v>933</v>
-      </c>
-      <c r="C476" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.15">
@@ -9959,10 +9960,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>934</v>
+      </c>
+      <c r="C477" t="s">
         <v>935</v>
-      </c>
-      <c r="C477" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.15">
@@ -9970,10 +9971,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C478" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.15">
@@ -9981,10 +9982,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>937</v>
+      </c>
+      <c r="C479" t="s">
         <v>938</v>
-      </c>
-      <c r="C479" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.15">
@@ -9992,10 +9993,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>939</v>
+      </c>
+      <c r="C480" t="s">
         <v>940</v>
-      </c>
-      <c r="C480" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.15">
@@ -10003,10 +10004,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>941</v>
+      </c>
+      <c r="C481" t="s">
         <v>942</v>
-      </c>
-      <c r="C481" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.15">
@@ -10014,10 +10015,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>943</v>
+      </c>
+      <c r="C482" t="s">
         <v>944</v>
-      </c>
-      <c r="C482" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.15">
@@ -10025,10 +10026,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>945</v>
+      </c>
+      <c r="C483" t="s">
         <v>946</v>
-      </c>
-      <c r="C483" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.15">
@@ -10036,10 +10037,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>947</v>
+      </c>
+      <c r="C484" t="s">
         <v>948</v>
-      </c>
-      <c r="C484" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.15">
@@ -10047,10 +10048,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>949</v>
+      </c>
+      <c r="C485" t="s">
         <v>950</v>
-      </c>
-      <c r="C485" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.15">
@@ -10058,10 +10059,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>951</v>
+      </c>
+      <c r="C486" t="s">
         <v>952</v>
-      </c>
-      <c r="C486" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.15">
@@ -10069,10 +10070,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>953</v>
+      </c>
+      <c r="C487" t="s">
         <v>954</v>
-      </c>
-      <c r="C487" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.15">
@@ -10080,10 +10081,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>955</v>
+      </c>
+      <c r="C488" t="s">
         <v>956</v>
-      </c>
-      <c r="C488" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.15">
@@ -10091,10 +10092,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>957</v>
+      </c>
+      <c r="C489" t="s">
         <v>958</v>
-      </c>
-      <c r="C489" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.15">
@@ -10102,10 +10103,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>959</v>
+      </c>
+      <c r="C490" t="s">
         <v>960</v>
-      </c>
-      <c r="C490" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.15">
@@ -10113,10 +10114,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>961</v>
+      </c>
+      <c r="C491" t="s">
         <v>962</v>
-      </c>
-      <c r="C491" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.15">
@@ -10124,10 +10125,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>963</v>
+      </c>
+      <c r="C492" t="s">
         <v>964</v>
-      </c>
-      <c r="C492" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.15">
@@ -10135,10 +10136,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>965</v>
+      </c>
+      <c r="C493" t="s">
         <v>966</v>
-      </c>
-      <c r="C493" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.15">
@@ -10146,10 +10147,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>967</v>
+      </c>
+      <c r="C494" t="s">
         <v>968</v>
-      </c>
-      <c r="C494" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.15">
@@ -10157,10 +10158,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>969</v>
+      </c>
+      <c r="C495" t="s">
         <v>970</v>
-      </c>
-      <c r="C495" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.15">
@@ -10168,10 +10169,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>971</v>
+      </c>
+      <c r="C496" t="s">
         <v>972</v>
-      </c>
-      <c r="C496" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.15">
@@ -10179,10 +10180,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>973</v>
+      </c>
+      <c r="C497" t="s">
         <v>974</v>
-      </c>
-      <c r="C497" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.15">
@@ -10190,10 +10191,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>975</v>
+      </c>
+      <c r="C498" t="s">
         <v>976</v>
-      </c>
-      <c r="C498" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.15">
@@ -10201,7 +10202,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.15">
@@ -10209,10 +10210,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>978</v>
+      </c>
+      <c r="C500" t="s">
         <v>979</v>
-      </c>
-      <c r="C500" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.15">
@@ -10220,10 +10221,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>980</v>
+      </c>
+      <c r="C501" t="s">
         <v>981</v>
-      </c>
-      <c r="C501" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.15">
@@ -10231,10 +10232,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>982</v>
+      </c>
+      <c r="C502" t="s">
         <v>983</v>
-      </c>
-      <c r="C502" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.15">
@@ -10242,10 +10243,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.15">
@@ -10253,10 +10254,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>985</v>
+      </c>
+      <c r="C504" t="s">
         <v>986</v>
-      </c>
-      <c r="C504" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.15">
@@ -10264,10 +10265,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>987</v>
+      </c>
+      <c r="C505" t="s">
         <v>988</v>
-      </c>
-      <c r="C505" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.15">
@@ -10275,10 +10276,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>989</v>
+      </c>
+      <c r="C506" t="s">
         <v>990</v>
-      </c>
-      <c r="C506" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.15">
@@ -10286,10 +10287,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>991</v>
+      </c>
+      <c r="C507" t="s">
         <v>992</v>
-      </c>
-      <c r="C507" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.15">
@@ -10297,10 +10298,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>993</v>
+      </c>
+      <c r="C508" t="s">
         <v>994</v>
-      </c>
-      <c r="C508" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.15">
@@ -10308,10 +10309,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>995</v>
+      </c>
+      <c r="C509" t="s">
         <v>996</v>
-      </c>
-      <c r="C509" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.15">
@@ -10319,10 +10320,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>997</v>
+      </c>
+      <c r="C510" t="s">
         <v>998</v>
-      </c>
-      <c r="C510" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.15">
@@ -10330,10 +10331,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>999</v>
+      </c>
+      <c r="C511" t="s">
         <v>1000</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.15">
@@ -10341,10 +10342,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C512" t="s">
         <v>1002</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.15">
@@ -10352,10 +10353,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C513" t="s">
         <v>1004</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.15">
@@ -10363,10 +10364,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C514" t="s">
         <v>1006</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.15">
@@ -10374,10 +10375,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C515" t="s">
         <v>1008</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.15">
@@ -10385,10 +10386,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C516" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.15">
@@ -10396,10 +10397,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C517" t="s">
         <v>1011</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.15">
@@ -10407,7 +10408,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.15">
@@ -10415,10 +10416,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C519" t="s">
         <v>1014</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.15">
@@ -10426,10 +10427,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C520" t="s">
         <v>1016</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.15">
@@ -10437,10 +10438,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C521" t="s">
         <v>1018</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.15">
@@ -10448,10 +10449,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C522" t="s">
         <v>1020</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.15">
@@ -10459,10 +10460,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C523" t="s">
         <v>1022</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.15">
@@ -10470,10 +10471,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C524" t="s">
         <v>1024</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.15">
@@ -10481,10 +10482,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.15">
@@ -10492,10 +10493,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C526" t="s">
         <v>1027</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.15">
@@ -10503,10 +10504,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C527" t="s">
         <v>1029</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.15">
@@ -10514,10 +10515,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C528" t="s">
         <v>1031</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.15">
@@ -10525,10 +10526,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C529" t="s">
         <v>1033</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.15">
@@ -10536,10 +10537,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.15">
@@ -10547,10 +10548,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C531" t="s">
         <v>1036</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.15">
@@ -10558,10 +10559,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C532" t="s">
         <v>1038</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.15">
@@ -10569,10 +10570,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C533" t="s">
         <v>1040</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.15">
@@ -10580,10 +10581,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C534" t="s">
         <v>1042</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.15">
@@ -10591,10 +10592,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C535" t="s">
         <v>1044</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.15">
@@ -10602,10 +10603,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C536" t="s">
         <v>1046</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.15">
@@ -10613,10 +10614,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C537" t="s">
         <v>1048</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.15">
@@ -10624,10 +10625,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C538" t="s">
         <v>1050</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.15">
@@ -10635,10 +10636,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C539" t="s">
         <v>1052</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.15">
@@ -10646,10 +10647,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C540" t="s">
         <v>1054</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.15">
@@ -10657,10 +10658,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C541" t="s">
         <v>1056</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.15">
@@ -10668,10 +10669,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C542" t="s">
         <v>1058</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.15">
@@ -10679,10 +10680,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C543" t="s">
         <v>1060</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.15">
@@ -10690,10 +10691,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C544" t="s">
         <v>1062</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.15">
@@ -10701,10 +10702,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C545" t="s">
         <v>1064</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.15">
@@ -10712,10 +10713,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C546" t="s">
         <v>1066</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.15">
@@ -10723,7 +10724,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.15">
@@ -10731,10 +10732,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C548" t="s">
         <v>1069</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.15">
@@ -10742,10 +10743,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C549" t="s">
         <v>1071</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.15">
@@ -10753,10 +10754,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C550" t="s">
         <v>1073</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.15">
@@ -10764,10 +10765,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C551" t="s">
         <v>1075</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.15">
@@ -10775,10 +10776,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C552" t="s">
         <v>1077</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.15">
@@ -10786,10 +10787,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C553" t="s">
         <v>1079</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.15">
@@ -10797,10 +10798,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C554" t="s">
         <v>1081</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.15">
@@ -10808,10 +10809,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C555" t="s">
         <v>1083</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.15">
@@ -10819,10 +10820,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C556" t="s">
         <v>1085</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.15">
@@ -10830,10 +10831,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C557" t="s">
         <v>1087</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.15">
@@ -10841,10 +10842,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C558" t="s">
         <v>1089</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.15">
@@ -10852,7 +10853,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.15">
@@ -10860,10 +10861,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C560" t="s">
         <v>1092</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.15">
@@ -10871,10 +10872,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C561" t="s">
         <v>1094</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.15">
@@ -10882,10 +10883,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C562" t="s">
         <v>1096</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.15">
@@ -10893,10 +10894,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C563" t="s">
         <v>1098</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.15">
@@ -10904,10 +10905,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C564" t="s">
         <v>1100</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.15">
@@ -10915,10 +10916,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C565" t="s">
         <v>1102</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.15">
@@ -10926,10 +10927,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C566" t="s">
         <v>1104</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.15">
@@ -10937,10 +10938,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C567" t="s">
         <v>1106</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.15">
@@ -10948,10 +10949,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C568" t="s">
         <v>1108</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.15">
@@ -10959,10 +10960,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C569" t="s">
         <v>1110</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.15">
@@ -10970,10 +10971,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C570" t="s">
         <v>1112</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.15">
@@ -10981,10 +10982,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C571" t="s">
         <v>1114</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.15">
@@ -10992,10 +10993,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C572" t="s">
         <v>1116</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.15">
@@ -11003,10 +11004,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C573" t="s">
         <v>1118</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.15">
@@ -11014,10 +11015,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C574" t="s">
         <v>1120</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.15">
@@ -11025,10 +11026,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.15">
@@ -11036,10 +11037,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C576" t="s">
         <v>1123</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.15">
@@ -11047,10 +11048,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.15">
@@ -11058,10 +11059,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.15">
@@ -11069,10 +11070,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C579" t="s">
         <v>1125</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.15">
@@ -11080,10 +11081,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C580" t="s">
         <v>1127</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.15">
@@ -11091,10 +11092,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C581" t="s">
         <v>1129</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.15">
@@ -11102,10 +11103,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C582" t="s">
         <v>1131</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.15">
@@ -11113,10 +11114,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.15">
@@ -11124,7 +11125,7 @@
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.15">
@@ -11132,10 +11133,10 @@
         <v>612</v>
       </c>
       <c r="B585" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C585" t="s">
         <v>1134</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.15">
@@ -11143,10 +11144,10 @@
         <v>615</v>
       </c>
       <c r="B586" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C586" t="s">
         <v>1136</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.15">
@@ -11154,10 +11155,10 @@
         <v>617</v>
       </c>
       <c r="B587" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C587" t="s">
         <v>1138</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.15">
@@ -11165,10 +11166,10 @@
         <v>618</v>
       </c>
       <c r="B588" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C588" t="s">
         <v>1140</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.15">
@@ -11176,10 +11177,10 @@
         <v>625</v>
       </c>
       <c r="B589" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C589" t="s">
         <v>1142</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.15">
@@ -11187,10 +11188,10 @@
         <v>624</v>
       </c>
       <c r="B590" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C590" t="s">
         <v>1144</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.15">
@@ -11198,10 +11199,10 @@
         <v>626</v>
       </c>
       <c r="B591" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C591" t="s">
         <v>1146</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.15">
@@ -11209,10 +11210,10 @@
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C592" t="s">
         <v>1148</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.15">
@@ -11220,10 +11221,10 @@
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C593" t="s">
         <v>1150</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.15">
@@ -11231,7 +11232,7 @@
         <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.15">
@@ -11239,10 +11240,10 @@
         <v>633</v>
       </c>
       <c r="B595" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C595" t="s">
         <v>1153</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.15">
@@ -11250,10 +11251,10 @@
         <v>635</v>
       </c>
       <c r="B596" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C596" t="s">
         <v>1155</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.15">
@@ -11261,10 +11262,10 @@
         <v>636</v>
       </c>
       <c r="B597" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C597" t="s">
         <v>1157</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.15">
@@ -11272,10 +11273,10 @@
         <v>642</v>
       </c>
       <c r="B598" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C598" t="s">
         <v>1159</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.15">
@@ -11283,10 +11284,10 @@
         <v>644</v>
       </c>
       <c r="B599" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C599" t="s">
         <v>1161</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.15">
@@ -11294,10 +11295,10 @@
         <v>646</v>
       </c>
       <c r="B600" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C600" t="s">
         <v>1163</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.15">
@@ -11305,10 +11306,10 @@
         <v>649</v>
       </c>
       <c r="B601" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C601" t="s">
         <v>1165</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.15">
@@ -11316,10 +11317,10 @@
         <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.15">
@@ -11327,10 +11328,10 @@
         <v>651</v>
       </c>
       <c r="B603" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C603" t="s">
         <v>1168</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.15">
@@ -11338,10 +11339,10 @@
         <v>653</v>
       </c>
       <c r="B604" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C604" t="s">
         <v>1170</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.15">
@@ -11349,10 +11350,10 @@
         <v>654</v>
       </c>
       <c r="B605" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C605" t="s">
         <v>1172</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.15">
@@ -11360,10 +11361,10 @@
         <v>655</v>
       </c>
       <c r="B606" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C606" t="s">
         <v>1174</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.15">
@@ -11371,10 +11372,10 @@
         <v>659</v>
       </c>
       <c r="B607" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C607" t="s">
         <v>1176</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.15">
@@ -11382,10 +11383,10 @@
         <v>660</v>
       </c>
       <c r="B608" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C608" t="s">
         <v>1178</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.15">
@@ -11393,10 +11394,10 @@
         <v>661</v>
       </c>
       <c r="B609" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C609" t="s">
         <v>1180</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.15">
@@ -11404,10 +11405,10 @@
         <v>663</v>
       </c>
       <c r="B610" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C610" t="s">
         <v>1182</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.15">
@@ -11415,10 +11416,10 @@
         <v>667</v>
       </c>
       <c r="B611" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C611" t="s">
         <v>1184</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.15">
@@ -11426,10 +11427,10 @@
         <v>670</v>
       </c>
       <c r="B612" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C612" t="s">
         <v>1186</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.15">
@@ -11437,10 +11438,10 @@
         <v>673</v>
       </c>
       <c r="B613" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C613" t="s">
         <v>1188</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.15">
@@ -11448,10 +11449,10 @@
         <v>674</v>
       </c>
       <c r="B614" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C614" t="s">
         <v>1190</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.15">
@@ -11459,10 +11460,10 @@
         <v>675</v>
       </c>
       <c r="B615" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C615" t="s">
         <v>1192</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.15">
@@ -11470,10 +11471,10 @@
         <v>680</v>
       </c>
       <c r="B616" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C616" t="s">
         <v>1194</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.15">
@@ -11481,10 +11482,10 @@
         <v>681</v>
       </c>
       <c r="B617" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C617" t="s">
         <v>1196</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.15">
@@ -11492,10 +11493,10 @@
         <v>682</v>
       </c>
       <c r="B618" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C618" t="s">
         <v>1198</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.15">
@@ -11503,10 +11504,10 @@
         <v>683</v>
       </c>
       <c r="B619" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C619" t="s">
         <v>1200</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.15">
@@ -11514,10 +11515,10 @@
         <v>684</v>
       </c>
       <c r="B620" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C620" t="s">
         <v>1202</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.15">
@@ -11525,10 +11526,10 @@
         <v>685</v>
       </c>
       <c r="B621" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C621" t="s">
         <v>1204</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.15">
@@ -11536,10 +11537,10 @@
         <v>686</v>
       </c>
       <c r="B622" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C622" t="s">
         <v>1206</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.15">
@@ -11547,10 +11548,10 @@
         <v>689</v>
       </c>
       <c r="B623" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C623" t="s">
         <v>1208</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.15">
@@ -11558,10 +11559,10 @@
         <v>697</v>
       </c>
       <c r="B624" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C624" t="s">
         <v>1210</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.15">
@@ -11569,10 +11570,10 @@
         <v>701</v>
       </c>
       <c r="B625" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C625" t="s">
         <v>1212</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.15">
@@ -11580,10 +11581,10 @@
         <v>702</v>
       </c>
       <c r="B626" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C626" t="s">
         <v>1214</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.15">
@@ -11591,10 +11592,10 @@
         <v>704</v>
       </c>
       <c r="B627" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C627" t="s">
         <v>1216</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.15">
@@ -11602,10 +11603,10 @@
         <v>705</v>
       </c>
       <c r="B628" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C628" t="s">
         <v>1218</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.15">
@@ -11613,10 +11614,10 @@
         <v>710</v>
       </c>
       <c r="B629" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C629" t="s">
         <v>1220</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.15">
@@ -11624,10 +11625,10 @@
         <v>711</v>
       </c>
       <c r="B630" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C630" t="s">
         <v>1222</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.15">
@@ -11635,10 +11636,10 @@
         <v>712</v>
       </c>
       <c r="B631" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C631" t="s">
         <v>1224</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.15">
@@ -11646,10 +11647,10 @@
         <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.15">
@@ -11657,10 +11658,10 @@
         <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.15">
@@ -11668,10 +11669,10 @@
         <v>718</v>
       </c>
       <c r="B634" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C634" t="s">
         <v>1228</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.15">
@@ -11679,10 +11680,10 @@
         <v>719</v>
       </c>
       <c r="B635" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C635" t="s">
         <v>1230</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
@@ -11690,10 +11691,10 @@
         <v>721</v>
       </c>
       <c r="B636" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C636" t="s">
         <v>1232</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.15">
@@ -11701,10 +11702,10 @@
         <v>722</v>
       </c>
       <c r="B637" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C637" t="s">
         <v>1234</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.15">
@@ -11712,10 +11713,10 @@
         <v>723</v>
       </c>
       <c r="B638" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C638" t="s">
         <v>1236</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.15">
@@ -11723,7 +11724,7 @@
         <v>724</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.15">
@@ -11731,10 +11732,10 @@
         <v>725</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C640" t="s">
         <v>1238</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.15">
@@ -11742,10 +11743,10 @@
         <v>726</v>
       </c>
       <c r="B641" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C641" t="s">
         <v>1240</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.15">
@@ -11753,10 +11754,10 @@
         <v>727</v>
       </c>
       <c r="B642" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C642" t="s">
         <v>1242</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
@@ -11764,10 +11765,10 @@
         <v>728</v>
       </c>
       <c r="B643" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C643" t="s">
         <v>1244</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
@@ -11775,10 +11776,10 @@
         <v>729</v>
       </c>
       <c r="B644" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C644" t="s">
         <v>1246</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.15">
@@ -11786,10 +11787,10 @@
         <v>730</v>
       </c>
       <c r="B645" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C645" t="s">
         <v>1248</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.15">
@@ -11797,10 +11798,10 @@
         <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.15">
@@ -11808,10 +11809,10 @@
         <v>733</v>
       </c>
       <c r="B647" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C647" t="s">
         <v>1251</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.15">
@@ -11819,10 +11820,10 @@
         <v>735</v>
       </c>
       <c r="B648" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C648" t="s">
         <v>1253</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.15">
@@ -11830,10 +11831,10 @@
         <v>736</v>
       </c>
       <c r="B649" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C649" t="s">
         <v>1255</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.15">
@@ -11841,10 +11842,10 @@
         <v>737</v>
       </c>
       <c r="B650" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C650" t="s">
         <v>1257</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.15">
@@ -11852,10 +11853,10 @@
         <v>738</v>
       </c>
       <c r="B651" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C651" t="s">
         <v>1259</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.15">
@@ -11863,10 +11864,10 @@
         <v>739</v>
       </c>
       <c r="B652" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C652" t="s">
         <v>1261</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.15">
@@ -11874,10 +11875,10 @@
         <v>740</v>
       </c>
       <c r="B653" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C653" t="s">
         <v>1263</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.15">
@@ -11885,10 +11886,10 @@
         <v>741</v>
       </c>
       <c r="B654" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C654" t="s">
         <v>1265</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.15">
@@ -11896,10 +11897,10 @@
         <v>742</v>
       </c>
       <c r="B655" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C655" t="s">
         <v>1267</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.15">
@@ -11907,10 +11908,10 @@
         <v>743</v>
       </c>
       <c r="B656" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C656" t="s">
         <v>1269</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.15">
@@ -11918,10 +11919,10 @@
         <v>744</v>
       </c>
       <c r="B657" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C657" t="s">
         <v>1271</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
@@ -11929,10 +11930,10 @@
         <v>745</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C658" t="s">
         <v>1273</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.15">
@@ -11940,10 +11941,10 @@
         <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C659" t="s">
         <v>1275</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.15">
@@ -11951,10 +11952,10 @@
         <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C660" t="s">
         <v>1277</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.15">
@@ -11962,10 +11963,10 @@
         <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C661" t="s">
         <v>1279</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.15">
@@ -11973,10 +11974,10 @@
         <v>749</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C662" t="s">
         <v>1281</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.15">
@@ -11985,7 +11986,7 @@
       </c>
       <c r="B663" s="1"/>
       <c r="C663" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.15">
@@ -11993,10 +11994,10 @@
         <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C664" t="s">
         <v>1283</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.15">
@@ -12004,10 +12005,10 @@
         <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.15">
@@ -12015,10 +12016,10 @@
         <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C666" t="s">
         <v>1286</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.15">
@@ -12026,10 +12027,10 @@
         <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C667" t="s">
         <v>1288</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.15">
@@ -12037,10 +12038,10 @@
         <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C668" t="s">
         <v>1290</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.15">
@@ -12048,10 +12049,10 @@
         <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.15">
@@ -12059,10 +12060,10 @@
         <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C670" t="s">
         <v>1293</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.15">
@@ -12070,10 +12071,10 @@
         <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C671" t="s">
         <v>1295</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.15">
@@ -12081,10 +12082,10 @@
         <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C672" t="s">
         <v>1297</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.15">
@@ -12092,10 +12093,10 @@
         <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C673" t="s">
         <v>1299</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.15">
@@ -12103,10 +12104,10 @@
         <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C674" t="s">
         <v>1301</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.15">
@@ -12114,10 +12115,10 @@
         <v>765</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C675" t="s">
         <v>1303</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.15">
@@ -12131,10 +12132,10 @@
         <v>767</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C677" t="s">
         <v>1305</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.15">
@@ -12143,7 +12144,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.15">
@@ -12151,10 +12152,10 @@
         <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C679" t="s">
         <v>1308</v>
-      </c>
-      <c r="C679" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.15">
@@ -12162,10 +12163,10 @@
         <v>772</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C680" s="3" t="s">
         <v>1313</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.15">
@@ -12174,7 +12175,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.15">
@@ -12183,7 +12184,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.15">
@@ -12192,7 +12193,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.15">
@@ -12201,7 +12202,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.15">
@@ -12210,7 +12211,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.15">
@@ -12219,7 +12220,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.15">
@@ -12228,7 +12229,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.15">
@@ -12237,7 +12238,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.15">
@@ -12246,7 +12247,7 @@
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.15">
@@ -12254,10 +12255,10 @@
         <v>10001</v>
       </c>
       <c r="B690" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.15">
@@ -12265,10 +12266,10 @@
         <v>10003</v>
       </c>
       <c r="B691" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C691" t="s">
         <v>1308</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1309</v>
       </c>
     </row>
   </sheetData>
@@ -12276,7 +12277,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254 A153:C153 A152:B152" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154764E1-0675-46E7-8DBC-4A9BC5551E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D408D7D9-613B-415F-A8DC-A43B2AC2F574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24480" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -1316,9 +1316,6 @@
     <t>What's the POPIPA!?</t>
   </si>
   <si>
-    <t>啥是破琵琶,什么是破琵琶啊（战术后仰）,啥是薄饼趴,啥是ppp,wtppp,什么是破琵琶啊(战术后仰),ppp战歌</t>
-  </si>
-  <si>
     <t>コレカラ</t>
   </si>
   <si>
@@ -4292,6 +4289,10 @@
   </si>
   <si>
     <t>riot,come in,暴乱,骚乱,暴动</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>啥是破琵琶,什么是破琵琶啊（战术后仰）,啥是薄饼趴,啥是ppp,wtppp,什么是破琵琶啊(战术后仰),ppp战歌,什么是ppp,什么是popipa,啥是ppp,啥是popipa,什么事ppp,什么事popipa,啥事ppp,啥事popipa,什么事破琵琶,啥事破琵琶,</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5346,7 +5347,7 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
@@ -5962,7 +5963,7 @@
         <v>224</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
@@ -6149,7 +6150,7 @@
         <v>257</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.15">
@@ -6391,7 +6392,7 @@
         <v>300</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.15">
@@ -6556,7 +6557,7 @@
         <v>329</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.15">
@@ -7039,8 +7040,8 @@
       <c r="B211" t="s">
         <v>416</v>
       </c>
-      <c r="C211" t="s">
-        <v>417</v>
+      <c r="C211" s="3" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.15">
@@ -7048,10 +7049,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
+        <v>417</v>
+      </c>
+      <c r="C212" t="s">
         <v>418</v>
-      </c>
-      <c r="C212" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.15">
@@ -7059,10 +7060,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
+        <v>419</v>
+      </c>
+      <c r="C213" t="s">
         <v>420</v>
-      </c>
-      <c r="C213" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.15">
@@ -7070,10 +7071,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
+        <v>421</v>
+      </c>
+      <c r="C214" t="s">
         <v>422</v>
-      </c>
-      <c r="C214" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.15">
@@ -7081,10 +7082,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
+        <v>423</v>
+      </c>
+      <c r="C215" t="s">
         <v>424</v>
-      </c>
-      <c r="C215" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.15">
@@ -7092,10 +7093,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
+        <v>425</v>
+      </c>
+      <c r="C216" t="s">
         <v>426</v>
-      </c>
-      <c r="C216" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.15">
@@ -7103,10 +7104,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
+        <v>427</v>
+      </c>
+      <c r="C217" t="s">
         <v>428</v>
-      </c>
-      <c r="C217" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.15">
@@ -7114,10 +7115,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
+        <v>429</v>
+      </c>
+      <c r="C218" t="s">
         <v>430</v>
-      </c>
-      <c r="C218" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.15">
@@ -7125,10 +7126,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
+        <v>431</v>
+      </c>
+      <c r="C219" t="s">
         <v>432</v>
-      </c>
-      <c r="C219" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.15">
@@ -7136,10 +7137,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
+        <v>433</v>
+      </c>
+      <c r="C220" t="s">
         <v>434</v>
-      </c>
-      <c r="C220" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.15">
@@ -7147,10 +7148,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
+        <v>435</v>
+      </c>
+      <c r="C221" t="s">
         <v>436</v>
-      </c>
-      <c r="C221" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.15">
@@ -7158,10 +7159,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
+        <v>437</v>
+      </c>
+      <c r="C222" t="s">
         <v>438</v>
-      </c>
-      <c r="C222" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.15">
@@ -7169,10 +7170,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
+        <v>439</v>
+      </c>
+      <c r="C223" t="s">
         <v>440</v>
-      </c>
-      <c r="C223" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.15">
@@ -7180,10 +7181,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.15">
@@ -7191,10 +7192,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>442</v>
+      </c>
+      <c r="C225" t="s">
         <v>443</v>
-      </c>
-      <c r="C225" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.15">
@@ -7202,10 +7203,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>444</v>
+      </c>
+      <c r="C226" t="s">
         <v>445</v>
-      </c>
-      <c r="C226" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.15">
@@ -7213,10 +7214,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>446</v>
+      </c>
+      <c r="C227" t="s">
         <v>447</v>
-      </c>
-      <c r="C227" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.15">
@@ -7224,10 +7225,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>448</v>
+      </c>
+      <c r="C228" t="s">
         <v>449</v>
-      </c>
-      <c r="C228" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.15">
@@ -7235,10 +7236,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
+        <v>450</v>
+      </c>
+      <c r="C229" t="s">
         <v>451</v>
-      </c>
-      <c r="C229" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.15">
@@ -7246,10 +7247,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
+        <v>452</v>
+      </c>
+      <c r="C230" t="s">
         <v>453</v>
-      </c>
-      <c r="C230" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.15">
@@ -7257,10 +7258,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>454</v>
+      </c>
+      <c r="C231" t="s">
         <v>455</v>
-      </c>
-      <c r="C231" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.15">
@@ -7268,10 +7269,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>456</v>
+      </c>
+      <c r="C232" t="s">
         <v>457</v>
-      </c>
-      <c r="C232" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.15">
@@ -7279,10 +7280,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>458</v>
+      </c>
+      <c r="C233" t="s">
         <v>459</v>
-      </c>
-      <c r="C233" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.15">
@@ -7290,10 +7291,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
+        <v>460</v>
+      </c>
+      <c r="C234" t="s">
         <v>461</v>
-      </c>
-      <c r="C234" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.15">
@@ -7301,10 +7302,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>462</v>
+      </c>
+      <c r="C235" t="s">
         <v>463</v>
-      </c>
-      <c r="C235" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.15">
@@ -7312,10 +7313,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>464</v>
+      </c>
+      <c r="C236" t="s">
         <v>465</v>
-      </c>
-      <c r="C236" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.15">
@@ -7323,10 +7324,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>466</v>
+      </c>
+      <c r="C237" t="s">
         <v>467</v>
-      </c>
-      <c r="C237" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.15">
@@ -7334,10 +7335,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>468</v>
+      </c>
+      <c r="C238" t="s">
         <v>469</v>
-      </c>
-      <c r="C238" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.15">
@@ -7345,10 +7346,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>470</v>
+      </c>
+      <c r="C239" t="s">
         <v>471</v>
-      </c>
-      <c r="C239" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.15">
@@ -7356,10 +7357,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>472</v>
+      </c>
+      <c r="C240" t="s">
         <v>473</v>
-      </c>
-      <c r="C240" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.15">
@@ -7367,10 +7368,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>474</v>
+      </c>
+      <c r="C241" t="s">
         <v>475</v>
-      </c>
-      <c r="C241" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.15">
@@ -7378,10 +7379,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>476</v>
+      </c>
+      <c r="C242" t="s">
         <v>477</v>
-      </c>
-      <c r="C242" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.15">
@@ -7389,10 +7390,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>478</v>
+      </c>
+      <c r="C243" t="s">
         <v>479</v>
-      </c>
-      <c r="C243" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.15">
@@ -7400,10 +7401,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>480</v>
+      </c>
+      <c r="C244" t="s">
         <v>481</v>
-      </c>
-      <c r="C244" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.15">
@@ -7411,10 +7412,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>482</v>
+      </c>
+      <c r="C245" t="s">
         <v>483</v>
-      </c>
-      <c r="C245" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.15">
@@ -7422,10 +7423,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>484</v>
+      </c>
+      <c r="C246" t="s">
         <v>485</v>
-      </c>
-      <c r="C246" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.15">
@@ -7433,10 +7434,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>486</v>
+      </c>
+      <c r="C247" t="s">
         <v>487</v>
-      </c>
-      <c r="C247" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.15">
@@ -7444,10 +7445,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>488</v>
+      </c>
+      <c r="C248" t="s">
         <v>489</v>
-      </c>
-      <c r="C248" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.15">
@@ -7455,10 +7456,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>490</v>
+      </c>
+      <c r="C249" t="s">
         <v>491</v>
-      </c>
-      <c r="C249" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.15">
@@ -7466,10 +7467,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
+        <v>492</v>
+      </c>
+      <c r="C250" t="s">
         <v>493</v>
-      </c>
-      <c r="C250" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.15">
@@ -7477,10 +7478,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.15">
@@ -7488,10 +7489,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C252" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.15">
@@ -7499,10 +7500,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>496</v>
+      </c>
+      <c r="C253" t="s">
         <v>497</v>
-      </c>
-      <c r="C253" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.15">
@@ -7510,10 +7511,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.15">
@@ -7521,10 +7522,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>499</v>
+      </c>
+      <c r="C255" t="s">
         <v>500</v>
-      </c>
-      <c r="C255" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.15">
@@ -7532,10 +7533,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>501</v>
+      </c>
+      <c r="C256" t="s">
         <v>502</v>
-      </c>
-      <c r="C256" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.15">
@@ -7543,10 +7544,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>503</v>
+      </c>
+      <c r="C257" t="s">
         <v>504</v>
-      </c>
-      <c r="C257" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.15">
@@ -7554,10 +7555,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>505</v>
+      </c>
+      <c r="C258" t="s">
         <v>506</v>
-      </c>
-      <c r="C258" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.15">
@@ -7565,10 +7566,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>507</v>
+      </c>
+      <c r="C259" t="s">
         <v>508</v>
-      </c>
-      <c r="C259" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.15">
@@ -7576,10 +7577,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>509</v>
+      </c>
+      <c r="C260" t="s">
         <v>510</v>
-      </c>
-      <c r="C260" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.15">
@@ -7587,10 +7588,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>511</v>
+      </c>
+      <c r="C261" t="s">
         <v>512</v>
-      </c>
-      <c r="C261" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.15">
@@ -7598,10 +7599,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>513</v>
+      </c>
+      <c r="C262" t="s">
         <v>514</v>
-      </c>
-      <c r="C262" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.15">
@@ -7609,10 +7610,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>515</v>
+      </c>
+      <c r="C263" t="s">
         <v>516</v>
-      </c>
-      <c r="C263" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.15">
@@ -7620,10 +7621,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>517</v>
+      </c>
+      <c r="C264" t="s">
         <v>518</v>
-      </c>
-      <c r="C264" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.15">
@@ -7631,10 +7632,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>519</v>
+      </c>
+      <c r="C265" t="s">
         <v>520</v>
-      </c>
-      <c r="C265" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.15">
@@ -7642,10 +7643,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>521</v>
+      </c>
+      <c r="C266" t="s">
         <v>522</v>
-      </c>
-      <c r="C266" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.15">
@@ -7653,10 +7654,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>523</v>
+      </c>
+      <c r="C267" t="s">
         <v>524</v>
-      </c>
-      <c r="C267" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.15">
@@ -7664,10 +7665,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>525</v>
+      </c>
+      <c r="C268" t="s">
         <v>526</v>
-      </c>
-      <c r="C268" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.15">
@@ -7675,10 +7676,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>527</v>
+      </c>
+      <c r="C269" t="s">
         <v>528</v>
-      </c>
-      <c r="C269" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.15">
@@ -7686,10 +7687,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>529</v>
+      </c>
+      <c r="C270" t="s">
         <v>530</v>
-      </c>
-      <c r="C270" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.15">
@@ -7697,10 +7698,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.15">
@@ -7708,10 +7709,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>532</v>
+      </c>
+      <c r="C272" t="s">
         <v>533</v>
-      </c>
-      <c r="C272" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.15">
@@ -7719,10 +7720,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>534</v>
+      </c>
+      <c r="C273" t="s">
         <v>535</v>
-      </c>
-      <c r="C273" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.15">
@@ -7730,10 +7731,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>536</v>
+      </c>
+      <c r="C274" t="s">
         <v>537</v>
-      </c>
-      <c r="C274" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.15">
@@ -7741,10 +7742,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>538</v>
+      </c>
+      <c r="C275" t="s">
         <v>539</v>
-      </c>
-      <c r="C275" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.15">
@@ -7752,10 +7753,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>540</v>
+      </c>
+      <c r="C276" t="s">
         <v>541</v>
-      </c>
-      <c r="C276" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.15">
@@ -7763,10 +7764,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>542</v>
+      </c>
+      <c r="C277" t="s">
         <v>543</v>
-      </c>
-      <c r="C277" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.15">
@@ -7774,10 +7775,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>544</v>
+      </c>
+      <c r="C278" t="s">
         <v>545</v>
-      </c>
-      <c r="C278" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.15">
@@ -7785,10 +7786,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>546</v>
+      </c>
+      <c r="C279" t="s">
         <v>547</v>
-      </c>
-      <c r="C279" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.15">
@@ -7796,10 +7797,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>548</v>
+      </c>
+      <c r="C280" t="s">
         <v>549</v>
-      </c>
-      <c r="C280" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.15">
@@ -7807,10 +7808,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>550</v>
+      </c>
+      <c r="C281" t="s">
         <v>551</v>
-      </c>
-      <c r="C281" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.15">
@@ -7818,10 +7819,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>552</v>
+      </c>
+      <c r="C282" t="s">
         <v>553</v>
-      </c>
-      <c r="C282" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.15">
@@ -7829,10 +7830,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>554</v>
+      </c>
+      <c r="C283" t="s">
         <v>555</v>
-      </c>
-      <c r="C283" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.15">
@@ -7840,10 +7841,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>556</v>
+      </c>
+      <c r="C284" t="s">
         <v>557</v>
-      </c>
-      <c r="C284" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.15">
@@ -7851,10 +7852,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>558</v>
+      </c>
+      <c r="C285" t="s">
         <v>559</v>
-      </c>
-      <c r="C285" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.15">
@@ -7862,10 +7863,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>560</v>
+      </c>
+      <c r="C286" t="s">
         <v>561</v>
-      </c>
-      <c r="C286" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.15">
@@ -7873,10 +7874,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>562</v>
+      </c>
+      <c r="C287" t="s">
         <v>563</v>
-      </c>
-      <c r="C287" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.15">
@@ -7884,10 +7885,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>564</v>
+      </c>
+      <c r="C288" t="s">
         <v>565</v>
-      </c>
-      <c r="C288" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.15">
@@ -7895,10 +7896,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>566</v>
+      </c>
+      <c r="C289" t="s">
         <v>567</v>
-      </c>
-      <c r="C289" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.15">
@@ -7906,10 +7907,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>568</v>
+      </c>
+      <c r="C290" t="s">
         <v>569</v>
-      </c>
-      <c r="C290" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.15">
@@ -7917,10 +7918,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>570</v>
+      </c>
+      <c r="C291" t="s">
         <v>571</v>
-      </c>
-      <c r="C291" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.15">
@@ -7928,10 +7929,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>572</v>
+      </c>
+      <c r="C292" t="s">
         <v>573</v>
-      </c>
-      <c r="C292" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.15">
@@ -7939,10 +7940,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>574</v>
+      </c>
+      <c r="C293" t="s">
         <v>575</v>
-      </c>
-      <c r="C293" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.15">
@@ -7950,10 +7951,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>576</v>
+      </c>
+      <c r="C294" t="s">
         <v>577</v>
-      </c>
-      <c r="C294" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.15">
@@ -7961,10 +7962,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>578</v>
+      </c>
+      <c r="C295" t="s">
         <v>579</v>
-      </c>
-      <c r="C295" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.15">
@@ -7972,10 +7973,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.15">
@@ -7983,10 +7984,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>581</v>
+      </c>
+      <c r="C297" t="s">
         <v>582</v>
-      </c>
-      <c r="C297" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.15">
@@ -7994,10 +7995,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>583</v>
+      </c>
+      <c r="C298" t="s">
         <v>584</v>
-      </c>
-      <c r="C298" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.15">
@@ -8005,10 +8006,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>585</v>
+      </c>
+      <c r="C299" t="s">
         <v>586</v>
-      </c>
-      <c r="C299" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.15">
@@ -8016,10 +8017,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>587</v>
+      </c>
+      <c r="C300" t="s">
         <v>588</v>
-      </c>
-      <c r="C300" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.15">
@@ -8027,10 +8028,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>589</v>
+      </c>
+      <c r="C301" t="s">
         <v>590</v>
-      </c>
-      <c r="C301" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.15">
@@ -8038,10 +8039,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>591</v>
+      </c>
+      <c r="C302" t="s">
         <v>592</v>
-      </c>
-      <c r="C302" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.15">
@@ -8049,10 +8050,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>593</v>
+      </c>
+      <c r="C303" t="s">
         <v>594</v>
-      </c>
-      <c r="C303" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.15">
@@ -8060,10 +8061,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>595</v>
+      </c>
+      <c r="C304" t="s">
         <v>596</v>
-      </c>
-      <c r="C304" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.15">
@@ -8071,10 +8072,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>597</v>
+      </c>
+      <c r="C305" t="s">
         <v>598</v>
-      </c>
-      <c r="C305" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.15">
@@ -8082,10 +8083,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>599</v>
+      </c>
+      <c r="C306" t="s">
         <v>600</v>
-      </c>
-      <c r="C306" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.15">
@@ -8093,10 +8094,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>601</v>
+      </c>
+      <c r="C307" t="s">
         <v>602</v>
-      </c>
-      <c r="C307" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.15">
@@ -8104,10 +8105,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>603</v>
+      </c>
+      <c r="C308" t="s">
         <v>604</v>
-      </c>
-      <c r="C308" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.15">
@@ -8115,10 +8116,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>605</v>
+      </c>
+      <c r="C309" t="s">
         <v>606</v>
-      </c>
-      <c r="C309" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.15">
@@ -8126,10 +8127,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>607</v>
+      </c>
+      <c r="C310" t="s">
         <v>608</v>
-      </c>
-      <c r="C310" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.15">
@@ -8137,10 +8138,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>609</v>
+      </c>
+      <c r="C311" t="s">
         <v>610</v>
-      </c>
-      <c r="C311" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.15">
@@ -8148,10 +8149,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>611</v>
+      </c>
+      <c r="C312" t="s">
         <v>612</v>
-      </c>
-      <c r="C312" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.15">
@@ -8159,10 +8160,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>613</v>
+      </c>
+      <c r="C313" t="s">
         <v>614</v>
-      </c>
-      <c r="C313" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.15">
@@ -8170,10 +8171,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>615</v>
+      </c>
+      <c r="C314" t="s">
         <v>616</v>
-      </c>
-      <c r="C314" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.15">
@@ -8181,10 +8182,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>617</v>
+      </c>
+      <c r="C315" t="s">
         <v>618</v>
-      </c>
-      <c r="C315" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.15">
@@ -8192,10 +8193,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>619</v>
+      </c>
+      <c r="C316" t="s">
         <v>620</v>
-      </c>
-      <c r="C316" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.15">
@@ -8203,10 +8204,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>621</v>
+      </c>
+      <c r="C317" t="s">
         <v>622</v>
-      </c>
-      <c r="C317" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.15">
@@ -8214,10 +8215,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>623</v>
+      </c>
+      <c r="C318" t="s">
         <v>624</v>
-      </c>
-      <c r="C318" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.15">
@@ -8225,10 +8226,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>625</v>
+      </c>
+      <c r="C319" t="s">
         <v>626</v>
-      </c>
-      <c r="C319" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.15">
@@ -8236,10 +8237,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>627</v>
+      </c>
+      <c r="C320" t="s">
         <v>628</v>
-      </c>
-      <c r="C320" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.15">
@@ -8247,10 +8248,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>629</v>
+      </c>
+      <c r="C321" t="s">
         <v>630</v>
-      </c>
-      <c r="C321" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.15">
@@ -8258,10 +8259,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>631</v>
+      </c>
+      <c r="C322" t="s">
         <v>632</v>
-      </c>
-      <c r="C322" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.15">
@@ -8269,10 +8270,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>633</v>
+      </c>
+      <c r="C323" t="s">
         <v>634</v>
-      </c>
-      <c r="C323" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.15">
@@ -8280,10 +8281,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>635</v>
+      </c>
+      <c r="C324" t="s">
         <v>636</v>
-      </c>
-      <c r="C324" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.15">
@@ -8291,10 +8292,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>637</v>
+      </c>
+      <c r="C325" t="s">
         <v>638</v>
-      </c>
-      <c r="C325" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.15">
@@ -8302,10 +8303,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>639</v>
+      </c>
+      <c r="C326" t="s">
         <v>640</v>
-      </c>
-      <c r="C326" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.15">
@@ -8313,10 +8314,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>641</v>
+      </c>
+      <c r="C327" t="s">
         <v>642</v>
-      </c>
-      <c r="C327" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.15">
@@ -8324,10 +8325,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>643</v>
+      </c>
+      <c r="C328" t="s">
         <v>644</v>
-      </c>
-      <c r="C328" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.15">
@@ -8335,10 +8336,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>645</v>
+      </c>
+      <c r="C329" t="s">
         <v>646</v>
-      </c>
-      <c r="C329" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.15">
@@ -8346,10 +8347,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>647</v>
+      </c>
+      <c r="C330" t="s">
         <v>648</v>
-      </c>
-      <c r="C330" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.15">
@@ -8357,10 +8358,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>649</v>
+      </c>
+      <c r="C331" t="s">
         <v>650</v>
-      </c>
-      <c r="C331" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.15">
@@ -8368,10 +8369,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>651</v>
+      </c>
+      <c r="C332" t="s">
         <v>652</v>
-      </c>
-      <c r="C332" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.15">
@@ -8379,10 +8380,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>653</v>
+      </c>
+      <c r="C333" t="s">
         <v>654</v>
-      </c>
-      <c r="C333" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.15">
@@ -8390,10 +8391,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>655</v>
+      </c>
+      <c r="C334" t="s">
         <v>656</v>
-      </c>
-      <c r="C334" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.15">
@@ -8401,10 +8402,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>657</v>
+      </c>
+      <c r="C335" t="s">
         <v>658</v>
-      </c>
-      <c r="C335" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.15">
@@ -8412,10 +8413,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>659</v>
+      </c>
+      <c r="C336" t="s">
         <v>660</v>
-      </c>
-      <c r="C336" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.15">
@@ -8423,10 +8424,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>661</v>
+      </c>
+      <c r="C337" t="s">
         <v>662</v>
-      </c>
-      <c r="C337" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.15">
@@ -8434,10 +8435,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.15">
@@ -8445,10 +8446,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.15">
@@ -8456,10 +8457,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>665</v>
+      </c>
+      <c r="C340" t="s">
         <v>666</v>
-      </c>
-      <c r="C340" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.15">
@@ -8467,10 +8468,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>667</v>
+      </c>
+      <c r="C341" t="s">
         <v>668</v>
-      </c>
-      <c r="C341" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.15">
@@ -8478,10 +8479,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>669</v>
+      </c>
+      <c r="C342" t="s">
         <v>670</v>
-      </c>
-      <c r="C342" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.15">
@@ -8489,10 +8490,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>671</v>
+      </c>
+      <c r="C343" t="s">
         <v>672</v>
-      </c>
-      <c r="C343" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.15">
@@ -8500,10 +8501,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>673</v>
+      </c>
+      <c r="C344" t="s">
         <v>674</v>
-      </c>
-      <c r="C344" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.15">
@@ -8511,10 +8512,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>675</v>
+      </c>
+      <c r="C345" t="s">
         <v>676</v>
-      </c>
-      <c r="C345" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.15">
@@ -8522,10 +8523,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>677</v>
+      </c>
+      <c r="C346" t="s">
         <v>678</v>
-      </c>
-      <c r="C346" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.15">
@@ -8533,10 +8534,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>679</v>
+      </c>
+      <c r="C347" t="s">
         <v>680</v>
-      </c>
-      <c r="C347" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.15">
@@ -8544,10 +8545,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>681</v>
+      </c>
+      <c r="C348" t="s">
         <v>682</v>
-      </c>
-      <c r="C348" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.15">
@@ -8555,10 +8556,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>683</v>
+      </c>
+      <c r="C349" t="s">
         <v>684</v>
-      </c>
-      <c r="C349" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.15">
@@ -8566,10 +8567,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>685</v>
+      </c>
+      <c r="C350" t="s">
         <v>686</v>
-      </c>
-      <c r="C350" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.15">
@@ -8577,10 +8578,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>687</v>
+      </c>
+      <c r="C351" t="s">
         <v>688</v>
-      </c>
-      <c r="C351" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.15">
@@ -8588,10 +8589,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>689</v>
+      </c>
+      <c r="C352" t="s">
         <v>690</v>
-      </c>
-      <c r="C352" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.15">
@@ -8599,10 +8600,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>691</v>
+      </c>
+      <c r="C353" t="s">
         <v>692</v>
-      </c>
-      <c r="C353" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.15">
@@ -8610,10 +8611,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>693</v>
+      </c>
+      <c r="C354" t="s">
         <v>694</v>
-      </c>
-      <c r="C354" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.15">
@@ -8621,10 +8622,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>695</v>
+      </c>
+      <c r="C355" t="s">
         <v>696</v>
-      </c>
-      <c r="C355" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.15">
@@ -8632,10 +8633,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>697</v>
+      </c>
+      <c r="C356" t="s">
         <v>698</v>
-      </c>
-      <c r="C356" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.15">
@@ -8643,10 +8644,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>699</v>
+      </c>
+      <c r="C357" t="s">
         <v>700</v>
-      </c>
-      <c r="C357" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.15">
@@ -8654,10 +8655,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>701</v>
+      </c>
+      <c r="C358" t="s">
         <v>702</v>
-      </c>
-      <c r="C358" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.15">
@@ -8665,10 +8666,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>703</v>
+      </c>
+      <c r="C359" t="s">
         <v>704</v>
-      </c>
-      <c r="C359" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.15">
@@ -8676,10 +8677,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>705</v>
+      </c>
+      <c r="C360" t="s">
         <v>706</v>
-      </c>
-      <c r="C360" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.15">
@@ -8687,10 +8688,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>707</v>
+      </c>
+      <c r="C361" t="s">
         <v>708</v>
-      </c>
-      <c r="C361" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.15">
@@ -8698,10 +8699,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>709</v>
+      </c>
+      <c r="C362" t="s">
         <v>710</v>
-      </c>
-      <c r="C362" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.15">
@@ -8709,10 +8710,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>711</v>
+      </c>
+      <c r="C363" t="s">
         <v>712</v>
-      </c>
-      <c r="C363" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.15">
@@ -8720,10 +8721,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>713</v>
+      </c>
+      <c r="C364" t="s">
         <v>714</v>
-      </c>
-      <c r="C364" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.15">
@@ -8731,10 +8732,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>715</v>
+      </c>
+      <c r="C365" t="s">
         <v>716</v>
-      </c>
-      <c r="C365" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.15">
@@ -8742,10 +8743,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>717</v>
+      </c>
+      <c r="C366" t="s">
         <v>718</v>
-      </c>
-      <c r="C366" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.15">
@@ -8753,10 +8754,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>719</v>
+      </c>
+      <c r="C367" t="s">
         <v>720</v>
-      </c>
-      <c r="C367" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.15">
@@ -8764,10 +8765,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>721</v>
+      </c>
+      <c r="C368" t="s">
         <v>722</v>
-      </c>
-      <c r="C368" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.15">
@@ -8775,10 +8776,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>723</v>
+      </c>
+      <c r="C369" t="s">
         <v>724</v>
-      </c>
-      <c r="C369" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.15">
@@ -8786,10 +8787,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>725</v>
+      </c>
+      <c r="C370" t="s">
         <v>726</v>
-      </c>
-      <c r="C370" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.15">
@@ -8797,10 +8798,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>727</v>
+      </c>
+      <c r="C371" t="s">
         <v>728</v>
-      </c>
-      <c r="C371" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.15">
@@ -8808,10 +8809,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>729</v>
+      </c>
+      <c r="C372" t="s">
         <v>730</v>
-      </c>
-      <c r="C372" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.15">
@@ -8819,10 +8820,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>731</v>
+      </c>
+      <c r="C373" t="s">
         <v>732</v>
-      </c>
-      <c r="C373" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.15">
@@ -8830,10 +8831,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>733</v>
+      </c>
+      <c r="C374" t="s">
         <v>734</v>
-      </c>
-      <c r="C374" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.15">
@@ -8841,10 +8842,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>735</v>
+      </c>
+      <c r="C375" t="s">
         <v>736</v>
-      </c>
-      <c r="C375" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.15">
@@ -8852,10 +8853,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>737</v>
+      </c>
+      <c r="C376" t="s">
         <v>738</v>
-      </c>
-      <c r="C376" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.15">
@@ -8863,10 +8864,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>739</v>
+      </c>
+      <c r="C377" t="s">
         <v>740</v>
-      </c>
-      <c r="C377" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.15">
@@ -8874,10 +8875,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>741</v>
+      </c>
+      <c r="C378" t="s">
         <v>742</v>
-      </c>
-      <c r="C378" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.15">
@@ -8885,10 +8886,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>743</v>
+      </c>
+      <c r="C379" t="s">
         <v>744</v>
-      </c>
-      <c r="C379" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.15">
@@ -8896,10 +8897,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>745</v>
+      </c>
+      <c r="C380" t="s">
         <v>746</v>
-      </c>
-      <c r="C380" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.15">
@@ -8907,10 +8908,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>747</v>
+      </c>
+      <c r="C381" t="s">
         <v>748</v>
-      </c>
-      <c r="C381" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.15">
@@ -8918,10 +8919,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>749</v>
+      </c>
+      <c r="C382" t="s">
         <v>750</v>
-      </c>
-      <c r="C382" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.15">
@@ -8929,10 +8930,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>751</v>
+      </c>
+      <c r="C383" t="s">
         <v>752</v>
-      </c>
-      <c r="C383" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.15">
@@ -8940,10 +8941,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>753</v>
+      </c>
+      <c r="C384" t="s">
         <v>754</v>
-      </c>
-      <c r="C384" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.15">
@@ -8951,10 +8952,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>755</v>
+      </c>
+      <c r="C385" t="s">
         <v>756</v>
-      </c>
-      <c r="C385" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.15">
@@ -8962,10 +8963,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>757</v>
+      </c>
+      <c r="C386" t="s">
         <v>758</v>
-      </c>
-      <c r="C386" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.15">
@@ -8973,10 +8974,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>759</v>
+      </c>
+      <c r="C387" t="s">
         <v>760</v>
-      </c>
-      <c r="C387" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.15">
@@ -8984,10 +8985,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>761</v>
+      </c>
+      <c r="C388" t="s">
         <v>762</v>
-      </c>
-      <c r="C388" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.15">
@@ -8995,10 +8996,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>763</v>
+      </c>
+      <c r="C389" t="s">
         <v>764</v>
-      </c>
-      <c r="C389" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.15">
@@ -9006,10 +9007,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>765</v>
+      </c>
+      <c r="C390" t="s">
         <v>766</v>
-      </c>
-      <c r="C390" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.15">
@@ -9017,10 +9018,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>767</v>
+      </c>
+      <c r="C391" t="s">
         <v>768</v>
-      </c>
-      <c r="C391" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
@@ -9028,10 +9029,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>769</v>
+      </c>
+      <c r="C392" t="s">
         <v>770</v>
-      </c>
-      <c r="C392" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.15">
@@ -9039,10 +9040,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>771</v>
+      </c>
+      <c r="C393" t="s">
         <v>772</v>
-      </c>
-      <c r="C393" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.15">
@@ -9050,10 +9051,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>773</v>
+      </c>
+      <c r="C394" t="s">
         <v>774</v>
-      </c>
-      <c r="C394" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.15">
@@ -9061,10 +9062,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>775</v>
+      </c>
+      <c r="C395" t="s">
         <v>776</v>
-      </c>
-      <c r="C395" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.15">
@@ -9072,10 +9073,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>777</v>
+      </c>
+      <c r="C396" t="s">
         <v>778</v>
-      </c>
-      <c r="C396" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.15">
@@ -9083,10 +9084,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>779</v>
+      </c>
+      <c r="C397" t="s">
         <v>780</v>
-      </c>
-      <c r="C397" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.15">
@@ -9094,10 +9095,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>781</v>
+      </c>
+      <c r="C398" t="s">
         <v>782</v>
-      </c>
-      <c r="C398" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.15">
@@ -9105,10 +9106,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>783</v>
+      </c>
+      <c r="C399" t="s">
         <v>784</v>
-      </c>
-      <c r="C399" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.15">
@@ -9116,10 +9117,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>785</v>
+      </c>
+      <c r="C400" t="s">
         <v>786</v>
-      </c>
-      <c r="C400" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.15">
@@ -9127,10 +9128,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>787</v>
+      </c>
+      <c r="C401" t="s">
         <v>788</v>
-      </c>
-      <c r="C401" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.15">
@@ -9138,10 +9139,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>789</v>
+      </c>
+      <c r="C402" t="s">
         <v>790</v>
-      </c>
-      <c r="C402" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.15">
@@ -9149,10 +9150,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>791</v>
+      </c>
+      <c r="C403" t="s">
         <v>792</v>
-      </c>
-      <c r="C403" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.15">
@@ -9160,10 +9161,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>793</v>
+      </c>
+      <c r="C404" t="s">
         <v>794</v>
-      </c>
-      <c r="C404" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.15">
@@ -9171,10 +9172,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>795</v>
+      </c>
+      <c r="C405" t="s">
         <v>796</v>
-      </c>
-      <c r="C405" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.15">
@@ -9182,10 +9183,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>797</v>
+      </c>
+      <c r="C406" t="s">
         <v>798</v>
-      </c>
-      <c r="C406" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.15">
@@ -9193,10 +9194,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>799</v>
+      </c>
+      <c r="C407" t="s">
         <v>800</v>
-      </c>
-      <c r="C407" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.15">
@@ -9204,10 +9205,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>801</v>
+      </c>
+      <c r="C408" t="s">
         <v>802</v>
-      </c>
-      <c r="C408" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.15">
@@ -9215,10 +9216,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>803</v>
+      </c>
+      <c r="C409" t="s">
         <v>804</v>
-      </c>
-      <c r="C409" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.15">
@@ -9226,10 +9227,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>805</v>
+      </c>
+      <c r="C410" t="s">
         <v>806</v>
-      </c>
-      <c r="C410" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.15">
@@ -9237,10 +9238,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>807</v>
+      </c>
+      <c r="C411" t="s">
         <v>808</v>
-      </c>
-      <c r="C411" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.15">
@@ -9248,10 +9249,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>809</v>
+      </c>
+      <c r="C412" t="s">
         <v>810</v>
-      </c>
-      <c r="C412" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.15">
@@ -9259,10 +9260,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>811</v>
+      </c>
+      <c r="C413" t="s">
         <v>812</v>
-      </c>
-      <c r="C413" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.15">
@@ -9270,10 +9271,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>813</v>
+      </c>
+      <c r="C414" t="s">
         <v>814</v>
-      </c>
-      <c r="C414" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.15">
@@ -9281,10 +9282,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>815</v>
+      </c>
+      <c r="C415" t="s">
         <v>816</v>
-      </c>
-      <c r="C415" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.15">
@@ -9292,10 +9293,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>817</v>
+      </c>
+      <c r="C416" t="s">
         <v>818</v>
-      </c>
-      <c r="C416" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.15">
@@ -9303,10 +9304,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>819</v>
+      </c>
+      <c r="C417" t="s">
         <v>820</v>
-      </c>
-      <c r="C417" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.15">
@@ -9314,10 +9315,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>821</v>
+      </c>
+      <c r="C418" t="s">
         <v>822</v>
-      </c>
-      <c r="C418" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.15">
@@ -9325,10 +9326,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>823</v>
+      </c>
+      <c r="C419" t="s">
         <v>824</v>
-      </c>
-      <c r="C419" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.15">
@@ -9336,10 +9337,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>825</v>
+      </c>
+      <c r="C420" t="s">
         <v>826</v>
-      </c>
-      <c r="C420" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.15">
@@ -9347,10 +9348,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>827</v>
+      </c>
+      <c r="C421" t="s">
         <v>828</v>
-      </c>
-      <c r="C421" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.15">
@@ -9358,10 +9359,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>829</v>
+      </c>
+      <c r="C422" t="s">
         <v>830</v>
-      </c>
-      <c r="C422" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.15">
@@ -9369,10 +9370,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>831</v>
+      </c>
+      <c r="C423" t="s">
         <v>832</v>
-      </c>
-      <c r="C423" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.15">
@@ -9380,10 +9381,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>833</v>
+      </c>
+      <c r="C424" t="s">
         <v>834</v>
-      </c>
-      <c r="C424" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.15">
@@ -9391,10 +9392,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>835</v>
+      </c>
+      <c r="C425" t="s">
         <v>836</v>
-      </c>
-      <c r="C425" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.15">
@@ -9402,10 +9403,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>837</v>
+      </c>
+      <c r="C426" t="s">
         <v>838</v>
-      </c>
-      <c r="C426" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.15">
@@ -9413,10 +9414,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>839</v>
+      </c>
+      <c r="C427" t="s">
         <v>840</v>
-      </c>
-      <c r="C427" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.15">
@@ -9424,10 +9425,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C428" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.15">
@@ -9435,10 +9436,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C429" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.15">
@@ -9446,10 +9447,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>843</v>
+      </c>
+      <c r="C430" t="s">
         <v>844</v>
-      </c>
-      <c r="C430" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.15">
@@ -9457,10 +9458,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>845</v>
+      </c>
+      <c r="C431" t="s">
         <v>846</v>
-      </c>
-      <c r="C431" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.15">
@@ -9468,10 +9469,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>847</v>
+      </c>
+      <c r="C432" t="s">
         <v>848</v>
-      </c>
-      <c r="C432" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.15">
@@ -9479,10 +9480,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>849</v>
+      </c>
+      <c r="C433" t="s">
         <v>850</v>
-      </c>
-      <c r="C433" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.15">
@@ -9490,10 +9491,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>851</v>
+      </c>
+      <c r="C434" t="s">
         <v>852</v>
-      </c>
-      <c r="C434" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.15">
@@ -9501,10 +9502,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>853</v>
+      </c>
+      <c r="C435" t="s">
         <v>854</v>
-      </c>
-      <c r="C435" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.15">
@@ -9512,10 +9513,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>855</v>
+      </c>
+      <c r="C436" t="s">
         <v>856</v>
-      </c>
-      <c r="C436" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.15">
@@ -9523,10 +9524,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>857</v>
+      </c>
+      <c r="C437" t="s">
         <v>858</v>
-      </c>
-      <c r="C437" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.15">
@@ -9534,10 +9535,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>859</v>
+      </c>
+      <c r="C438" t="s">
         <v>860</v>
-      </c>
-      <c r="C438" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.15">
@@ -9545,10 +9546,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>861</v>
+      </c>
+      <c r="C439" t="s">
         <v>862</v>
-      </c>
-      <c r="C439" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.15">
@@ -9556,10 +9557,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>863</v>
+      </c>
+      <c r="C440" t="s">
         <v>864</v>
-      </c>
-      <c r="C440" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.15">
@@ -9567,10 +9568,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>865</v>
+      </c>
+      <c r="C441" t="s">
         <v>866</v>
-      </c>
-      <c r="C441" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.15">
@@ -9578,10 +9579,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>867</v>
+      </c>
+      <c r="C442" t="s">
         <v>868</v>
-      </c>
-      <c r="C442" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.15">
@@ -9589,10 +9590,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>869</v>
+      </c>
+      <c r="C443" t="s">
         <v>870</v>
-      </c>
-      <c r="C443" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.15">
@@ -9600,10 +9601,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>871</v>
+      </c>
+      <c r="C444" t="s">
         <v>872</v>
-      </c>
-      <c r="C444" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.15">
@@ -9611,10 +9612,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>873</v>
+      </c>
+      <c r="C445" t="s">
         <v>874</v>
-      </c>
-      <c r="C445" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.15">
@@ -9622,10 +9623,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>875</v>
+      </c>
+      <c r="C446" t="s">
         <v>876</v>
-      </c>
-      <c r="C446" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.15">
@@ -9633,10 +9634,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>877</v>
+      </c>
+      <c r="C447" t="s">
         <v>878</v>
-      </c>
-      <c r="C447" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.15">
@@ -9644,10 +9645,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>879</v>
+      </c>
+      <c r="C448" t="s">
         <v>880</v>
-      </c>
-      <c r="C448" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.15">
@@ -9655,10 +9656,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>881</v>
+      </c>
+      <c r="C449" t="s">
         <v>882</v>
-      </c>
-      <c r="C449" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.15">
@@ -9666,10 +9667,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>883</v>
+      </c>
+      <c r="C450" t="s">
         <v>884</v>
-      </c>
-      <c r="C450" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.15">
@@ -9677,10 +9678,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C451" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.15">
@@ -9688,10 +9689,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>886</v>
+      </c>
+      <c r="C452" t="s">
         <v>887</v>
-      </c>
-      <c r="C452" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.15">
@@ -9699,10 +9700,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>888</v>
+      </c>
+      <c r="C453" t="s">
         <v>889</v>
-      </c>
-      <c r="C453" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.15">
@@ -9710,10 +9711,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>890</v>
+      </c>
+      <c r="C454" t="s">
         <v>891</v>
-      </c>
-      <c r="C454" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.15">
@@ -9721,10 +9722,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>892</v>
+      </c>
+      <c r="C455" t="s">
         <v>893</v>
-      </c>
-      <c r="C455" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.15">
@@ -9732,10 +9733,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C456" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.15">
@@ -9743,10 +9744,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>895</v>
+      </c>
+      <c r="C457" t="s">
         <v>896</v>
-      </c>
-      <c r="C457" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.15">
@@ -9754,10 +9755,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>897</v>
+      </c>
+      <c r="C458" t="s">
         <v>898</v>
-      </c>
-      <c r="C458" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.15">
@@ -9765,10 +9766,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>899</v>
+      </c>
+      <c r="C459" t="s">
         <v>900</v>
-      </c>
-      <c r="C459" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.15">
@@ -9776,7 +9777,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.15">
@@ -9784,10 +9785,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>902</v>
+      </c>
+      <c r="C461" t="s">
         <v>903</v>
-      </c>
-      <c r="C461" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.15">
@@ -9795,10 +9796,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>904</v>
+      </c>
+      <c r="C462" t="s">
         <v>905</v>
-      </c>
-      <c r="C462" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.15">
@@ -9806,10 +9807,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>906</v>
+      </c>
+      <c r="C463" t="s">
         <v>907</v>
-      </c>
-      <c r="C463" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.15">
@@ -9817,10 +9818,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>908</v>
+      </c>
+      <c r="C464" t="s">
         <v>909</v>
-      </c>
-      <c r="C464" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.15">
@@ -9828,10 +9829,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>910</v>
+      </c>
+      <c r="C465" t="s">
         <v>911</v>
-      </c>
-      <c r="C465" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.15">
@@ -9839,10 +9840,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>912</v>
+      </c>
+      <c r="C466" t="s">
         <v>913</v>
-      </c>
-      <c r="C466" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.15">
@@ -9850,10 +9851,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.15">
@@ -9861,10 +9862,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>915</v>
+      </c>
+      <c r="C468" t="s">
         <v>916</v>
-      </c>
-      <c r="C468" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.15">
@@ -9872,10 +9873,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>917</v>
+      </c>
+      <c r="C469" t="s">
         <v>918</v>
-      </c>
-      <c r="C469" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.15">
@@ -9883,10 +9884,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>919</v>
+      </c>
+      <c r="C470" t="s">
         <v>920</v>
-      </c>
-      <c r="C470" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.15">
@@ -9894,10 +9895,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>921</v>
+      </c>
+      <c r="C471" t="s">
         <v>922</v>
-      </c>
-      <c r="C471" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.15">
@@ -9905,10 +9906,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>923</v>
+      </c>
+      <c r="C472" t="s">
         <v>924</v>
-      </c>
-      <c r="C472" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
@@ -9916,10 +9917,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>925</v>
+      </c>
+      <c r="C473" t="s">
         <v>926</v>
-      </c>
-      <c r="C473" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.15">
@@ -9927,10 +9928,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>927</v>
+      </c>
+      <c r="C474" t="s">
         <v>928</v>
-      </c>
-      <c r="C474" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.15">
@@ -9938,10 +9939,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>929</v>
+      </c>
+      <c r="C475" t="s">
         <v>930</v>
-      </c>
-      <c r="C475" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.15">
@@ -9949,10 +9950,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>931</v>
+      </c>
+      <c r="C476" t="s">
         <v>932</v>
-      </c>
-      <c r="C476" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.15">
@@ -9960,10 +9961,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>933</v>
+      </c>
+      <c r="C477" t="s">
         <v>934</v>
-      </c>
-      <c r="C477" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.15">
@@ -9971,10 +9972,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C478" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.15">
@@ -9982,10 +9983,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>936</v>
+      </c>
+      <c r="C479" t="s">
         <v>937</v>
-      </c>
-      <c r="C479" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.15">
@@ -9993,10 +9994,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>938</v>
+      </c>
+      <c r="C480" t="s">
         <v>939</v>
-      </c>
-      <c r="C480" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.15">
@@ -10004,10 +10005,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>940</v>
+      </c>
+      <c r="C481" t="s">
         <v>941</v>
-      </c>
-      <c r="C481" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.15">
@@ -10015,10 +10016,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>942</v>
+      </c>
+      <c r="C482" t="s">
         <v>943</v>
-      </c>
-      <c r="C482" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.15">
@@ -10026,10 +10027,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>944</v>
+      </c>
+      <c r="C483" t="s">
         <v>945</v>
-      </c>
-      <c r="C483" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.15">
@@ -10037,10 +10038,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>946</v>
+      </c>
+      <c r="C484" t="s">
         <v>947</v>
-      </c>
-      <c r="C484" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.15">
@@ -10048,10 +10049,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>948</v>
+      </c>
+      <c r="C485" t="s">
         <v>949</v>
-      </c>
-      <c r="C485" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.15">
@@ -10059,10 +10060,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>950</v>
+      </c>
+      <c r="C486" t="s">
         <v>951</v>
-      </c>
-      <c r="C486" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.15">
@@ -10070,10 +10071,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>952</v>
+      </c>
+      <c r="C487" t="s">
         <v>953</v>
-      </c>
-      <c r="C487" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.15">
@@ -10081,10 +10082,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>954</v>
+      </c>
+      <c r="C488" t="s">
         <v>955</v>
-      </c>
-      <c r="C488" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.15">
@@ -10092,10 +10093,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>956</v>
+      </c>
+      <c r="C489" t="s">
         <v>957</v>
-      </c>
-      <c r="C489" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.15">
@@ -10103,10 +10104,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>958</v>
+      </c>
+      <c r="C490" t="s">
         <v>959</v>
-      </c>
-      <c r="C490" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.15">
@@ -10114,10 +10115,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>960</v>
+      </c>
+      <c r="C491" t="s">
         <v>961</v>
-      </c>
-      <c r="C491" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.15">
@@ -10125,10 +10126,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>962</v>
+      </c>
+      <c r="C492" t="s">
         <v>963</v>
-      </c>
-      <c r="C492" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.15">
@@ -10136,10 +10137,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>964</v>
+      </c>
+      <c r="C493" t="s">
         <v>965</v>
-      </c>
-      <c r="C493" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.15">
@@ -10147,10 +10148,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>966</v>
+      </c>
+      <c r="C494" t="s">
         <v>967</v>
-      </c>
-      <c r="C494" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.15">
@@ -10158,10 +10159,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>968</v>
+      </c>
+      <c r="C495" t="s">
         <v>969</v>
-      </c>
-      <c r="C495" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.15">
@@ -10169,10 +10170,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>970</v>
+      </c>
+      <c r="C496" t="s">
         <v>971</v>
-      </c>
-      <c r="C496" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.15">
@@ -10180,10 +10181,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>972</v>
+      </c>
+      <c r="C497" t="s">
         <v>973</v>
-      </c>
-      <c r="C497" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.15">
@@ -10191,10 +10192,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>974</v>
+      </c>
+      <c r="C498" t="s">
         <v>975</v>
-      </c>
-      <c r="C498" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.15">
@@ -10202,7 +10203,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.15">
@@ -10210,10 +10211,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>977</v>
+      </c>
+      <c r="C500" t="s">
         <v>978</v>
-      </c>
-      <c r="C500" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.15">
@@ -10221,10 +10222,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>979</v>
+      </c>
+      <c r="C501" t="s">
         <v>980</v>
-      </c>
-      <c r="C501" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.15">
@@ -10232,10 +10233,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>981</v>
+      </c>
+      <c r="C502" t="s">
         <v>982</v>
-      </c>
-      <c r="C502" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.15">
@@ -10243,10 +10244,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.15">
@@ -10254,10 +10255,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>984</v>
+      </c>
+      <c r="C504" t="s">
         <v>985</v>
-      </c>
-      <c r="C504" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.15">
@@ -10265,10 +10266,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>986</v>
+      </c>
+      <c r="C505" t="s">
         <v>987</v>
-      </c>
-      <c r="C505" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.15">
@@ -10276,10 +10277,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>988</v>
+      </c>
+      <c r="C506" t="s">
         <v>989</v>
-      </c>
-      <c r="C506" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.15">
@@ -10287,10 +10288,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>990</v>
+      </c>
+      <c r="C507" t="s">
         <v>991</v>
-      </c>
-      <c r="C507" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.15">
@@ -10298,10 +10299,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>992</v>
+      </c>
+      <c r="C508" t="s">
         <v>993</v>
-      </c>
-      <c r="C508" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.15">
@@ -10309,10 +10310,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>994</v>
+      </c>
+      <c r="C509" t="s">
         <v>995</v>
-      </c>
-      <c r="C509" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.15">
@@ -10320,10 +10321,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>996</v>
+      </c>
+      <c r="C510" t="s">
         <v>997</v>
-      </c>
-      <c r="C510" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.15">
@@ -10331,10 +10332,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>998</v>
+      </c>
+      <c r="C511" t="s">
         <v>999</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.15">
@@ -10342,10 +10343,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C512" t="s">
         <v>1001</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.15">
@@ -10353,10 +10354,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C513" t="s">
         <v>1003</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.15">
@@ -10364,10 +10365,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C514" t="s">
         <v>1005</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.15">
@@ -10375,10 +10376,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C515" t="s">
         <v>1007</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.15">
@@ -10386,10 +10387,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C516" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.15">
@@ -10397,10 +10398,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C517" t="s">
         <v>1010</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.15">
@@ -10408,7 +10409,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.15">
@@ -10416,10 +10417,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C519" t="s">
         <v>1013</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.15">
@@ -10427,10 +10428,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C520" t="s">
         <v>1015</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.15">
@@ -10438,10 +10439,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C521" t="s">
         <v>1017</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.15">
@@ -10449,10 +10450,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C522" t="s">
         <v>1019</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.15">
@@ -10460,10 +10461,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C523" t="s">
         <v>1021</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.15">
@@ -10471,10 +10472,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C524" t="s">
         <v>1023</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.15">
@@ -10482,10 +10483,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.15">
@@ -10493,10 +10494,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C526" t="s">
         <v>1026</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.15">
@@ -10504,10 +10505,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C527" t="s">
         <v>1028</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.15">
@@ -10515,10 +10516,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C528" t="s">
         <v>1030</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.15">
@@ -10526,10 +10527,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C529" t="s">
         <v>1032</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.15">
@@ -10537,10 +10538,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.15">
@@ -10548,10 +10549,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C531" t="s">
         <v>1035</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.15">
@@ -10559,10 +10560,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C532" t="s">
         <v>1037</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.15">
@@ -10570,10 +10571,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C533" t="s">
         <v>1039</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.15">
@@ -10581,10 +10582,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C534" t="s">
         <v>1041</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.15">
@@ -10592,10 +10593,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C535" t="s">
         <v>1043</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.15">
@@ -10603,10 +10604,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C536" t="s">
         <v>1045</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.15">
@@ -10614,10 +10615,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C537" t="s">
         <v>1047</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.15">
@@ -10625,10 +10626,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C538" t="s">
         <v>1049</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.15">
@@ -10636,10 +10637,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C539" t="s">
         <v>1051</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.15">
@@ -10647,10 +10648,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C540" t="s">
         <v>1053</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.15">
@@ -10658,10 +10659,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C541" t="s">
         <v>1055</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.15">
@@ -10669,10 +10670,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C542" t="s">
         <v>1057</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.15">
@@ -10680,10 +10681,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C543" t="s">
         <v>1059</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.15">
@@ -10691,10 +10692,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C544" t="s">
         <v>1061</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.15">
@@ -10702,10 +10703,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C545" t="s">
         <v>1063</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.15">
@@ -10713,10 +10714,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C546" t="s">
         <v>1065</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.15">
@@ -10724,7 +10725,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.15">
@@ -10732,10 +10733,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C548" t="s">
         <v>1068</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.15">
@@ -10743,10 +10744,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C549" t="s">
         <v>1070</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.15">
@@ -10754,10 +10755,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C550" t="s">
         <v>1072</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.15">
@@ -10765,10 +10766,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C551" t="s">
         <v>1074</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.15">
@@ -10776,10 +10777,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C552" t="s">
         <v>1076</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.15">
@@ -10787,10 +10788,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C553" t="s">
         <v>1078</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.15">
@@ -10798,10 +10799,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C554" t="s">
         <v>1080</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.15">
@@ -10809,10 +10810,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C555" t="s">
         <v>1082</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.15">
@@ -10820,10 +10821,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C556" t="s">
         <v>1084</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.15">
@@ -10831,10 +10832,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C557" t="s">
         <v>1086</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.15">
@@ -10842,10 +10843,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C558" t="s">
         <v>1088</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.15">
@@ -10853,7 +10854,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.15">
@@ -10861,10 +10862,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C560" t="s">
         <v>1091</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.15">
@@ -10872,10 +10873,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C561" t="s">
         <v>1093</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.15">
@@ -10883,10 +10884,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C562" t="s">
         <v>1095</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.15">
@@ -10894,10 +10895,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C563" t="s">
         <v>1097</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.15">
@@ -10905,10 +10906,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C564" t="s">
         <v>1099</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.15">
@@ -10916,10 +10917,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C565" t="s">
         <v>1101</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.15">
@@ -10927,10 +10928,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C566" t="s">
         <v>1103</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.15">
@@ -10938,10 +10939,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C567" t="s">
         <v>1105</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.15">
@@ -10949,10 +10950,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C568" t="s">
         <v>1107</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.15">
@@ -10960,10 +10961,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C569" t="s">
         <v>1109</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.15">
@@ -10971,10 +10972,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C570" t="s">
         <v>1111</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.15">
@@ -10982,10 +10983,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C571" t="s">
         <v>1113</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.15">
@@ -10993,10 +10994,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C572" t="s">
         <v>1115</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.15">
@@ -11004,10 +11005,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C573" t="s">
         <v>1117</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.15">
@@ -11015,10 +11016,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C574" t="s">
         <v>1119</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.15">
@@ -11026,10 +11027,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.15">
@@ -11037,10 +11038,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C576" t="s">
         <v>1122</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.15">
@@ -11048,10 +11049,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.15">
@@ -11059,10 +11060,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.15">
@@ -11070,10 +11071,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C579" t="s">
         <v>1124</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.15">
@@ -11081,10 +11082,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C580" t="s">
         <v>1126</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.15">
@@ -11092,10 +11093,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C581" t="s">
         <v>1128</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.15">
@@ -11103,10 +11104,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C582" t="s">
         <v>1130</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.15">
@@ -11114,10 +11115,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.15">
@@ -11125,7 +11126,7 @@
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.15">
@@ -11133,10 +11134,10 @@
         <v>612</v>
       </c>
       <c r="B585" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C585" t="s">
         <v>1133</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.15">
@@ -11144,10 +11145,10 @@
         <v>615</v>
       </c>
       <c r="B586" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C586" t="s">
         <v>1135</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.15">
@@ -11155,10 +11156,10 @@
         <v>617</v>
       </c>
       <c r="B587" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C587" t="s">
         <v>1137</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.15">
@@ -11166,10 +11167,10 @@
         <v>618</v>
       </c>
       <c r="B588" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C588" t="s">
         <v>1139</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.15">
@@ -11177,10 +11178,10 @@
         <v>625</v>
       </c>
       <c r="B589" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C589" t="s">
         <v>1141</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.15">
@@ -11188,10 +11189,10 @@
         <v>624</v>
       </c>
       <c r="B590" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C590" t="s">
         <v>1143</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.15">
@@ -11199,10 +11200,10 @@
         <v>626</v>
       </c>
       <c r="B591" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C591" t="s">
         <v>1145</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.15">
@@ -11210,10 +11211,10 @@
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C592" t="s">
         <v>1147</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.15">
@@ -11221,10 +11222,10 @@
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C593" t="s">
         <v>1149</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.15">
@@ -11232,7 +11233,7 @@
         <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.15">
@@ -11240,10 +11241,10 @@
         <v>633</v>
       </c>
       <c r="B595" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C595" t="s">
         <v>1152</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.15">
@@ -11251,10 +11252,10 @@
         <v>635</v>
       </c>
       <c r="B596" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C596" t="s">
         <v>1154</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.15">
@@ -11262,10 +11263,10 @@
         <v>636</v>
       </c>
       <c r="B597" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C597" t="s">
         <v>1156</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.15">
@@ -11273,10 +11274,10 @@
         <v>642</v>
       </c>
       <c r="B598" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C598" t="s">
         <v>1158</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.15">
@@ -11284,10 +11285,10 @@
         <v>644</v>
       </c>
       <c r="B599" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C599" t="s">
         <v>1160</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.15">
@@ -11295,10 +11296,10 @@
         <v>646</v>
       </c>
       <c r="B600" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C600" t="s">
         <v>1162</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.15">
@@ -11306,10 +11307,10 @@
         <v>649</v>
       </c>
       <c r="B601" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C601" t="s">
         <v>1164</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.15">
@@ -11317,10 +11318,10 @@
         <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.15">
@@ -11328,10 +11329,10 @@
         <v>651</v>
       </c>
       <c r="B603" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C603" t="s">
         <v>1167</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.15">
@@ -11339,10 +11340,10 @@
         <v>653</v>
       </c>
       <c r="B604" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C604" t="s">
         <v>1169</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.15">
@@ -11350,10 +11351,10 @@
         <v>654</v>
       </c>
       <c r="B605" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C605" t="s">
         <v>1171</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.15">
@@ -11361,10 +11362,10 @@
         <v>655</v>
       </c>
       <c r="B606" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C606" t="s">
         <v>1173</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.15">
@@ -11372,10 +11373,10 @@
         <v>659</v>
       </c>
       <c r="B607" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C607" t="s">
         <v>1175</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.15">
@@ -11383,10 +11384,10 @@
         <v>660</v>
       </c>
       <c r="B608" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C608" t="s">
         <v>1177</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.15">
@@ -11394,10 +11395,10 @@
         <v>661</v>
       </c>
       <c r="B609" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C609" t="s">
         <v>1179</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.15">
@@ -11405,10 +11406,10 @@
         <v>663</v>
       </c>
       <c r="B610" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C610" t="s">
         <v>1181</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.15">
@@ -11416,10 +11417,10 @@
         <v>667</v>
       </c>
       <c r="B611" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C611" t="s">
         <v>1183</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.15">
@@ -11427,10 +11428,10 @@
         <v>670</v>
       </c>
       <c r="B612" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C612" t="s">
         <v>1185</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.15">
@@ -11438,10 +11439,10 @@
         <v>673</v>
       </c>
       <c r="B613" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C613" t="s">
         <v>1187</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.15">
@@ -11449,10 +11450,10 @@
         <v>674</v>
       </c>
       <c r="B614" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C614" t="s">
         <v>1189</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.15">
@@ -11460,10 +11461,10 @@
         <v>675</v>
       </c>
       <c r="B615" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C615" t="s">
         <v>1191</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.15">
@@ -11471,10 +11472,10 @@
         <v>680</v>
       </c>
       <c r="B616" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C616" t="s">
         <v>1193</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.15">
@@ -11482,10 +11483,10 @@
         <v>681</v>
       </c>
       <c r="B617" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C617" t="s">
         <v>1195</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.15">
@@ -11493,10 +11494,10 @@
         <v>682</v>
       </c>
       <c r="B618" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C618" t="s">
         <v>1197</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.15">
@@ -11504,10 +11505,10 @@
         <v>683</v>
       </c>
       <c r="B619" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C619" t="s">
         <v>1199</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.15">
@@ -11515,10 +11516,10 @@
         <v>684</v>
       </c>
       <c r="B620" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C620" t="s">
         <v>1201</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.15">
@@ -11526,10 +11527,10 @@
         <v>685</v>
       </c>
       <c r="B621" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C621" t="s">
         <v>1203</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.15">
@@ -11537,10 +11538,10 @@
         <v>686</v>
       </c>
       <c r="B622" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C622" t="s">
         <v>1205</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.15">
@@ -11548,10 +11549,10 @@
         <v>689</v>
       </c>
       <c r="B623" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C623" t="s">
         <v>1207</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.15">
@@ -11559,10 +11560,10 @@
         <v>697</v>
       </c>
       <c r="B624" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C624" t="s">
         <v>1209</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.15">
@@ -11570,10 +11571,10 @@
         <v>701</v>
       </c>
       <c r="B625" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C625" t="s">
         <v>1211</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.15">
@@ -11581,10 +11582,10 @@
         <v>702</v>
       </c>
       <c r="B626" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C626" t="s">
         <v>1213</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.15">
@@ -11592,10 +11593,10 @@
         <v>704</v>
       </c>
       <c r="B627" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C627" t="s">
         <v>1215</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.15">
@@ -11603,10 +11604,10 @@
         <v>705</v>
       </c>
       <c r="B628" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C628" t="s">
         <v>1217</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.15">
@@ -11614,10 +11615,10 @@
         <v>710</v>
       </c>
       <c r="B629" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C629" t="s">
         <v>1219</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.15">
@@ -11625,10 +11626,10 @@
         <v>711</v>
       </c>
       <c r="B630" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C630" t="s">
         <v>1221</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.15">
@@ -11636,10 +11637,10 @@
         <v>712</v>
       </c>
       <c r="B631" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C631" t="s">
         <v>1223</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.15">
@@ -11647,10 +11648,10 @@
         <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.15">
@@ -11658,10 +11659,10 @@
         <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.15">
@@ -11669,10 +11670,10 @@
         <v>718</v>
       </c>
       <c r="B634" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C634" t="s">
         <v>1227</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.15">
@@ -11680,10 +11681,10 @@
         <v>719</v>
       </c>
       <c r="B635" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C635" t="s">
         <v>1229</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
@@ -11691,10 +11692,10 @@
         <v>721</v>
       </c>
       <c r="B636" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C636" t="s">
         <v>1231</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.15">
@@ -11702,10 +11703,10 @@
         <v>722</v>
       </c>
       <c r="B637" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C637" t="s">
         <v>1233</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.15">
@@ -11713,10 +11714,10 @@
         <v>723</v>
       </c>
       <c r="B638" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C638" t="s">
         <v>1235</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.15">
@@ -11724,7 +11725,7 @@
         <v>724</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.15">
@@ -11732,10 +11733,10 @@
         <v>725</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C640" t="s">
         <v>1237</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.15">
@@ -11743,10 +11744,10 @@
         <v>726</v>
       </c>
       <c r="B641" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C641" t="s">
         <v>1239</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.15">
@@ -11754,10 +11755,10 @@
         <v>727</v>
       </c>
       <c r="B642" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C642" t="s">
         <v>1241</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
@@ -11765,10 +11766,10 @@
         <v>728</v>
       </c>
       <c r="B643" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C643" t="s">
         <v>1243</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
@@ -11776,10 +11777,10 @@
         <v>729</v>
       </c>
       <c r="B644" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C644" t="s">
         <v>1245</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.15">
@@ -11787,10 +11788,10 @@
         <v>730</v>
       </c>
       <c r="B645" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C645" t="s">
         <v>1247</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.15">
@@ -11798,10 +11799,10 @@
         <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.15">
@@ -11809,10 +11810,10 @@
         <v>733</v>
       </c>
       <c r="B647" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C647" t="s">
         <v>1250</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.15">
@@ -11820,10 +11821,10 @@
         <v>735</v>
       </c>
       <c r="B648" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C648" t="s">
         <v>1252</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.15">
@@ -11831,10 +11832,10 @@
         <v>736</v>
       </c>
       <c r="B649" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C649" t="s">
         <v>1254</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.15">
@@ -11842,10 +11843,10 @@
         <v>737</v>
       </c>
       <c r="B650" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C650" t="s">
         <v>1256</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.15">
@@ -11853,10 +11854,10 @@
         <v>738</v>
       </c>
       <c r="B651" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C651" t="s">
         <v>1258</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.15">
@@ -11864,10 +11865,10 @@
         <v>739</v>
       </c>
       <c r="B652" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C652" t="s">
         <v>1260</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.15">
@@ -11875,10 +11876,10 @@
         <v>740</v>
       </c>
       <c r="B653" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C653" t="s">
         <v>1262</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.15">
@@ -11886,10 +11887,10 @@
         <v>741</v>
       </c>
       <c r="B654" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C654" t="s">
         <v>1264</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.15">
@@ -11897,10 +11898,10 @@
         <v>742</v>
       </c>
       <c r="B655" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C655" t="s">
         <v>1266</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.15">
@@ -11908,10 +11909,10 @@
         <v>743</v>
       </c>
       <c r="B656" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C656" t="s">
         <v>1268</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.15">
@@ -11919,10 +11920,10 @@
         <v>744</v>
       </c>
       <c r="B657" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C657" t="s">
         <v>1270</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
@@ -11930,10 +11931,10 @@
         <v>745</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C658" t="s">
         <v>1272</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.15">
@@ -11941,10 +11942,10 @@
         <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C659" t="s">
         <v>1274</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.15">
@@ -11952,10 +11953,10 @@
         <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C660" t="s">
         <v>1276</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.15">
@@ -11963,10 +11964,10 @@
         <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C661" t="s">
         <v>1278</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.15">
@@ -11974,10 +11975,10 @@
         <v>749</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C662" t="s">
         <v>1280</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.15">
@@ -11986,7 +11987,7 @@
       </c>
       <c r="B663" s="1"/>
       <c r="C663" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.15">
@@ -11994,10 +11995,10 @@
         <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C664" t="s">
         <v>1282</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.15">
@@ -12005,10 +12006,10 @@
         <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.15">
@@ -12016,10 +12017,10 @@
         <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C666" t="s">
         <v>1285</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.15">
@@ -12027,10 +12028,10 @@
         <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C667" t="s">
         <v>1287</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.15">
@@ -12038,10 +12039,10 @@
         <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C668" t="s">
         <v>1289</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.15">
@@ -12049,10 +12050,10 @@
         <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.15">
@@ -12060,10 +12061,10 @@
         <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C670" t="s">
         <v>1292</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.15">
@@ -12071,10 +12072,10 @@
         <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C671" t="s">
         <v>1294</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.15">
@@ -12082,10 +12083,10 @@
         <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C672" t="s">
         <v>1296</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.15">
@@ -12093,10 +12094,10 @@
         <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C673" t="s">
         <v>1298</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.15">
@@ -12104,10 +12105,10 @@
         <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C674" t="s">
         <v>1300</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.15">
@@ -12115,10 +12116,10 @@
         <v>765</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C675" t="s">
         <v>1302</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.15">
@@ -12132,10 +12133,10 @@
         <v>767</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C677" t="s">
         <v>1304</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.15">
@@ -12144,7 +12145,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.15">
@@ -12152,10 +12153,10 @@
         <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C679" t="s">
         <v>1307</v>
-      </c>
-      <c r="C679" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.15">
@@ -12163,10 +12164,10 @@
         <v>772</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C680" s="3" t="s">
         <v>1312</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.15">
@@ -12175,7 +12176,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.15">
@@ -12184,7 +12185,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.15">
@@ -12193,7 +12194,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.15">
@@ -12202,7 +12203,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.15">
@@ -12211,7 +12212,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.15">
@@ -12220,7 +12221,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.15">
@@ -12229,7 +12230,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.15">
@@ -12238,7 +12239,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.15">
@@ -12247,7 +12248,7 @@
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.15">
@@ -12255,10 +12256,10 @@
         <v>10001</v>
       </c>
       <c r="B690" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.15">
@@ -12266,10 +12267,10 @@
         <v>10003</v>
       </c>
       <c r="B691" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C691" t="s">
         <v>1307</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1308</v>
       </c>
     </row>
   </sheetData>
@@ -12277,7 +12278,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C223 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254 A153:C153 A152:B152" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C210 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254 A153:C153 A152:B152 A212:C223 A211:B211" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D408D7D9-613B-415F-A8DC-A43B2AC2F574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4175BE74-CAE3-45AA-81A5-1C1A406CB35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24480" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="0" windowWidth="19785" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2075,9 +2075,6 @@
     <t>COLORFUL BOX</t>
   </si>
   <si>
-    <t>白箱,彩箱</t>
-  </si>
-  <si>
     <t>絆色のアンサンブル</t>
   </si>
   <si>
@@ -3570,9 +3567,6 @@
     <t>雑踏、僕らの街</t>
   </si>
   <si>
-    <t>杂沓,杂踏,雑踏,gbcop,熙熙攘攘,gbc,糟蹋</t>
-  </si>
-  <si>
     <t>過惰幻</t>
   </si>
   <si>
@@ -4293,6 +4287,14 @@
   </si>
   <si>
     <t>啥是破琵琶,什么是破琵琶啊（战术后仰）,啥是薄饼趴,啥是ppp,wtppp,什么是破琵琶啊(战术后仰),ppp战歌,什么是ppp,什么是popipa,啥是ppp,啥是popipa,什么事ppp,什么事popipa,啥事ppp,啥事popipa,什么事破琵琶,啥事破琵琶,</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>白箱,彩箱，颜色盒子,颜色的盒子,颜色箱子,颜色的箱子</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>杂沓,杂踏,雑踏,gbcop,熙熙攘攘,gbc,糟蹋,踏街</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4715,15 +4717,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C691"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="50.75" customWidth="1"/>
-    <col min="3" max="3" width="65.75" customWidth="1"/>
-    <col min="4" max="4" width="55.75" customWidth="1"/>
+    <col min="1" max="1" width="10.69921875" customWidth="1"/>
+    <col min="2" max="2" width="50.69921875" customWidth="1"/>
+    <col min="3" max="3" width="65.69921875" customWidth="1"/>
+    <col min="4" max="4" width="55.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4734,7 +4736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4745,7 +4747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4756,7 +4758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4767,7 +4769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4778,7 +4780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4789,7 +4791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4800,7 +4802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4811,7 +4813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4822,7 +4824,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4833,7 +4835,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4844,7 +4846,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4855,7 +4857,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4866,7 +4868,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4877,7 +4879,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4888,7 +4890,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4899,7 +4901,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4910,7 +4912,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4921,7 +4923,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4932,7 +4934,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4943,7 +4945,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4954,7 +4956,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4965,7 +4967,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>24</v>
       </c>
@@ -4976,7 +4978,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25</v>
       </c>
@@ -4987,7 +4989,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26</v>
       </c>
@@ -4998,7 +5000,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>27</v>
       </c>
@@ -5009,7 +5011,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>28</v>
       </c>
@@ -5020,7 +5022,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5031,7 +5033,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>30</v>
       </c>
@@ -5042,7 +5044,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5053,7 +5055,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5064,7 +5066,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5075,7 +5077,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5086,7 +5088,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>35</v>
       </c>
@@ -5097,7 +5099,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5108,7 +5110,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5119,7 +5121,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>40</v>
       </c>
@@ -5130,7 +5132,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5141,7 +5143,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5152,7 +5154,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5163,7 +5165,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5174,7 +5176,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5185,7 +5187,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5196,7 +5198,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5207,7 +5209,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5218,7 +5220,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5229,7 +5231,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5240,7 +5242,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5251,7 +5253,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5262,7 +5264,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5273,7 +5275,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5284,7 +5286,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5295,7 +5297,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5306,7 +5308,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5317,7 +5319,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5328,7 +5330,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5339,7 +5341,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5347,10 +5349,10 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5361,7 +5363,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5372,7 +5374,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5383,7 +5385,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5394,7 +5396,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5405,7 +5407,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5416,7 +5418,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5427,7 +5429,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5438,7 +5440,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5449,7 +5451,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5460,7 +5462,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5471,7 +5473,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5482,7 +5484,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>73</v>
       </c>
@@ -5493,7 +5495,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>74</v>
       </c>
@@ -5504,7 +5506,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>75</v>
       </c>
@@ -5515,7 +5517,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>76</v>
       </c>
@@ -5526,7 +5528,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>77</v>
       </c>
@@ -5537,7 +5539,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>78</v>
       </c>
@@ -5548,7 +5550,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>79</v>
       </c>
@@ -5559,7 +5561,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>80</v>
       </c>
@@ -5570,7 +5572,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>81</v>
       </c>
@@ -5581,7 +5583,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>82</v>
       </c>
@@ -5592,7 +5594,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>83</v>
       </c>
@@ -5603,7 +5605,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>84</v>
       </c>
@@ -5614,7 +5616,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>85</v>
       </c>
@@ -5625,7 +5627,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>86</v>
       </c>
@@ -5636,7 +5638,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>87</v>
       </c>
@@ -5647,7 +5649,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>88</v>
       </c>
@@ -5658,7 +5660,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>89</v>
       </c>
@@ -5669,7 +5671,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>90</v>
       </c>
@@ -5680,7 +5682,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>91</v>
       </c>
@@ -5691,7 +5693,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>92</v>
       </c>
@@ -5702,7 +5704,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5713,7 +5715,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5724,7 +5726,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5735,7 +5737,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5746,7 +5748,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5757,7 +5759,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5768,7 +5770,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5779,7 +5781,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5790,7 +5792,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5801,7 +5803,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5812,7 +5814,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5823,7 +5825,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5834,7 +5836,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5845,7 +5847,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5856,7 +5858,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5867,7 +5869,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5878,7 +5880,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5889,7 +5891,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5900,7 +5902,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5911,7 +5913,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5922,7 +5924,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5933,7 +5935,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5944,7 +5946,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5955,7 +5957,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5963,10 +5965,10 @@
         <v>224</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>122</v>
       </c>
@@ -5977,7 +5979,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>123</v>
       </c>
@@ -5988,7 +5990,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>124</v>
       </c>
@@ -5999,7 +6001,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>125</v>
       </c>
@@ -6010,7 +6012,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126</v>
       </c>
@@ -6021,7 +6023,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>127</v>
       </c>
@@ -6032,7 +6034,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>128</v>
       </c>
@@ -6043,7 +6045,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>129</v>
       </c>
@@ -6054,7 +6056,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>130</v>
       </c>
@@ -6065,7 +6067,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>131</v>
       </c>
@@ -6076,7 +6078,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>132</v>
       </c>
@@ -6087,7 +6089,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>133</v>
       </c>
@@ -6098,7 +6100,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>134</v>
       </c>
@@ -6109,7 +6111,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>135</v>
       </c>
@@ -6120,7 +6122,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6131,7 +6133,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6142,7 +6144,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6150,10 +6152,10 @@
         <v>257</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6164,7 +6166,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6175,7 +6177,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6186,7 +6188,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6197,7 +6199,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6208,7 +6210,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6219,7 +6221,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6230,7 +6232,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6241,7 +6243,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6252,7 +6254,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6263,7 +6265,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6274,7 +6276,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6285,7 +6287,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6296,7 +6298,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6307,7 +6309,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6318,7 +6320,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6329,7 +6331,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6340,7 +6342,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6351,7 +6353,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6362,7 +6364,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6373,7 +6375,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6384,7 +6386,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6392,10 +6394,10 @@
         <v>300</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6406,7 +6408,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6417,7 +6419,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6428,7 +6430,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6439,7 +6441,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6450,7 +6452,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6461,7 +6463,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6472,7 +6474,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6483,7 +6485,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>169</v>
       </c>
@@ -6494,7 +6496,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>170</v>
       </c>
@@ -6505,7 +6507,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>171</v>
       </c>
@@ -6516,7 +6518,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>172</v>
       </c>
@@ -6527,7 +6529,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>173</v>
       </c>
@@ -6538,7 +6540,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>174</v>
       </c>
@@ -6549,7 +6551,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>175</v>
       </c>
@@ -6557,10 +6559,10 @@
         <v>329</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>176</v>
       </c>
@@ -6571,7 +6573,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>177</v>
       </c>
@@ -6582,7 +6584,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>178</v>
       </c>
@@ -6593,7 +6595,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>179</v>
       </c>
@@ -6604,7 +6606,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>180</v>
       </c>
@@ -6615,7 +6617,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>181</v>
       </c>
@@ -6626,7 +6628,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>182</v>
       </c>
@@ -6637,7 +6639,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>183</v>
       </c>
@@ -6648,7 +6650,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>184</v>
       </c>
@@ -6659,7 +6661,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>185</v>
       </c>
@@ -6670,7 +6672,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>186</v>
       </c>
@@ -6681,7 +6683,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>187</v>
       </c>
@@ -6692,7 +6694,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>188</v>
       </c>
@@ -6703,7 +6705,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>189</v>
       </c>
@@ -6714,7 +6716,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>190</v>
       </c>
@@ -6725,7 +6727,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>191</v>
       </c>
@@ -6736,7 +6738,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>192</v>
       </c>
@@ -6747,7 +6749,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6758,7 +6760,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6769,7 +6771,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6780,7 +6782,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6791,7 +6793,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6802,7 +6804,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6813,7 +6815,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6824,7 +6826,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6835,7 +6837,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6846,7 +6848,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6857,7 +6859,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6868,7 +6870,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6879,7 +6881,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6890,7 +6892,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6901,7 +6903,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6912,7 +6914,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6923,7 +6925,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6934,7 +6936,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6945,7 +6947,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6956,7 +6958,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6967,7 +6969,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>213</v>
       </c>
@@ -6978,7 +6980,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>214</v>
       </c>
@@ -6989,7 +6991,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>215</v>
       </c>
@@ -7000,7 +7002,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>217</v>
       </c>
@@ -7011,7 +7013,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>218</v>
       </c>
@@ -7022,7 +7024,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>219</v>
       </c>
@@ -7033,7 +7035,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>220</v>
       </c>
@@ -7041,10 +7043,10 @@
         <v>416</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>221</v>
       </c>
@@ -7055,7 +7057,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>222</v>
       </c>
@@ -7066,7 +7068,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>223</v>
       </c>
@@ -7077,7 +7079,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>224</v>
       </c>
@@ -7088,7 +7090,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>225</v>
       </c>
@@ -7099,7 +7101,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>226</v>
       </c>
@@ -7110,7 +7112,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>227</v>
       </c>
@@ -7121,7 +7123,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7132,7 +7134,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7143,7 +7145,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7154,7 +7156,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7165,7 +7167,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7176,7 +7178,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>233</v>
       </c>
@@ -7184,10 +7186,10 @@
         <v>441</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>234</v>
       </c>
@@ -7198,7 +7200,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>235</v>
       </c>
@@ -7209,7 +7211,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>236</v>
       </c>
@@ -7220,7 +7222,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>237</v>
       </c>
@@ -7231,7 +7233,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>238</v>
       </c>
@@ -7242,7 +7244,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>239</v>
       </c>
@@ -7253,7 +7255,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>240</v>
       </c>
@@ -7264,7 +7266,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>241</v>
       </c>
@@ -7275,7 +7277,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>242</v>
       </c>
@@ -7286,7 +7288,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>243</v>
       </c>
@@ -7297,7 +7299,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>244</v>
       </c>
@@ -7308,7 +7310,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>245</v>
       </c>
@@ -7319,7 +7321,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>246</v>
       </c>
@@ -7330,7 +7332,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>247</v>
       </c>
@@ -7341,7 +7343,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>248</v>
       </c>
@@ -7352,7 +7354,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>249</v>
       </c>
@@ -7363,7 +7365,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>250</v>
       </c>
@@ -7374,7 +7376,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>251</v>
       </c>
@@ -7385,7 +7387,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>252</v>
       </c>
@@ -7396,7 +7398,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>253</v>
       </c>
@@ -7407,7 +7409,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>254</v>
       </c>
@@ -7418,7 +7420,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>255</v>
       </c>
@@ -7429,7 +7431,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>256</v>
       </c>
@@ -7440,7 +7442,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>257</v>
       </c>
@@ -7451,7 +7453,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>258</v>
       </c>
@@ -7462,7 +7464,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>259</v>
       </c>
@@ -7473,7 +7475,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>260</v>
       </c>
@@ -7481,10 +7483,10 @@
         <v>494</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>261</v>
       </c>
@@ -7495,7 +7497,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>262</v>
       </c>
@@ -7506,7 +7508,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>263</v>
       </c>
@@ -7514,10 +7516,10 @@
         <v>498</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>264</v>
       </c>
@@ -7528,7 +7530,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>265</v>
       </c>
@@ -7539,7 +7541,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>266</v>
       </c>
@@ -7550,7 +7552,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>267</v>
       </c>
@@ -7561,7 +7563,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>268</v>
       </c>
@@ -7572,7 +7574,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>269</v>
       </c>
@@ -7583,7 +7585,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>270</v>
       </c>
@@ -7594,7 +7596,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>271</v>
       </c>
@@ -7605,7 +7607,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>272</v>
       </c>
@@ -7616,7 +7618,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>274</v>
       </c>
@@ -7627,7 +7629,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>275</v>
       </c>
@@ -7638,7 +7640,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>276</v>
       </c>
@@ -7649,7 +7651,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>277</v>
       </c>
@@ -7660,7 +7662,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>278</v>
       </c>
@@ -7671,7 +7673,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>279</v>
       </c>
@@ -7682,7 +7684,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>280</v>
       </c>
@@ -7693,7 +7695,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>281</v>
       </c>
@@ -7701,10 +7703,10 @@
         <v>531</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>282</v>
       </c>
@@ -7715,7 +7717,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>283</v>
       </c>
@@ -7726,7 +7728,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>284</v>
       </c>
@@ -7737,7 +7739,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>285</v>
       </c>
@@ -7748,7 +7750,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>286</v>
       </c>
@@ -7759,7 +7761,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>287</v>
       </c>
@@ -7770,7 +7772,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>288</v>
       </c>
@@ -7781,7 +7783,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>289</v>
       </c>
@@ -7792,7 +7794,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>290</v>
       </c>
@@ -7803,7 +7805,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>291</v>
       </c>
@@ -7814,7 +7816,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>292</v>
       </c>
@@ -7825,7 +7827,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>293</v>
       </c>
@@ -7836,7 +7838,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>294</v>
       </c>
@@ -7847,7 +7849,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>295</v>
       </c>
@@ -7858,7 +7860,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>296</v>
       </c>
@@ -7869,7 +7871,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>297</v>
       </c>
@@ -7880,7 +7882,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>298</v>
       </c>
@@ -7891,7 +7893,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>299</v>
       </c>
@@ -7902,7 +7904,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>300</v>
       </c>
@@ -7913,7 +7915,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>301</v>
       </c>
@@ -7924,7 +7926,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>302</v>
       </c>
@@ -7935,7 +7937,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>303</v>
       </c>
@@ -7946,7 +7948,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>304</v>
       </c>
@@ -7957,7 +7959,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>305</v>
       </c>
@@ -7968,7 +7970,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>306</v>
       </c>
@@ -7976,10 +7978,10 @@
         <v>580</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>307</v>
       </c>
@@ -7990,7 +7992,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>308</v>
       </c>
@@ -8001,7 +8003,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>309</v>
       </c>
@@ -8012,7 +8014,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>310</v>
       </c>
@@ -8023,7 +8025,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>311</v>
       </c>
@@ -8034,7 +8036,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>312</v>
       </c>
@@ -8045,7 +8047,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>313</v>
       </c>
@@ -8056,7 +8058,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>314</v>
       </c>
@@ -8067,7 +8069,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>315</v>
       </c>
@@ -8078,7 +8080,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>316</v>
       </c>
@@ -8089,7 +8091,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>317</v>
       </c>
@@ -8100,7 +8102,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>318</v>
       </c>
@@ -8111,7 +8113,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>319</v>
       </c>
@@ -8122,7 +8124,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>320</v>
       </c>
@@ -8133,7 +8135,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>321</v>
       </c>
@@ -8144,7 +8146,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>322</v>
       </c>
@@ -8155,7 +8157,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>323</v>
       </c>
@@ -8166,7 +8168,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>324</v>
       </c>
@@ -8177,7 +8179,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>325</v>
       </c>
@@ -8188,7 +8190,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>326</v>
       </c>
@@ -8199,7 +8201,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>327</v>
       </c>
@@ -8210,7 +8212,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>328</v>
       </c>
@@ -8221,7 +8223,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>329</v>
       </c>
@@ -8232,7 +8234,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>330</v>
       </c>
@@ -8243,7 +8245,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>331</v>
       </c>
@@ -8254,7 +8256,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>332</v>
       </c>
@@ -8265,7 +8267,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>333</v>
       </c>
@@ -8276,7 +8278,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>334</v>
       </c>
@@ -8287,7 +8289,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>335</v>
       </c>
@@ -8298,7 +8300,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>336</v>
       </c>
@@ -8309,7 +8311,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>337</v>
       </c>
@@ -8320,7 +8322,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>338</v>
       </c>
@@ -8331,7 +8333,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>339</v>
       </c>
@@ -8342,7 +8344,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>340</v>
       </c>
@@ -8353,7 +8355,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>341</v>
       </c>
@@ -8364,7 +8366,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>342</v>
       </c>
@@ -8375,7 +8377,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>343</v>
       </c>
@@ -8386,7 +8388,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>344</v>
       </c>
@@ -8397,7 +8399,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>345</v>
       </c>
@@ -8408,7 +8410,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>346</v>
       </c>
@@ -8419,7 +8421,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>347</v>
       </c>
@@ -8430,7 +8432,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>348</v>
       </c>
@@ -8438,10 +8440,10 @@
         <v>663</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>349</v>
       </c>
@@ -8449,10 +8451,10 @@
         <v>664</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>350</v>
       </c>
@@ -8463,7 +8465,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>351</v>
       </c>
@@ -8474,3803 +8476,3803 @@
         <v>668</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>352</v>
       </c>
       <c r="B342" t="s">
         <v>669</v>
       </c>
-      <c r="C342" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C342" s="3" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>670</v>
+      </c>
+      <c r="C343" t="s">
         <v>671</v>
       </c>
-      <c r="C343" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>672</v>
+      </c>
+      <c r="C344" t="s">
         <v>673</v>
       </c>
-      <c r="C344" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>674</v>
+      </c>
+      <c r="C345" t="s">
         <v>675</v>
       </c>
-      <c r="C345" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>676</v>
+      </c>
+      <c r="C346" t="s">
         <v>677</v>
       </c>
-      <c r="C346" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>678</v>
+      </c>
+      <c r="C347" t="s">
         <v>679</v>
       </c>
-      <c r="C347" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>680</v>
+      </c>
+      <c r="C348" t="s">
         <v>681</v>
       </c>
-      <c r="C348" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>682</v>
+      </c>
+      <c r="C349" t="s">
         <v>683</v>
       </c>
-      <c r="C349" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>684</v>
+      </c>
+      <c r="C350" t="s">
         <v>685</v>
       </c>
-      <c r="C350" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>686</v>
+      </c>
+      <c r="C351" t="s">
         <v>687</v>
       </c>
-      <c r="C351" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>688</v>
+      </c>
+      <c r="C352" t="s">
         <v>689</v>
       </c>
-      <c r="C352" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>690</v>
+      </c>
+      <c r="C353" t="s">
         <v>691</v>
       </c>
-      <c r="C353" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>692</v>
+      </c>
+      <c r="C354" t="s">
         <v>693</v>
       </c>
-      <c r="C354" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>694</v>
+      </c>
+      <c r="C355" t="s">
         <v>695</v>
       </c>
-      <c r="C355" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>696</v>
+      </c>
+      <c r="C356" t="s">
         <v>697</v>
       </c>
-      <c r="C356" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>698</v>
+      </c>
+      <c r="C357" t="s">
         <v>699</v>
       </c>
-      <c r="C357" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>700</v>
+      </c>
+      <c r="C358" t="s">
         <v>701</v>
       </c>
-      <c r="C358" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>702</v>
+      </c>
+      <c r="C359" t="s">
         <v>703</v>
       </c>
-      <c r="C359" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>704</v>
+      </c>
+      <c r="C360" t="s">
         <v>705</v>
       </c>
-      <c r="C360" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>706</v>
+      </c>
+      <c r="C361" t="s">
         <v>707</v>
       </c>
-      <c r="C361" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>708</v>
+      </c>
+      <c r="C362" t="s">
         <v>709</v>
       </c>
-      <c r="C362" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>710</v>
+      </c>
+      <c r="C363" t="s">
         <v>711</v>
       </c>
-      <c r="C363" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>712</v>
+      </c>
+      <c r="C364" t="s">
         <v>713</v>
       </c>
-      <c r="C364" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>714</v>
+      </c>
+      <c r="C365" t="s">
         <v>715</v>
       </c>
-      <c r="C365" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>716</v>
+      </c>
+      <c r="C366" t="s">
         <v>717</v>
       </c>
-      <c r="C366" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>718</v>
+      </c>
+      <c r="C367" t="s">
         <v>719</v>
       </c>
-      <c r="C367" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>720</v>
+      </c>
+      <c r="C368" t="s">
         <v>721</v>
       </c>
-      <c r="C368" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>722</v>
+      </c>
+      <c r="C369" t="s">
         <v>723</v>
       </c>
-      <c r="C369" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>724</v>
+      </c>
+      <c r="C370" t="s">
         <v>725</v>
       </c>
-      <c r="C370" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>726</v>
+      </c>
+      <c r="C371" t="s">
         <v>727</v>
       </c>
-      <c r="C371" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>728</v>
+      </c>
+      <c r="C372" t="s">
         <v>729</v>
       </c>
-      <c r="C372" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>730</v>
+      </c>
+      <c r="C373" t="s">
         <v>731</v>
       </c>
-      <c r="C373" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>732</v>
+      </c>
+      <c r="C374" t="s">
         <v>733</v>
       </c>
-      <c r="C374" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>734</v>
+      </c>
+      <c r="C375" t="s">
         <v>735</v>
       </c>
-      <c r="C375" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>736</v>
+      </c>
+      <c r="C376" t="s">
         <v>737</v>
       </c>
-      <c r="C376" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>738</v>
+      </c>
+      <c r="C377" t="s">
         <v>739</v>
       </c>
-      <c r="C377" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>740</v>
+      </c>
+      <c r="C378" t="s">
         <v>741</v>
       </c>
-      <c r="C378" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>742</v>
+      </c>
+      <c r="C379" t="s">
         <v>743</v>
       </c>
-      <c r="C379" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>744</v>
+      </c>
+      <c r="C380" t="s">
         <v>745</v>
       </c>
-      <c r="C380" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>746</v>
+      </c>
+      <c r="C381" t="s">
         <v>747</v>
       </c>
-      <c r="C381" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>748</v>
+      </c>
+      <c r="C382" t="s">
         <v>749</v>
       </c>
-      <c r="C382" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>750</v>
+      </c>
+      <c r="C383" t="s">
         <v>751</v>
       </c>
-      <c r="C383" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>752</v>
+      </c>
+      <c r="C384" t="s">
         <v>753</v>
       </c>
-      <c r="C384" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>754</v>
+      </c>
+      <c r="C385" t="s">
         <v>755</v>
       </c>
-      <c r="C385" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>756</v>
+      </c>
+      <c r="C386" t="s">
         <v>757</v>
       </c>
-      <c r="C386" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>758</v>
+      </c>
+      <c r="C387" t="s">
         <v>759</v>
       </c>
-      <c r="C387" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>760</v>
+      </c>
+      <c r="C388" t="s">
         <v>761</v>
       </c>
-      <c r="C388" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>762</v>
+      </c>
+      <c r="C389" t="s">
         <v>763</v>
       </c>
-      <c r="C389" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>764</v>
+      </c>
+      <c r="C390" t="s">
         <v>765</v>
       </c>
-      <c r="C390" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>766</v>
+      </c>
+      <c r="C391" t="s">
         <v>767</v>
       </c>
-      <c r="C391" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>768</v>
+      </c>
+      <c r="C392" t="s">
         <v>769</v>
       </c>
-      <c r="C392" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>770</v>
+      </c>
+      <c r="C393" t="s">
         <v>771</v>
       </c>
-      <c r="C393" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>772</v>
+      </c>
+      <c r="C394" t="s">
         <v>773</v>
       </c>
-      <c r="C394" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>774</v>
+      </c>
+      <c r="C395" t="s">
         <v>775</v>
       </c>
-      <c r="C395" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>776</v>
+      </c>
+      <c r="C396" t="s">
         <v>777</v>
       </c>
-      <c r="C396" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>778</v>
+      </c>
+      <c r="C397" t="s">
         <v>779</v>
       </c>
-      <c r="C397" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>780</v>
+      </c>
+      <c r="C398" t="s">
         <v>781</v>
       </c>
-      <c r="C398" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>782</v>
+      </c>
+      <c r="C399" t="s">
         <v>783</v>
       </c>
-      <c r="C399" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>784</v>
+      </c>
+      <c r="C400" t="s">
         <v>785</v>
       </c>
-      <c r="C400" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>786</v>
+      </c>
+      <c r="C401" t="s">
         <v>787</v>
       </c>
-      <c r="C401" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>788</v>
+      </c>
+      <c r="C402" t="s">
         <v>789</v>
       </c>
-      <c r="C402" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>790</v>
+      </c>
+      <c r="C403" t="s">
         <v>791</v>
       </c>
-      <c r="C403" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>792</v>
+      </c>
+      <c r="C404" t="s">
         <v>793</v>
       </c>
-      <c r="C404" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>794</v>
+      </c>
+      <c r="C405" t="s">
         <v>795</v>
       </c>
-      <c r="C405" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>796</v>
+      </c>
+      <c r="C406" t="s">
         <v>797</v>
       </c>
-      <c r="C406" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>798</v>
+      </c>
+      <c r="C407" t="s">
         <v>799</v>
       </c>
-      <c r="C407" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>800</v>
+      </c>
+      <c r="C408" t="s">
         <v>801</v>
       </c>
-      <c r="C408" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>802</v>
+      </c>
+      <c r="C409" t="s">
         <v>803</v>
       </c>
-      <c r="C409" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>804</v>
+      </c>
+      <c r="C410" t="s">
         <v>805</v>
       </c>
-      <c r="C410" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>806</v>
+      </c>
+      <c r="C411" t="s">
         <v>807</v>
       </c>
-      <c r="C411" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>808</v>
+      </c>
+      <c r="C412" t="s">
         <v>809</v>
       </c>
-      <c r="C412" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>810</v>
+      </c>
+      <c r="C413" t="s">
         <v>811</v>
       </c>
-      <c r="C413" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>812</v>
+      </c>
+      <c r="C414" t="s">
         <v>813</v>
       </c>
-      <c r="C414" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>814</v>
+      </c>
+      <c r="C415" t="s">
         <v>815</v>
       </c>
-      <c r="C415" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>816</v>
+      </c>
+      <c r="C416" t="s">
         <v>817</v>
       </c>
-      <c r="C416" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>818</v>
+      </c>
+      <c r="C417" t="s">
         <v>819</v>
       </c>
-      <c r="C417" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>820</v>
+      </c>
+      <c r="C418" t="s">
         <v>821</v>
       </c>
-      <c r="C418" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>822</v>
+      </c>
+      <c r="C419" t="s">
         <v>823</v>
       </c>
-      <c r="C419" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>824</v>
+      </c>
+      <c r="C420" t="s">
         <v>825</v>
       </c>
-      <c r="C420" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>826</v>
+      </c>
+      <c r="C421" t="s">
         <v>827</v>
       </c>
-      <c r="C421" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>828</v>
+      </c>
+      <c r="C422" t="s">
         <v>829</v>
       </c>
-      <c r="C422" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>830</v>
+      </c>
+      <c r="C423" t="s">
         <v>831</v>
       </c>
-      <c r="C423" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>832</v>
+      </c>
+      <c r="C424" t="s">
         <v>833</v>
       </c>
-      <c r="C424" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>834</v>
+      </c>
+      <c r="C425" t="s">
         <v>835</v>
       </c>
-      <c r="C425" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>836</v>
+      </c>
+      <c r="C426" t="s">
         <v>837</v>
       </c>
-      <c r="C426" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>838</v>
+      </c>
+      <c r="C427" t="s">
         <v>839</v>
       </c>
-      <c r="C427" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C428" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.15">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C429" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.15">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>842</v>
+      </c>
+      <c r="C430" t="s">
         <v>843</v>
       </c>
-      <c r="C430" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>844</v>
+      </c>
+      <c r="C431" t="s">
         <v>845</v>
       </c>
-      <c r="C431" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>846</v>
+      </c>
+      <c r="C432" t="s">
         <v>847</v>
       </c>
-      <c r="C432" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>848</v>
+      </c>
+      <c r="C433" t="s">
         <v>849</v>
       </c>
-      <c r="C433" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>850</v>
+      </c>
+      <c r="C434" t="s">
         <v>851</v>
       </c>
-      <c r="C434" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>852</v>
+      </c>
+      <c r="C435" t="s">
         <v>853</v>
       </c>
-      <c r="C435" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>854</v>
+      </c>
+      <c r="C436" t="s">
         <v>855</v>
       </c>
-      <c r="C436" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>856</v>
+      </c>
+      <c r="C437" t="s">
         <v>857</v>
       </c>
-      <c r="C437" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>858</v>
+      </c>
+      <c r="C438" t="s">
         <v>859</v>
       </c>
-      <c r="C438" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>860</v>
+      </c>
+      <c r="C439" t="s">
         <v>861</v>
       </c>
-      <c r="C439" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>862</v>
+      </c>
+      <c r="C440" t="s">
         <v>863</v>
       </c>
-      <c r="C440" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>864</v>
+      </c>
+      <c r="C441" t="s">
         <v>865</v>
       </c>
-      <c r="C441" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>866</v>
+      </c>
+      <c r="C442" t="s">
         <v>867</v>
       </c>
-      <c r="C442" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>868</v>
+      </c>
+      <c r="C443" t="s">
         <v>869</v>
       </c>
-      <c r="C443" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>870</v>
+      </c>
+      <c r="C444" t="s">
         <v>871</v>
       </c>
-      <c r="C444" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>872</v>
+      </c>
+      <c r="C445" t="s">
         <v>873</v>
       </c>
-      <c r="C445" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>874</v>
+      </c>
+      <c r="C446" t="s">
         <v>875</v>
       </c>
-      <c r="C446" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>876</v>
+      </c>
+      <c r="C447" t="s">
         <v>877</v>
       </c>
-      <c r="C447" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>878</v>
+      </c>
+      <c r="C448" t="s">
         <v>879</v>
       </c>
-      <c r="C448" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>880</v>
+      </c>
+      <c r="C449" t="s">
         <v>881</v>
       </c>
-      <c r="C449" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>882</v>
+      </c>
+      <c r="C450" t="s">
         <v>883</v>
       </c>
-      <c r="C450" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C451" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.15">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>885</v>
+      </c>
+      <c r="C452" t="s">
         <v>886</v>
       </c>
-      <c r="C452" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>887</v>
+      </c>
+      <c r="C453" t="s">
         <v>888</v>
       </c>
-      <c r="C453" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>889</v>
+      </c>
+      <c r="C454" t="s">
         <v>890</v>
       </c>
-      <c r="C454" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>891</v>
+      </c>
+      <c r="C455" t="s">
         <v>892</v>
       </c>
-      <c r="C455" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C456" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.15">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>894</v>
+      </c>
+      <c r="C457" t="s">
         <v>895</v>
       </c>
-      <c r="C457" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>896</v>
+      </c>
+      <c r="C458" t="s">
         <v>897</v>
       </c>
-      <c r="C458" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>898</v>
+      </c>
+      <c r="C459" t="s">
         <v>899</v>
       </c>
-      <c r="C459" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.15">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>901</v>
+      </c>
+      <c r="C461" t="s">
         <v>902</v>
       </c>
-      <c r="C461" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>903</v>
+      </c>
+      <c r="C462" t="s">
         <v>904</v>
       </c>
-      <c r="C462" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>905</v>
+      </c>
+      <c r="C463" t="s">
         <v>906</v>
       </c>
-      <c r="C463" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>907</v>
+      </c>
+      <c r="C464" t="s">
         <v>908</v>
       </c>
-      <c r="C464" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>909</v>
+      </c>
+      <c r="C465" t="s">
         <v>910</v>
       </c>
-      <c r="C465" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>911</v>
+      </c>
+      <c r="C466" t="s">
         <v>912</v>
       </c>
-      <c r="C466" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>914</v>
+      </c>
+      <c r="C468" t="s">
         <v>915</v>
       </c>
-      <c r="C468" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>916</v>
+      </c>
+      <c r="C469" t="s">
         <v>917</v>
       </c>
-      <c r="C469" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>918</v>
+      </c>
+      <c r="C470" t="s">
         <v>919</v>
       </c>
-      <c r="C470" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>920</v>
+      </c>
+      <c r="C471" t="s">
         <v>921</v>
       </c>
-      <c r="C471" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>922</v>
+      </c>
+      <c r="C472" t="s">
         <v>923</v>
       </c>
-      <c r="C472" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A473">
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>924</v>
+      </c>
+      <c r="C473" t="s">
         <v>925</v>
       </c>
-      <c r="C473" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>926</v>
+      </c>
+      <c r="C474" t="s">
         <v>927</v>
       </c>
-      <c r="C474" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>928</v>
+      </c>
+      <c r="C475" t="s">
         <v>929</v>
       </c>
-      <c r="C475" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>930</v>
+      </c>
+      <c r="C476" t="s">
         <v>931</v>
       </c>
-      <c r="C476" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>932</v>
+      </c>
+      <c r="C477" t="s">
         <v>933</v>
       </c>
-      <c r="C477" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C478" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.15">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>935</v>
+      </c>
+      <c r="C479" t="s">
         <v>936</v>
       </c>
-      <c r="C479" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>937</v>
+      </c>
+      <c r="C480" t="s">
         <v>938</v>
       </c>
-      <c r="C480" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>939</v>
+      </c>
+      <c r="C481" t="s">
         <v>940</v>
       </c>
-      <c r="C481" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>941</v>
+      </c>
+      <c r="C482" t="s">
         <v>942</v>
       </c>
-      <c r="C482" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>943</v>
+      </c>
+      <c r="C483" t="s">
         <v>944</v>
       </c>
-      <c r="C483" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>945</v>
+      </c>
+      <c r="C484" t="s">
         <v>946</v>
       </c>
-      <c r="C484" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>947</v>
+      </c>
+      <c r="C485" t="s">
         <v>948</v>
       </c>
-      <c r="C485" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>949</v>
+      </c>
+      <c r="C486" t="s">
         <v>950</v>
       </c>
-      <c r="C486" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>951</v>
+      </c>
+      <c r="C487" t="s">
         <v>952</v>
       </c>
-      <c r="C487" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>953</v>
+      </c>
+      <c r="C488" t="s">
         <v>954</v>
       </c>
-      <c r="C488" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>955</v>
+      </c>
+      <c r="C489" t="s">
         <v>956</v>
       </c>
-      <c r="C489" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>957</v>
+      </c>
+      <c r="C490" t="s">
         <v>958</v>
       </c>
-      <c r="C490" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>959</v>
+      </c>
+      <c r="C491" t="s">
         <v>960</v>
       </c>
-      <c r="C491" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>961</v>
+      </c>
+      <c r="C492" t="s">
         <v>962</v>
       </c>
-      <c r="C492" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>963</v>
+      </c>
+      <c r="C493" t="s">
         <v>964</v>
       </c>
-      <c r="C493" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>965</v>
+      </c>
+      <c r="C494" t="s">
         <v>966</v>
       </c>
-      <c r="C494" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>967</v>
+      </c>
+      <c r="C495" t="s">
         <v>968</v>
       </c>
-      <c r="C495" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>969</v>
+      </c>
+      <c r="C496" t="s">
         <v>970</v>
       </c>
-      <c r="C496" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>971</v>
+      </c>
+      <c r="C497" t="s">
         <v>972</v>
       </c>
-      <c r="C497" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>973</v>
+      </c>
+      <c r="C498" t="s">
         <v>974</v>
       </c>
-      <c r="C498" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.15">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>976</v>
+      </c>
+      <c r="C500" t="s">
         <v>977</v>
       </c>
-      <c r="C500" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>978</v>
+      </c>
+      <c r="C501" t="s">
         <v>979</v>
       </c>
-      <c r="C501" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>980</v>
+      </c>
+      <c r="C502" t="s">
         <v>981</v>
       </c>
-      <c r="C502" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>983</v>
+      </c>
+      <c r="C504" t="s">
         <v>984</v>
       </c>
-      <c r="C504" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>985</v>
+      </c>
+      <c r="C505" t="s">
         <v>986</v>
       </c>
-      <c r="C505" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>987</v>
+      </c>
+      <c r="C506" t="s">
         <v>988</v>
       </c>
-      <c r="C506" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>989</v>
+      </c>
+      <c r="C507" t="s">
         <v>990</v>
       </c>
-      <c r="C507" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>991</v>
+      </c>
+      <c r="C508" t="s">
         <v>992</v>
       </c>
-      <c r="C508" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>993</v>
+      </c>
+      <c r="C509" t="s">
         <v>994</v>
       </c>
-      <c r="C509" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>995</v>
+      </c>
+      <c r="C510" t="s">
         <v>996</v>
       </c>
-      <c r="C510" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>997</v>
+      </c>
+      <c r="C511" t="s">
         <v>998</v>
       </c>
-      <c r="C511" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>999</v>
+      </c>
+      <c r="C512" t="s">
         <v>1000</v>
       </c>
-      <c r="C512" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C513" t="s">
         <v>1002</v>
       </c>
-      <c r="C513" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C514" t="s">
         <v>1004</v>
       </c>
-      <c r="C514" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C515" t="s">
         <v>1006</v>
       </c>
-      <c r="C515" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C516" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C517" t="s">
         <v>1009</v>
       </c>
-      <c r="C517" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C519" t="s">
         <v>1012</v>
       </c>
-      <c r="C519" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C520" t="s">
         <v>1014</v>
       </c>
-      <c r="C520" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C521" t="s">
         <v>1016</v>
       </c>
-      <c r="C521" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C522" t="s">
         <v>1018</v>
       </c>
-      <c r="C522" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C523" t="s">
         <v>1020</v>
       </c>
-      <c r="C523" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C524" t="s">
         <v>1022</v>
       </c>
-      <c r="C524" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C526" t="s">
         <v>1025</v>
       </c>
-      <c r="C526" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C527" t="s">
         <v>1027</v>
       </c>
-      <c r="C527" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C528" t="s">
         <v>1029</v>
       </c>
-      <c r="C528" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C529" t="s">
         <v>1031</v>
       </c>
-      <c r="C529" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C531" t="s">
         <v>1034</v>
       </c>
-      <c r="C531" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C532" t="s">
         <v>1036</v>
       </c>
-      <c r="C532" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C533" t="s">
         <v>1038</v>
       </c>
-      <c r="C533" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C534" t="s">
         <v>1040</v>
       </c>
-      <c r="C534" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C535" t="s">
         <v>1042</v>
       </c>
-      <c r="C535" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C536" t="s">
         <v>1044</v>
       </c>
-      <c r="C536" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C537" t="s">
         <v>1046</v>
       </c>
-      <c r="C537" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C538" t="s">
         <v>1048</v>
       </c>
-      <c r="C538" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C539" t="s">
         <v>1050</v>
       </c>
-      <c r="C539" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C540" t="s">
         <v>1052</v>
       </c>
-      <c r="C540" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C541" t="s">
         <v>1054</v>
       </c>
-      <c r="C541" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C542" t="s">
         <v>1056</v>
       </c>
-      <c r="C542" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C543" t="s">
         <v>1058</v>
       </c>
-      <c r="C543" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C544" t="s">
         <v>1060</v>
       </c>
-      <c r="C544" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C545" t="s">
         <v>1062</v>
       </c>
-      <c r="C545" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C546" t="s">
         <v>1064</v>
       </c>
-      <c r="C546" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C548" t="s">
         <v>1067</v>
       </c>
-      <c r="C548" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C549" t="s">
         <v>1069</v>
       </c>
-      <c r="C549" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C550" t="s">
         <v>1071</v>
       </c>
-      <c r="C550" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C551" t="s">
         <v>1073</v>
       </c>
-      <c r="C551" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C552" t="s">
         <v>1075</v>
       </c>
-      <c r="C552" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C553" t="s">
         <v>1077</v>
       </c>
-      <c r="C553" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C554" t="s">
         <v>1079</v>
       </c>
-      <c r="C554" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C555" t="s">
         <v>1081</v>
       </c>
-      <c r="C555" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C556" t="s">
         <v>1083</v>
       </c>
-      <c r="C556" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C557" t="s">
         <v>1085</v>
       </c>
-      <c r="C557" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C558" t="s">
         <v>1087</v>
       </c>
-      <c r="C558" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C560" t="s">
         <v>1090</v>
       </c>
-      <c r="C560" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C561" t="s">
         <v>1092</v>
       </c>
-      <c r="C561" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C562" t="s">
         <v>1094</v>
       </c>
-      <c r="C562" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C563" t="s">
         <v>1096</v>
       </c>
-      <c r="C563" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C564" t="s">
         <v>1098</v>
       </c>
-      <c r="C564" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C565" t="s">
         <v>1100</v>
       </c>
-      <c r="C565" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C566" t="s">
         <v>1102</v>
       </c>
-      <c r="C566" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C567" t="s">
         <v>1104</v>
       </c>
-      <c r="C567" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C568" t="s">
         <v>1106</v>
       </c>
-      <c r="C568" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C569" t="s">
         <v>1108</v>
       </c>
-      <c r="C569" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C570" t="s">
         <v>1110</v>
       </c>
-      <c r="C570" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C571" t="s">
         <v>1112</v>
       </c>
-      <c r="C571" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C572" t="s">
         <v>1114</v>
       </c>
-      <c r="C572" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C573" t="s">
         <v>1116</v>
       </c>
-      <c r="C573" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C574" t="s">
         <v>1118</v>
       </c>
-      <c r="C574" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C576" t="s">
         <v>1121</v>
       </c>
-      <c r="C576" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C579" t="s">
         <v>1123</v>
       </c>
-      <c r="C579" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C580" t="s">
         <v>1125</v>
       </c>
-      <c r="C580" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C581" t="s">
         <v>1127</v>
       </c>
-      <c r="C581" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C582" t="s">
         <v>1129</v>
       </c>
-      <c r="C582" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>612</v>
       </c>
       <c r="B585" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C585" t="s">
         <v>1132</v>
       </c>
-      <c r="C585" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>615</v>
       </c>
       <c r="B586" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C586" t="s">
         <v>1134</v>
       </c>
-      <c r="C586" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>617</v>
       </c>
       <c r="B587" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C587" t="s">
         <v>1136</v>
       </c>
-      <c r="C587" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>618</v>
       </c>
       <c r="B588" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C588" t="s">
         <v>1138</v>
       </c>
-      <c r="C588" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>625</v>
       </c>
       <c r="B589" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C589" t="s">
         <v>1140</v>
       </c>
-      <c r="C589" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>624</v>
       </c>
       <c r="B590" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C590" t="s">
         <v>1142</v>
       </c>
-      <c r="C590" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>626</v>
       </c>
       <c r="B591" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C591" t="s">
         <v>1144</v>
       </c>
-      <c r="C591" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C592" t="s">
         <v>1146</v>
       </c>
-      <c r="C592" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C593" t="s">
         <v>1148</v>
       </c>
-      <c r="C593" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>632</v>
       </c>
       <c r="C594" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>633</v>
       </c>
       <c r="B595" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1150</v>
+      </c>
+      <c r="C595" s="3" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>635</v>
       </c>
       <c r="B596" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C596" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>636</v>
       </c>
       <c r="B597" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C597" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>642</v>
       </c>
       <c r="B598" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C598" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>644</v>
       </c>
       <c r="B599" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C599" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>646</v>
       </c>
       <c r="B600" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C600" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>649</v>
       </c>
       <c r="B601" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C601" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>650</v>
       </c>
       <c r="B602" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>651</v>
       </c>
       <c r="B603" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C603" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>653</v>
       </c>
       <c r="B604" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C604" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>654</v>
       </c>
       <c r="B605" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C605" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>655</v>
       </c>
       <c r="B606" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C606" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>659</v>
       </c>
       <c r="B607" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C607" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>660</v>
       </c>
       <c r="B608" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C608" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>661</v>
       </c>
       <c r="B609" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C609" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>663</v>
       </c>
       <c r="B610" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C610" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>667</v>
       </c>
       <c r="B611" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C611" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>670</v>
       </c>
       <c r="B612" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C612" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>673</v>
       </c>
       <c r="B613" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C613" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>674</v>
       </c>
       <c r="B614" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C614" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>675</v>
       </c>
       <c r="B615" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C615" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>680</v>
       </c>
       <c r="B616" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C616" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>681</v>
       </c>
       <c r="B617" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C617" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>682</v>
       </c>
       <c r="B618" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C618" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>683</v>
       </c>
       <c r="B619" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C619" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>684</v>
       </c>
       <c r="B620" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C620" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>685</v>
       </c>
       <c r="B621" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C621" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>686</v>
       </c>
       <c r="B622" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C622" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>689</v>
       </c>
       <c r="B623" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C623" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>697</v>
       </c>
       <c r="B624" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C624" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>701</v>
       </c>
       <c r="B625" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C625" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>702</v>
       </c>
       <c r="B626" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C626" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>704</v>
       </c>
       <c r="B627" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C627" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>705</v>
       </c>
       <c r="B628" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C628" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>710</v>
       </c>
       <c r="B629" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C629" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>711</v>
       </c>
       <c r="B630" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C630" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>712</v>
       </c>
       <c r="B631" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C631" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>714</v>
       </c>
       <c r="B632" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>717</v>
       </c>
       <c r="B633" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>718</v>
       </c>
       <c r="B634" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="C634" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>719</v>
       </c>
       <c r="B635" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C635" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A636">
         <v>721</v>
       </c>
       <c r="B636" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C636" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>722</v>
       </c>
       <c r="B637" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C637" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>723</v>
       </c>
       <c r="B638" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C638" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>724</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>725</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="C640" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>726</v>
       </c>
       <c r="B641" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C641" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>727</v>
       </c>
       <c r="B642" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="C642" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A643">
         <v>728</v>
       </c>
       <c r="B643" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C643" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="644" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A644">
         <v>729</v>
       </c>
       <c r="B644" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="C644" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>730</v>
       </c>
       <c r="B645" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C645" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>731</v>
       </c>
       <c r="B646" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>733</v>
       </c>
       <c r="B647" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C647" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>735</v>
       </c>
       <c r="B648" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C648" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>736</v>
       </c>
       <c r="B649" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C649" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>737</v>
       </c>
       <c r="B650" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C650" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>738</v>
       </c>
       <c r="B651" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C651" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>739</v>
       </c>
       <c r="B652" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C652" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>740</v>
       </c>
       <c r="B653" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C653" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>741</v>
       </c>
       <c r="B654" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C654" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>742</v>
       </c>
       <c r="B655" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C655" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>743</v>
       </c>
       <c r="B656" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C656" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>744</v>
       </c>
       <c r="B657" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C657" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A658">
         <v>745</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C658" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>746</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C659" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>747</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C660" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>748</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C661" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>749</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C662" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>750</v>
       </c>
       <c r="B663" s="1"/>
       <c r="C663" s="3" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>753</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C664" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>755</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>756</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C666" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>757</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C667" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>758</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C668" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>759</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>760</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C670" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>761</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C671" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>762</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C672" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>763</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C673" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>764</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C674" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>765</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C675" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>766</v>
       </c>
       <c r="B676" s="1"/>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>767</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C677" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>768</v>
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C679" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>772</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C680" s="3" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>773</v>
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>774</v>
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>776</v>
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>779</v>
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>780</v>
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>781</v>
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>783</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>784</v>
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>782</v>
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>10001</v>
       </c>
       <c r="B690" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>10003</v>
       </c>
       <c r="B691" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C691" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>
@@ -12278,7 +12280,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C210 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254 A153:C153 A152:B152 A212:C223 A211:B211" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C210 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C341 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254 A153:C153 A152:B152 A212:C223 A211:B211 A343:C344 A342:B342" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B8559B-493C-4BEF-AE99-4B8A7BD51897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59EE84E-E1C4-40D1-A2A3-C00302107A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19785" windowHeight="10800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="1355">
   <si>
     <t>Id</t>
   </si>
@@ -4296,6 +4296,22 @@
   </si>
   <si>
     <t>pp2,引牛之主,再来,再一次 闪耀,再次闪耀,再度闪耀</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>pnd</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>月岛麻里奈,麻里奈,月岛麻里奈新手教程</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>向着光,向光</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>证赫,証赫,证赤</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4717,7 +4733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C691"/>
+  <dimension ref="A1:C696"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
@@ -12238,41 +12254,82 @@
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A688">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A689">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1327</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A690">
-        <v>10001</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1305</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="B690" s="1"/>
       <c r="C690" s="3" t="s">
-        <v>1336</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A691">
+        <v>785</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A692">
+        <v>787</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A693">
+        <v>788</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A694">
+        <v>790</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A695">
+        <v>10001</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C695" s="3" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A696">
         <v>10003</v>
       </c>
-      <c r="B691" t="s">
+      <c r="B696" t="s">
         <v>1303</v>
       </c>
-      <c r="C691" t="s">
+      <c r="C696" t="s">
         <v>1304</v>
       </c>
     </row>
@@ -12281,7 +12338,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A690:B690 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C96 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C210 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C341 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254 A153:C153 A152:B152 A212:C223 A211:B211 A343:C344 A342:B342 A98:C98 A97:B97" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A695:B695 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C96 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C210 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C341 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254 A153:C153 A152:B152 A212:C223 A211:B211 A343:C344 A342:B342 A98:C98 A97:B97" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59EE84E-E1C4-40D1-A2A3-C00302107A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175B5895-7BC2-497F-B8B3-32C3DDD1E35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="1355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="1356">
   <si>
     <t>Id</t>
   </si>
@@ -4312,6 +4312,10 @@
   </si>
   <si>
     <t>证赫,証赫,证赤</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>逃逸恒星,逃跑的恒星,失控之星</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -12146,6 +12150,9 @@
         <v>766</v>
       </c>
       <c r="B676" s="1"/>
+      <c r="C676" s="3" t="s">
+        <v>1355</v>
+      </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A677">

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175B5895-7BC2-497F-B8B3-32C3DDD1E35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255A2EDB-94AE-4BA3-98C4-05FA6707D7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="1357">
   <si>
     <t>Id</t>
   </si>
@@ -4316,6 +4316,10 @@
   </si>
   <si>
     <t>逃逸恒星,逃跑的恒星,失控之星</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号B,信号 B,标志是B,B标志,B信号,我推的孩子B,我推B,我推2</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4737,7 +4741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C696"/>
+  <dimension ref="A1:C697"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
@@ -11294,1049 +11298,1057 @@
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A598">
-        <v>642</v>
-      </c>
-      <c r="B598" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1155</v>
+        <v>637</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A599">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B599" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C599" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A600">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B600" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C600" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A601">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B601" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C601" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A602">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B602" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C602" s="3" t="s">
-        <v>1310</v>
+        <v>1160</v>
+      </c>
+      <c r="C602" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A603">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B603" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1164</v>
+        <v>1162</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>1310</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A604">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B604" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C604" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A605">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B605" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C605" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A606">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B606" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C606" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A607">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B607" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C607" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A608">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B608" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C608" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A609">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B609" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C609" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A610">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B610" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C610" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A611">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B611" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C611" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A612">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B612" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C612" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A613">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B613" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C613" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A614">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B614" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C614" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A615">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B615" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C615" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A616">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B616" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C616" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A617">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B617" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C617" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A618">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B618" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C618" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A619">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B619" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C619" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A620">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B620" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C620" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A621">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B621" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C621" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A622">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B622" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C622" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A623">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B623" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C623" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A624">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B624" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C624" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A625">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B625" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C625" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A626">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B626" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C626" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A627">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B627" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C627" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A628">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B628" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C628" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A629">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B629" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C629" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A630">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B630" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C630" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A631">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B631" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C631" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A632">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B632" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C632" s="3" t="s">
-        <v>1311</v>
+        <v>1219</v>
+      </c>
+      <c r="C632" t="s">
+        <v>1220</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A633">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B633" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1334</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A634">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B634" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1224</v>
+        <v>1222</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>1334</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A635">
+        <v>718</v>
+      </c>
+      <c r="B635" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C635" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A636">
         <v>719</v>
       </c>
-      <c r="B635" t="s">
+      <c r="B636" t="s">
         <v>1225</v>
       </c>
-      <c r="C635" t="s">
+      <c r="C636" t="s">
         <v>1226</v>
       </c>
     </row>
-    <row r="636" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A636">
+    <row r="637" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A637">
         <v>721</v>
       </c>
-      <c r="B636" t="s">
+      <c r="B637" t="s">
         <v>1227</v>
       </c>
-      <c r="C636" t="s">
+      <c r="C637" t="s">
         <v>1228</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A637">
-        <v>722</v>
-      </c>
-      <c r="B637" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A638">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B638" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C638" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A639">
-        <v>724</v>
-      </c>
-      <c r="C639" s="3" t="s">
-        <v>1328</v>
+        <v>723</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C639" t="s">
+        <v>1232</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A640">
-        <v>725</v>
-      </c>
-      <c r="B640" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1234</v>
+        <v>724</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>1328</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A641">
-        <v>726</v>
-      </c>
-      <c r="B641" t="s">
-        <v>1235</v>
+        <v>725</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>1233</v>
       </c>
       <c r="C641" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A642">
+        <v>726</v>
+      </c>
+      <c r="B642" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C642" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A643">
         <v>727</v>
       </c>
-      <c r="B642" t="s">
+      <c r="B643" t="s">
         <v>1237</v>
       </c>
-      <c r="C642" t="s">
+      <c r="C643" t="s">
         <v>1238</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A643">
-        <v>728</v>
-      </c>
-      <c r="B643" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A644">
+        <v>728</v>
+      </c>
+      <c r="B644" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C644" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A645">
         <v>729</v>
       </c>
-      <c r="B644" t="s">
+      <c r="B645" t="s">
         <v>1241</v>
       </c>
-      <c r="C644" t="s">
+      <c r="C645" t="s">
         <v>1242</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A645">
-        <v>730</v>
-      </c>
-      <c r="B645" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A646">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B646" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C646" s="3" t="s">
-        <v>1307</v>
+        <v>1243</v>
+      </c>
+      <c r="C646" t="s">
+        <v>1244</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A647">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B647" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1247</v>
+        <v>1245</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>1307</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A648">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B648" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C648" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A649">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B649" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C649" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A650">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B650" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C650" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A651">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B651" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C651" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A652">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B652" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C652" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A653">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B653" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C653" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A654">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B654" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C654" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A655">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B655" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C655" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A656">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B656" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C656" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A657">
+        <v>743</v>
+      </c>
+      <c r="B657" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C657" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A658">
         <v>744</v>
       </c>
-      <c r="B657" t="s">
+      <c r="B658" t="s">
         <v>1266</v>
       </c>
-      <c r="C657" t="s">
+      <c r="C658" t="s">
         <v>1267</v>
       </c>
     </row>
-    <row r="658" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A658">
+    <row r="659" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A659">
         <v>745</v>
       </c>
-      <c r="B658" s="1" t="s">
+      <c r="B659" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C658" t="s">
+      <c r="C659" t="s">
         <v>1269</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A659">
-        <v>746</v>
-      </c>
-      <c r="B659" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A660">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C660" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A661">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C661" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A662">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C662" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A663">
-        <v>750</v>
-      </c>
-      <c r="B663" s="1"/>
-      <c r="C663" s="3" t="s">
-        <v>1333</v>
+        <v>749</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C663" t="s">
+        <v>1277</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A664">
-        <v>753</v>
-      </c>
-      <c r="B664" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1279</v>
+        <v>750</v>
+      </c>
+      <c r="B664" s="1"/>
+      <c r="C664" s="3" t="s">
+        <v>1333</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A665">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C665" s="3" t="s">
-        <v>1329</v>
+        <v>1278</v>
+      </c>
+      <c r="C665" t="s">
+        <v>1279</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A666">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1282</v>
+        <v>1280</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>1329</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A667">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C667" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A668">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C668" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A669">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C669" s="3" t="s">
-        <v>1337</v>
+        <v>1285</v>
+      </c>
+      <c r="C669" t="s">
+        <v>1286</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A670">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1289</v>
+        <v>1287</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>1337</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A671">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C671" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A672">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C672" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A673">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C673" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A674">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C674" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A675">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C675" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A676">
-        <v>766</v>
-      </c>
-      <c r="B676" s="1"/>
-      <c r="C676" s="3" t="s">
-        <v>1355</v>
+        <v>765</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C676" t="s">
+        <v>1299</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A677">
-        <v>767</v>
-      </c>
-      <c r="B677" s="1" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1301</v>
+        <v>766</v>
+      </c>
+      <c r="B677" s="1"/>
+      <c r="C677" s="3" t="s">
+        <v>1355</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A678">
-        <v>768</v>
-      </c>
-      <c r="B678" s="1"/>
+        <v>767</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>1300</v>
+      </c>
       <c r="C678" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A679">
-        <v>769</v>
-      </c>
-      <c r="B679" s="1" t="s">
-        <v>1303</v>
-      </c>
+        <v>768</v>
+      </c>
+      <c r="B679" s="1"/>
       <c r="C679" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A680">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>1309</v>
+        <v>1303</v>
+      </c>
+      <c r="C680" t="s">
+        <v>1304</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A681">
-        <v>773</v>
-      </c>
-      <c r="B681" s="1"/>
+        <v>772</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>1308</v>
+      </c>
       <c r="C681" s="3" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A682">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A683">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A684">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1323</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A685">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A686">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A687">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A688">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1327</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A689">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A690">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B690" s="1"/>
       <c r="C690" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A691">
-        <v>785</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="B691" s="1"/>
       <c r="C691" s="3" t="s">
-        <v>1351</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A692">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C692" s="3" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A693">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C693" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A694">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C694" s="3" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A695">
-        <v>10001</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1305</v>
+        <v>790</v>
       </c>
       <c r="C695" s="3" t="s">
-        <v>1336</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A696">
+        <v>10001</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A697">
         <v>10003</v>
       </c>
-      <c r="B696" t="s">
+      <c r="B697" t="s">
         <v>1303</v>
       </c>
-      <c r="C696" t="s">
+      <c r="C697" t="s">
         <v>1304</v>
       </c>
     </row>
@@ -12345,7 +12357,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A695:B695 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A618:C618 A235:C246 A247:B247 A248:C249 A234:B234 A95:C96 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A621:C623 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A609:C609 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A616:B616 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A596:C598 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A603:C604 A600:B600 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A606:C606 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A611:B611 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C210 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A613:B614 A426:C431 A602:B602 A113:B113 A340:C341 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B530 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B57 A255:C256 A254:B254 A153:C153 A152:B152 A212:C223 A211:B211 A343:C344 A342:B342 A98:C98 A97:B97" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A696:B696 A315:B315 A316:C326 A352:C352 A351:B351 A591:C591 A575 A574:B574 A460:C463 A459:B459 A619:C619 A235:C246 A247:B247 A248:C249 A234:B234 A95:C96 A146:C149 A145:B145 A541:C549 A540:B540 A55:C56 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A622:C624 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A610:C610 A21:C22 A20:B20 A420:C420 A115:C119 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A617:B617 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A155:C161 A154:B154 A129:C129 A128:B128 A71 A9:C12 A8:B8 A599:C599 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C524 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A44:C50 A43:B43 A604:C605 A601:B601 A595:B595 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A607:C607 A587:C588 A585:B585 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A612:B612 A592:B592 A134:C144 A133:B133 A314:C314 A313:B313 A209:C210 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A614:B615 A426:C431 A603:B603 A113:B114 A340:C341 A338:B339 A295:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B531 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A57:B58 A255:C256 A254:B254 A153:C153 A152:B152 A212:C223 A211:B211 A343:C344 A342:B342 A98:C98 A97:B97 A596:C597" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255A2EDB-94AE-4BA3-98C4-05FA6707D7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36C744-2D84-4AB2-AB6B-093297AC81F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24480" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -4092,9 +4092,6 @@
     <t>Shining Leaves</t>
   </si>
   <si>
-    <t>闪亮的叶子</t>
-  </si>
-  <si>
     <t>START!! True dreams</t>
   </si>
   <si>
@@ -4320,6 +4317,10 @@
   </si>
   <si>
     <t>信号B,信号 B,标志是B,B标志,B信号,我推的孩子B,我推B,我推2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪亮的叶子,闪耀树叶,闪光树叶,闪耀的树叶,闪光的树叶</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5374,7 +5375,7 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
@@ -5814,7 +5815,7 @@
         <v>192</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.15">
@@ -5990,7 +5991,7 @@
         <v>223</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
@@ -6177,7 +6178,7 @@
         <v>256</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.15">
@@ -6419,7 +6420,7 @@
         <v>299</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.15">
@@ -6584,7 +6585,7 @@
         <v>328</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.15">
@@ -7068,7 +7069,7 @@
         <v>415</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.15">
@@ -7211,7 +7212,7 @@
         <v>440</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.15">
@@ -7508,7 +7509,7 @@
         <v>493</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.15">
@@ -7541,7 +7542,7 @@
         <v>497</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.15">
@@ -7728,7 +7729,7 @@
         <v>530</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.15">
@@ -8003,7 +8004,7 @@
         <v>579</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.15">
@@ -8465,7 +8466,7 @@
         <v>662</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.15">
@@ -8476,7 +8477,7 @@
         <v>663</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.15">
@@ -8509,7 +8510,7 @@
         <v>668</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.15">
@@ -9881,7 +9882,7 @@
         <v>912</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.15">
@@ -10274,7 +10275,7 @@
         <v>981</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.15">
@@ -10513,7 +10514,7 @@
         <v>1022</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.15">
@@ -10568,7 +10569,7 @@
         <v>1031</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.15">
@@ -11057,7 +11058,7 @@
         <v>1118</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.15">
@@ -11079,7 +11080,7 @@
         <v>927</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.15">
@@ -11090,7 +11091,7 @@
         <v>929</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.15">
@@ -11145,7 +11146,7 @@
         <v>1129</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.15">
@@ -11153,7 +11154,7 @@
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.15">
@@ -11271,7 +11272,7 @@
         <v>1149</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.15">
@@ -11301,7 +11302,7 @@
         <v>637</v>
       </c>
       <c r="C598" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.15">
@@ -11356,7 +11357,7 @@
         <v>1162</v>
       </c>
       <c r="C603" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.15">
@@ -11686,7 +11687,7 @@
         <v>1221</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.15">
@@ -11697,7 +11698,7 @@
         <v>1222</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.15">
@@ -11760,7 +11761,7 @@
         <v>724</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.15">
@@ -11837,7 +11838,7 @@
         <v>1245</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.15">
@@ -12022,7 +12023,7 @@
       </c>
       <c r="B664" s="1"/>
       <c r="C664" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.15">
@@ -12044,7 +12045,7 @@
         <v>1280</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.15">
@@ -12088,7 +12089,7 @@
         <v>1287</v>
       </c>
       <c r="C670" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.15">
@@ -12142,8 +12143,8 @@
       <c r="B675" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="C675" t="s">
-        <v>1297</v>
+      <c r="C675" s="3" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.15">
@@ -12151,10 +12152,10 @@
         <v>765</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C676" t="s">
         <v>1298</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.15">
@@ -12163,7 +12164,7 @@
       </c>
       <c r="B677" s="1"/>
       <c r="C677" s="3" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.15">
@@ -12171,10 +12172,10 @@
         <v>767</v>
       </c>
       <c r="B678" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C678" t="s">
         <v>1300</v>
-      </c>
-      <c r="C678" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.15">
@@ -12183,7 +12184,7 @@
       </c>
       <c r="B679" s="1"/>
       <c r="C679" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.15">
@@ -12191,10 +12192,10 @@
         <v>769</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C680" t="s">
         <v>1303</v>
-      </c>
-      <c r="C680" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.15">
@@ -12202,10 +12203,10 @@
         <v>772</v>
       </c>
       <c r="B681" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C681" s="3" t="s">
         <v>1308</v>
-      </c>
-      <c r="C681" s="3" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.15">
@@ -12214,7 +12215,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.15">
@@ -12223,7 +12224,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.15">
@@ -12232,7 +12233,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.15">
@@ -12241,7 +12242,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.15">
@@ -12250,7 +12251,7 @@
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.15">
@@ -12259,7 +12260,7 @@
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.15">
@@ -12268,7 +12269,7 @@
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.15">
@@ -12277,7 +12278,7 @@
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.15">
@@ -12286,7 +12287,7 @@
       </c>
       <c r="B690" s="1"/>
       <c r="C690" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.15">
@@ -12295,7 +12296,7 @@
       </c>
       <c r="B691" s="1"/>
       <c r="C691" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.15">
@@ -12303,7 +12304,7 @@
         <v>785</v>
       </c>
       <c r="C692" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.15">
@@ -12311,7 +12312,7 @@
         <v>787</v>
       </c>
       <c r="C693" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.15">
@@ -12319,7 +12320,7 @@
         <v>788</v>
       </c>
       <c r="C694" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.15">
@@ -12327,7 +12328,7 @@
         <v>790</v>
       </c>
       <c r="C695" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.15">
@@ -12335,10 +12336,10 @@
         <v>10001</v>
       </c>
       <c r="B696" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C696" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.15">
@@ -12346,10 +12347,10 @@
         <v>10003</v>
       </c>
       <c r="B697" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C697" t="s">
         <v>1303</v>
-      </c>
-      <c r="C697" t="s">
-        <v>1304</v>
       </c>
     </row>
   </sheetData>

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36C744-2D84-4AB2-AB6B-093297AC81F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6016BF4-097C-4875-B203-46C9C001C03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24480" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3918,12 +3918,6 @@
     <t>怪兽</t>
   </si>
   <si>
-    <t>エガクミライ</t>
-  </si>
-  <si>
-    <t>Mirai</t>
-  </si>
-  <si>
     <t>Velonica</t>
   </si>
   <si>
@@ -4321,6 +4315,14 @@
   </si>
   <si>
     <t>闪亮的叶子,闪耀树叶,闪光树叶,闪耀的树叶,闪光的树叶</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>エガクミライ</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mirai,描绘未来,描繪未來,描写未来,绘写未来</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4743,15 +4745,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C697"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="50.75" customWidth="1"/>
-    <col min="3" max="3" width="65.75" customWidth="1"/>
-    <col min="4" max="4" width="55.75" customWidth="1"/>
+    <col min="1" max="1" width="10.69921875" customWidth="1"/>
+    <col min="2" max="2" width="50.69921875" customWidth="1"/>
+    <col min="3" max="3" width="65.69921875" customWidth="1"/>
+    <col min="4" max="4" width="55.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4762,7 +4764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4773,7 +4775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4784,7 +4786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4795,7 +4797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4806,7 +4808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4817,7 +4819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4828,7 +4830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4839,7 +4841,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4850,7 +4852,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4861,7 +4863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4872,7 +4874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4883,7 +4885,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4894,7 +4896,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4905,7 +4907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4916,7 +4918,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4927,7 +4929,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4938,7 +4940,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4949,7 +4951,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4960,7 +4962,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4971,7 +4973,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4982,7 +4984,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4993,7 +4995,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>24</v>
       </c>
@@ -5004,7 +5006,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25</v>
       </c>
@@ -5015,7 +5017,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26</v>
       </c>
@@ -5026,7 +5028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>27</v>
       </c>
@@ -5037,7 +5039,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>28</v>
       </c>
@@ -5048,7 +5050,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5059,7 +5061,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>30</v>
       </c>
@@ -5070,7 +5072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5081,7 +5083,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5092,7 +5094,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5103,7 +5105,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5114,7 +5116,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>35</v>
       </c>
@@ -5125,7 +5127,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5136,7 +5138,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5147,7 +5149,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>40</v>
       </c>
@@ -5158,7 +5160,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5169,7 +5171,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5180,7 +5182,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5191,7 +5193,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5202,7 +5204,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5213,7 +5215,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5224,7 +5226,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5235,7 +5237,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5246,7 +5248,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5257,7 +5259,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5268,7 +5270,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5279,7 +5281,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5290,7 +5292,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5301,7 +5303,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5312,7 +5314,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5323,7 +5325,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5334,7 +5336,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5345,7 +5347,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5356,7 +5358,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5367,7 +5369,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5375,10 +5377,10 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5389,7 +5391,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5400,7 +5402,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5411,7 +5413,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5422,7 +5424,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5433,7 +5435,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5444,7 +5446,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5455,7 +5457,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5466,7 +5468,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5477,7 +5479,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5488,7 +5490,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5499,7 +5501,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5510,7 +5512,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>73</v>
       </c>
@@ -5521,7 +5523,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>74</v>
       </c>
@@ -5532,7 +5534,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>75</v>
       </c>
@@ -5543,7 +5545,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>76</v>
       </c>
@@ -5554,7 +5556,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>77</v>
       </c>
@@ -5565,7 +5567,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>78</v>
       </c>
@@ -5576,7 +5578,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>79</v>
       </c>
@@ -5587,7 +5589,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>80</v>
       </c>
@@ -5598,7 +5600,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>81</v>
       </c>
@@ -5609,7 +5611,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>82</v>
       </c>
@@ -5620,7 +5622,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>83</v>
       </c>
@@ -5631,7 +5633,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>84</v>
       </c>
@@ -5642,7 +5644,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>85</v>
       </c>
@@ -5653,7 +5655,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>86</v>
       </c>
@@ -5664,7 +5666,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>87</v>
       </c>
@@ -5675,7 +5677,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>88</v>
       </c>
@@ -5686,7 +5688,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>89</v>
       </c>
@@ -5697,7 +5699,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>90</v>
       </c>
@@ -5708,7 +5710,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>91</v>
       </c>
@@ -5719,7 +5721,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>92</v>
       </c>
@@ -5730,7 +5732,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5741,7 +5743,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5752,7 +5754,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5763,7 +5765,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5774,7 +5776,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5785,7 +5787,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5796,7 +5798,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5807,7 +5809,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5815,10 +5817,10 @@
         <v>192</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5829,7 +5831,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5840,7 +5842,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5851,7 +5853,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5862,7 +5864,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5873,7 +5875,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5884,7 +5886,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5895,7 +5897,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5906,7 +5908,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5917,7 +5919,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5928,7 +5930,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5939,7 +5941,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5950,7 +5952,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5961,7 +5963,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5972,7 +5974,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5983,7 +5985,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5991,10 +5993,10 @@
         <v>223</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>122</v>
       </c>
@@ -6005,7 +6007,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>123</v>
       </c>
@@ -6016,7 +6018,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>124</v>
       </c>
@@ -6027,7 +6029,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>125</v>
       </c>
@@ -6038,7 +6040,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126</v>
       </c>
@@ -6049,7 +6051,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>127</v>
       </c>
@@ -6060,7 +6062,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>128</v>
       </c>
@@ -6071,7 +6073,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>129</v>
       </c>
@@ -6082,7 +6084,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>130</v>
       </c>
@@ -6093,7 +6095,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>131</v>
       </c>
@@ -6104,7 +6106,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>132</v>
       </c>
@@ -6115,7 +6117,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>133</v>
       </c>
@@ -6126,7 +6128,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>134</v>
       </c>
@@ -6137,7 +6139,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>135</v>
       </c>
@@ -6148,7 +6150,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6159,7 +6161,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6170,7 +6172,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6178,10 +6180,10 @@
         <v>256</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6192,7 +6194,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6203,7 +6205,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6214,7 +6216,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6225,7 +6227,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6236,7 +6238,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6247,7 +6249,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6258,7 +6260,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6269,7 +6271,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6280,7 +6282,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6291,7 +6293,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6302,7 +6304,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6313,7 +6315,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6324,7 +6326,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6335,7 +6337,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6346,7 +6348,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6357,7 +6359,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6368,7 +6370,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6379,7 +6381,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6390,7 +6392,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6401,7 +6403,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6412,7 +6414,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6420,10 +6422,10 @@
         <v>299</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6434,7 +6436,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6445,7 +6447,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6456,7 +6458,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6467,7 +6469,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6478,7 +6480,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6489,7 +6491,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6500,7 +6502,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6511,7 +6513,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>169</v>
       </c>
@@ -6522,7 +6524,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>170</v>
       </c>
@@ -6533,7 +6535,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>171</v>
       </c>
@@ -6544,7 +6546,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>172</v>
       </c>
@@ -6555,7 +6557,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>173</v>
       </c>
@@ -6566,7 +6568,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>174</v>
       </c>
@@ -6577,7 +6579,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>175</v>
       </c>
@@ -6585,10 +6587,10 @@
         <v>328</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>176</v>
       </c>
@@ -6599,7 +6601,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>177</v>
       </c>
@@ -6610,7 +6612,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>178</v>
       </c>
@@ -6621,7 +6623,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>179</v>
       </c>
@@ -6632,7 +6634,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>180</v>
       </c>
@@ -6643,7 +6645,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>181</v>
       </c>
@@ -6654,7 +6656,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>182</v>
       </c>
@@ -6665,7 +6667,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>183</v>
       </c>
@@ -6676,7 +6678,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>184</v>
       </c>
@@ -6687,7 +6689,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>185</v>
       </c>
@@ -6698,7 +6700,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>186</v>
       </c>
@@ -6709,7 +6711,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>187</v>
       </c>
@@ -6720,7 +6722,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>188</v>
       </c>
@@ -6731,7 +6733,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>189</v>
       </c>
@@ -6742,7 +6744,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>190</v>
       </c>
@@ -6753,7 +6755,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>191</v>
       </c>
@@ -6764,7 +6766,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>192</v>
       </c>
@@ -6775,7 +6777,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6786,7 +6788,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6797,7 +6799,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6808,7 +6810,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6819,7 +6821,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6830,7 +6832,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6841,7 +6843,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6852,7 +6854,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6863,7 +6865,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6874,7 +6876,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6885,7 +6887,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6896,7 +6898,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6907,7 +6909,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6918,7 +6920,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6929,7 +6931,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6940,7 +6942,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6951,7 +6953,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6962,7 +6964,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6973,7 +6975,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6984,7 +6986,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6995,7 +6997,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>213</v>
       </c>
@@ -7006,7 +7008,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>214</v>
       </c>
@@ -7017,7 +7019,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>215</v>
       </c>
@@ -7028,7 +7030,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>217</v>
       </c>
@@ -7039,7 +7041,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>218</v>
       </c>
@@ -7050,7 +7052,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>219</v>
       </c>
@@ -7061,7 +7063,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>220</v>
       </c>
@@ -7069,10 +7071,10 @@
         <v>415</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>221</v>
       </c>
@@ -7083,7 +7085,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>222</v>
       </c>
@@ -7094,7 +7096,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>223</v>
       </c>
@@ -7105,7 +7107,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>224</v>
       </c>
@@ -7116,7 +7118,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>225</v>
       </c>
@@ -7127,7 +7129,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>226</v>
       </c>
@@ -7138,7 +7140,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>227</v>
       </c>
@@ -7149,7 +7151,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7160,7 +7162,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7171,7 +7173,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7182,7 +7184,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7193,7 +7195,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7204,7 +7206,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>233</v>
       </c>
@@ -7212,10 +7214,10 @@
         <v>440</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>234</v>
       </c>
@@ -7226,7 +7228,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>235</v>
       </c>
@@ -7237,7 +7239,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>236</v>
       </c>
@@ -7248,7 +7250,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>237</v>
       </c>
@@ -7259,7 +7261,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>238</v>
       </c>
@@ -7270,7 +7272,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>239</v>
       </c>
@@ -7281,7 +7283,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>240</v>
       </c>
@@ -7292,7 +7294,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>241</v>
       </c>
@@ -7303,7 +7305,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>242</v>
       </c>
@@ -7314,7 +7316,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>243</v>
       </c>
@@ -7325,7 +7327,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>244</v>
       </c>
@@ -7336,7 +7338,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>245</v>
       </c>
@@ -7347,7 +7349,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>246</v>
       </c>
@@ -7358,7 +7360,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>247</v>
       </c>
@@ -7369,7 +7371,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>248</v>
       </c>
@@ -7380,7 +7382,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>249</v>
       </c>
@@ -7391,7 +7393,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>250</v>
       </c>
@@ -7402,7 +7404,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>251</v>
       </c>
@@ -7413,7 +7415,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>252</v>
       </c>
@@ -7424,7 +7426,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>253</v>
       </c>
@@ -7435,7 +7437,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>254</v>
       </c>
@@ -7446,7 +7448,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>255</v>
       </c>
@@ -7457,7 +7459,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>256</v>
       </c>
@@ -7468,7 +7470,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>257</v>
       </c>
@@ -7479,7 +7481,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>258</v>
       </c>
@@ -7490,7 +7492,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>259</v>
       </c>
@@ -7501,7 +7503,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>260</v>
       </c>
@@ -7509,10 +7511,10 @@
         <v>493</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>261</v>
       </c>
@@ -7523,7 +7525,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>262</v>
       </c>
@@ -7534,7 +7536,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>263</v>
       </c>
@@ -7542,10 +7544,10 @@
         <v>497</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>264</v>
       </c>
@@ -7556,7 +7558,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>265</v>
       </c>
@@ -7567,7 +7569,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>266</v>
       </c>
@@ -7578,7 +7580,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>267</v>
       </c>
@@ -7589,7 +7591,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>268</v>
       </c>
@@ -7600,7 +7602,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>269</v>
       </c>
@@ -7611,7 +7613,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>270</v>
       </c>
@@ -7622,7 +7624,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>271</v>
       </c>
@@ -7633,7 +7635,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>272</v>
       </c>
@@ -7644,7 +7646,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>274</v>
       </c>
@@ -7655,7 +7657,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>275</v>
       </c>
@@ -7666,7 +7668,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>276</v>
       </c>
@@ -7677,7 +7679,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>277</v>
       </c>
@@ -7688,7 +7690,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>278</v>
       </c>
@@ -7699,7 +7701,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>279</v>
       </c>
@@ -7710,7 +7712,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>280</v>
       </c>
@@ -7721,7 +7723,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>281</v>
       </c>
@@ -7729,10 +7731,10 @@
         <v>530</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>282</v>
       </c>
@@ -7743,7 +7745,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>283</v>
       </c>
@@ -7754,7 +7756,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>284</v>
       </c>
@@ -7765,7 +7767,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>285</v>
       </c>
@@ -7776,7 +7778,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>286</v>
       </c>
@@ -7787,7 +7789,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>287</v>
       </c>
@@ -7798,7 +7800,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>288</v>
       </c>
@@ -7809,7 +7811,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>289</v>
       </c>
@@ -7820,7 +7822,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>290</v>
       </c>
@@ -7831,7 +7833,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>291</v>
       </c>
@@ -7842,7 +7844,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>292</v>
       </c>
@@ -7853,7 +7855,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>293</v>
       </c>
@@ -7864,7 +7866,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>294</v>
       </c>
@@ -7875,7 +7877,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>295</v>
       </c>
@@ -7886,7 +7888,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>296</v>
       </c>
@@ -7897,7 +7899,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>297</v>
       </c>
@@ -7908,7 +7910,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>298</v>
       </c>
@@ -7919,7 +7921,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>299</v>
       </c>
@@ -7930,7 +7932,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>300</v>
       </c>
@@ -7941,7 +7943,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>301</v>
       </c>
@@ -7952,7 +7954,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>302</v>
       </c>
@@ -7963,7 +7965,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>303</v>
       </c>
@@ -7974,7 +7976,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>304</v>
       </c>
@@ -7985,7 +7987,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>305</v>
       </c>
@@ -7996,7 +7998,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>306</v>
       </c>
@@ -8004,10 +8006,10 @@
         <v>579</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>307</v>
       </c>
@@ -8018,7 +8020,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>308</v>
       </c>
@@ -8029,7 +8031,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>309</v>
       </c>
@@ -8040,7 +8042,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>310</v>
       </c>
@@ -8051,7 +8053,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>311</v>
       </c>
@@ -8062,7 +8064,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>312</v>
       </c>
@@ -8073,7 +8075,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>313</v>
       </c>
@@ -8084,7 +8086,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>314</v>
       </c>
@@ -8095,7 +8097,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>315</v>
       </c>
@@ -8106,7 +8108,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>316</v>
       </c>
@@ -8117,7 +8119,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>317</v>
       </c>
@@ -8128,7 +8130,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>318</v>
       </c>
@@ -8139,7 +8141,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>319</v>
       </c>
@@ -8150,7 +8152,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>320</v>
       </c>
@@ -8161,7 +8163,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>321</v>
       </c>
@@ -8172,7 +8174,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>322</v>
       </c>
@@ -8183,7 +8185,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>323</v>
       </c>
@@ -8194,7 +8196,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>324</v>
       </c>
@@ -8205,7 +8207,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>325</v>
       </c>
@@ -8216,7 +8218,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>326</v>
       </c>
@@ -8227,7 +8229,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>327</v>
       </c>
@@ -8238,7 +8240,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>328</v>
       </c>
@@ -8249,7 +8251,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>329</v>
       </c>
@@ -8260,7 +8262,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>330</v>
       </c>
@@ -8271,7 +8273,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>331</v>
       </c>
@@ -8282,7 +8284,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>332</v>
       </c>
@@ -8293,7 +8295,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>333</v>
       </c>
@@ -8304,7 +8306,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>334</v>
       </c>
@@ -8315,7 +8317,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>335</v>
       </c>
@@ -8326,7 +8328,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>336</v>
       </c>
@@ -8337,7 +8339,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>337</v>
       </c>
@@ -8348,7 +8350,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>338</v>
       </c>
@@ -8359,7 +8361,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>339</v>
       </c>
@@ -8370,7 +8372,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>340</v>
       </c>
@@ -8381,7 +8383,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>341</v>
       </c>
@@ -8392,7 +8394,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>342</v>
       </c>
@@ -8403,7 +8405,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>343</v>
       </c>
@@ -8414,7 +8416,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>344</v>
       </c>
@@ -8425,7 +8427,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>345</v>
       </c>
@@ -8436,7 +8438,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>346</v>
       </c>
@@ -8447,7 +8449,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>347</v>
       </c>
@@ -8458,7 +8460,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>348</v>
       </c>
@@ -8466,10 +8468,10 @@
         <v>662</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>349</v>
       </c>
@@ -8477,10 +8479,10 @@
         <v>663</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>350</v>
       </c>
@@ -8491,7 +8493,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>351</v>
       </c>
@@ -8502,7 +8504,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>352</v>
       </c>
@@ -8510,10 +8512,10 @@
         <v>668</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>353</v>
       </c>
@@ -8524,7 +8526,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>354</v>
       </c>
@@ -8535,7 +8537,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>355</v>
       </c>
@@ -8546,7 +8548,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>356</v>
       </c>
@@ -8557,7 +8559,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>357</v>
       </c>
@@ -8568,7 +8570,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>358</v>
       </c>
@@ -8579,7 +8581,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>359</v>
       </c>
@@ -8590,7 +8592,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>360</v>
       </c>
@@ -8601,7 +8603,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>361</v>
       </c>
@@ -8612,7 +8614,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>362</v>
       </c>
@@ -8623,7 +8625,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>363</v>
       </c>
@@ -8634,7 +8636,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>364</v>
       </c>
@@ -8645,7 +8647,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>365</v>
       </c>
@@ -8656,7 +8658,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>366</v>
       </c>
@@ -8667,7 +8669,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>367</v>
       </c>
@@ -8678,7 +8680,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>368</v>
       </c>
@@ -8689,7 +8691,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>369</v>
       </c>
@@ -8700,7 +8702,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>370</v>
       </c>
@@ -8711,7 +8713,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>371</v>
       </c>
@@ -8722,7 +8724,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>372</v>
       </c>
@@ -8733,7 +8735,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>373</v>
       </c>
@@ -8744,7 +8746,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>374</v>
       </c>
@@ -8755,7 +8757,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>375</v>
       </c>
@@ -8766,7 +8768,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>376</v>
       </c>
@@ -8777,7 +8779,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>377</v>
       </c>
@@ -8788,7 +8790,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>378</v>
       </c>
@@ -8799,7 +8801,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>379</v>
       </c>
@@ -8810,7 +8812,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>380</v>
       </c>
@@ -8821,7 +8823,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>381</v>
       </c>
@@ -8832,7 +8834,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>382</v>
       </c>
@@ -8843,7 +8845,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>383</v>
       </c>
@@ -8854,7 +8856,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>384</v>
       </c>
@@ -8865,7 +8867,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>385</v>
       </c>
@@ -8876,7 +8878,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>386</v>
       </c>
@@ -8887,7 +8889,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>387</v>
       </c>
@@ -8898,7 +8900,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>388</v>
       </c>
@@ -8909,7 +8911,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>389</v>
       </c>
@@ -8920,7 +8922,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>390</v>
       </c>
@@ -8931,7 +8933,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>391</v>
       </c>
@@ -8942,7 +8944,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>392</v>
       </c>
@@ -8953,7 +8955,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>393</v>
       </c>
@@ -8964,7 +8966,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>394</v>
       </c>
@@ -8975,7 +8977,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>395</v>
       </c>
@@ -8986,7 +8988,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>396</v>
       </c>
@@ -8997,7 +8999,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>397</v>
       </c>
@@ -9008,7 +9010,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>398</v>
       </c>
@@ -9019,7 +9021,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>399</v>
       </c>
@@ -9030,7 +9032,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>400</v>
       </c>
@@ -9041,7 +9043,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>401</v>
       </c>
@@ -9052,7 +9054,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>402</v>
       </c>
@@ -9063,7 +9065,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>403</v>
       </c>
@@ -9074,7 +9076,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>404</v>
       </c>
@@ -9085,7 +9087,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>405</v>
       </c>
@@ -9096,7 +9098,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>406</v>
       </c>
@@ -9107,7 +9109,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>407</v>
       </c>
@@ -9118,7 +9120,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>408</v>
       </c>
@@ -9129,7 +9131,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>409</v>
       </c>
@@ -9140,7 +9142,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>410</v>
       </c>
@@ -9151,7 +9153,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>411</v>
       </c>
@@ -9162,7 +9164,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>412</v>
       </c>
@@ -9173,7 +9175,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>413</v>
       </c>
@@ -9184,7 +9186,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>414</v>
       </c>
@@ -9195,7 +9197,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>415</v>
       </c>
@@ -9206,7 +9208,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>416</v>
       </c>
@@ -9217,7 +9219,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>417</v>
       </c>
@@ -9228,7 +9230,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>418</v>
       </c>
@@ -9239,7 +9241,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>419</v>
       </c>
@@ -9250,7 +9252,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>420</v>
       </c>
@@ -9261,7 +9263,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>421</v>
       </c>
@@ -9272,7 +9274,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>422</v>
       </c>
@@ -9283,7 +9285,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>423</v>
       </c>
@@ -9294,7 +9296,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>424</v>
       </c>
@@ -9305,7 +9307,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>425</v>
       </c>
@@ -9316,7 +9318,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>426</v>
       </c>
@@ -9327,7 +9329,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>427</v>
       </c>
@@ -9338,7 +9340,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>428</v>
       </c>
@@ -9349,7 +9351,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>429</v>
       </c>
@@ -9360,7 +9362,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>430</v>
       </c>
@@ -9371,7 +9373,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>431</v>
       </c>
@@ -9382,7 +9384,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>432</v>
       </c>
@@ -9393,7 +9395,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>433</v>
       </c>
@@ -9404,7 +9406,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>434</v>
       </c>
@@ -9415,7 +9417,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>435</v>
       </c>
@@ -9426,7 +9428,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>436</v>
       </c>
@@ -9437,7 +9439,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>437</v>
       </c>
@@ -9448,7 +9450,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>438</v>
       </c>
@@ -9459,7 +9461,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>439</v>
       </c>
@@ -9470,7 +9472,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>440</v>
       </c>
@@ -9481,7 +9483,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>441</v>
       </c>
@@ -9492,7 +9494,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>442</v>
       </c>
@@ -9503,7 +9505,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>443</v>
       </c>
@@ -9514,7 +9516,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>444</v>
       </c>
@@ -9525,7 +9527,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>445</v>
       </c>
@@ -9536,7 +9538,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>446</v>
       </c>
@@ -9547,7 +9549,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>447</v>
       </c>
@@ -9558,7 +9560,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>448</v>
       </c>
@@ -9569,7 +9571,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>449</v>
       </c>
@@ -9580,7 +9582,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>450</v>
       </c>
@@ -9591,7 +9593,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>451</v>
       </c>
@@ -9602,7 +9604,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>452</v>
       </c>
@@ -9613,7 +9615,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>453</v>
       </c>
@@ -9624,7 +9626,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>455</v>
       </c>
@@ -9635,7 +9637,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>456</v>
       </c>
@@ -9646,7 +9648,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>457</v>
       </c>
@@ -9657,7 +9659,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>458</v>
       </c>
@@ -9668,7 +9670,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>459</v>
       </c>
@@ -9679,7 +9681,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>460</v>
       </c>
@@ -9690,7 +9692,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>461</v>
       </c>
@@ -9701,7 +9703,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>462</v>
       </c>
@@ -9712,7 +9714,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>463</v>
       </c>
@@ -9723,7 +9725,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>464</v>
       </c>
@@ -9734,7 +9736,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>465</v>
       </c>
@@ -9745,7 +9747,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>466</v>
       </c>
@@ -9756,7 +9758,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>467</v>
       </c>
@@ -9767,7 +9769,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>468</v>
       </c>
@@ -9778,7 +9780,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>469</v>
       </c>
@@ -9789,7 +9791,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>470</v>
       </c>
@@ -9800,7 +9802,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>471</v>
       </c>
@@ -9808,7 +9810,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>472</v>
       </c>
@@ -9819,7 +9821,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>473</v>
       </c>
@@ -9830,7 +9832,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>474</v>
       </c>
@@ -9841,7 +9843,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>475</v>
       </c>
@@ -9852,7 +9854,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>476</v>
       </c>
@@ -9863,7 +9865,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>477</v>
       </c>
@@ -9874,7 +9876,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>478</v>
       </c>
@@ -9882,10 +9884,10 @@
         <v>912</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>479</v>
       </c>
@@ -9896,7 +9898,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>480</v>
       </c>
@@ -9907,7 +9909,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>481</v>
       </c>
@@ -9918,7 +9920,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>482</v>
       </c>
@@ -9929,7 +9931,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>483</v>
       </c>
@@ -9940,7 +9942,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A473">
         <v>484</v>
       </c>
@@ -9951,7 +9953,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>485</v>
       </c>
@@ -9962,7 +9964,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>486</v>
       </c>
@@ -9973,7 +9975,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>487</v>
       </c>
@@ -9984,7 +9986,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>488</v>
       </c>
@@ -9995,7 +9997,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>489</v>
       </c>
@@ -10006,7 +10008,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>490</v>
       </c>
@@ -10017,7 +10019,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>491</v>
       </c>
@@ -10028,7 +10030,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>492</v>
       </c>
@@ -10039,7 +10041,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>493</v>
       </c>
@@ -10050,7 +10052,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>494</v>
       </c>
@@ -10061,7 +10063,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>496</v>
       </c>
@@ -10072,7 +10074,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>497</v>
       </c>
@@ -10083,7 +10085,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>498</v>
       </c>
@@ -10094,7 +10096,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>499</v>
       </c>
@@ -10105,7 +10107,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>500</v>
       </c>
@@ -10116,7 +10118,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>501</v>
       </c>
@@ -10127,7 +10129,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>502</v>
       </c>
@@ -10138,7 +10140,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>503</v>
       </c>
@@ -10149,7 +10151,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>504</v>
       </c>
@@ -10160,7 +10162,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>505</v>
       </c>
@@ -10171,7 +10173,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>506</v>
       </c>
@@ -10182,7 +10184,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>507</v>
       </c>
@@ -10193,7 +10195,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>508</v>
       </c>
@@ -10204,7 +10206,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>509</v>
       </c>
@@ -10215,7 +10217,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>510</v>
       </c>
@@ -10226,7 +10228,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>511</v>
       </c>
@@ -10234,7 +10236,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>512</v>
       </c>
@@ -10245,7 +10247,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>513</v>
       </c>
@@ -10256,7 +10258,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>514</v>
       </c>
@@ -10267,7 +10269,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>515</v>
       </c>
@@ -10275,10 +10277,10 @@
         <v>981</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>516</v>
       </c>
@@ -10289,7 +10291,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>517</v>
       </c>
@@ -10300,7 +10302,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>518</v>
       </c>
@@ -10311,7 +10313,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>519</v>
       </c>
@@ -10322,7 +10324,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>520</v>
       </c>
@@ -10333,7 +10335,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>521</v>
       </c>
@@ -10344,7 +10346,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>522</v>
       </c>
@@ -10355,7 +10357,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>523</v>
       </c>
@@ -10366,7 +10368,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>524</v>
       </c>
@@ -10377,7 +10379,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>525</v>
       </c>
@@ -10388,7 +10390,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>526</v>
       </c>
@@ -10399,7 +10401,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>527</v>
       </c>
@@ -10410,7 +10412,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>528</v>
       </c>
@@ -10421,7 +10423,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>529</v>
       </c>
@@ -10432,7 +10434,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>530</v>
       </c>
@@ -10440,7 +10442,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>531</v>
       </c>
@@ -10451,7 +10453,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>532</v>
       </c>
@@ -10462,7 +10464,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>533</v>
       </c>
@@ -10473,7 +10475,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>534</v>
       </c>
@@ -10484,7 +10486,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>535</v>
       </c>
@@ -10495,7 +10497,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>536</v>
       </c>
@@ -10506,7 +10508,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>537</v>
       </c>
@@ -10514,10 +10516,10 @@
         <v>1022</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>538</v>
       </c>
@@ -10528,7 +10530,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>539</v>
       </c>
@@ -10539,7 +10541,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>540</v>
       </c>
@@ -10550,7 +10552,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>542</v>
       </c>
@@ -10561,7 +10563,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>543</v>
       </c>
@@ -10569,10 +10571,10 @@
         <v>1031</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>545</v>
       </c>
@@ -10583,7 +10585,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>546</v>
       </c>
@@ -10594,7 +10596,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>547</v>
       </c>
@@ -10605,7 +10607,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>548</v>
       </c>
@@ -10616,7 +10618,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>549</v>
       </c>
@@ -10627,7 +10629,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>550</v>
       </c>
@@ -10638,7 +10640,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>551</v>
       </c>
@@ -10649,7 +10651,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>552</v>
       </c>
@@ -10660,7 +10662,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>553</v>
       </c>
@@ -10671,7 +10673,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>554</v>
       </c>
@@ -10682,7 +10684,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>555</v>
       </c>
@@ -10693,7 +10695,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>556</v>
       </c>
@@ -10704,7 +10706,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>557</v>
       </c>
@@ -10715,7 +10717,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>558</v>
       </c>
@@ -10726,7 +10728,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>559</v>
       </c>
@@ -10737,7 +10739,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>562</v>
       </c>
@@ -10748,7 +10750,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>563</v>
       </c>
@@ -10756,7 +10758,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>564</v>
       </c>
@@ -10767,7 +10769,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>565</v>
       </c>
@@ -10778,7 +10780,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>566</v>
       </c>
@@ -10789,7 +10791,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>567</v>
       </c>
@@ -10800,7 +10802,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>568</v>
       </c>
@@ -10811,7 +10813,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>569</v>
       </c>
@@ -10822,7 +10824,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>570</v>
       </c>
@@ -10833,7 +10835,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>571</v>
       </c>
@@ -10844,7 +10846,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>572</v>
       </c>
@@ -10855,7 +10857,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>577</v>
       </c>
@@ -10866,7 +10868,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>578</v>
       </c>
@@ -10877,7 +10879,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>579</v>
       </c>
@@ -10885,7 +10887,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>580</v>
       </c>
@@ -10896,7 +10898,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>581</v>
       </c>
@@ -10907,7 +10909,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>582</v>
       </c>
@@ -10918,7 +10920,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>583</v>
       </c>
@@ -10929,7 +10931,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>584</v>
       </c>
@@ -10940,7 +10942,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>585</v>
       </c>
@@ -10951,7 +10953,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>586</v>
       </c>
@@ -10962,7 +10964,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>587</v>
       </c>
@@ -10973,7 +10975,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>588</v>
       </c>
@@ -10984,7 +10986,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>589</v>
       </c>
@@ -10995,7 +10997,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>590</v>
       </c>
@@ -11006,7 +11008,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>591</v>
       </c>
@@ -11017,7 +11019,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>592</v>
       </c>
@@ -11028,7 +11030,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>593</v>
       </c>
@@ -11039,7 +11041,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>594</v>
       </c>
@@ -11050,7 +11052,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>595</v>
       </c>
@@ -11058,10 +11060,10 @@
         <v>1118</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>596</v>
       </c>
@@ -11072,7 +11074,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>597</v>
       </c>
@@ -11080,10 +11082,10 @@
         <v>927</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>598</v>
       </c>
@@ -11091,10 +11093,10 @@
         <v>929</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>599</v>
       </c>
@@ -11105,7 +11107,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>601</v>
       </c>
@@ -11116,7 +11118,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>602</v>
       </c>
@@ -11127,7 +11129,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>604</v>
       </c>
@@ -11138,7 +11140,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>606</v>
       </c>
@@ -11146,18 +11148,18 @@
         <v>1129</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>612</v>
       </c>
@@ -11168,7 +11170,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>615</v>
       </c>
@@ -11179,7 +11181,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>617</v>
       </c>
@@ -11190,7 +11192,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>618</v>
       </c>
@@ -11201,7 +11203,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>625</v>
       </c>
@@ -11212,7 +11214,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>624</v>
       </c>
@@ -11223,7 +11225,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>626</v>
       </c>
@@ -11234,7 +11236,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>629</v>
       </c>
@@ -11245,7 +11247,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>630</v>
       </c>
@@ -11256,7 +11258,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>632</v>
       </c>
@@ -11264,7 +11266,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>633</v>
       </c>
@@ -11272,10 +11274,10 @@
         <v>1149</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>635</v>
       </c>
@@ -11286,7 +11288,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>636</v>
       </c>
@@ -11297,15 +11299,15 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>637</v>
       </c>
       <c r="C598" s="3" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>642</v>
       </c>
@@ -11316,7 +11318,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>644</v>
       </c>
@@ -11327,7 +11329,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>646</v>
       </c>
@@ -11338,7 +11340,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>649</v>
       </c>
@@ -11349,7 +11351,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>650</v>
       </c>
@@ -11357,10 +11359,10 @@
         <v>1162</v>
       </c>
       <c r="C603" s="3" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>651</v>
       </c>
@@ -11371,7 +11373,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>653</v>
       </c>
@@ -11382,7 +11384,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>654</v>
       </c>
@@ -11393,7 +11395,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>655</v>
       </c>
@@ -11404,7 +11406,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>659</v>
       </c>
@@ -11415,7 +11417,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>660</v>
       </c>
@@ -11426,7 +11428,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>661</v>
       </c>
@@ -11437,7 +11439,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>663</v>
       </c>
@@ -11448,7 +11450,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>667</v>
       </c>
@@ -11459,7 +11461,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>670</v>
       </c>
@@ -11470,7 +11472,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>673</v>
       </c>
@@ -11481,7 +11483,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>674</v>
       </c>
@@ -11492,7 +11494,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>675</v>
       </c>
@@ -11503,7 +11505,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>680</v>
       </c>
@@ -11514,7 +11516,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>681</v>
       </c>
@@ -11525,7 +11527,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>682</v>
       </c>
@@ -11536,7 +11538,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>683</v>
       </c>
@@ -11547,7 +11549,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>684</v>
       </c>
@@ -11558,7 +11560,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>685</v>
       </c>
@@ -11569,7 +11571,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>686</v>
       </c>
@@ -11580,7 +11582,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>689</v>
       </c>
@@ -11591,7 +11593,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>697</v>
       </c>
@@ -11602,7 +11604,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>701</v>
       </c>
@@ -11613,7 +11615,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>702</v>
       </c>
@@ -11624,7 +11626,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>704</v>
       </c>
@@ -11635,7 +11637,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>705</v>
       </c>
@@ -11646,7 +11648,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>710</v>
       </c>
@@ -11657,7 +11659,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>711</v>
       </c>
@@ -11668,7 +11670,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>712</v>
       </c>
@@ -11679,7 +11681,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>714</v>
       </c>
@@ -11687,10 +11689,10 @@
         <v>1221</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>717</v>
       </c>
@@ -11698,10 +11700,10 @@
         <v>1222</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>718</v>
       </c>
@@ -11712,7 +11714,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>719</v>
       </c>
@@ -11723,7 +11725,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="637" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A637">
         <v>721</v>
       </c>
@@ -11734,7 +11736,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>722</v>
       </c>
@@ -11745,7 +11747,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>723</v>
       </c>
@@ -11756,15 +11758,15 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>724</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>725</v>
       </c>
@@ -11775,7 +11777,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>726</v>
       </c>
@@ -11786,7 +11788,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>727</v>
       </c>
@@ -11797,7 +11799,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="644" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A644">
         <v>728</v>
       </c>
@@ -11808,7 +11810,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="645" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A645">
         <v>729</v>
       </c>
@@ -11819,7 +11821,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>730</v>
       </c>
@@ -11830,7 +11832,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>731</v>
       </c>
@@ -11838,10 +11840,10 @@
         <v>1245</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>733</v>
       </c>
@@ -11852,505 +11854,505 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>735</v>
       </c>
-      <c r="B649" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B649" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>736</v>
       </c>
       <c r="B650" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C650" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>737</v>
       </c>
       <c r="B651" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C651" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>738</v>
       </c>
       <c r="B652" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C652" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>739</v>
       </c>
       <c r="B653" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C653" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>740</v>
       </c>
       <c r="B654" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C654" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>741</v>
       </c>
       <c r="B655" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C655" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>742</v>
       </c>
       <c r="B656" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C656" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>743</v>
       </c>
       <c r="B657" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C657" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658">
         <v>744</v>
       </c>
       <c r="B658" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C658" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A659">
         <v>745</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C659" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>746</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C660" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>747</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C661" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>748</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C662" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>749</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C663" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>750</v>
       </c>
       <c r="B664" s="1"/>
       <c r="C664" s="3" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>753</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C665" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>755</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>756</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C667" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>757</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C668" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>758</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C669" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>759</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C670" s="3" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>760</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C671" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>761</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C672" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>762</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C673" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>763</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C674" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>764</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C675" s="3" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>765</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C676" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>766</v>
       </c>
       <c r="B677" s="1"/>
       <c r="C677" s="3" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>767</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C678" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>768</v>
       </c>
       <c r="B679" s="1"/>
       <c r="C679" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>769</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C680" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>772</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="C681" s="3" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>773</v>
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>774</v>
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>776</v>
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>779</v>
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>780</v>
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>781</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>783</v>
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>782</v>
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>783</v>
       </c>
       <c r="B690" s="1"/>
       <c r="C690" s="3" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>784</v>
       </c>
       <c r="B691" s="1"/>
       <c r="C691" s="3" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>785</v>
       </c>
       <c r="C692" s="3" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>787</v>
       </c>
       <c r="C693" s="3" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>788</v>
       </c>
       <c r="C694" s="3" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>790</v>
       </c>
       <c r="C695" s="3" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>10001</v>
       </c>
       <c r="B696" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C696" s="3" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>10003</v>
       </c>
       <c r="B697" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C697" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
   </sheetData>

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6016BF4-097C-4875-B203-46C9C001C03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EF89CA-2A79-406C-B336-9F23D9BF06BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3927,9 +3927,6 @@
     <t>Mas?uerade Rhapsody Re?uest</t>
   </si>
   <si>
-    <t>12兆年,十二兆年,mas,mas?,mas？,Mas,Mas?,Mas？</t>
-  </si>
-  <si>
     <t>Part of the Life</t>
   </si>
   <si>
@@ -4242,10 +4239,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>花天堂</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>卢卡卢卡,露卡露卡,LukaLuka,LucaLuca,lukaluka,时停</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -4323,6 +4316,14 @@
   </si>
   <si>
     <t>Mirai,描绘未来,描繪未來,描写未来,绘写未来</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>12兆年,十二兆年,mas,mas?,mas？,Mas,Mas?,Mas？,假面舞会</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花天堂,fh</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4745,15 +4746,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C697"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.69921875" customWidth="1"/>
-    <col min="2" max="2" width="50.69921875" customWidth="1"/>
-    <col min="3" max="3" width="65.69921875" customWidth="1"/>
-    <col min="4" max="4" width="55.69921875" customWidth="1"/>
+    <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="50.75" customWidth="1"/>
+    <col min="3" max="3" width="65.75" customWidth="1"/>
+    <col min="4" max="4" width="55.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4764,7 +4765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4775,7 +4776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4786,7 +4787,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4797,7 +4798,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4808,7 +4809,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4819,7 +4820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4830,7 +4831,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4841,7 +4842,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4852,7 +4853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4863,7 +4864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4874,7 +4875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4918,7 +4919,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4929,7 +4930,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4940,7 +4941,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4951,7 +4952,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4962,7 +4963,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4973,7 +4974,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4995,7 +4996,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>24</v>
       </c>
@@ -5006,7 +5007,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>25</v>
       </c>
@@ -5017,7 +5018,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>26</v>
       </c>
@@ -5028,7 +5029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>27</v>
       </c>
@@ -5039,7 +5040,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>28</v>
       </c>
@@ -5050,7 +5051,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5061,7 +5062,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>30</v>
       </c>
@@ -5072,7 +5073,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5083,7 +5084,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5094,7 +5095,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5105,7 +5106,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5116,7 +5117,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>35</v>
       </c>
@@ -5127,7 +5128,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5138,7 +5139,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5149,7 +5150,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>40</v>
       </c>
@@ -5160,7 +5161,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5171,7 +5172,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5182,7 +5183,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5193,7 +5194,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5204,7 +5205,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5215,7 +5216,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5226,7 +5227,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5237,7 +5238,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5270,7 +5271,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5281,7 +5282,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5292,7 +5293,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5303,7 +5304,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5314,7 +5315,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5325,7 +5326,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5336,7 +5337,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5347,7 +5348,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5358,7 +5359,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5369,7 +5370,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5377,10 +5378,10 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5391,7 +5392,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5402,7 +5403,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5413,7 +5414,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5424,7 +5425,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5435,7 +5436,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5446,7 +5447,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5457,7 +5458,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5468,7 +5469,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5479,7 +5480,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5490,7 +5491,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5501,7 +5502,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5512,7 +5513,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>73</v>
       </c>
@@ -5523,7 +5524,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>74</v>
       </c>
@@ -5534,7 +5535,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>75</v>
       </c>
@@ -5545,7 +5546,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>76</v>
       </c>
@@ -5556,7 +5557,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>77</v>
       </c>
@@ -5567,7 +5568,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>78</v>
       </c>
@@ -5578,7 +5579,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>79</v>
       </c>
@@ -5589,7 +5590,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>80</v>
       </c>
@@ -5600,7 +5601,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>81</v>
       </c>
@@ -5611,7 +5612,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>82</v>
       </c>
@@ -5622,7 +5623,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>83</v>
       </c>
@@ -5633,7 +5634,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>84</v>
       </c>
@@ -5644,7 +5645,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>85</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>86</v>
       </c>
@@ -5666,7 +5667,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>87</v>
       </c>
@@ -5677,7 +5678,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>88</v>
       </c>
@@ -5688,7 +5689,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>89</v>
       </c>
@@ -5699,7 +5700,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>90</v>
       </c>
@@ -5710,7 +5711,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>91</v>
       </c>
@@ -5721,7 +5722,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>92</v>
       </c>
@@ -5732,7 +5733,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5743,7 +5744,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5765,7 +5766,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5776,7 +5777,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5787,7 +5788,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5798,7 +5799,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5809,7 +5810,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5817,10 +5818,10 @@
         <v>192</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5831,7 +5832,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5842,7 +5843,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5853,7 +5854,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5864,7 +5865,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5886,7 +5887,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5897,7 +5898,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5919,7 +5920,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5930,7 +5931,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5941,7 +5942,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5952,7 +5953,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5963,7 +5964,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5974,7 +5975,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5985,7 +5986,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5993,10 +5994,10 @@
         <v>223</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114">
         <v>122</v>
       </c>
@@ -6007,7 +6008,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115">
         <v>123</v>
       </c>
@@ -6018,7 +6019,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116">
         <v>124</v>
       </c>
@@ -6029,7 +6030,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117">
         <v>125</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118">
         <v>126</v>
       </c>
@@ -6051,7 +6052,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119">
         <v>127</v>
       </c>
@@ -6062,7 +6063,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120">
         <v>128</v>
       </c>
@@ -6073,7 +6074,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121">
         <v>129</v>
       </c>
@@ -6084,7 +6085,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122">
         <v>130</v>
       </c>
@@ -6095,7 +6096,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123">
         <v>131</v>
       </c>
@@ -6106,7 +6107,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124">
         <v>132</v>
       </c>
@@ -6117,7 +6118,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125">
         <v>133</v>
       </c>
@@ -6128,7 +6129,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126">
         <v>134</v>
       </c>
@@ -6139,7 +6140,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127">
         <v>135</v>
       </c>
@@ -6150,7 +6151,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6161,7 +6162,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6172,7 +6173,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6180,10 +6181,10 @@
         <v>256</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6194,7 +6195,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6205,7 +6206,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6216,7 +6217,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6227,7 +6228,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6249,7 +6250,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6260,7 +6261,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6271,7 +6272,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6282,7 +6283,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6293,7 +6294,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6304,7 +6305,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6315,7 +6316,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6326,7 +6327,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6337,7 +6338,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6348,7 +6349,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6359,7 +6360,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6370,7 +6371,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6381,7 +6382,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6392,7 +6393,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6403,7 +6404,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6414,7 +6415,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6422,10 +6423,10 @@
         <v>299</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6436,7 +6437,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6447,7 +6448,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6458,7 +6459,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6469,7 +6470,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6480,7 +6481,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6491,7 +6492,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6502,7 +6503,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A161">
         <v>169</v>
       </c>
@@ -6524,7 +6525,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A162">
         <v>170</v>
       </c>
@@ -6535,7 +6536,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A163">
         <v>171</v>
       </c>
@@ -6546,7 +6547,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A164">
         <v>172</v>
       </c>
@@ -6557,7 +6558,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A165">
         <v>173</v>
       </c>
@@ -6568,7 +6569,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A166">
         <v>174</v>
       </c>
@@ -6579,7 +6580,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A167">
         <v>175</v>
       </c>
@@ -6587,10 +6588,10 @@
         <v>328</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A168">
         <v>176</v>
       </c>
@@ -6601,7 +6602,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A169">
         <v>177</v>
       </c>
@@ -6612,7 +6613,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A170">
         <v>178</v>
       </c>
@@ -6623,7 +6624,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A171">
         <v>179</v>
       </c>
@@ -6634,7 +6635,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A172">
         <v>180</v>
       </c>
@@ -6645,7 +6646,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A173">
         <v>181</v>
       </c>
@@ -6656,7 +6657,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A174">
         <v>182</v>
       </c>
@@ -6667,7 +6668,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A175">
         <v>183</v>
       </c>
@@ -6678,7 +6679,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A176">
         <v>184</v>
       </c>
@@ -6689,7 +6690,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A177">
         <v>185</v>
       </c>
@@ -6700,7 +6701,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A178">
         <v>186</v>
       </c>
@@ -6711,7 +6712,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A179">
         <v>187</v>
       </c>
@@ -6722,7 +6723,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A180">
         <v>188</v>
       </c>
@@ -6733,7 +6734,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A181">
         <v>189</v>
       </c>
@@ -6744,7 +6745,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A182">
         <v>190</v>
       </c>
@@ -6755,7 +6756,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A183">
         <v>191</v>
       </c>
@@ -6766,7 +6767,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A184">
         <v>192</v>
       </c>
@@ -6777,7 +6778,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6788,7 +6789,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6799,7 +6800,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6810,7 +6811,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6821,7 +6822,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6832,7 +6833,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6843,7 +6844,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6854,7 +6855,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6865,7 +6866,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6876,7 +6877,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6887,7 +6888,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6898,7 +6899,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6909,7 +6910,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6920,7 +6921,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6931,7 +6932,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6942,7 +6943,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6953,7 +6954,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6964,7 +6965,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6975,7 +6976,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6986,7 +6987,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6997,7 +6998,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A205">
         <v>213</v>
       </c>
@@ -7008,7 +7009,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A206">
         <v>214</v>
       </c>
@@ -7019,7 +7020,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A207">
         <v>215</v>
       </c>
@@ -7030,7 +7031,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A208">
         <v>217</v>
       </c>
@@ -7041,7 +7042,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A209">
         <v>218</v>
       </c>
@@ -7052,7 +7053,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A210">
         <v>219</v>
       </c>
@@ -7063,7 +7064,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A211">
         <v>220</v>
       </c>
@@ -7071,10 +7072,10 @@
         <v>415</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A212">
         <v>221</v>
       </c>
@@ -7085,7 +7086,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A213">
         <v>222</v>
       </c>
@@ -7096,7 +7097,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A214">
         <v>223</v>
       </c>
@@ -7107,7 +7108,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A215">
         <v>224</v>
       </c>
@@ -7118,7 +7119,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A216">
         <v>225</v>
       </c>
@@ -7129,7 +7130,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A217">
         <v>226</v>
       </c>
@@ -7140,7 +7141,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A218">
         <v>227</v>
       </c>
@@ -7151,7 +7152,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7162,7 +7163,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7173,7 +7174,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7184,7 +7185,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7195,7 +7196,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7206,7 +7207,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A224">
         <v>233</v>
       </c>
@@ -7214,10 +7215,10 @@
         <v>440</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A225">
         <v>234</v>
       </c>
@@ -7228,7 +7229,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A226">
         <v>235</v>
       </c>
@@ -7239,7 +7240,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A227">
         <v>236</v>
       </c>
@@ -7250,7 +7251,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A228">
         <v>237</v>
       </c>
@@ -7261,7 +7262,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A229">
         <v>238</v>
       </c>
@@ -7272,7 +7273,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A230">
         <v>239</v>
       </c>
@@ -7283,7 +7284,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A231">
         <v>240</v>
       </c>
@@ -7294,7 +7295,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A232">
         <v>241</v>
       </c>
@@ -7305,7 +7306,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A233">
         <v>242</v>
       </c>
@@ -7316,7 +7317,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A234">
         <v>243</v>
       </c>
@@ -7327,7 +7328,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A235">
         <v>244</v>
       </c>
@@ -7338,7 +7339,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A236">
         <v>245</v>
       </c>
@@ -7349,7 +7350,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A237">
         <v>246</v>
       </c>
@@ -7360,7 +7361,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A238">
         <v>247</v>
       </c>
@@ -7371,7 +7372,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A239">
         <v>248</v>
       </c>
@@ -7382,7 +7383,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A240">
         <v>249</v>
       </c>
@@ -7393,7 +7394,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A241">
         <v>250</v>
       </c>
@@ -7404,7 +7405,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A242">
         <v>251</v>
       </c>
@@ -7415,7 +7416,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A243">
         <v>252</v>
       </c>
@@ -7426,7 +7427,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A244">
         <v>253</v>
       </c>
@@ -7437,7 +7438,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A245">
         <v>254</v>
       </c>
@@ -7448,7 +7449,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A246">
         <v>255</v>
       </c>
@@ -7459,7 +7460,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A247">
         <v>256</v>
       </c>
@@ -7470,7 +7471,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A248">
         <v>257</v>
       </c>
@@ -7481,7 +7482,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A249">
         <v>258</v>
       </c>
@@ -7492,7 +7493,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A250">
         <v>259</v>
       </c>
@@ -7503,7 +7504,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A251">
         <v>260</v>
       </c>
@@ -7511,10 +7512,10 @@
         <v>493</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A252">
         <v>261</v>
       </c>
@@ -7525,7 +7526,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A253">
         <v>262</v>
       </c>
@@ -7536,7 +7537,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A254">
         <v>263</v>
       </c>
@@ -7544,10 +7545,10 @@
         <v>497</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A255">
         <v>264</v>
       </c>
@@ -7558,7 +7559,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A256">
         <v>265</v>
       </c>
@@ -7569,7 +7570,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A257">
         <v>266</v>
       </c>
@@ -7580,7 +7581,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A258">
         <v>267</v>
       </c>
@@ -7591,7 +7592,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A259">
         <v>268</v>
       </c>
@@ -7602,7 +7603,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A260">
         <v>269</v>
       </c>
@@ -7613,7 +7614,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A261">
         <v>270</v>
       </c>
@@ -7624,7 +7625,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A262">
         <v>271</v>
       </c>
@@ -7635,7 +7636,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A263">
         <v>272</v>
       </c>
@@ -7646,7 +7647,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A264">
         <v>274</v>
       </c>
@@ -7657,7 +7658,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A265">
         <v>275</v>
       </c>
@@ -7668,7 +7669,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A266">
         <v>276</v>
       </c>
@@ -7679,7 +7680,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A267">
         <v>277</v>
       </c>
@@ -7690,7 +7691,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A268">
         <v>278</v>
       </c>
@@ -7701,7 +7702,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A269">
         <v>279</v>
       </c>
@@ -7712,7 +7713,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A270">
         <v>280</v>
       </c>
@@ -7723,7 +7724,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A271">
         <v>281</v>
       </c>
@@ -7731,10 +7732,10 @@
         <v>530</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A272">
         <v>282</v>
       </c>
@@ -7745,7 +7746,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A273">
         <v>283</v>
       </c>
@@ -7756,7 +7757,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A274">
         <v>284</v>
       </c>
@@ -7767,7 +7768,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A275">
         <v>285</v>
       </c>
@@ -7778,7 +7779,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A276">
         <v>286</v>
       </c>
@@ -7789,7 +7790,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A277">
         <v>287</v>
       </c>
@@ -7800,7 +7801,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A278">
         <v>288</v>
       </c>
@@ -7811,7 +7812,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A279">
         <v>289</v>
       </c>
@@ -7822,7 +7823,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A280">
         <v>290</v>
       </c>
@@ -7833,7 +7834,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A281">
         <v>291</v>
       </c>
@@ -7844,7 +7845,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A282">
         <v>292</v>
       </c>
@@ -7855,7 +7856,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A283">
         <v>293</v>
       </c>
@@ -7866,7 +7867,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A284">
         <v>294</v>
       </c>
@@ -7877,7 +7878,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A285">
         <v>295</v>
       </c>
@@ -7888,7 +7889,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A286">
         <v>296</v>
       </c>
@@ -7899,7 +7900,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A287">
         <v>297</v>
       </c>
@@ -7910,7 +7911,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A288">
         <v>298</v>
       </c>
@@ -7921,7 +7922,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A289">
         <v>299</v>
       </c>
@@ -7932,7 +7933,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A290">
         <v>300</v>
       </c>
@@ -7943,7 +7944,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A291">
         <v>301</v>
       </c>
@@ -7954,7 +7955,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A292">
         <v>302</v>
       </c>
@@ -7965,7 +7966,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A293">
         <v>303</v>
       </c>
@@ -7976,7 +7977,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A294">
         <v>304</v>
       </c>
@@ -7987,7 +7988,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A295">
         <v>305</v>
       </c>
@@ -7998,7 +7999,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A296">
         <v>306</v>
       </c>
@@ -8006,10 +8007,10 @@
         <v>579</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A297">
         <v>307</v>
       </c>
@@ -8020,7 +8021,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A298">
         <v>308</v>
       </c>
@@ -8031,7 +8032,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A299">
         <v>309</v>
       </c>
@@ -8042,7 +8043,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A300">
         <v>310</v>
       </c>
@@ -8053,7 +8054,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A301">
         <v>311</v>
       </c>
@@ -8064,7 +8065,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A302">
         <v>312</v>
       </c>
@@ -8075,7 +8076,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A303">
         <v>313</v>
       </c>
@@ -8086,7 +8087,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A304">
         <v>314</v>
       </c>
@@ -8097,7 +8098,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A305">
         <v>315</v>
       </c>
@@ -8108,7 +8109,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A306">
         <v>316</v>
       </c>
@@ -8119,7 +8120,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A307">
         <v>317</v>
       </c>
@@ -8130,7 +8131,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A308">
         <v>318</v>
       </c>
@@ -8141,7 +8142,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A309">
         <v>319</v>
       </c>
@@ -8152,7 +8153,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A310">
         <v>320</v>
       </c>
@@ -8163,7 +8164,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A311">
         <v>321</v>
       </c>
@@ -8174,7 +8175,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A312">
         <v>322</v>
       </c>
@@ -8185,7 +8186,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A313">
         <v>323</v>
       </c>
@@ -8196,7 +8197,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A314">
         <v>324</v>
       </c>
@@ -8207,7 +8208,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A315">
         <v>325</v>
       </c>
@@ -8218,7 +8219,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A316">
         <v>326</v>
       </c>
@@ -8229,7 +8230,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A317">
         <v>327</v>
       </c>
@@ -8240,7 +8241,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A318">
         <v>328</v>
       </c>
@@ -8251,7 +8252,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A319">
         <v>329</v>
       </c>
@@ -8262,7 +8263,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A320">
         <v>330</v>
       </c>
@@ -8273,7 +8274,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A321">
         <v>331</v>
       </c>
@@ -8284,7 +8285,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A322">
         <v>332</v>
       </c>
@@ -8295,7 +8296,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A323">
         <v>333</v>
       </c>
@@ -8306,7 +8307,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A324">
         <v>334</v>
       </c>
@@ -8317,7 +8318,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A325">
         <v>335</v>
       </c>
@@ -8328,7 +8329,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A326">
         <v>336</v>
       </c>
@@ -8339,7 +8340,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A327">
         <v>337</v>
       </c>
@@ -8350,7 +8351,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A328">
         <v>338</v>
       </c>
@@ -8361,7 +8362,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A329">
         <v>339</v>
       </c>
@@ -8372,7 +8373,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A330">
         <v>340</v>
       </c>
@@ -8383,7 +8384,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A331">
         <v>341</v>
       </c>
@@ -8394,7 +8395,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A332">
         <v>342</v>
       </c>
@@ -8405,7 +8406,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A333">
         <v>343</v>
       </c>
@@ -8416,7 +8417,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A334">
         <v>344</v>
       </c>
@@ -8427,7 +8428,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A335">
         <v>345</v>
       </c>
@@ -8438,7 +8439,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A336">
         <v>346</v>
       </c>
@@ -8449,7 +8450,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A337">
         <v>347</v>
       </c>
@@ -8460,7 +8461,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A338">
         <v>348</v>
       </c>
@@ -8468,10 +8469,10 @@
         <v>662</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A339">
         <v>349</v>
       </c>
@@ -8479,10 +8480,10 @@
         <v>663</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A340">
         <v>350</v>
       </c>
@@ -8493,7 +8494,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A341">
         <v>351</v>
       </c>
@@ -8504,7 +8505,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A342">
         <v>352</v>
       </c>
@@ -8512,10 +8513,10 @@
         <v>668</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A343">
         <v>353</v>
       </c>
@@ -8526,7 +8527,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A344">
         <v>354</v>
       </c>
@@ -8537,7 +8538,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A345">
         <v>355</v>
       </c>
@@ -8548,7 +8549,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A346">
         <v>356</v>
       </c>
@@ -8559,7 +8560,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A347">
         <v>357</v>
       </c>
@@ -8570,7 +8571,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A348">
         <v>358</v>
       </c>
@@ -8581,7 +8582,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A349">
         <v>359</v>
       </c>
@@ -8592,7 +8593,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A350">
         <v>360</v>
       </c>
@@ -8603,7 +8604,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A351">
         <v>361</v>
       </c>
@@ -8614,7 +8615,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A352">
         <v>362</v>
       </c>
@@ -8625,7 +8626,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A353">
         <v>363</v>
       </c>
@@ -8636,7 +8637,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A354">
         <v>364</v>
       </c>
@@ -8647,7 +8648,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A355">
         <v>365</v>
       </c>
@@ -8658,7 +8659,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A356">
         <v>366</v>
       </c>
@@ -8669,7 +8670,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A357">
         <v>367</v>
       </c>
@@ -8680,7 +8681,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A358">
         <v>368</v>
       </c>
@@ -8691,7 +8692,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A359">
         <v>369</v>
       </c>
@@ -8702,7 +8703,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A360">
         <v>370</v>
       </c>
@@ -8713,7 +8714,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A361">
         <v>371</v>
       </c>
@@ -8724,7 +8725,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A362">
         <v>372</v>
       </c>
@@ -8735,7 +8736,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A363">
         <v>373</v>
       </c>
@@ -8746,7 +8747,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A364">
         <v>374</v>
       </c>
@@ -8757,7 +8758,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A365">
         <v>375</v>
       </c>
@@ -8768,7 +8769,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A366">
         <v>376</v>
       </c>
@@ -8779,7 +8780,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A367">
         <v>377</v>
       </c>
@@ -8790,7 +8791,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A368">
         <v>378</v>
       </c>
@@ -8801,7 +8802,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A369">
         <v>379</v>
       </c>
@@ -8812,7 +8813,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A370">
         <v>380</v>
       </c>
@@ -8823,7 +8824,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A371">
         <v>381</v>
       </c>
@@ -8834,7 +8835,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A372">
         <v>382</v>
       </c>
@@ -8845,7 +8846,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A373">
         <v>383</v>
       </c>
@@ -8856,7 +8857,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A374">
         <v>384</v>
       </c>
@@ -8867,7 +8868,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A375">
         <v>385</v>
       </c>
@@ -8878,7 +8879,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A376">
         <v>386</v>
       </c>
@@ -8889,7 +8890,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A377">
         <v>387</v>
       </c>
@@ -8900,7 +8901,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A378">
         <v>388</v>
       </c>
@@ -8911,7 +8912,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A379">
         <v>389</v>
       </c>
@@ -8922,7 +8923,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A380">
         <v>390</v>
       </c>
@@ -8933,7 +8934,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A381">
         <v>391</v>
       </c>
@@ -8944,7 +8945,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A382">
         <v>392</v>
       </c>
@@ -8955,7 +8956,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A383">
         <v>393</v>
       </c>
@@ -8966,7 +8967,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A384">
         <v>394</v>
       </c>
@@ -8977,7 +8978,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A385">
         <v>395</v>
       </c>
@@ -8988,7 +8989,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A386">
         <v>396</v>
       </c>
@@ -8999,7 +9000,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A387">
         <v>397</v>
       </c>
@@ -9010,7 +9011,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A388">
         <v>398</v>
       </c>
@@ -9021,7 +9022,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A389">
         <v>399</v>
       </c>
@@ -9032,7 +9033,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A390">
         <v>400</v>
       </c>
@@ -9043,7 +9044,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A391">
         <v>401</v>
       </c>
@@ -9054,7 +9055,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>402</v>
       </c>
@@ -9065,7 +9066,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A393">
         <v>403</v>
       </c>
@@ -9076,7 +9077,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A394">
         <v>404</v>
       </c>
@@ -9087,7 +9088,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A395">
         <v>405</v>
       </c>
@@ -9098,7 +9099,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A396">
         <v>406</v>
       </c>
@@ -9109,7 +9110,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A397">
         <v>407</v>
       </c>
@@ -9120,7 +9121,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A398">
         <v>408</v>
       </c>
@@ -9131,7 +9132,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A399">
         <v>409</v>
       </c>
@@ -9142,7 +9143,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A400">
         <v>410</v>
       </c>
@@ -9153,7 +9154,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A401">
         <v>411</v>
       </c>
@@ -9164,7 +9165,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A402">
         <v>412</v>
       </c>
@@ -9175,7 +9176,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A403">
         <v>413</v>
       </c>
@@ -9186,7 +9187,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A404">
         <v>414</v>
       </c>
@@ -9197,7 +9198,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A405">
         <v>415</v>
       </c>
@@ -9208,7 +9209,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A406">
         <v>416</v>
       </c>
@@ -9219,7 +9220,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A407">
         <v>417</v>
       </c>
@@ -9230,7 +9231,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A408">
         <v>418</v>
       </c>
@@ -9241,7 +9242,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A409">
         <v>419</v>
       </c>
@@ -9252,7 +9253,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A410">
         <v>420</v>
       </c>
@@ -9263,7 +9264,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A411">
         <v>421</v>
       </c>
@@ -9274,7 +9275,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A412">
         <v>422</v>
       </c>
@@ -9285,7 +9286,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A413">
         <v>423</v>
       </c>
@@ -9296,7 +9297,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A414">
         <v>424</v>
       </c>
@@ -9307,7 +9308,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A415">
         <v>425</v>
       </c>
@@ -9318,7 +9319,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A416">
         <v>426</v>
       </c>
@@ -9329,7 +9330,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A417">
         <v>427</v>
       </c>
@@ -9340,7 +9341,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A418">
         <v>428</v>
       </c>
@@ -9351,7 +9352,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A419">
         <v>429</v>
       </c>
@@ -9362,7 +9363,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A420">
         <v>430</v>
       </c>
@@ -9373,7 +9374,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A421">
         <v>431</v>
       </c>
@@ -9384,7 +9385,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A422">
         <v>432</v>
       </c>
@@ -9395,7 +9396,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A423">
         <v>433</v>
       </c>
@@ -9406,7 +9407,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A424">
         <v>434</v>
       </c>
@@ -9417,7 +9418,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A425">
         <v>435</v>
       </c>
@@ -9428,7 +9429,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A426">
         <v>436</v>
       </c>
@@ -9439,7 +9440,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A427">
         <v>437</v>
       </c>
@@ -9450,7 +9451,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A428">
         <v>438</v>
       </c>
@@ -9461,7 +9462,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A429">
         <v>439</v>
       </c>
@@ -9472,7 +9473,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A430">
         <v>440</v>
       </c>
@@ -9483,7 +9484,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A431">
         <v>441</v>
       </c>
@@ -9494,7 +9495,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A432">
         <v>442</v>
       </c>
@@ -9505,7 +9506,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A433">
         <v>443</v>
       </c>
@@ -9516,7 +9517,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A434">
         <v>444</v>
       </c>
@@ -9527,7 +9528,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A435">
         <v>445</v>
       </c>
@@ -9538,7 +9539,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A436">
         <v>446</v>
       </c>
@@ -9549,7 +9550,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A437">
         <v>447</v>
       </c>
@@ -9560,7 +9561,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A438">
         <v>448</v>
       </c>
@@ -9571,7 +9572,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A439">
         <v>449</v>
       </c>
@@ -9582,7 +9583,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A440">
         <v>450</v>
       </c>
@@ -9593,7 +9594,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A441">
         <v>451</v>
       </c>
@@ -9604,7 +9605,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A442">
         <v>452</v>
       </c>
@@ -9615,7 +9616,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A443">
         <v>453</v>
       </c>
@@ -9626,7 +9627,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A444">
         <v>455</v>
       </c>
@@ -9637,7 +9638,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A445">
         <v>456</v>
       </c>
@@ -9648,7 +9649,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A446">
         <v>457</v>
       </c>
@@ -9659,7 +9660,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A447">
         <v>458</v>
       </c>
@@ -9670,7 +9671,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A448">
         <v>459</v>
       </c>
@@ -9681,7 +9682,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A449">
         <v>460</v>
       </c>
@@ -9692,7 +9693,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A450">
         <v>461</v>
       </c>
@@ -9703,7 +9704,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A451">
         <v>462</v>
       </c>
@@ -9714,7 +9715,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A452">
         <v>463</v>
       </c>
@@ -9725,7 +9726,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A453">
         <v>464</v>
       </c>
@@ -9736,7 +9737,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A454">
         <v>465</v>
       </c>
@@ -9747,7 +9748,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A455">
         <v>466</v>
       </c>
@@ -9758,7 +9759,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A456">
         <v>467</v>
       </c>
@@ -9769,7 +9770,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A457">
         <v>468</v>
       </c>
@@ -9780,7 +9781,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A458">
         <v>469</v>
       </c>
@@ -9791,7 +9792,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A459">
         <v>470</v>
       </c>
@@ -9802,7 +9803,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A460">
         <v>471</v>
       </c>
@@ -9810,7 +9811,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A461">
         <v>472</v>
       </c>
@@ -9821,7 +9822,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A462">
         <v>473</v>
       </c>
@@ -9832,7 +9833,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A463">
         <v>474</v>
       </c>
@@ -9843,7 +9844,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A464">
         <v>475</v>
       </c>
@@ -9854,7 +9855,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A465">
         <v>476</v>
       </c>
@@ -9865,7 +9866,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A466">
         <v>477</v>
       </c>
@@ -9876,7 +9877,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A467">
         <v>478</v>
       </c>
@@ -9884,10 +9885,10 @@
         <v>912</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A468">
         <v>479</v>
       </c>
@@ -9898,7 +9899,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A469">
         <v>480</v>
       </c>
@@ -9909,7 +9910,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A470">
         <v>481</v>
       </c>
@@ -9920,7 +9921,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A471">
         <v>482</v>
       </c>
@@ -9931,7 +9932,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A472">
         <v>483</v>
       </c>
@@ -9942,7 +9943,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>484</v>
       </c>
@@ -9953,7 +9954,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A474">
         <v>485</v>
       </c>
@@ -9964,7 +9965,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A475">
         <v>486</v>
       </c>
@@ -9975,7 +9976,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A476">
         <v>487</v>
       </c>
@@ -9986,7 +9987,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A477">
         <v>488</v>
       </c>
@@ -9997,7 +9998,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A478">
         <v>489</v>
       </c>
@@ -10008,7 +10009,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A479">
         <v>490</v>
       </c>
@@ -10019,7 +10020,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A480">
         <v>491</v>
       </c>
@@ -10030,7 +10031,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A481">
         <v>492</v>
       </c>
@@ -10041,7 +10042,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A482">
         <v>493</v>
       </c>
@@ -10052,7 +10053,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A483">
         <v>494</v>
       </c>
@@ -10063,7 +10064,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A484">
         <v>496</v>
       </c>
@@ -10074,7 +10075,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A485">
         <v>497</v>
       </c>
@@ -10085,7 +10086,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A486">
         <v>498</v>
       </c>
@@ -10096,7 +10097,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A487">
         <v>499</v>
       </c>
@@ -10107,7 +10108,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A488">
         <v>500</v>
       </c>
@@ -10118,7 +10119,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A489">
         <v>501</v>
       </c>
@@ -10129,7 +10130,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A490">
         <v>502</v>
       </c>
@@ -10140,7 +10141,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A491">
         <v>503</v>
       </c>
@@ -10151,7 +10152,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A492">
         <v>504</v>
       </c>
@@ -10162,7 +10163,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A493">
         <v>505</v>
       </c>
@@ -10173,7 +10174,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A494">
         <v>506</v>
       </c>
@@ -10184,7 +10185,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A495">
         <v>507</v>
       </c>
@@ -10195,7 +10196,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A496">
         <v>508</v>
       </c>
@@ -10206,7 +10207,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A497">
         <v>509</v>
       </c>
@@ -10217,7 +10218,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A498">
         <v>510</v>
       </c>
@@ -10228,7 +10229,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A499">
         <v>511</v>
       </c>
@@ -10236,7 +10237,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A500">
         <v>512</v>
       </c>
@@ -10247,7 +10248,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A501">
         <v>513</v>
       </c>
@@ -10258,7 +10259,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A502">
         <v>514</v>
       </c>
@@ -10269,7 +10270,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A503">
         <v>515</v>
       </c>
@@ -10277,10 +10278,10 @@
         <v>981</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A504">
         <v>516</v>
       </c>
@@ -10291,7 +10292,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A505">
         <v>517</v>
       </c>
@@ -10302,7 +10303,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A506">
         <v>518</v>
       </c>
@@ -10313,7 +10314,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A507">
         <v>519</v>
       </c>
@@ -10324,7 +10325,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A508">
         <v>520</v>
       </c>
@@ -10335,7 +10336,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A509">
         <v>521</v>
       </c>
@@ -10346,7 +10347,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A510">
         <v>522</v>
       </c>
@@ -10357,7 +10358,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A511">
         <v>523</v>
       </c>
@@ -10368,7 +10369,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A512">
         <v>524</v>
       </c>
@@ -10379,7 +10380,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A513">
         <v>525</v>
       </c>
@@ -10390,7 +10391,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A514">
         <v>526</v>
       </c>
@@ -10401,7 +10402,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A515">
         <v>527</v>
       </c>
@@ -10412,7 +10413,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A516">
         <v>528</v>
       </c>
@@ -10423,7 +10424,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A517">
         <v>529</v>
       </c>
@@ -10434,7 +10435,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A518">
         <v>530</v>
       </c>
@@ -10442,7 +10443,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A519">
         <v>531</v>
       </c>
@@ -10453,7 +10454,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A520">
         <v>532</v>
       </c>
@@ -10464,7 +10465,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A521">
         <v>533</v>
       </c>
@@ -10475,7 +10476,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A522">
         <v>534</v>
       </c>
@@ -10486,7 +10487,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A523">
         <v>535</v>
       </c>
@@ -10497,7 +10498,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A524">
         <v>536</v>
       </c>
@@ -10508,7 +10509,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A525">
         <v>537</v>
       </c>
@@ -10516,10 +10517,10 @@
         <v>1022</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A526">
         <v>538</v>
       </c>
@@ -10530,7 +10531,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A527">
         <v>539</v>
       </c>
@@ -10541,7 +10542,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A528">
         <v>540</v>
       </c>
@@ -10552,7 +10553,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A529">
         <v>542</v>
       </c>
@@ -10563,7 +10564,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A530">
         <v>543</v>
       </c>
@@ -10571,10 +10572,10 @@
         <v>1031</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A531">
         <v>545</v>
       </c>
@@ -10585,7 +10586,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A532">
         <v>546</v>
       </c>
@@ -10596,7 +10597,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A533">
         <v>547</v>
       </c>
@@ -10607,7 +10608,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A534">
         <v>548</v>
       </c>
@@ -10618,7 +10619,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A535">
         <v>549</v>
       </c>
@@ -10629,7 +10630,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A536">
         <v>550</v>
       </c>
@@ -10640,7 +10641,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A537">
         <v>551</v>
       </c>
@@ -10651,7 +10652,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A538">
         <v>552</v>
       </c>
@@ -10662,7 +10663,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A539">
         <v>553</v>
       </c>
@@ -10673,7 +10674,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A540">
         <v>554</v>
       </c>
@@ -10684,7 +10685,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A541">
         <v>555</v>
       </c>
@@ -10695,7 +10696,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A542">
         <v>556</v>
       </c>
@@ -10706,7 +10707,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A543">
         <v>557</v>
       </c>
@@ -10717,7 +10718,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A544">
         <v>558</v>
       </c>
@@ -10728,7 +10729,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A545">
         <v>559</v>
       </c>
@@ -10739,7 +10740,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A546">
         <v>562</v>
       </c>
@@ -10750,7 +10751,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A547">
         <v>563</v>
       </c>
@@ -10758,7 +10759,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A548">
         <v>564</v>
       </c>
@@ -10769,7 +10770,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A549">
         <v>565</v>
       </c>
@@ -10780,7 +10781,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A550">
         <v>566</v>
       </c>
@@ -10791,7 +10792,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A551">
         <v>567</v>
       </c>
@@ -10802,7 +10803,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A552">
         <v>568</v>
       </c>
@@ -10813,7 +10814,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A553">
         <v>569</v>
       </c>
@@ -10824,7 +10825,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A554">
         <v>570</v>
       </c>
@@ -10835,7 +10836,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A555">
         <v>571</v>
       </c>
@@ -10846,7 +10847,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A556">
         <v>572</v>
       </c>
@@ -10857,7 +10858,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A557">
         <v>577</v>
       </c>
@@ -10868,7 +10869,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A558">
         <v>578</v>
       </c>
@@ -10879,7 +10880,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A559">
         <v>579</v>
       </c>
@@ -10887,7 +10888,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A560">
         <v>580</v>
       </c>
@@ -10898,7 +10899,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A561">
         <v>581</v>
       </c>
@@ -10909,7 +10910,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A562">
         <v>582</v>
       </c>
@@ -10920,7 +10921,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A563">
         <v>583</v>
       </c>
@@ -10931,7 +10932,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A564">
         <v>584</v>
       </c>
@@ -10942,7 +10943,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A565">
         <v>585</v>
       </c>
@@ -10953,7 +10954,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A566">
         <v>586</v>
       </c>
@@ -10964,7 +10965,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A567">
         <v>587</v>
       </c>
@@ -10975,7 +10976,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A568">
         <v>588</v>
       </c>
@@ -10986,7 +10987,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A569">
         <v>589</v>
       </c>
@@ -10997,7 +10998,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A570">
         <v>590</v>
       </c>
@@ -11008,7 +11009,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A571">
         <v>591</v>
       </c>
@@ -11019,7 +11020,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A572">
         <v>592</v>
       </c>
@@ -11030,7 +11031,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A573">
         <v>593</v>
       </c>
@@ -11041,7 +11042,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A574">
         <v>594</v>
       </c>
@@ -11052,7 +11053,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A575">
         <v>595</v>
       </c>
@@ -11060,10 +11061,10 @@
         <v>1118</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A576">
         <v>596</v>
       </c>
@@ -11074,7 +11075,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A577">
         <v>597</v>
       </c>
@@ -11082,10 +11083,10 @@
         <v>927</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A578">
         <v>598</v>
       </c>
@@ -11093,10 +11094,10 @@
         <v>929</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A579">
         <v>599</v>
       </c>
@@ -11107,7 +11108,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A580">
         <v>601</v>
       </c>
@@ -11118,7 +11119,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A581">
         <v>602</v>
       </c>
@@ -11129,7 +11130,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A582">
         <v>604</v>
       </c>
@@ -11140,7 +11141,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A583">
         <v>606</v>
       </c>
@@ -11148,18 +11149,18 @@
         <v>1129</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A584">
         <v>609</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A585">
         <v>612</v>
       </c>
@@ -11170,7 +11171,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A586">
         <v>615</v>
       </c>
@@ -11181,7 +11182,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A587">
         <v>617</v>
       </c>
@@ -11192,7 +11193,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A588">
         <v>618</v>
       </c>
@@ -11203,7 +11204,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A589">
         <v>625</v>
       </c>
@@ -11214,7 +11215,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A590">
         <v>624</v>
       </c>
@@ -11225,7 +11226,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A591">
         <v>626</v>
       </c>
@@ -11236,7 +11237,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A592">
         <v>629</v>
       </c>
@@ -11247,7 +11248,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A593">
         <v>630</v>
       </c>
@@ -11258,7 +11259,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A594">
         <v>632</v>
       </c>
@@ -11266,7 +11267,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A595">
         <v>633</v>
       </c>
@@ -11274,10 +11275,10 @@
         <v>1149</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A596">
         <v>635</v>
       </c>
@@ -11288,7 +11289,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A597">
         <v>636</v>
       </c>
@@ -11299,15 +11300,15 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A598">
         <v>637</v>
       </c>
       <c r="C598" s="3" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A599">
         <v>642</v>
       </c>
@@ -11318,7 +11319,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A600">
         <v>644</v>
       </c>
@@ -11329,7 +11330,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A601">
         <v>646</v>
       </c>
@@ -11340,7 +11341,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A602">
         <v>649</v>
       </c>
@@ -11351,7 +11352,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A603">
         <v>650</v>
       </c>
@@ -11359,10 +11360,10 @@
         <v>1162</v>
       </c>
       <c r="C603" s="3" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A604">
         <v>651</v>
       </c>
@@ -11373,7 +11374,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A605">
         <v>653</v>
       </c>
@@ -11384,7 +11385,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A606">
         <v>654</v>
       </c>
@@ -11395,7 +11396,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A607">
         <v>655</v>
       </c>
@@ -11406,7 +11407,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A608">
         <v>659</v>
       </c>
@@ -11417,7 +11418,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A609">
         <v>660</v>
       </c>
@@ -11428,7 +11429,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A610">
         <v>661</v>
       </c>
@@ -11439,7 +11440,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A611">
         <v>663</v>
       </c>
@@ -11450,7 +11451,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A612">
         <v>667</v>
       </c>
@@ -11461,7 +11462,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A613">
         <v>670</v>
       </c>
@@ -11472,7 +11473,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A614">
         <v>673</v>
       </c>
@@ -11483,7 +11484,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A615">
         <v>674</v>
       </c>
@@ -11494,7 +11495,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A616">
         <v>675</v>
       </c>
@@ -11505,7 +11506,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A617">
         <v>680</v>
       </c>
@@ -11516,7 +11517,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A618">
         <v>681</v>
       </c>
@@ -11527,7 +11528,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A619">
         <v>682</v>
       </c>
@@ -11538,7 +11539,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A620">
         <v>683</v>
       </c>
@@ -11549,7 +11550,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A621">
         <v>684</v>
       </c>
@@ -11560,7 +11561,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A622">
         <v>685</v>
       </c>
@@ -11571,7 +11572,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A623">
         <v>686</v>
       </c>
@@ -11582,7 +11583,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A624">
         <v>689</v>
       </c>
@@ -11593,7 +11594,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A625">
         <v>697</v>
       </c>
@@ -11604,7 +11605,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A626">
         <v>701</v>
       </c>
@@ -11615,7 +11616,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A627">
         <v>702</v>
       </c>
@@ -11626,7 +11627,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A628">
         <v>704</v>
       </c>
@@ -11637,7 +11638,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A629">
         <v>705</v>
       </c>
@@ -11648,7 +11649,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A630">
         <v>710</v>
       </c>
@@ -11659,7 +11660,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A631">
         <v>711</v>
       </c>
@@ -11670,7 +11671,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A632">
         <v>712</v>
       </c>
@@ -11681,7 +11682,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A633">
         <v>714</v>
       </c>
@@ -11689,10 +11690,10 @@
         <v>1221</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A634">
         <v>717</v>
       </c>
@@ -11700,10 +11701,10 @@
         <v>1222</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A635">
         <v>718</v>
       </c>
@@ -11714,7 +11715,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A636">
         <v>719</v>
       </c>
@@ -11725,7 +11726,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    <row r="637" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A637">
         <v>721</v>
       </c>
@@ -11736,7 +11737,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A638">
         <v>722</v>
       </c>
@@ -11747,7 +11748,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A639">
         <v>723</v>
       </c>
@@ -11758,15 +11759,15 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A640">
         <v>724</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A641">
         <v>725</v>
       </c>
@@ -11777,7 +11778,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A642">
         <v>726</v>
       </c>
@@ -11788,7 +11789,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A643">
         <v>727</v>
       </c>
@@ -11799,7 +11800,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="644" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    <row r="644" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A644">
         <v>728</v>
       </c>
@@ -11810,7 +11811,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="645" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    <row r="645" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A645">
         <v>729</v>
       </c>
@@ -11821,7 +11822,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A646">
         <v>730</v>
       </c>
@@ -11832,7 +11833,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A647">
         <v>731</v>
       </c>
@@ -11840,10 +11841,10 @@
         <v>1245</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A648">
         <v>733</v>
       </c>
@@ -11854,18 +11855,18 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A649">
         <v>735</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A650">
         <v>736</v>
       </c>
@@ -11876,483 +11877,483 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A651">
         <v>737</v>
       </c>
       <c r="B651" t="s">
         <v>1250</v>
       </c>
-      <c r="C651" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C651" s="3" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A652">
         <v>738</v>
       </c>
       <c r="B652" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C652" t="s">
         <v>1252</v>
       </c>
-      <c r="C652" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A653">
         <v>739</v>
       </c>
       <c r="B653" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C653" t="s">
         <v>1254</v>
       </c>
-      <c r="C653" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A654">
         <v>740</v>
       </c>
       <c r="B654" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C654" t="s">
         <v>1256</v>
       </c>
-      <c r="C654" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A655">
         <v>741</v>
       </c>
       <c r="B655" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C655" t="s">
         <v>1258</v>
       </c>
-      <c r="C655" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A656">
         <v>742</v>
       </c>
       <c r="B656" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C656" t="s">
         <v>1260</v>
       </c>
-      <c r="C656" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A657">
         <v>743</v>
       </c>
       <c r="B657" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C657" t="s">
         <v>1262</v>
       </c>
-      <c r="C657" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A658">
         <v>744</v>
       </c>
       <c r="B658" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C658" t="s">
         <v>1264</v>
       </c>
-      <c r="C658" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    </row>
+    <row r="659" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A659">
         <v>745</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C659" t="s">
         <v>1266</v>
       </c>
-      <c r="C659" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A660">
         <v>746</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C660" t="s">
         <v>1268</v>
       </c>
-      <c r="C660" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A661">
         <v>747</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C661" t="s">
         <v>1270</v>
       </c>
-      <c r="C661" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A662">
         <v>748</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C662" t="s">
         <v>1272</v>
       </c>
-      <c r="C662" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A663">
         <v>749</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C663" t="s">
         <v>1274</v>
       </c>
-      <c r="C663" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A664">
         <v>750</v>
       </c>
       <c r="B664" s="1"/>
       <c r="C664" s="3" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A665">
         <v>753</v>
       </c>
       <c r="B665" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C665" t="s">
         <v>1276</v>
       </c>
-      <c r="C665" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A666">
         <v>755</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A667">
         <v>756</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C667" t="s">
         <v>1279</v>
       </c>
-      <c r="C667" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A668">
         <v>757</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C668" t="s">
         <v>1281</v>
       </c>
-      <c r="C668" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A669">
         <v>758</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C669" t="s">
         <v>1283</v>
       </c>
-      <c r="C669" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A670">
         <v>759</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C670" s="3" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A671">
         <v>760</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C671" t="s">
         <v>1286</v>
       </c>
-      <c r="C671" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A672">
         <v>761</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C672" t="s">
         <v>1288</v>
       </c>
-      <c r="C672" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A673">
         <v>762</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C673" t="s">
         <v>1290</v>
       </c>
-      <c r="C673" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A674">
         <v>763</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C674" t="s">
         <v>1292</v>
       </c>
-      <c r="C674" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A675">
         <v>764</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C675" s="3" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A676">
         <v>765</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C676" t="s">
         <v>1295</v>
       </c>
-      <c r="C676" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A677">
         <v>766</v>
       </c>
       <c r="B677" s="1"/>
       <c r="C677" s="3" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A678">
         <v>767</v>
       </c>
       <c r="B678" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C678" t="s">
         <v>1297</v>
       </c>
-      <c r="C678" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A679">
         <v>768</v>
       </c>
       <c r="B679" s="1"/>
       <c r="C679" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A680">
         <v>769</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C680" t="s">
         <v>1300</v>
       </c>
-      <c r="C680" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A681">
         <v>772</v>
       </c>
       <c r="B681" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C681" s="3" t="s">
         <v>1305</v>
       </c>
-      <c r="C681" s="3" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A682">
         <v>773</v>
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A683">
         <v>774</v>
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A684">
         <v>776</v>
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A685">
         <v>779</v>
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A686">
         <v>780</v>
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A687">
         <v>781</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="3" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A688">
         <v>783</v>
       </c>
       <c r="B688" s="1"/>
       <c r="C688" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A689">
         <v>782</v>
       </c>
       <c r="B689" s="1"/>
       <c r="C689" s="3" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A690">
         <v>783</v>
       </c>
       <c r="B690" s="1"/>
       <c r="C690" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A691">
         <v>784</v>
       </c>
       <c r="B691" s="1"/>
       <c r="C691" s="3" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A692">
         <v>785</v>
       </c>
       <c r="C692" s="3" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A693">
         <v>787</v>
       </c>
       <c r="C693" s="3" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A694">
         <v>788</v>
       </c>
       <c r="C694" s="3" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A695">
         <v>790</v>
       </c>
       <c r="C695" s="3" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A696">
         <v>10001</v>
       </c>
       <c r="B696" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C696" s="3" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A697">
         <v>10003</v>
       </c>
       <c r="B697" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C697" t="s">
         <v>1300</v>
-      </c>
-      <c r="C697" t="s">
-        <v>1301</v>
       </c>
     </row>
   </sheetData>

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EF89CA-2A79-406C-B336-9F23D9BF06BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FA6184-4880-4404-A16D-EF4C6D57CE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3696,9 +3696,6 @@
     <t>八芒星ダンス</t>
   </si>
   <si>
-    <t>八芒星</t>
-  </si>
-  <si>
     <t>聿日箋秋</t>
   </si>
   <si>
@@ -4324,6 +4321,10 @@
   </si>
   <si>
     <t>花天堂,fh</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>八芒星,八芒星之舞</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4746,15 +4747,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C697"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="50.75" customWidth="1"/>
-    <col min="3" max="3" width="65.75" customWidth="1"/>
-    <col min="4" max="4" width="55.75" customWidth="1"/>
+    <col min="1" max="1" width="10.69921875" customWidth="1"/>
+    <col min="2" max="2" width="50.69921875" customWidth="1"/>
+    <col min="3" max="3" width="65.69921875" customWidth="1"/>
+    <col min="4" max="4" width="55.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4765,7 +4766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4776,7 +4777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4787,7 +4788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4809,7 +4810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4820,7 +4821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4831,7 +4832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4842,7 +4843,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4853,7 +4854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4864,7 +4865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4875,7 +4876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4886,7 +4887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4897,7 +4898,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4908,7 +4909,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4919,7 +4920,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4930,7 +4931,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4941,7 +4942,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4952,7 +4953,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4963,7 +4964,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4974,7 +4975,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4985,7 +4986,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4996,7 +4997,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>24</v>
       </c>
@@ -5007,7 +5008,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25</v>
       </c>
@@ -5018,7 +5019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26</v>
       </c>
@@ -5029,7 +5030,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>27</v>
       </c>
@@ -5040,7 +5041,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>28</v>
       </c>
@@ -5051,7 +5052,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5062,7 +5063,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>30</v>
       </c>
@@ -5073,7 +5074,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5084,7 +5085,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5095,7 +5096,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5106,7 +5107,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5117,7 +5118,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>35</v>
       </c>
@@ -5128,7 +5129,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5139,7 +5140,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5150,7 +5151,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>40</v>
       </c>
@@ -5161,7 +5162,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5172,7 +5173,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5183,7 +5184,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5194,7 +5195,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5205,7 +5206,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5216,7 +5217,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5227,7 +5228,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5238,7 +5239,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5249,7 +5250,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5260,7 +5261,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5271,7 +5272,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5282,7 +5283,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5293,7 +5294,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5304,7 +5305,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5315,7 +5316,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5326,7 +5327,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5337,7 +5338,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5348,7 +5349,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5359,7 +5360,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5370,7 +5371,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5378,10 +5379,10 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5392,7 +5393,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5403,7 +5404,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5414,7 +5415,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5425,7 +5426,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5436,7 +5437,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5447,7 +5448,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5458,7 +5459,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5469,7 +5470,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5480,7 +5481,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5491,7 +5492,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5502,7 +5503,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5513,7 +5514,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>73</v>
       </c>
@@ -5524,7 +5525,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>74</v>
       </c>
@@ -5535,7 +5536,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>75</v>
       </c>
@@ -5546,7 +5547,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>76</v>
       </c>
@@ -5557,7 +5558,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>77</v>
       </c>
@@ -5568,7 +5569,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>78</v>
       </c>
@@ -5579,7 +5580,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>79</v>
       </c>
@@ -5590,7 +5591,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>80</v>
       </c>
@@ -5601,7 +5602,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>81</v>
       </c>
@@ -5612,7 +5613,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>82</v>
       </c>
@@ -5623,7 +5624,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>83</v>
       </c>
@@ -5634,7 +5635,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>84</v>
       </c>
@@ -5645,7 +5646,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>85</v>
       </c>
@@ -5656,7 +5657,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>86</v>
       </c>
@@ -5667,7 +5668,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>87</v>
       </c>
@@ -5678,7 +5679,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>88</v>
       </c>
@@ -5689,7 +5690,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>89</v>
       </c>
@@ -5700,7 +5701,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>90</v>
       </c>
@@ -5711,7 +5712,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>91</v>
       </c>
@@ -5722,7 +5723,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>92</v>
       </c>
@@ -5733,7 +5734,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5744,7 +5745,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5755,7 +5756,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5766,7 +5767,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5777,7 +5778,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5788,7 +5789,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5799,7 +5800,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5810,7 +5811,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5818,10 +5819,10 @@
         <v>192</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5832,7 +5833,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5843,7 +5844,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5854,7 +5855,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5865,7 +5866,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5876,7 +5877,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5887,7 +5888,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5898,7 +5899,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5909,7 +5910,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5920,7 +5921,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5931,7 +5932,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5942,7 +5943,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5953,7 +5954,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5975,7 +5976,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5986,7 +5987,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5994,10 +5995,10 @@
         <v>223</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>122</v>
       </c>
@@ -6008,7 +6009,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>123</v>
       </c>
@@ -6019,7 +6020,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>124</v>
       </c>
@@ -6030,7 +6031,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>125</v>
       </c>
@@ -6041,7 +6042,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126</v>
       </c>
@@ -6052,7 +6053,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>127</v>
       </c>
@@ -6063,7 +6064,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>128</v>
       </c>
@@ -6074,7 +6075,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>129</v>
       </c>
@@ -6085,7 +6086,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>130</v>
       </c>
@@ -6096,7 +6097,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>131</v>
       </c>
@@ -6107,7 +6108,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>132</v>
       </c>
@@ -6118,7 +6119,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>133</v>
       </c>
@@ -6129,7 +6130,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>134</v>
       </c>
@@ -6140,7 +6141,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>135</v>
       </c>
@@ -6151,7 +6152,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6162,7 +6163,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6173,7 +6174,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6181,10 +6182,10 @@
         <v>256</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6195,7 +6196,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6206,7 +6207,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6217,7 +6218,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6228,7 +6229,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6239,7 +6240,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6250,7 +6251,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6261,7 +6262,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6272,7 +6273,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6283,7 +6284,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6294,7 +6295,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6305,7 +6306,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6316,7 +6317,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6327,7 +6328,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6338,7 +6339,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6349,7 +6350,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6360,7 +6361,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6371,7 +6372,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6382,7 +6383,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6393,7 +6394,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6404,7 +6405,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6415,7 +6416,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6423,10 +6424,10 @@
         <v>299</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6437,7 +6438,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6448,7 +6449,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6459,7 +6460,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6470,7 +6471,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6481,7 +6482,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6492,7 +6493,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6503,7 +6504,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6514,7 +6515,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>169</v>
       </c>
@@ -6525,7 +6526,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>170</v>
       </c>
@@ -6536,7 +6537,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>171</v>
       </c>
@@ -6547,7 +6548,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>172</v>
       </c>
@@ -6558,7 +6559,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>173</v>
       </c>
@@ -6569,7 +6570,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>174</v>
       </c>
@@ -6580,7 +6581,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>175</v>
       </c>
@@ -6588,10 +6589,10 @@
         <v>328</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>176</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>177</v>
       </c>
@@ -6613,7 +6614,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>178</v>
       </c>
@@ -6624,7 +6625,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>179</v>
       </c>
@@ -6635,7 +6636,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>180</v>
       </c>
@@ -6646,7 +6647,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>181</v>
       </c>
@@ -6657,7 +6658,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>182</v>
       </c>
@@ -6668,7 +6669,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>183</v>
       </c>
@@ -6679,7 +6680,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>184</v>
       </c>
@@ -6690,7 +6691,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>185</v>
       </c>
@@ -6701,7 +6702,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>186</v>
       </c>
@@ -6712,7 +6713,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>187</v>
       </c>
@@ -6723,7 +6724,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>188</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>189</v>
       </c>
@@ -6745,7 +6746,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>190</v>
       </c>
@@ -6756,7 +6757,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>191</v>
       </c>
@@ -6767,7 +6768,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>192</v>
       </c>
@@ -6778,7 +6779,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6789,7 +6790,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6800,7 +6801,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6811,7 +6812,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6822,7 +6823,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6833,7 +6834,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6844,7 +6845,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6855,7 +6856,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6866,7 +6867,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6877,7 +6878,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6888,7 +6889,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6899,7 +6900,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6910,7 +6911,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6921,7 +6922,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6932,7 +6933,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6943,7 +6944,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6954,7 +6955,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6965,7 +6966,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6976,7 +6977,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6987,7 +6988,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6998,7 +6999,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>213</v>
       </c>
@@ -7009,7 +7010,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>214</v>
       </c>
@@ -7020,7 +7021,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>215</v>
       </c>
@@ -7031,7 +7032,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>217</v>
       </c>
@@ -7042,7 +7043,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>218</v>
       </c>
@@ -7053,7 +7054,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>219</v>
       </c>
@@ -7064,7 +7065,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>220</v>
       </c>
@@ -7072,10 +7073,10 @@
         <v>415</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>221</v>
       </c>
@@ -7086,7 +7087,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>222</v>
       </c>
@@ -7097,7 +7098,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>223</v>
       </c>
@@ -7108,7 +7109,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>224</v>
       </c>
@@ -7119,7 +7120,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>225</v>
       </c>
@@ -7130,7 +7131,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>226</v>
       </c>
@@ -7141,7 +7142,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>227</v>
       </c>
@@ -7152,7 +7153,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7163,7 +7164,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7174,7 +7175,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7185,7 +7186,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7196,7 +7197,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7207,7 +7208,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>233</v>
       </c>
@@ -7215,10 +7216,10 @@
         <v>440</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>234</v>
       </c>
@@ -7229,7 +7230,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>235</v>
       </c>
@@ -7240,7 +7241,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>236</v>
       </c>
@@ -7251,7 +7252,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>237</v>
       </c>
@@ -7262,7 +7263,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>238</v>
       </c>
@@ -7273,7 +7274,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>239</v>
       </c>
@@ -7284,7 +7285,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>240</v>
       </c>
@@ -7295,7 +7296,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>241</v>
       </c>
@@ -7306,7 +7307,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>242</v>
       </c>
@@ -7317,7 +7318,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>243</v>
       </c>
@@ -7328,7 +7329,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>244</v>
       </c>
@@ -7339,7 +7340,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>245</v>
       </c>
@@ -7350,7 +7351,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>246</v>
       </c>
@@ -7361,7 +7362,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>247</v>
       </c>
@@ -7372,7 +7373,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>248</v>
       </c>
@@ -7383,7 +7384,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>249</v>
       </c>
@@ -7394,7 +7395,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>250</v>
       </c>
@@ -7405,7 +7406,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>251</v>
       </c>
@@ -7416,7 +7417,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>252</v>
       </c>
@@ -7427,7 +7428,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>253</v>
       </c>
@@ -7438,7 +7439,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>254</v>
       </c>
@@ -7449,7 +7450,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>255</v>
       </c>
@@ -7460,7 +7461,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>256</v>
       </c>
@@ -7471,7 +7472,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>257</v>
       </c>
@@ -7482,7 +7483,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>258</v>
       </c>
@@ -7493,7 +7494,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>259</v>
       </c>
@@ -7504,7 +7505,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>260</v>
       </c>
@@ -7512,10 +7513,10 @@
         <v>493</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>261</v>
       </c>
@@ -7526,7 +7527,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>262</v>
       </c>
@@ -7537,7 +7538,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>263</v>
       </c>
@@ -7545,10 +7546,10 @@
         <v>497</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>264</v>
       </c>
@@ -7559,7 +7560,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>265</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>266</v>
       </c>
@@ -7581,7 +7582,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>267</v>
       </c>
@@ -7592,7 +7593,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>268</v>
       </c>
@@ -7603,7 +7604,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>269</v>
       </c>
@@ -7614,7 +7615,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>270</v>
       </c>
@@ -7625,7 +7626,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>271</v>
       </c>
@@ -7636,7 +7637,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>272</v>
       </c>
@@ -7647,7 +7648,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>274</v>
       </c>
@@ -7658,7 +7659,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>275</v>
       </c>
@@ -7669,7 +7670,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>276</v>
       </c>
@@ -7680,7 +7681,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>277</v>
       </c>
@@ -7691,7 +7692,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>278</v>
       </c>
@@ -7702,7 +7703,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>279</v>
       </c>
@@ -7713,7 +7714,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>280</v>
       </c>
@@ -7724,7 +7725,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>281</v>
       </c>
@@ -7732,10 +7733,10 @@
         <v>530</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>282</v>
       </c>
@@ -7746,7 +7747,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>283</v>
       </c>
@@ -7757,7 +7758,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>284</v>
       </c>
@@ -7768,7 +7769,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>285</v>
       </c>
@@ -7779,7 +7780,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>286</v>
       </c>
@@ -7790,7 +7791,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>287</v>
       </c>
@@ -7801,7 +7802,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>288</v>
       </c>
@@ -7812,7 +7813,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>289</v>
       </c>
@@ -7823,7 +7824,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>290</v>
       </c>
@@ -7834,7 +7835,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>291</v>
       </c>
@@ -7845,7 +7846,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>292</v>
       </c>
@@ -7856,7 +7857,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>293</v>
       </c>
@@ -7867,7 +7868,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>294</v>
       </c>
@@ -7878,7 +7879,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>295</v>
       </c>
@@ -7889,7 +7890,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>296</v>
       </c>
@@ -7900,7 +7901,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>297</v>
       </c>
@@ -7911,7 +7912,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>298</v>
       </c>
@@ -7922,7 +7923,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>299</v>
       </c>
@@ -7933,7 +7934,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>300</v>
       </c>
@@ -7944,7 +7945,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>301</v>
       </c>
@@ -7955,7 +7956,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>302</v>
       </c>
@@ -7966,7 +7967,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>303</v>
       </c>
@@ -7977,7 +7978,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>304</v>
       </c>
@@ -7988,7 +7989,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>305</v>
       </c>
@@ -7999,7 +8000,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>306</v>
       </c>
@@ -8007,10 +8008,10 @@
         <v>579</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>307</v>
       </c>
@@ -8021,7 +8022,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>308</v>
       </c>
@@ -8032,7 +8033,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>309</v>
       </c>
@@ -8043,7 +8044,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>310</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>311</v>
       </c>
@@ -8065,7 +8066,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>312</v>
       </c>
@@ -8076,7 +8077,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>313</v>
       </c>
@@ -8087,7 +8088,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>314</v>
       </c>
@@ -8098,7 +8099,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>315</v>
       </c>
@@ -8109,7 +8110,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>316</v>
       </c>
@@ -8120,7 +8121,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>317</v>
       </c>
@@ -8131,7 +8132,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>318</v>
       </c>
@@ -8142,7 +8143,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>319</v>
       </c>
@@ -8153,7 +8154,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>320</v>
       </c>
@@ -8164,7 +8165,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>321</v>
       </c>
@@ -8175,7 +8176,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>322</v>
       </c>
@@ -8186,7 +8187,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>323</v>
       </c>
@@ -8197,7 +8198,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>324</v>
       </c>
@@ -8208,7 +8209,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>325</v>
       </c>
@@ -8219,7 +8220,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>326</v>
       </c>
@@ -8230,7 +8231,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>327</v>
       </c>
@@ -8241,7 +8242,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>328</v>
       </c>
@@ -8252,7 +8253,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>329</v>
       </c>
@@ -8263,7 +8264,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>330</v>
       </c>
@@ -8274,7 +8275,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>331</v>
       </c>
@@ -8285,7 +8286,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>332</v>
       </c>
@@ -8296,7 +8297,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>333</v>
       </c>
@@ -8307,7 +8308,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>334</v>
       </c>
@@ -8318,7 +8319,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>335</v>
       </c>
@@ -8329,7 +8330,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>336</v>
       </c>
@@ -8340,7 +8341,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>337</v>
       </c>
@@ -8351,7 +8352,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>338</v>
       </c>
@@ -8362,7 +8363,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>339</v>
       </c>
@@ -8373,7 +8374,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>340</v>
       </c>
@@ -8384,7 +8385,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>341</v>
       </c>
@@ -8395,7 +8396,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>342</v>
       </c>
@@ -8406,7 +8407,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>343</v>
       </c>
@@ -8417,7 +8418,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>344</v>
       </c>
@@ -8428,7 +8429,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>345</v>
       </c>
@@ -8439,7 +8440,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>346</v>
       </c>
@@ -8450,7 +8451,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>347</v>
       </c>
@@ -8461,7 +8462,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>348</v>
       </c>
@@ -8469,10 +8470,10 @@
         <v>662</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>349</v>
       </c>
@@ -8480,10 +8481,10 @@
         <v>663</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>350</v>
       </c>
@@ -8494,7 +8495,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>351</v>
       </c>
@@ -8505,7 +8506,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>352</v>
       </c>
@@ -8513,10 +8514,10 @@
         <v>668</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>353</v>
       </c>
@@ -8527,7 +8528,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>354</v>
       </c>
@@ -8538,7 +8539,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>355</v>
       </c>
@@ -8549,7 +8550,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>356</v>
       </c>
@@ -8560,7 +8561,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>357</v>
       </c>
@@ -8571,7 +8572,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>358</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>359</v>
       </c>
@@ -8593,7 +8594,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>360</v>
       </c>
@@ -8604,7 +8605,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>361</v>
       </c>
@@ -8615,7 +8616,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>362</v>
       </c>
@@ -8626,7 +8627,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>363</v>
       </c>
@@ -8637,7 +8638,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>364</v>
       </c>
@@ -8648,7 +8649,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>365</v>
       </c>
@@ -8659,7 +8660,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>366</v>
       </c>
@@ -8670,7 +8671,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>367</v>
       </c>
@@ -8681,7 +8682,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>368</v>
       </c>
@@ -8692,7 +8693,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>369</v>
       </c>
@@ -8703,7 +8704,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>370</v>
       </c>
@@ -8714,7 +8715,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>371</v>
       </c>
@@ -8725,7 +8726,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>372</v>
       </c>
@@ -8736,7 +8737,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>373</v>
       </c>
@@ -8747,7 +8748,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>374</v>
       </c>
@@ -8758,7 +8759,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>375</v>
       </c>
@@ -8769,7 +8770,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>376</v>
       </c>
@@ -8780,7 +8781,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>377</v>
       </c>
@@ -8791,7 +8792,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>378</v>
       </c>
@@ -8802,7 +8803,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>379</v>
       </c>
@@ -8813,7 +8814,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>380</v>
       </c>
@@ -8824,7 +8825,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>381</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>382</v>
       </c>
@@ -8846,7 +8847,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>383</v>
       </c>
@@ -8857,7 +8858,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>384</v>
       </c>
@@ -8868,7 +8869,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>385</v>
       </c>
@@ -8879,7 +8880,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>386</v>
       </c>
@@ -8890,7 +8891,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>387</v>
       </c>
@@ -8901,7 +8902,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>388</v>
       </c>
@@ -8912,7 +8913,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>389</v>
       </c>
@@ -8923,7 +8924,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>390</v>
       </c>
@@ -8934,7 +8935,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>391</v>
       </c>
@@ -8945,7 +8946,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>392</v>
       </c>
@@ -8956,7 +8957,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>393</v>
       </c>
@@ -8967,7 +8968,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>394</v>
       </c>
@@ -8978,7 +8979,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>395</v>
       </c>
@@ -8989,7 +8990,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>396</v>
       </c>
@@ -9000,7 +9001,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>397</v>
       </c>
@@ -9011,7 +9012,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>398</v>
       </c>
@@ -9022,7 +9023,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>399</v>
       </c>
@@ -9033,7 +9034,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>400</v>
       </c>
@@ -9044,7 +9045,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>401</v>
       </c>
@@ -9055,7 +9056,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3" ht="19.2" x14ac